--- a/docs/database/column-definition/BOMI_컬럼정의서.xlsx
+++ b/docs/database/column-definition/BOMI_컬럼정의서.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_읽는법" sheetId="1" r:id="R0722c54e4cc04afc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_테이블정의" sheetId="2" r:id="Rd304820ff6de404f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_컬럼정의" sheetId="3" r:id="Rbb5ce2b7744442e5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_관계_제약조건" sheetId="4" r:id="R6227dc0046974c97"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_인덱스정의" sheetId="5" r:id="R47d5f8ad805849e0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_JSONB정의" sheetId="6" r:id="R7677bde8ad424213"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_벡터정의" sheetId="7" r:id="R9061264fb10c4fe4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_코드정의" sheetId="8" r:id="Rd81f70d309014879"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_연계매핑" sheetId="9" r:id="R567eeca81ee44810"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_변경이력" sheetId="10" r:id="R5d87a12907884390"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_읽는법" sheetId="1" r:id="R8757394870c54724"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_테이블정의" sheetId="2" r:id="R100d7ce3d9614f09"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_컬럼정의" sheetId="3" r:id="Ra006a8731b824daa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_관계_제약조건" sheetId="4" r:id="Rbc4ea6b5bd3d4636"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_인덱스정의" sheetId="5" r:id="R9a8c3c02148049a2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_JSONB정의" sheetId="6" r:id="R8a5e96db589a4f56"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_벡터정의" sheetId="7" r:id="Rc6ae52a3df5744d2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_코드정의" sheetId="8" r:id="R7925aafe537d44c6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_연계매핑" sheetId="9" r:id="Red2e43469dd74108"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_변경이력" sheetId="10" r:id="Rd9f4961c87e14d21"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -401,7 +401,7 @@
     </x:row>
     <x:row r="2" ht="28" customHeight="1">
       <x:c r="A2" s="7" t="str">
-        <x:v>형식을 위한 형식이 아니라 12개 테이블의 의미·생명주기·권한 경계를 팀이 같은 말로 이해하기 위한 문서입니다.</x:v>
+        <x:v>형식을 위한 형식이 아니라 13개 테이블의 의미·생명주기·권한 경계를 팀이 같은 말로 이해하기 위한 문서입니다.</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="30" customHeight="1">
@@ -437,7 +437,7 @@
         <x:v>기준 모델</x:v>
       </x:c>
       <x:c r="B6" s="25" t="str">
-        <x:v>물리 테이블 12개, 컬럼 151개이며 ENUM 박스는 코드 사전이다.</x:v>
+        <x:v>물리 테이블 13개, 컬럼 171개이며 ENUM 박스는 코드 사전이다.</x:v>
       </x:c>
       <x:c r="C6" s="25" t="str">
         <x:v>ERD 변경 시 테이블·컬럼·제약·코드·CSV를 함께 바꾼다.</x:v>
@@ -641,6 +641,20 @@
       </x:c>
       <x:c r="D5" s="31" t="str">
         <x:v>Raw·요약·장기 기억을 분리하고 앱/로봇 공용 온보딩과 민감정보 확인·PRIMARY 협의를 실행 가능하게 만들기 위해</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="30" hidden="0" customHeight="1">
+      <x:c r="A6" t="str">
+        <x:v>2026-08-05</x:v>
+      </x:c>
+      <x:c r="B6" t="str">
+        <x:v>WAKE_WORD_CALL 호출 런타임·영속 멱등 receipt·상관 필드·코드 사전 추가</x:v>
+      </x:c>
+      <x:c r="C6" t="str">
+        <x:v>scenario, wake_word_trigger_receipt, 인덱스·제약·JSONB·연계매핑</x:v>
+      </x:c>
+      <x:c r="D6" t="str">
+        <x:v>AI 자체 대화와 Backend 이동 책임을 분리하고 QoS 1 재전송·재시작에도 호출 이동을 중복 생성하지 않기 위해</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -932,6 +946,26 @@
       </x:c>
       <x:c r="F16" s="27" t="str">
         <x:v>변경은 기존 행 덮어쓰기가 아니라 새 행과 parent_record_id로 연결한다.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="30" hidden="0" customHeight="1">
+      <x:c r="A17" t="str">
+        <x:v>wake_word_trigger_receipt</x:v>
+      </x:c>
+      <x:c r="B17" t="str">
+        <x:v>호출 트리거 처리 영수증</x:v>
+      </x:c>
+      <x:c r="C17" t="str">
+        <x:v>검증된 WAKE_WORD_DETECTED 이벤트 한 건의 최종 처리 결정</x:v>
+      </x:c>
+      <x:c r="D17" t="str">
+        <x:v>QoS 1 재전송과 Backend 재시작 뒤에도 수락·거절 이벤트를 다시 실행하지 않게 한다.</x:v>
+      </x:c>
+      <x:c r="E17" t="str">
+        <x:v>robot_device_id로 robot을 권위 조회하고, 수락 건은 scenario_id를 논리 연결</x:v>
+      </x:c>
+      <x:c r="F17" t="str">
+        <x:v>원본 음성·전체 STT는 저장하지 않으며 event_id 재사용 시 원래 최소 문맥과 일치해야 한다.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1031,7 +1065,7 @@
       <x:c r="G5" s="24" t="str">
         <x:v>PK</x:v>
       </x:c>
-      <x:c r="H5" s="24" t="str"/>
+      <x:c r="H5" s="24"/>
       <x:c r="I5" s="24" t="str">
         <x:v>app_user.id에는 사용자를 변하지 않게 식별하는 값을 저장한다.</x:v>
       </x:c>
@@ -1064,8 +1098,8 @@
       <x:c r="F6" s="25" t="str">
         <x:v>Y</x:v>
       </x:c>
-      <x:c r="G6" s="25" t="str"/>
-      <x:c r="H6" s="25" t="str"/>
+      <x:c r="G6" s="25"/>
+      <x:c r="H6" s="25"/>
       <x:c r="I6" s="25" t="str">
         <x:v>app_user.user_type에는 시니어와 보호자를 구분하는 값을 저장한다.</x:v>
       </x:c>
@@ -1098,8 +1132,8 @@
       <x:c r="F7" s="26" t="str">
         <x:v>Y</x:v>
       </x:c>
-      <x:c r="G7" s="26" t="str"/>
-      <x:c r="H7" s="26" t="str"/>
+      <x:c r="G7" s="26"/>
+      <x:c r="H7" s="26"/>
       <x:c r="I7" s="26" t="str">
         <x:v>app_user.name에는 가입 때 확인한 이름을 표시하는 값을 저장한다.</x:v>
       </x:c>
@@ -1132,8 +1166,8 @@
       <x:c r="F8" s="25" t="str">
         <x:v>조건부</x:v>
       </x:c>
-      <x:c r="G8" s="25" t="str"/>
-      <x:c r="H8" s="25" t="str"/>
+      <x:c r="G8" s="25"/>
+      <x:c r="H8" s="25"/>
       <x:c r="I8" s="25" t="str">
         <x:v>app_user.email에는 로그인 또는 연락 주소를 보관하는 값을 저장한다.</x:v>
       </x:c>
@@ -1166,8 +1200,8 @@
       <x:c r="F9" s="26" t="str">
         <x:v>N</x:v>
       </x:c>
-      <x:c r="G9" s="26" t="str"/>
-      <x:c r="H9" s="26" t="str"/>
+      <x:c r="G9" s="26"/>
+      <x:c r="H9" s="26"/>
       <x:c r="I9" s="26" t="str">
         <x:v>app_user.preferred_name에는 로봇이 부를 호칭을 제공하는 값을 저장한다.</x:v>
       </x:c>
@@ -1200,8 +1234,8 @@
       <x:c r="F10" s="25" t="str">
         <x:v>N</x:v>
       </x:c>
-      <x:c r="G10" s="25" t="str"/>
-      <x:c r="H10" s="25" t="str"/>
+      <x:c r="G10" s="25"/>
+      <x:c r="H10" s="25"/>
       <x:c r="I10" s="25" t="str">
         <x:v>app_user.conversation_preferences에는 말하기 속도·음량·반복 방식을 구조화하는 값을 저장한다.</x:v>
       </x:c>
@@ -1234,8 +1268,8 @@
       <x:c r="F11" s="26" t="str">
         <x:v>Y</x:v>
       </x:c>
-      <x:c r="G11" s="26" t="str"/>
-      <x:c r="H11" s="26" t="str"/>
+      <x:c r="G11" s="26"/>
+      <x:c r="H11" s="26"/>
       <x:c r="I11" s="26" t="str">
         <x:v>app_user.onboarding_status에는 앱 진입과 온보딩 재개를 빠르게 분기하는 값을 저장한다.</x:v>
       </x:c>
@@ -1268,8 +1302,8 @@
       <x:c r="F12" s="25" t="str">
         <x:v>Y</x:v>
       </x:c>
-      <x:c r="G12" s="25" t="str"/>
-      <x:c r="H12" s="25" t="str"/>
+      <x:c r="G12" s="25"/>
+      <x:c r="H12" s="25"/>
       <x:c r="I12" s="25" t="str">
         <x:v>app_user.time_zone에는 일정·일간 요약의 현지 날짜를 계산하는 값을 저장한다.</x:v>
       </x:c>
@@ -1302,8 +1336,8 @@
       <x:c r="F13" s="26" t="str">
         <x:v>Y</x:v>
       </x:c>
-      <x:c r="G13" s="26" t="str"/>
-      <x:c r="H13" s="26" t="str"/>
+      <x:c r="G13" s="26"/>
+      <x:c r="H13" s="26"/>
       <x:c r="I13" s="26" t="str">
         <x:v>app_user.personalization_consent_status에는 기억 저장·검색 허용 여부를 결정하는 값을 저장한다.</x:v>
       </x:c>
@@ -1336,8 +1370,8 @@
       <x:c r="F14" s="25" t="str">
         <x:v>Y</x:v>
       </x:c>
-      <x:c r="G14" s="25" t="str"/>
-      <x:c r="H14" s="25" t="str"/>
+      <x:c r="G14" s="25"/>
+      <x:c r="H14" s="25"/>
       <x:c r="I14" s="25" t="str">
         <x:v>app_user.health_data_consent_status에는 건강·복약 처리 게이트를 제공하는 값을 저장한다.</x:v>
       </x:c>
@@ -1370,8 +1404,8 @@
       <x:c r="F15" s="26" t="str">
         <x:v>Y</x:v>
       </x:c>
-      <x:c r="G15" s="26" t="str"/>
-      <x:c r="H15" s="26" t="str"/>
+      <x:c r="G15" s="26"/>
+      <x:c r="H15" s="26"/>
       <x:c r="I15" s="26" t="str">
         <x:v>app_user.schedule_consent_status에는 병원·개인 일정 저장과 알림을 제어하는 값을 저장한다.</x:v>
       </x:c>
@@ -1404,8 +1438,8 @@
       <x:c r="F16" s="25" t="str">
         <x:v>Y</x:v>
       </x:c>
-      <x:c r="G16" s="25" t="str"/>
-      <x:c r="H16" s="25" t="str"/>
+      <x:c r="G16" s="25"/>
+      <x:c r="H16" s="25"/>
       <x:c r="I16" s="25" t="str">
         <x:v>app_user.guardian_sharing_consent_status에는 보호자 공유의 사용자 동의를 표시하는 값을 저장한다.</x:v>
       </x:c>
@@ -1438,8 +1472,8 @@
       <x:c r="F17" s="26" t="str">
         <x:v>Y</x:v>
       </x:c>
-      <x:c r="G17" s="26" t="str"/>
-      <x:c r="H17" s="26" t="str"/>
+      <x:c r="G17" s="26"/>
+      <x:c r="H17" s="26"/>
       <x:c r="I17" s="26" t="str">
         <x:v>app_user.status에는 정상·정지·탈퇴 계정을 구분하는 값을 저장한다.</x:v>
       </x:c>
@@ -1472,8 +1506,8 @@
       <x:c r="F18" s="25" t="str">
         <x:v>Y</x:v>
       </x:c>
-      <x:c r="G18" s="25" t="str"/>
-      <x:c r="H18" s="25" t="str"/>
+      <x:c r="G18" s="25"/>
+      <x:c r="H18" s="25"/>
       <x:c r="I18" s="25" t="str">
         <x:v>app_user.created_at에는 사용자 행 최초 생성 시각을 기록하는 값을 저장한다.</x:v>
       </x:c>
@@ -1506,8 +1540,8 @@
       <x:c r="F19" s="26" t="str">
         <x:v>Y</x:v>
       </x:c>
-      <x:c r="G19" s="26" t="str"/>
-      <x:c r="H19" s="26" t="str"/>
+      <x:c r="G19" s="26"/>
+      <x:c r="H19" s="26"/>
       <x:c r="I19" s="26" t="str">
         <x:v>app_user.updated_at에는 프로필·상태의 마지막 변경을 표시하는 값을 저장한다.</x:v>
       </x:c>
@@ -1543,7 +1577,7 @@
       <x:c r="G20" s="25" t="str">
         <x:v>PK</x:v>
       </x:c>
-      <x:c r="H20" s="25" t="str"/>
+      <x:c r="H20" s="25"/>
       <x:c r="I20" s="25" t="str">
         <x:v>care_relationship.id에는 시니어-보호자 연결을 식별하는 값을 저장한다.</x:v>
       </x:c>
@@ -1652,8 +1686,8 @@
       <x:c r="F23" s="26" t="str">
         <x:v>Y</x:v>
       </x:c>
-      <x:c r="G23" s="26" t="str"/>
-      <x:c r="H23" s="26" t="str"/>
+      <x:c r="G23" s="26"/>
+      <x:c r="H23" s="26"/>
       <x:c r="I23" s="26" t="str">
         <x:v>care_relationship.priority에는 PRIMARY와 SECONDARY를 구분하는 값을 저장한다.</x:v>
       </x:c>
@@ -1686,8 +1720,8 @@
       <x:c r="F24" s="25" t="str">
         <x:v>Y</x:v>
       </x:c>
-      <x:c r="G24" s="25" t="str"/>
-      <x:c r="H24" s="25" t="str"/>
+      <x:c r="G24" s="25"/>
+      <x:c r="H24" s="25"/>
       <x:c r="I24" s="25" t="str">
         <x:v>care_relationship.status에는 초대·활성·해제 상태를 표시하는 값을 저장한다.</x:v>
       </x:c>
@@ -1720,8 +1754,8 @@
       <x:c r="F25" s="26" t="str">
         <x:v>조건부</x:v>
       </x:c>
-      <x:c r="G25" s="26" t="str"/>
-      <x:c r="H25" s="26" t="str"/>
+      <x:c r="G25" s="26"/>
+      <x:c r="H25" s="26"/>
       <x:c r="I25" s="26" t="str">
         <x:v>care_relationship.connected_at에는 실제 관계가 활성화된 시점을 기록하는 값을 저장한다.</x:v>
       </x:c>
@@ -1754,8 +1788,8 @@
       <x:c r="F26" s="25" t="str">
         <x:v>Y</x:v>
       </x:c>
-      <x:c r="G26" s="25" t="str"/>
-      <x:c r="H26" s="25" t="str"/>
+      <x:c r="G26" s="25"/>
+      <x:c r="H26" s="25"/>
       <x:c r="I26" s="25" t="str">
         <x:v>care_relationship.care_management_permission_status에는 PRIMARY의 민감정보 대리 관리 허용을 표시하는 값을 저장한다.</x:v>
       </x:c>
@@ -1788,8 +1822,8 @@
       <x:c r="F27" s="26" t="str">
         <x:v>N</x:v>
       </x:c>
-      <x:c r="G27" s="26" t="str"/>
-      <x:c r="H27" s="26" t="str"/>
+      <x:c r="G27" s="26"/>
+      <x:c r="H27" s="26"/>
       <x:c r="I27" s="26" t="str">
         <x:v>care_relationship.care_management_permission_updated_at에는 관리 권한 동의가 마지막으로 바뀐 때를 기록하는 값을 저장한다.</x:v>
       </x:c>
@@ -1863,7 +1897,7 @@
       <x:c r="G29" s="26" t="str">
         <x:v>PK</x:v>
       </x:c>
-      <x:c r="H29" s="26" t="str"/>
+      <x:c r="H29" s="26"/>
       <x:c r="I29" s="26" t="str">
         <x:v>robot.id에는 로봇 한 대를 식별하는 값을 저장한다.</x:v>
       </x:c>
@@ -1934,8 +1968,8 @@
       <x:c r="F31" s="26" t="str">
         <x:v>Y</x:v>
       </x:c>
-      <x:c r="G31" s="26" t="str"/>
-      <x:c r="H31" s="26" t="str"/>
+      <x:c r="G31" s="26"/>
+      <x:c r="H31" s="26"/>
       <x:c r="I31" s="26" t="str">
         <x:v>robot.current_mode에는 명령 허용과 UI 상태를 결정하는 값을 저장한다.</x:v>
       </x:c>
@@ -1968,8 +2002,8 @@
       <x:c r="F32" s="25" t="str">
         <x:v>N</x:v>
       </x:c>
-      <x:c r="G32" s="25" t="str"/>
-      <x:c r="H32" s="25" t="str"/>
+      <x:c r="G32" s="25"/>
+      <x:c r="H32" s="25"/>
       <x:c r="I32" s="25" t="str">
         <x:v>robot.ambient_temperature_c에는 마지막 실내 온도를 섭씨로 보관하는 값을 저장한다.</x:v>
       </x:c>
@@ -2002,8 +2036,8 @@
       <x:c r="F33" s="26" t="str">
         <x:v>N</x:v>
       </x:c>
-      <x:c r="G33" s="26" t="str"/>
-      <x:c r="H33" s="26" t="str"/>
+      <x:c r="G33" s="26"/>
+      <x:c r="H33" s="26"/>
       <x:c r="I33" s="26" t="str">
         <x:v>robot.ambient_humidity_percent에는 마지막 상대습도를 퍼센트로 보관하는 값을 저장한다.</x:v>
       </x:c>
@@ -2036,8 +2070,8 @@
       <x:c r="F34" s="25" t="str">
         <x:v>N</x:v>
       </x:c>
-      <x:c r="G34" s="25" t="str"/>
-      <x:c r="H34" s="25" t="str"/>
+      <x:c r="G34" s="25"/>
+      <x:c r="H34" s="25"/>
       <x:c r="I34" s="25" t="str">
         <x:v>robot.ambient_observed_at에는 최신값이 실제 측정된 시각을 기록하는 값을 저장한다.</x:v>
       </x:c>
@@ -2070,8 +2104,8 @@
       <x:c r="F35" s="26" t="str">
         <x:v>Y</x:v>
       </x:c>
-      <x:c r="G35" s="26" t="str"/>
-      <x:c r="H35" s="26" t="str"/>
+      <x:c r="G35" s="26"/>
+      <x:c r="H35" s="26"/>
       <x:c r="I35" s="26" t="str">
         <x:v>robot.is_active에는 등록상 서비스 가능한 로봇인지 표시하는 값을 저장한다.</x:v>
       </x:c>
@@ -2107,7 +2141,7 @@
       <x:c r="G36" s="25" t="str">
         <x:v>PK</x:v>
       </x:c>
-      <x:c r="H36" s="25" t="str"/>
+      <x:c r="H36" s="25"/>
       <x:c r="I36" s="25" t="str">
         <x:v>onboarding_session.id에는 온보딩 한 번을 식별하는 값을 저장한다.</x:v>
       </x:c>
@@ -2216,8 +2250,8 @@
       <x:c r="F39" s="26" t="str">
         <x:v>Y</x:v>
       </x:c>
-      <x:c r="G39" s="26" t="str"/>
-      <x:c r="H39" s="26" t="str"/>
+      <x:c r="G39" s="26"/>
+      <x:c r="H39" s="26"/>
       <x:c r="I39" s="26" t="str">
         <x:v>onboarding_session.question_set_version에는 세션이 적용한 질문 계약 버전을 고정하는 값을 저장한다.</x:v>
       </x:c>
@@ -2250,8 +2284,8 @@
       <x:c r="F40" s="25" t="str">
         <x:v>Y</x:v>
       </x:c>
-      <x:c r="G40" s="25" t="str"/>
-      <x:c r="H40" s="25" t="str"/>
+      <x:c r="G40" s="25"/>
+      <x:c r="H40" s="25"/>
       <x:c r="I40" s="25" t="str">
         <x:v>onboarding_session.started_channel에는 온보딩을 처음 연 APP 또는 ROBOT을 기록하는 값을 저장한다.</x:v>
       </x:c>
@@ -2284,8 +2318,8 @@
       <x:c r="F41" s="26" t="str">
         <x:v>Y</x:v>
       </x:c>
-      <x:c r="G41" s="26" t="str"/>
-      <x:c r="H41" s="26" t="str"/>
+      <x:c r="G41" s="26"/>
+      <x:c r="H41" s="26"/>
       <x:c r="I41" s="26" t="str">
         <x:v>onboarding_session.status에는 진행·완료·거절·취소·만료를 구분하는 값을 저장한다.</x:v>
       </x:c>
@@ -2318,8 +2352,8 @@
       <x:c r="F42" s="25" t="str">
         <x:v>N</x:v>
       </x:c>
-      <x:c r="G42" s="25" t="str"/>
-      <x:c r="H42" s="25" t="str"/>
+      <x:c r="G42" s="25"/>
+      <x:c r="H42" s="25"/>
       <x:c r="I42" s="25" t="str">
         <x:v>onboarding_session.current_question_code에는 중단 후 이어갈 질문 위치를 표시하는 값을 저장한다.</x:v>
       </x:c>
@@ -2352,8 +2386,8 @@
       <x:c r="F43" s="26" t="str">
         <x:v>Y</x:v>
       </x:c>
-      <x:c r="G43" s="26" t="str"/>
-      <x:c r="H43" s="26" t="str"/>
+      <x:c r="G43" s="26"/>
+      <x:c r="H43" s="26"/>
       <x:c r="I43" s="26" t="str">
         <x:v>onboarding_session.started_at에는 첫 질문을 시작한 시각을 기록하는 값을 저장한다.</x:v>
       </x:c>
@@ -2386,8 +2420,8 @@
       <x:c r="F44" s="25" t="str">
         <x:v>N</x:v>
       </x:c>
-      <x:c r="G44" s="25" t="str"/>
-      <x:c r="H44" s="25" t="str"/>
+      <x:c r="G44" s="25"/>
+      <x:c r="H44" s="25"/>
       <x:c r="I44" s="25" t="str">
         <x:v>onboarding_session.completed_at에는 정상 완료한 경우의 완료 시각을 기록하는 값을 저장한다.</x:v>
       </x:c>
@@ -2420,8 +2454,8 @@
       <x:c r="F45" s="26" t="str">
         <x:v>N</x:v>
       </x:c>
-      <x:c r="G45" s="26" t="str"/>
-      <x:c r="H45" s="26" t="str"/>
+      <x:c r="G45" s="26"/>
+      <x:c r="H45" s="26"/>
       <x:c r="I45" s="26" t="str">
         <x:v>onboarding_session.ended_at에는 모든 종료 유형의 닫힌 시각을 기록하는 값을 저장한다.</x:v>
       </x:c>
@@ -2457,7 +2491,7 @@
       <x:c r="G46" s="25" t="str">
         <x:v>PK</x:v>
       </x:c>
-      <x:c r="H46" s="25" t="str"/>
+      <x:c r="H46" s="25"/>
       <x:c r="I46" s="25" t="str">
         <x:v>onboarding_answer.id에는 질문별 현재 답변 행을 식별하는 값을 저장한다.</x:v>
       </x:c>
@@ -2528,8 +2562,8 @@
       <x:c r="F48" s="25" t="str">
         <x:v>Y</x:v>
       </x:c>
-      <x:c r="G48" s="25" t="str"/>
-      <x:c r="H48" s="25" t="str"/>
+      <x:c r="G48" s="25"/>
+      <x:c r="H48" s="25"/>
       <x:c r="I48" s="25" t="str">
         <x:v>onboarding_answer.question_code에는 버전 계약의 질문을 식별하는 값을 저장한다.</x:v>
       </x:c>
@@ -2562,8 +2596,8 @@
       <x:c r="F49" s="26" t="str">
         <x:v>Y</x:v>
       </x:c>
-      <x:c r="G49" s="26" t="str"/>
-      <x:c r="H49" s="26" t="str"/>
+      <x:c r="G49" s="26"/>
+      <x:c r="H49" s="26"/>
       <x:c r="I49" s="26" t="str">
         <x:v>onboarding_answer.answer_value에는 앱·로봇 입력을 같은 질문별 JSON 구조로 저장하는 값을 저장한다.</x:v>
       </x:c>
@@ -2596,8 +2630,8 @@
       <x:c r="F50" s="25" t="str">
         <x:v>Y</x:v>
       </x:c>
-      <x:c r="G50" s="25" t="str"/>
-      <x:c r="H50" s="25" t="str"/>
+      <x:c r="G50" s="25"/>
+      <x:c r="H50" s="25"/>
       <x:c r="I50" s="25" t="str">
         <x:v>onboarding_answer.answered_channel에는 실제 답변이 들어온 APP 또는 ROBOT을 기록하는 값을 저장한다.</x:v>
       </x:c>
@@ -2744,8 +2778,8 @@
       <x:c r="F54" s="25" t="str">
         <x:v>Y</x:v>
       </x:c>
-      <x:c r="G54" s="25" t="str"/>
-      <x:c r="H54" s="25" t="str"/>
+      <x:c r="G54" s="25"/>
+      <x:c r="H54" s="25"/>
       <x:c r="I54" s="25" t="str">
         <x:v>onboarding_answer.verification_status에는 미확인·사람 확인·거절을 구분하는 값을 저장한다.</x:v>
       </x:c>
@@ -2816,8 +2850,8 @@
       <x:c r="F56" s="25" t="str">
         <x:v>Y</x:v>
       </x:c>
-      <x:c r="G56" s="25" t="str"/>
-      <x:c r="H56" s="25" t="str"/>
+      <x:c r="G56" s="25"/>
+      <x:c r="H56" s="25"/>
       <x:c r="I56" s="25" t="str">
         <x:v>onboarding_answer.answered_at에는 답변이 실제 캡처된 시각을 기록하는 값을 저장한다.</x:v>
       </x:c>
@@ -2850,8 +2884,8 @@
       <x:c r="F57" s="26" t="str">
         <x:v>N</x:v>
       </x:c>
-      <x:c r="G57" s="26" t="str"/>
-      <x:c r="H57" s="26" t="str"/>
+      <x:c r="G57" s="26"/>
+      <x:c r="H57" s="26"/>
       <x:c r="I57" s="26" t="str">
         <x:v>onboarding_answer.confirmed_at에는 사용자가 정규화 값을 확인한 시각을 기록하는 값을 저장한다.</x:v>
       </x:c>
@@ -2884,8 +2918,8 @@
       <x:c r="F58" s="25" t="str">
         <x:v>Y</x:v>
       </x:c>
-      <x:c r="G58" s="25" t="str"/>
-      <x:c r="H58" s="25" t="str"/>
+      <x:c r="G58" s="25"/>
+      <x:c r="H58" s="25"/>
       <x:c r="I58" s="25" t="str">
         <x:v>onboarding_answer.updated_at에는 현재 답변 행이 마지막으로 바뀐 시각을 기록하는 값을 저장한다.</x:v>
       </x:c>
@@ -2921,7 +2955,7 @@
       <x:c r="G59" s="26" t="str">
         <x:v>PK</x:v>
       </x:c>
-      <x:c r="H59" s="26" t="str"/>
+      <x:c r="H59" s="26"/>
       <x:c r="I59" s="26" t="str">
         <x:v>scenario.id에는 로봇 행동 흐름을 식별하는 값을 저장한다.</x:v>
       </x:c>
@@ -3030,8 +3064,8 @@
       <x:c r="F62" s="25" t="str">
         <x:v>N</x:v>
       </x:c>
-      <x:c r="G62" s="25" t="str"/>
-      <x:c r="H62" s="25" t="str"/>
+      <x:c r="G62" s="25"/>
+      <x:c r="H62" s="25"/>
       <x:c r="I62" s="25" t="str">
         <x:v>scenario.external_event_id에는 시나리오를 시작한 사건의 멱등 키를 저장하는 값을 저장한다.</x:v>
       </x:c>
@@ -3064,8 +3098,8 @@
       <x:c r="F63" s="26" t="str">
         <x:v>Y</x:v>
       </x:c>
-      <x:c r="G63" s="26" t="str"/>
-      <x:c r="H63" s="26" t="str"/>
+      <x:c r="G63" s="26"/>
+      <x:c r="H63" s="26"/>
       <x:c r="I63" s="26" t="str">
         <x:v>scenario.scenario_type에는 귀가·낙상·수동 상호작용을 구분하는 값을 저장한다.</x:v>
       </x:c>
@@ -3093,18 +3127,18 @@
         <x:v>진행·결과 상태</x:v>
       </x:c>
       <x:c r="E64" s="25" t="str">
-        <x:v>VARCHAR(255)</x:v>
+        <x:v>VARCHAR(50)</x:v>
       </x:c>
       <x:c r="F64" s="25" t="str">
         <x:v>Y</x:v>
       </x:c>
-      <x:c r="G64" s="25" t="str"/>
-      <x:c r="H64" s="25" t="str"/>
+      <x:c r="G64" s="25"/>
+      <x:c r="H64" s="25"/>
       <x:c r="I64" s="25" t="str">
-        <x:v>scenario.final_status에는 굵은 진행 단계와 종료 결과를 표시하는 값을 저장한다.</x:v>
+        <x:v>scenario.final_status에는 시나리오 유형별 굵은 진행 단계와 종료 결과를 저장한다.</x:v>
       </x:c>
       <x:c r="J64" s="25" t="str">
-        <x:v>진행·결과 상태은(는) 굵은 진행 단계와 종료 결과를 표시할 때 조회·검증·갱신한다.</x:v>
+        <x:v>현재 상태를 전이 검증·동시 실행 차단·대시보드 이력에 사용한다.</x:v>
       </x:c>
       <x:c r="K64" s="25" t="str">
         <x:v>종료 상태에서 진행 상태로 되돌리지 않는다.</x:v>
@@ -3113,201 +3147,191 @@
         <x:v>CONVERSING</x:v>
       </x:c>
     </x:row>
-    <x:row r="65">
+    <x:row r="65" ht="30" hidden="0" customHeight="1">
       <x:c r="A65" s="26" t="str">
-        <x:v>conversation</x:v>
+        <x:v>scenario</x:v>
       </x:c>
       <x:c r="B65" s="26" t="n">
-        <x:v>1</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C65" s="26" t="str">
-        <x:v>id</x:v>
+        <x:v>conversation_request</x:v>
       </x:c>
       <x:c r="D65" s="26" t="str">
-        <x:v>대화 ID</x:v>
+        <x:v>준비된 대화 요청</x:v>
       </x:c>
       <x:c r="E65" s="26" t="str">
-        <x:v>UUID</x:v>
+        <x:v>JSONB</x:v>
       </x:c>
       <x:c r="F65" s="26" t="str">
-        <x:v>Y</x:v>
-      </x:c>
-      <x:c r="G65" s="26" t="str">
-        <x:v>PK</x:v>
-      </x:c>
+        <x:v>N</x:v>
+      </x:c>
+      <x:c r="G65" s="26" t="str"/>
       <x:c r="H65" s="26" t="str"/>
       <x:c r="I65" s="26" t="str">
-        <x:v>conversation.id에는 대화 묶음을 식별하는 값을 저장한다.</x:v>
+        <x:v>대화형 시나리오가 이동 전에 확정한 intent·첫 문장·최소 triggerContext를 저장한다.</x:v>
       </x:c>
       <x:c r="J65" s="26" t="str">
-        <x:v>대화 ID은(는) 대화 묶음을 식별할 때 조회·검증·갱신한다.</x:v>
+        <x:v>도착 뒤 같은 요청으로 START_CONVERSATION을 재개할 때 사용한다.</x:v>
       </x:c>
       <x:c r="K65" s="26" t="str">
-        <x:v>메시지 ID와 혼동하지 않는다.</x:v>
+        <x:v>WAKE_WORD_CALL에는 값을 만들지 않고 원본 음성·전체 STT를 넣지 않는다.</x:v>
       </x:c>
       <x:c r="L65" s="26" t="str">
-        <x:v>1a4fe41a-6464-4e7e-b292-9a507333a3fa</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="66">
+        <x:v>{"intent":"HOMECOMING_GREETING","text":"어서 오세요","triggerContext":{"location":"ENTRANCE"}}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66" ht="30" hidden="0" customHeight="1">
       <x:c r="A66" s="25" t="str">
-        <x:v>conversation</x:v>
+        <x:v>scenario</x:v>
       </x:c>
       <x:c r="B66" s="25" t="n">
-        <x:v>2</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C66" s="25" t="str">
-        <x:v>senior_id</x:v>
+        <x:v>active_navigation_command_id</x:v>
       </x:c>
       <x:c r="D66" s="25" t="str">
-        <x:v>대화 시니어 ID</x:v>
+        <x:v>활성 이동 명령 ID</x:v>
       </x:c>
       <x:c r="E66" s="25" t="str">
-        <x:v>UUID</x:v>
+        <x:v>VARCHAR(64)</x:v>
       </x:c>
       <x:c r="F66" s="25" t="str">
-        <x:v>Y</x:v>
-      </x:c>
-      <x:c r="G66" s="25" t="str">
-        <x:v>FK</x:v>
-      </x:c>
-      <x:c r="H66" s="25" t="str">
-        <x:v>app_user.id</x:v>
-      </x:c>
+        <x:v>N</x:v>
+      </x:c>
+      <x:c r="G66" s="25" t="str"/>
+      <x:c r="H66" s="25" t="str"/>
       <x:c r="I66" s="25" t="str">
-        <x:v>conversation.senior_id에는 대화 소유자를 연결하는 값을 저장한다.</x:v>
+        <x:v>현재 결과를 기다리는 NAVIGATE commandId를 저장한다.</x:v>
       </x:c>
       <x:c r="J66" s="25" t="str">
-        <x:v>대화 시니어 ID은(는) 대화 소유자를 연결할 때 조회·검증·갱신한다.</x:v>
+        <x:v>NAVIGATION_RESULT.commandId가 현재 이동 명령과 같은지 검증한다.</x:v>
       </x:c>
       <x:c r="K66" s="25" t="str">
-        <x:v>보호자·로봇 ID를 넣지 않는다.</x:v>
+        <x:v>최종 결과 반영 뒤 target과 함께 null로 비우며 다른 명령 ID로 덮어쓰지 않는다.</x:v>
       </x:c>
       <x:c r="L66" s="25" t="str">
-        <x:v>a2b64af3-5ee5-42ea-98c5-35ac9de10570</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="67">
+        <x:v>01K1WAKECMD7F5M2N1Q9R6S3T8V</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67" ht="30" hidden="0" customHeight="1">
       <x:c r="A67" s="26" t="str">
-        <x:v>conversation</x:v>
+        <x:v>scenario</x:v>
       </x:c>
       <x:c r="B67" s="26" t="n">
-        <x:v>3</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C67" s="26" t="str">
-        <x:v>scenario_id</x:v>
+        <x:v>active_navigation_target</x:v>
       </x:c>
       <x:c r="D67" s="26" t="str">
-        <x:v>시나리오 ID</x:v>
+        <x:v>활성 이동 목적지</x:v>
       </x:c>
       <x:c r="E67" s="26" t="str">
-        <x:v>UUID</x:v>
+        <x:v>VARCHAR(30)</x:v>
       </x:c>
       <x:c r="F67" s="26" t="str">
         <x:v>N</x:v>
       </x:c>
-      <x:c r="G67" s="26" t="str">
-        <x:v>FK</x:v>
-      </x:c>
-      <x:c r="H67" s="26" t="str">
-        <x:v>scenario.id</x:v>
-      </x:c>
+      <x:c r="G67" s="26" t="str"/>
+      <x:c r="H67" s="26" t="str"/>
       <x:c r="I67" s="26" t="str">
-        <x:v>conversation.scenario_id에는 대화를 유발한 시나리오를 연결하는 값을 저장한다.</x:v>
+        <x:v>현재 NAVIGATE 명령의 합의된 논리 목적지를 저장한다.</x:v>
       </x:c>
       <x:c r="J67" s="26" t="str">
-        <x:v>시나리오 ID은(는) 대화를 유발한 시나리오를 연결할 때 조회·검증·갱신한다.</x:v>
+        <x:v>재시작 뒤에도 결과가 상태에 맞는 LIVING_ROOM·ENTRANCE·DEFAULT 명령인지 확인한다.</x:v>
       </x:c>
       <x:c r="K67" s="26" t="str">
-        <x:v>온보딩·수동 대화는 없을 수 있다.</x:v>
+        <x:v>commandId와 항상 함께 존재하거나 함께 null이어야 한다.</x:v>
       </x:c>
       <x:c r="L67" s="26" t="str">
-        <x:v>6fd94c8c-3903-4a01-a82d-819e0c8edb12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="68">
+        <x:v>LIVING_ROOM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68" ht="30" hidden="0" customHeight="1">
       <x:c r="A68" s="25" t="str">
-        <x:v>conversation</x:v>
+        <x:v>scenario</x:v>
       </x:c>
       <x:c r="B68" s="25" t="n">
-        <x:v>4</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C68" s="25" t="str">
-        <x:v>status</x:v>
+        <x:v>trigger_context</x:v>
       </x:c>
       <x:c r="D68" s="25" t="str">
-        <x:v>대화 상태</x:v>
+        <x:v>호출 트리거 최소 문맥</x:v>
       </x:c>
       <x:c r="E68" s="25" t="str">
-        <x:v>VARCHAR(30)</x:v>
+        <x:v>JSONB</x:v>
       </x:c>
       <x:c r="F68" s="25" t="str">
-        <x:v>Y</x:v>
+        <x:v>N</x:v>
       </x:c>
       <x:c r="G68" s="25" t="str"/>
       <x:c r="H68" s="25" t="str"/>
       <x:c r="I68" s="25" t="str">
-        <x:v>conversation.status에는 진행·완료·실패·취소를 구분하는 값을 저장한다.</x:v>
+        <x:v>호출을 확정한 robotId·occurredAt·keyword와 선택 confidence를 구조화해 저장한다.</x:v>
       </x:c>
       <x:c r="J68" s="25" t="str">
-        <x:v>대화 상태은(는) 진행·완료·실패·취소를 구분할 때 조회·검증·갱신한다.</x:v>
+        <x:v>호출 이력과 재시작 후 진단에 사용하고 음성 데이터 없이 감지 근거만 확인한다.</x:v>
       </x:c>
       <x:c r="K68" s="25" t="str">
-        <x:v>종료 뒤 새 메시지를 추가하지 않는다.</x:v>
+        <x:v>원본 음성·전체 STT·자유 대화 문장을 저장하지 않는다.</x:v>
       </x:c>
       <x:c r="L68" s="25" t="str">
-        <x:v>OPEN</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="69">
+        <x:v>{"robotId":"bomi-AA001","occurredAt":"2026-08-05T14:00:00+09:00","keyword":"보미야","confidence":0.92}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69" ht="30" hidden="0" customHeight="1">
       <x:c r="A69" s="26" t="str">
-        <x:v>conversation</x:v>
+        <x:v>scenario</x:v>
       </x:c>
       <x:c r="B69" s="26" t="n">
-        <x:v>5</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C69" s="26" t="str">
-        <x:v>started_at</x:v>
+        <x:v>completion_result_code</x:v>
       </x:c>
       <x:c r="D69" s="26" t="str">
-        <x:v>대화 시작 시각</x:v>
+        <x:v>종료 결과 코드</x:v>
       </x:c>
       <x:c r="E69" s="26" t="str">
-        <x:v>TIMESTAMPTZ</x:v>
+        <x:v>VARCHAR(50)</x:v>
       </x:c>
       <x:c r="F69" s="26" t="str">
-        <x:v>Y</x:v>
+        <x:v>N</x:v>
       </x:c>
       <x:c r="G69" s="26" t="str"/>
       <x:c r="H69" s="26" t="str"/>
       <x:c r="I69" s="26" t="str">
-        <x:v>conversation.started_at에는 첫 실제 대화가 시작된 시각을 기록하는 값을 저장한다.</x:v>
+        <x:v>상관 검증을 통과한 Robot 최종 resultCode를 저장한다.</x:v>
       </x:c>
       <x:c r="J69" s="26" t="str">
-        <x:v>대화 시작 시각은(는) 첫 실제 대화가 시작된 시각을 기록할 때 조회·검증·갱신한다.</x:v>
+        <x:v>호출 완료·실패·취소·시간 초과 이력을 구조화해 조회할 때 사용한다.</x:v>
       </x:c>
       <x:c r="K69" s="26" t="str">
-        <x:v>행 생성 시각으로 단정하지 않는다.</x:v>
+        <x:v>사람이 읽는 설명이나 STT 문장을 넣지 않는다.</x:v>
       </x:c>
       <x:c r="L69" s="26" t="str">
-        <x:v>UTC 2026-07-27T10:00:00Z</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="70">
+        <x:v>ARRIVED</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70" ht="30" hidden="0" customHeight="1">
       <x:c r="A70" s="25" t="str">
-        <x:v>conversation</x:v>
+        <x:v>scenario</x:v>
       </x:c>
       <x:c r="B70" s="25" t="n">
-        <x:v>6</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C70" s="25" t="str">
-        <x:v>ended_at</x:v>
+        <x:v>completion_reason_code</x:v>
       </x:c>
       <x:c r="D70" s="25" t="str">
-        <x:v>대화 종료 시각</x:v>
+        <x:v>종료 원인 코드</x:v>
       </x:c>
       <x:c r="E70" s="25" t="str">
-        <x:v>TIMESTAMPTZ</x:v>
+        <x:v>VARCHAR(100)</x:v>
       </x:c>
       <x:c r="F70" s="25" t="str">
         <x:v>N</x:v>
@@ -3315,97 +3339,95 @@
       <x:c r="G70" s="25" t="str"/>
       <x:c r="H70" s="25" t="str"/>
       <x:c r="I70" s="25" t="str">
-        <x:v>conversation.ended_at에는 정상·실패·취소를 포함한 종료 시각을 기록하는 값을 저장한다.</x:v>
+        <x:v>실패·취소·시간 초과의 안정적인 reasonCode를 저장한다.</x:v>
       </x:c>
       <x:c r="J70" s="25" t="str">
-        <x:v>대화 종료 시각은(는) 정상·실패·취소를 포함한 종료 시각을 기록할 때 조회·검증·갱신한다.</x:v>
+        <x:v>NOT_ARRIVED 결과의 운영 원인을 집계하고 진단할 때 사용한다.</x:v>
       </x:c>
       <x:c r="K70" s="25" t="str">
-        <x:v>Raw 삭제 예정 시각과 다르다.</x:v>
+        <x:v>성공이고 원인이 없으면 null이며 자유 문장을 저장하지 않는다.</x:v>
       </x:c>
       <x:c r="L70" s="25" t="str">
-        <x:v>UTC 2026-07-27T10:20:00Z</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="71">
+        <x:v>PATH_BLOCKED</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71" ht="30" hidden="0" customHeight="1">
       <x:c r="A71" s="26" t="str">
-        <x:v>conversation</x:v>
+        <x:v>scenario</x:v>
       </x:c>
       <x:c r="B71" s="26" t="n">
-        <x:v>7</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C71" s="26" t="str">
-        <x:v>raw_messages_expires_at</x:v>
+        <x:v>created_at</x:v>
       </x:c>
       <x:c r="D71" s="26" t="str">
-        <x:v>Raw 만료 예정 시각</x:v>
+        <x:v>시나리오 생성 시각</x:v>
       </x:c>
       <x:c r="E71" s="26" t="str">
         <x:v>TIMESTAMPTZ</x:v>
       </x:c>
       <x:c r="F71" s="26" t="str">
-        <x:v>N</x:v>
+        <x:v>Y</x:v>
       </x:c>
       <x:c r="G71" s="26" t="str"/>
       <x:c r="H71" s="26" t="str"/>
       <x:c r="I71" s="26" t="str">
-        <x:v>conversation.raw_messages_expires_at에는 Raw 메시지 보존기간 종료 시점을 기록하는 값을 저장한다.</x:v>
+        <x:v>시나리오 행이 처음 생성된 시각을 저장한다.</x:v>
       </x:c>
       <x:c r="J71" s="26" t="str">
-        <x:v>Raw 만료 예정 시각은(는) Raw 메시지 보존기간 종료 시점을 기록할 때 조회·검증·갱신한다.</x:v>
+        <x:v>멱등 처리와 이력 정렬의 생성 기준으로 사용한다.</x:v>
       </x:c>
       <x:c r="K71" s="26" t="str">
-        <x:v>삭제 조건 충족을 자동으로 증명하지 않는다.</x:v>
+        <x:v>센서 occurredAt이나 완료 시각으로 대체하지 않는다.</x:v>
       </x:c>
       <x:c r="L71" s="26" t="str">
-        <x:v>UTC 2026-08-03T10:20:00Z</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="72">
+        <x:v>UTC 2026-08-05T05:00:01Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72" ht="30" hidden="0" customHeight="1">
       <x:c r="A72" s="25" t="str">
-        <x:v>conversation_message</x:v>
+        <x:v>scenario</x:v>
       </x:c>
       <x:c r="B72" s="25" t="n">
-        <x:v>1</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C72" s="25" t="str">
-        <x:v>id</x:v>
+        <x:v>updated_at</x:v>
       </x:c>
       <x:c r="D72" s="25" t="str">
-        <x:v>메시지 ID</x:v>
+        <x:v>시나리오 수정 시각</x:v>
       </x:c>
       <x:c r="E72" s="25" t="str">
-        <x:v>UUID</x:v>
+        <x:v>TIMESTAMPTZ</x:v>
       </x:c>
       <x:c r="F72" s="25" t="str">
         <x:v>Y</x:v>
       </x:c>
-      <x:c r="G72" s="25" t="str">
-        <x:v>PK</x:v>
-      </x:c>
+      <x:c r="G72" s="25" t="str"/>
       <x:c r="H72" s="25" t="str"/>
       <x:c r="I72" s="25" t="str">
-        <x:v>conversation_message.id에는 실제 발화 한 번을 식별하는 값을 저장한다.</x:v>
+        <x:v>시나리오 상태가 마지막으로 갱신된 시각을 저장한다.</x:v>
       </x:c>
       <x:c r="J72" s="25" t="str">
-        <x:v>메시지 ID은(는) 실제 발화 한 번을 식별할 때 조회·검증·갱신한다.</x:v>
+        <x:v>활성 시나리오 watchdog과 운영 진단의 정체 기준으로 사용한다.</x:v>
       </x:c>
       <x:c r="K72" s="25" t="str">
-        <x:v>외부 AI requestId로 대체하지 않는다.</x:v>
+        <x:v>종료 시각 전용 컬럼으로 해석하지 않는다.</x:v>
       </x:c>
       <x:c r="L72" s="25" t="str">
-        <x:v>a6f8cb84-c91c-4a38-a7b6-386ce6aa027f</x:v>
+        <x:v>UTC 2026-08-05T05:00:09Z</x:v>
       </x:c>
     </x:row>
     <x:row r="73">
       <x:c r="A73" s="26" t="str">
-        <x:v>conversation_message</x:v>
+        <x:v>conversation</x:v>
       </x:c>
       <x:c r="B73" s="26" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C73" s="26" t="str">
-        <x:v>conversation_id</x:v>
+        <x:v>id</x:v>
       </x:c>
       <x:c r="D73" s="26" t="str">
         <x:v>대화 ID</x:v>
@@ -3417,19 +3439,17 @@
         <x:v>Y</x:v>
       </x:c>
       <x:c r="G73" s="26" t="str">
-        <x:v>FK</x:v>
-      </x:c>
-      <x:c r="H73" s="26" t="str">
-        <x:v>conversation.id</x:v>
-      </x:c>
+        <x:v>PK</x:v>
+      </x:c>
+      <x:c r="H73" s="26"/>
       <x:c r="I73" s="26" t="str">
-        <x:v>conversation_message.conversation_id에는 발화가 속한 대화를 연결하는 값을 저장한다.</x:v>
+        <x:v>conversation.id에는 대화 묶음을 식별하는 값을 저장한다.</x:v>
       </x:c>
       <x:c r="J73" s="26" t="str">
-        <x:v>대화 ID은(는) 발화가 속한 대화를 연결할 때 조회·검증·갱신한다.</x:v>
+        <x:v>대화 ID은(는) 대화 묶음을 식별할 때 조회·검증·갱신한다.</x:v>
       </x:c>
       <x:c r="K73" s="26" t="str">
-        <x:v>대화 senior와 접근 대상을 일치시킨다.</x:v>
+        <x:v>메시지 ID와 혼동하지 않는다.</x:v>
       </x:c>
       <x:c r="L73" s="26" t="str">
         <x:v>1a4fe41a-6464-4e7e-b292-9a507333a3fa</x:v>
@@ -3437,118 +3457,126 @@
     </x:row>
     <x:row r="74">
       <x:c r="A74" s="25" t="str">
-        <x:v>conversation_message</x:v>
+        <x:v>conversation</x:v>
       </x:c>
       <x:c r="B74" s="25" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C74" s="25" t="str">
-        <x:v>sequence_no</x:v>
+        <x:v>senior_id</x:v>
       </x:c>
       <x:c r="D74" s="25" t="str">
-        <x:v>대화 내 순번</x:v>
+        <x:v>대화 시니어 ID</x:v>
       </x:c>
       <x:c r="E74" s="25" t="str">
-        <x:v>INTEGER</x:v>
+        <x:v>UUID</x:v>
       </x:c>
       <x:c r="F74" s="25" t="str">
         <x:v>Y</x:v>
       </x:c>
-      <x:c r="G74" s="25" t="str"/>
-      <x:c r="H74" s="25" t="str"/>
+      <x:c r="G74" s="25" t="str">
+        <x:v>FK</x:v>
+      </x:c>
+      <x:c r="H74" s="25" t="str">
+        <x:v>app_user.id</x:v>
+      </x:c>
       <x:c r="I74" s="25" t="str">
-        <x:v>conversation_message.sequence_no에는 같은 대화의 발화 순서를 안정적으로 지정하는 값을 저장한다.</x:v>
+        <x:v>conversation.senior_id에는 대화 소유자를 연결하는 값을 저장한다.</x:v>
       </x:c>
       <x:c r="J74" s="25" t="str">
-        <x:v>대화 내 순번은(는) 같은 대화의 발화 순서를 안정적으로 지정할 때 조회·검증·갱신한다.</x:v>
+        <x:v>대화 시니어 ID은(는) 대화 소유자를 연결할 때 조회·검증·갱신한다.</x:v>
       </x:c>
       <x:c r="K74" s="25" t="str">
-        <x:v>1부터 증가하고 대화 안에서 유일해야 한다.</x:v>
+        <x:v>보호자·로봇 ID를 넣지 않는다.</x:v>
       </x:c>
       <x:c r="L74" s="25" t="str">
-        <x:v>7</x:v>
+        <x:v>a2b64af3-5ee5-42ea-98c5-35ac9de10570</x:v>
       </x:c>
     </x:row>
     <x:row r="75">
       <x:c r="A75" s="26" t="str">
-        <x:v>conversation_message</x:v>
+        <x:v>conversation</x:v>
       </x:c>
       <x:c r="B75" s="26" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C75" s="26" t="str">
-        <x:v>role</x:v>
+        <x:v>scenario_id</x:v>
       </x:c>
       <x:c r="D75" s="26" t="str">
-        <x:v>발화 역할</x:v>
+        <x:v>시나리오 ID</x:v>
       </x:c>
       <x:c r="E75" s="26" t="str">
-        <x:v>VARCHAR(20)</x:v>
+        <x:v>UUID</x:v>
       </x:c>
       <x:c r="F75" s="26" t="str">
-        <x:v>Y</x:v>
-      </x:c>
-      <x:c r="G75" s="26" t="str"/>
-      <x:c r="H75" s="26" t="str"/>
+        <x:v>N</x:v>
+      </x:c>
+      <x:c r="G75" s="26" t="str">
+        <x:v>FK</x:v>
+      </x:c>
+      <x:c r="H75" s="26" t="str">
+        <x:v>scenario.id</x:v>
+      </x:c>
       <x:c r="I75" s="26" t="str">
-        <x:v>conversation_message.role에는 시니어와 로봇 발화를 구분하는 값을 저장한다.</x:v>
+        <x:v>conversation.scenario_id에는 대화를 유발한 시나리오를 연결하는 값을 저장한다.</x:v>
       </x:c>
       <x:c r="J75" s="26" t="str">
-        <x:v>발화 역할은(는) 시니어와 로봇 발화를 구분할 때 조회·검증·갱신한다.</x:v>
+        <x:v>시나리오 ID은(는) 대화를 유발한 시나리오를 연결할 때 조회·검증·갱신한다.</x:v>
       </x:c>
       <x:c r="K75" s="26" t="str">
-        <x:v>SYSTEM·GUARDIAN을 임의 추가하지 않는다.</x:v>
+        <x:v>온보딩·수동 대화는 없을 수 있다.</x:v>
       </x:c>
       <x:c r="L75" s="26" t="str">
-        <x:v>SENIOR</x:v>
+        <x:v>6fd94c8c-3903-4a01-a82d-819e0c8edb12</x:v>
       </x:c>
     </x:row>
     <x:row r="76">
       <x:c r="A76" s="25" t="str">
-        <x:v>conversation_message</x:v>
+        <x:v>conversation</x:v>
       </x:c>
       <x:c r="B76" s="25" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C76" s="25" t="str">
-        <x:v>content</x:v>
+        <x:v>status</x:v>
       </x:c>
       <x:c r="D76" s="25" t="str">
-        <x:v>최종 텍스트</x:v>
+        <x:v>대화 상태</x:v>
       </x:c>
       <x:c r="E76" s="25" t="str">
-        <x:v>TEXT</x:v>
+        <x:v>VARCHAR(30)</x:v>
       </x:c>
       <x:c r="F76" s="25" t="str">
         <x:v>Y</x:v>
       </x:c>
-      <x:c r="G76" s="25" t="str"/>
-      <x:c r="H76" s="25" t="str"/>
+      <x:c r="G76" s="25"/>
+      <x:c r="H76" s="25"/>
       <x:c r="I76" s="25" t="str">
-        <x:v>conversation_message.content에는 실제로 사용한 최종 발화 텍스트를 저장하는 값을 저장한다.</x:v>
+        <x:v>conversation.status에는 진행·완료·실패·취소를 구분하는 값을 저장한다.</x:v>
       </x:c>
       <x:c r="J76" s="25" t="str">
-        <x:v>최종 텍스트은(는) 실제로 사용한 최종 발화 텍스트를 저장할 때 조회·검증·갱신한다.</x:v>
+        <x:v>대화 상태은(는) 진행·완료·실패·취소를 구분할 때 조회·검증·갱신한다.</x:v>
       </x:c>
       <x:c r="K76" s="25" t="str">
-        <x:v>음성 바이너리·전체 프롬프트를 넣지 않는다.</x:v>
+        <x:v>종료 뒤 새 메시지를 추가하지 않는다.</x:v>
       </x:c>
       <x:c r="L76" s="25" t="str">
-        <x:v>내일 병원은 오후 세 시야</x:v>
+        <x:v>OPEN</x:v>
       </x:c>
     </x:row>
     <x:row r="77">
       <x:c r="A77" s="26" t="str">
-        <x:v>conversation_message</x:v>
+        <x:v>conversation</x:v>
       </x:c>
       <x:c r="B77" s="26" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C77" s="26" t="str">
-        <x:v>occurred_at</x:v>
+        <x:v>started_at</x:v>
       </x:c>
       <x:c r="D77" s="26" t="str">
-        <x:v>발화 발생 시각</x:v>
+        <x:v>대화 시작 시각</x:v>
       </x:c>
       <x:c r="E77" s="26" t="str">
         <x:v>TIMESTAMPTZ</x:v>
@@ -3556,103 +3584,101 @@
       <x:c r="F77" s="26" t="str">
         <x:v>Y</x:v>
       </x:c>
-      <x:c r="G77" s="26" t="str"/>
-      <x:c r="H77" s="26" t="str"/>
+      <x:c r="G77" s="26"/>
+      <x:c r="H77" s="26"/>
       <x:c r="I77" s="26" t="str">
-        <x:v>conversation_message.occurred_at에는 발화가 실제 발생한 시각을 기록하는 값을 저장한다.</x:v>
+        <x:v>conversation.started_at에는 첫 실제 대화가 시작된 시각을 기록하는 값을 저장한다.</x:v>
       </x:c>
       <x:c r="J77" s="26" t="str">
-        <x:v>발화 발생 시각은(는) 발화가 실제 발생한 시각을 기록할 때 조회·검증·갱신한다.</x:v>
+        <x:v>대화 시작 시각은(는) 첫 실제 대화가 시작된 시각을 기록할 때 조회·검증·갱신한다.</x:v>
       </x:c>
       <x:c r="K77" s="26" t="str">
-        <x:v>DB 수신·행 생성 시각과 구분한다.</x:v>
+        <x:v>행 생성 시각으로 단정하지 않는다.</x:v>
       </x:c>
       <x:c r="L77" s="26" t="str">
-        <x:v>UTC 2026-07-27T10:12:30Z</x:v>
+        <x:v>UTC 2026-07-27T10:00:00Z</x:v>
       </x:c>
     </x:row>
     <x:row r="78">
       <x:c r="A78" s="25" t="str">
-        <x:v>conversation_message</x:v>
+        <x:v>conversation</x:v>
       </x:c>
       <x:c r="B78" s="25" t="n">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C78" s="25" t="str">
-        <x:v>created_at</x:v>
+        <x:v>ended_at</x:v>
       </x:c>
       <x:c r="D78" s="25" t="str">
-        <x:v>행 생성 시각</x:v>
+        <x:v>대화 종료 시각</x:v>
       </x:c>
       <x:c r="E78" s="25" t="str">
         <x:v>TIMESTAMPTZ</x:v>
       </x:c>
       <x:c r="F78" s="25" t="str">
-        <x:v>Y</x:v>
-      </x:c>
-      <x:c r="G78" s="25" t="str"/>
-      <x:c r="H78" s="25" t="str"/>
+        <x:v>N</x:v>
+      </x:c>
+      <x:c r="G78" s="25"/>
+      <x:c r="H78" s="25"/>
       <x:c r="I78" s="25" t="str">
-        <x:v>conversation_message.created_at에는 메시지 행이 DB에 생성된 시각을 기록하는 값을 저장한다.</x:v>
+        <x:v>conversation.ended_at에는 정상·실패·취소를 포함한 종료 시각을 기록하는 값을 저장한다.</x:v>
       </x:c>
       <x:c r="J78" s="25" t="str">
-        <x:v>행 생성 시각은(는) 메시지 행이 DB에 생성된 시각을 기록할 때 조회·검증·갱신한다.</x:v>
+        <x:v>대화 종료 시각은(는) 정상·실패·취소를 포함한 종료 시각을 기록할 때 조회·검증·갱신한다.</x:v>
       </x:c>
       <x:c r="K78" s="25" t="str">
-        <x:v>발화 시간 정렬에는 occurred_at을 쓴다.</x:v>
+        <x:v>Raw 삭제 예정 시각과 다르다.</x:v>
       </x:c>
       <x:c r="L78" s="25" t="str">
-        <x:v>UTC 2026-07-27T10:12:31Z</x:v>
+        <x:v>UTC 2026-07-27T10:20:00Z</x:v>
       </x:c>
     </x:row>
     <x:row r="79">
       <x:c r="A79" s="26" t="str">
-        <x:v>conversation_summary</x:v>
+        <x:v>conversation</x:v>
       </x:c>
       <x:c r="B79" s="26" t="n">
-        <x:v>1</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C79" s="26" t="str">
-        <x:v>id</x:v>
+        <x:v>raw_messages_expires_at</x:v>
       </x:c>
       <x:c r="D79" s="26" t="str">
-        <x:v>요약 ID</x:v>
+        <x:v>Raw 만료 예정 시각</x:v>
       </x:c>
       <x:c r="E79" s="26" t="str">
-        <x:v>UUID</x:v>
+        <x:v>TIMESTAMPTZ</x:v>
       </x:c>
       <x:c r="F79" s="26" t="str">
-        <x:v>Y</x:v>
-      </x:c>
-      <x:c r="G79" s="26" t="str">
-        <x:v>PK</x:v>
-      </x:c>
-      <x:c r="H79" s="26" t="str"/>
+        <x:v>N</x:v>
+      </x:c>
+      <x:c r="G79" s="26"/>
+      <x:c r="H79" s="26"/>
       <x:c r="I79" s="26" t="str">
-        <x:v>conversation_summary.id에는 요약 버전 한 건을 식별하는 값을 저장한다.</x:v>
+        <x:v>conversation.raw_messages_expires_at에는 Raw 메시지 보존기간 종료 시점을 기록하는 값을 저장한다.</x:v>
       </x:c>
       <x:c r="J79" s="26" t="str">
-        <x:v>요약 ID은(는) 요약 버전 한 건을 식별할 때 조회·검증·갱신한다.</x:v>
+        <x:v>Raw 만료 예정 시각은(는) Raw 메시지 보존기간 종료 시점을 기록할 때 조회·검증·갱신한다.</x:v>
       </x:c>
       <x:c r="K79" s="26" t="str">
-        <x:v>기간 키를 외부 식별자로 노출하지 않는다.</x:v>
+        <x:v>삭제 조건 충족을 자동으로 증명하지 않는다.</x:v>
       </x:c>
       <x:c r="L79" s="26" t="str">
-        <x:v>9cd9cbdd-1e7c-4cbb-9014-4ddfb82b73e0</x:v>
+        <x:v>UTC 2026-08-03T10:20:00Z</x:v>
       </x:c>
     </x:row>
     <x:row r="80">
       <x:c r="A80" s="25" t="str">
-        <x:v>conversation_summary</x:v>
+        <x:v>conversation_message</x:v>
       </x:c>
       <x:c r="B80" s="25" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C80" s="25" t="str">
-        <x:v>senior_id</x:v>
+        <x:v>id</x:v>
       </x:c>
       <x:c r="D80" s="25" t="str">
-        <x:v>시니어 ID</x:v>
+        <x:v>메시지 ID</x:v>
       </x:c>
       <x:c r="E80" s="25" t="str">
         <x:v>UUID</x:v>
@@ -3661,30 +3687,28 @@
         <x:v>Y</x:v>
       </x:c>
       <x:c r="G80" s="25" t="str">
-        <x:v>FK</x:v>
-      </x:c>
-      <x:c r="H80" s="25" t="str">
-        <x:v>app_user.id</x:v>
-      </x:c>
+        <x:v>PK</x:v>
+      </x:c>
+      <x:c r="H80" s="25"/>
       <x:c r="I80" s="25" t="str">
-        <x:v>conversation_summary.senior_id에는 요약 소유자를 연결하는 값을 저장한다.</x:v>
+        <x:v>conversation_message.id에는 실제 발화 한 번을 식별하는 값을 저장한다.</x:v>
       </x:c>
       <x:c r="J80" s="25" t="str">
-        <x:v>시니어 ID은(는) 요약 소유자를 연결할 때 조회·검증·갱신한다.</x:v>
+        <x:v>메시지 ID은(는) 실제 발화 한 번을 식별할 때 조회·검증·갱신한다.</x:v>
       </x:c>
       <x:c r="K80" s="25" t="str">
-        <x:v>다른 시니어의 메시지를 섞지 않는다.</x:v>
+        <x:v>외부 AI requestId로 대체하지 않는다.</x:v>
       </x:c>
       <x:c r="L80" s="25" t="str">
-        <x:v>a2b64af3-5ee5-42ea-98c5-35ac9de10570</x:v>
+        <x:v>a6f8cb84-c91c-4a38-a7b6-386ce6aa027f</x:v>
       </x:c>
     </x:row>
     <x:row r="81">
       <x:c r="A81" s="26" t="str">
-        <x:v>conversation_summary</x:v>
+        <x:v>conversation_message</x:v>
       </x:c>
       <x:c r="B81" s="26" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C81" s="26" t="str">
         <x:v>conversation_id</x:v>
@@ -3696,7 +3720,7 @@
         <x:v>UUID</x:v>
       </x:c>
       <x:c r="F81" s="26" t="str">
-        <x:v>N</x:v>
+        <x:v>Y</x:v>
       </x:c>
       <x:c r="G81" s="26" t="str">
         <x:v>FK</x:v>
@@ -3705,13 +3729,13 @@
         <x:v>conversation.id</x:v>
       </x:c>
       <x:c r="I81" s="26" t="str">
-        <x:v>conversation_summary.conversation_id에는 CONVERSATION 요약의 대상 대화를 연결하는 값을 저장한다.</x:v>
+        <x:v>conversation_message.conversation_id에는 발화가 속한 대화를 연결하는 값을 저장한다.</x:v>
       </x:c>
       <x:c r="J81" s="26" t="str">
-        <x:v>대화 ID은(는) CONVERSATION 요약의 대상 대화를 연결할 때 조회·검증·갱신한다.</x:v>
+        <x:v>대화 ID은(는) 발화가 속한 대화를 연결할 때 조회·검증·갱신한다.</x:v>
       </x:c>
       <x:c r="K81" s="26" t="str">
-        <x:v>DAILY 요약은 null이어야 한다.</x:v>
+        <x:v>대화 senior와 접근 대상을 일치시킨다.</x:v>
       </x:c>
       <x:c r="L81" s="26" t="str">
         <x:v>1a4fe41a-6464-4e7e-b292-9a507333a3fa</x:v>
@@ -3719,172 +3743,172 @@
     </x:row>
     <x:row r="82">
       <x:c r="A82" s="25" t="str">
-        <x:v>conversation_summary</x:v>
+        <x:v>conversation_message</x:v>
       </x:c>
       <x:c r="B82" s="25" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C82" s="25" t="str">
-        <x:v>summary_type</x:v>
+        <x:v>sequence_no</x:v>
       </x:c>
       <x:c r="D82" s="25" t="str">
-        <x:v>요약 유형</x:v>
+        <x:v>대화 내 순번</x:v>
       </x:c>
       <x:c r="E82" s="25" t="str">
-        <x:v>VARCHAR(30)</x:v>
+        <x:v>INTEGER</x:v>
       </x:c>
       <x:c r="F82" s="25" t="str">
         <x:v>Y</x:v>
       </x:c>
-      <x:c r="G82" s="25" t="str"/>
-      <x:c r="H82" s="25" t="str"/>
+      <x:c r="G82" s="25"/>
+      <x:c r="H82" s="25"/>
       <x:c r="I82" s="25" t="str">
-        <x:v>conversation_summary.summary_type에는 대화 단위와 일간 요약을 구분하는 값을 저장한다.</x:v>
+        <x:v>conversation_message.sequence_no에는 같은 대화의 발화 순서를 안정적으로 지정하는 값을 저장한다.</x:v>
       </x:c>
       <x:c r="J82" s="25" t="str">
-        <x:v>요약 유형은(는) 대화 단위와 일간 요약을 구분할 때 조회·검증·갱신한다.</x:v>
+        <x:v>대화 내 순번은(는) 같은 대화의 발화 순서를 안정적으로 지정할 때 조회·검증·갱신한다.</x:v>
       </x:c>
       <x:c r="K82" s="25" t="str">
-        <x:v>TIME_WINDOW는 MVP에 쓰지 않는다.</x:v>
+        <x:v>1부터 증가하고 대화 안에서 유일해야 한다.</x:v>
       </x:c>
       <x:c r="L82" s="25" t="str">
-        <x:v>CONVERSATION</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="83">
       <x:c r="A83" s="26" t="str">
-        <x:v>conversation_summary</x:v>
+        <x:v>conversation_message</x:v>
       </x:c>
       <x:c r="B83" s="26" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C83" s="26" t="str">
-        <x:v>period_started_at</x:v>
+        <x:v>role</x:v>
       </x:c>
       <x:c r="D83" s="26" t="str">
-        <x:v>요약 구간 시작</x:v>
+        <x:v>발화 역할</x:v>
       </x:c>
       <x:c r="E83" s="26" t="str">
-        <x:v>TIMESTAMPTZ</x:v>
+        <x:v>VARCHAR(20)</x:v>
       </x:c>
       <x:c r="F83" s="26" t="str">
         <x:v>Y</x:v>
       </x:c>
-      <x:c r="G83" s="26" t="str"/>
-      <x:c r="H83" s="26" t="str"/>
+      <x:c r="G83" s="26"/>
+      <x:c r="H83" s="26"/>
       <x:c r="I83" s="26" t="str">
-        <x:v>conversation_summary.period_started_at에는 요약에 포함된 첫 시간 경계를 기록하는 값을 저장한다.</x:v>
+        <x:v>conversation_message.role에는 시니어와 로봇 발화를 구분하는 값을 저장한다.</x:v>
       </x:c>
       <x:c r="J83" s="26" t="str">
-        <x:v>요약 구간 시작은(는) 요약에 포함된 첫 시간 경계를 기록할 때 조회·검증·갱신한다.</x:v>
+        <x:v>발화 역할은(는) 시니어와 로봇 발화를 구분할 때 조회·검증·갱신한다.</x:v>
       </x:c>
       <x:c r="K83" s="26" t="str">
-        <x:v>사용자 현지 구간을 UTC로 변환해 저장한다.</x:v>
+        <x:v>SYSTEM·GUARDIAN을 임의 추가하지 않는다.</x:v>
       </x:c>
       <x:c r="L83" s="26" t="str">
-        <x:v>UTC 2026-07-27T00:00:00Z</x:v>
+        <x:v>SENIOR</x:v>
       </x:c>
     </x:row>
     <x:row r="84">
       <x:c r="A84" s="25" t="str">
-        <x:v>conversation_summary</x:v>
+        <x:v>conversation_message</x:v>
       </x:c>
       <x:c r="B84" s="25" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C84" s="25" t="str">
-        <x:v>period_ended_at</x:v>
+        <x:v>content</x:v>
       </x:c>
       <x:c r="D84" s="25" t="str">
-        <x:v>요약 구간 종료</x:v>
+        <x:v>최종 텍스트</x:v>
       </x:c>
       <x:c r="E84" s="25" t="str">
-        <x:v>TIMESTAMPTZ</x:v>
+        <x:v>TEXT</x:v>
       </x:c>
       <x:c r="F84" s="25" t="str">
         <x:v>Y</x:v>
       </x:c>
-      <x:c r="G84" s="25" t="str"/>
-      <x:c r="H84" s="25" t="str"/>
+      <x:c r="G84" s="25"/>
+      <x:c r="H84" s="25"/>
       <x:c r="I84" s="25" t="str">
-        <x:v>conversation_summary.period_ended_at에는 요약에 포함된 끝 시간 경계를 기록하는 값을 저장한다.</x:v>
+        <x:v>conversation_message.content에는 실제로 사용한 최종 발화 텍스트를 저장하는 값을 저장한다.</x:v>
       </x:c>
       <x:c r="J84" s="25" t="str">
-        <x:v>요약 구간 종료은(는) 요약에 포함된 끝 시간 경계를 기록할 때 조회·검증·갱신한다.</x:v>
+        <x:v>최종 텍스트은(는) 실제로 사용한 최종 발화 텍스트를 저장할 때 조회·검증·갱신한다.</x:v>
       </x:c>
       <x:c r="K84" s="25" t="str">
-        <x:v>시작보다 늦어야 하고 경계 규칙을 일관되게 쓴다.</x:v>
+        <x:v>음성 바이너리·전체 프롬프트를 넣지 않는다.</x:v>
       </x:c>
       <x:c r="L84" s="25" t="str">
-        <x:v>UTC 2026-07-27T10:20:00Z</x:v>
+        <x:v>내일 병원은 오후 세 시야</x:v>
       </x:c>
     </x:row>
     <x:row r="85">
       <x:c r="A85" s="26" t="str">
-        <x:v>conversation_summary</x:v>
+        <x:v>conversation_message</x:v>
       </x:c>
       <x:c r="B85" s="26" t="n">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C85" s="26" t="str">
-        <x:v>content</x:v>
+        <x:v>occurred_at</x:v>
       </x:c>
       <x:c r="D85" s="26" t="str">
-        <x:v>요약 내용</x:v>
+        <x:v>발화 발생 시각</x:v>
       </x:c>
       <x:c r="E85" s="26" t="str">
-        <x:v>TEXT</x:v>
+        <x:v>TIMESTAMPTZ</x:v>
       </x:c>
       <x:c r="F85" s="26" t="str">
         <x:v>Y</x:v>
       </x:c>
-      <x:c r="G85" s="26" t="str"/>
-      <x:c r="H85" s="26" t="str"/>
+      <x:c r="G85" s="26"/>
+      <x:c r="H85" s="26"/>
       <x:c r="I85" s="26" t="str">
-        <x:v>conversation_summary.content에는 대화 문맥을 압축한 텍스트를 저장하는 값을 저장한다.</x:v>
+        <x:v>conversation_message.occurred_at에는 발화가 실제 발생한 시각을 기록하는 값을 저장한다.</x:v>
       </x:c>
       <x:c r="J85" s="26" t="str">
-        <x:v>요약 내용은(는) 대화 문맥을 압축한 텍스트를 저장할 때 조회·검증·갱신한다.</x:v>
+        <x:v>발화 발생 시각은(는) 발화가 실제 발생한 시각을 기록할 때 조회·검증·갱신한다.</x:v>
       </x:c>
       <x:c r="K85" s="26" t="str">
-        <x:v>장기 사실 전문이나 근거 발화를 복제하지 않는다.</x:v>
+        <x:v>DB 수신·행 생성 시각과 구분한다.</x:v>
       </x:c>
       <x:c r="L85" s="26" t="str">
-        <x:v>병원 일정과 저녁 복약 시간을 확인했다.</x:v>
+        <x:v>UTC 2026-07-27T10:12:30Z</x:v>
       </x:c>
     </x:row>
     <x:row r="86">
       <x:c r="A86" s="25" t="str">
-        <x:v>conversation_summary</x:v>
+        <x:v>conversation_message</x:v>
       </x:c>
       <x:c r="B86" s="25" t="n">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C86" s="25" t="str">
-        <x:v>source_message_count</x:v>
+        <x:v>created_at</x:v>
       </x:c>
       <x:c r="D86" s="25" t="str">
-        <x:v>원본 메시지 수</x:v>
+        <x:v>행 생성 시각</x:v>
       </x:c>
       <x:c r="E86" s="25" t="str">
-        <x:v>INTEGER</x:v>
+        <x:v>TIMESTAMPTZ</x:v>
       </x:c>
       <x:c r="F86" s="25" t="str">
         <x:v>Y</x:v>
       </x:c>
-      <x:c r="G86" s="25" t="str"/>
-      <x:c r="H86" s="25" t="str"/>
+      <x:c r="G86" s="25"/>
+      <x:c r="H86" s="25"/>
       <x:c r="I86" s="25" t="str">
-        <x:v>conversation_summary.source_message_count에는 요약에 실제 사용한 Raw 발화 수를 기록하는 값을 저장한다.</x:v>
+        <x:v>conversation_message.created_at에는 메시지 행이 DB에 생성된 시각을 기록하는 값을 저장한다.</x:v>
       </x:c>
       <x:c r="J86" s="25" t="str">
-        <x:v>원본 메시지 수은(는) 요약에 실제 사용한 Raw 발화 수를 기록할 때 조회·검증·갱신한다.</x:v>
+        <x:v>행 생성 시각은(는) 메시지 행이 DB에 생성된 시각을 기록할 때 조회·검증·갱신한다.</x:v>
       </x:c>
       <x:c r="K86" s="25" t="str">
-        <x:v>0보다 커야 하며 품질 점검에 사용한다.</x:v>
+        <x:v>발화 시간 정렬에는 occurred_at을 쓴다.</x:v>
       </x:c>
       <x:c r="L86" s="25" t="str">
-        <x:v>18</x:v>
+        <x:v>UTC 2026-07-27T10:12:31Z</x:v>
       </x:c>
     </x:row>
     <x:row r="87">
@@ -3892,33 +3916,35 @@
         <x:v>conversation_summary</x:v>
       </x:c>
       <x:c r="B87" s="26" t="n">
-        <x:v>9</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C87" s="26" t="str">
-        <x:v>generated_at</x:v>
+        <x:v>id</x:v>
       </x:c>
       <x:c r="D87" s="26" t="str">
-        <x:v>요약 생성 시각</x:v>
+        <x:v>요약 ID</x:v>
       </x:c>
       <x:c r="E87" s="26" t="str">
-        <x:v>TIMESTAMPTZ</x:v>
+        <x:v>UUID</x:v>
       </x:c>
       <x:c r="F87" s="26" t="str">
         <x:v>Y</x:v>
       </x:c>
-      <x:c r="G87" s="26" t="str"/>
-      <x:c r="H87" s="26" t="str"/>
+      <x:c r="G87" s="26" t="str">
+        <x:v>PK</x:v>
+      </x:c>
+      <x:c r="H87" s="26"/>
       <x:c r="I87" s="26" t="str">
-        <x:v>conversation_summary.generated_at에는 요약 결과가 생성된 시각을 기록하는 값을 저장한다.</x:v>
+        <x:v>conversation_summary.id에는 요약 버전 한 건을 식별하는 값을 저장한다.</x:v>
       </x:c>
       <x:c r="J87" s="26" t="str">
-        <x:v>요약 생성 시각은(는) 요약 결과가 생성된 시각을 기록할 때 조회·검증·갱신한다.</x:v>
+        <x:v>요약 ID은(는) 요약 버전 한 건을 식별할 때 조회·검증·갱신한다.</x:v>
       </x:c>
       <x:c r="K87" s="26" t="str">
-        <x:v>period_ended_at과 의미가 다르다.</x:v>
+        <x:v>기간 키를 외부 식별자로 노출하지 않는다.</x:v>
       </x:c>
       <x:c r="L87" s="26" t="str">
-        <x:v>UTC 2026-07-27T10:21:00Z</x:v>
+        <x:v>9cd9cbdd-1e7c-4cbb-9014-4ddfb82b73e0</x:v>
       </x:c>
     </x:row>
     <x:row r="88">
@@ -3926,37 +3952,37 @@
         <x:v>conversation_summary</x:v>
       </x:c>
       <x:c r="B88" s="25" t="n">
-        <x:v>10</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C88" s="25" t="str">
-        <x:v>superseded_by_id</x:v>
+        <x:v>senior_id</x:v>
       </x:c>
       <x:c r="D88" s="25" t="str">
-        <x:v>대체 요약 ID</x:v>
+        <x:v>시니어 ID</x:v>
       </x:c>
       <x:c r="E88" s="25" t="str">
         <x:v>UUID</x:v>
       </x:c>
       <x:c r="F88" s="25" t="str">
-        <x:v>N</x:v>
+        <x:v>Y</x:v>
       </x:c>
       <x:c r="G88" s="25" t="str">
-        <x:v>SELF FK</x:v>
+        <x:v>FK</x:v>
       </x:c>
       <x:c r="H88" s="25" t="str">
-        <x:v>conversation_summary.id</x:v>
+        <x:v>app_user.id</x:v>
       </x:c>
       <x:c r="I88" s="25" t="str">
-        <x:v>conversation_summary.superseded_by_id에는 재생성된 새 요약을 연결하는 값을 저장한다.</x:v>
+        <x:v>conversation_summary.senior_id에는 요약 소유자를 연결하는 값을 저장한다.</x:v>
       </x:c>
       <x:c r="J88" s="25" t="str">
-        <x:v>대체 요약 ID은(는) 재생성된 새 요약을 연결할 때 조회·검증·갱신한다.</x:v>
+        <x:v>시니어 ID은(는) 요약 소유자를 연결할 때 조회·검증·갱신한다.</x:v>
       </x:c>
       <x:c r="K88" s="25" t="str">
-        <x:v>요약 자기 참조와 순환을 금지한다.</x:v>
+        <x:v>다른 시니어의 메시지를 섞지 않는다.</x:v>
       </x:c>
       <x:c r="L88" s="25" t="str">
-        <x:v>f3d0dd43-e3dc-4079-9a84-4186c4775327</x:v>
+        <x:v>a2b64af3-5ee5-42ea-98c5-35ac9de10570</x:v>
       </x:c>
     </x:row>
     <x:row r="89">
@@ -3964,306 +3990,296 @@
         <x:v>conversation_summary</x:v>
       </x:c>
       <x:c r="B89" s="26" t="n">
-        <x:v>11</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C89" s="26" t="str">
-        <x:v>embedding</x:v>
+        <x:v>conversation_id</x:v>
       </x:c>
       <x:c r="D89" s="26" t="str">
-        <x:v>요약 임베딩</x:v>
+        <x:v>대화 ID</x:v>
       </x:c>
       <x:c r="E89" s="26" t="str">
-        <x:v>VECTOR</x:v>
+        <x:v>UUID</x:v>
       </x:c>
       <x:c r="F89" s="26" t="str">
         <x:v>N</x:v>
       </x:c>
-      <x:c r="G89" s="26" t="str"/>
-      <x:c r="H89" s="26" t="str"/>
+      <x:c r="G89" s="26" t="str">
+        <x:v>FK</x:v>
+      </x:c>
+      <x:c r="H89" s="26" t="str">
+        <x:v>conversation.id</x:v>
+      </x:c>
       <x:c r="I89" s="26" t="str">
-        <x:v>conversation_summary.embedding에는 관련 요약 의미 검색용 벡터를 저장하는 값을 저장한다.</x:v>
+        <x:v>conversation_summary.conversation_id에는 CONVERSATION 요약의 대상 대화를 연결하는 값을 저장한다.</x:v>
       </x:c>
       <x:c r="J89" s="26" t="str">
-        <x:v>요약 임베딩은(는) 관련 요약 의미 검색용 벡터를 저장할 때 조회·검증·갱신한다.</x:v>
+        <x:v>대화 ID은(는) CONVERSATION 요약의 대상 대화를 연결할 때 조회·검증·갱신한다.</x:v>
       </x:c>
       <x:c r="K89" s="26" t="str">
-        <x:v>모델·차원·인덱스는 아직 TBD다.</x:v>
+        <x:v>DAILY 요약은 null이어야 한다.</x:v>
       </x:c>
       <x:c r="L89" s="26" t="str">
-        <x:v>TBD</x:v>
+        <x:v>1a4fe41a-6464-4e7e-b292-9a507333a3fa</x:v>
       </x:c>
     </x:row>
     <x:row r="90">
       <x:c r="A90" s="25" t="str">
-        <x:v>fact_candidate</x:v>
+        <x:v>conversation_summary</x:v>
       </x:c>
       <x:c r="B90" s="25" t="n">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C90" s="25" t="str">
-        <x:v>id</x:v>
+        <x:v>summary_type</x:v>
       </x:c>
       <x:c r="D90" s="25" t="str">
-        <x:v>후보 ID</x:v>
+        <x:v>요약 유형</x:v>
       </x:c>
       <x:c r="E90" s="25" t="str">
-        <x:v>UUID</x:v>
+        <x:v>VARCHAR(30)</x:v>
       </x:c>
       <x:c r="F90" s="25" t="str">
         <x:v>Y</x:v>
       </x:c>
-      <x:c r="G90" s="25" t="str">
-        <x:v>PK</x:v>
-      </x:c>
-      <x:c r="H90" s="25" t="str"/>
+      <x:c r="G90" s="25"/>
+      <x:c r="H90" s="25"/>
       <x:c r="I90" s="25" t="str">
-        <x:v>fact_candidate.id에는 미확정 사실 후보를 식별하는 값을 저장한다.</x:v>
+        <x:v>conversation_summary.summary_type에는 대화 단위와 일간 요약을 구분하는 값을 저장한다.</x:v>
       </x:c>
       <x:c r="J90" s="25" t="str">
-        <x:v>후보 ID은(는) 미확정 사실 후보를 식별할 때 조회·검증·갱신한다.</x:v>
+        <x:v>요약 유형은(는) 대화 단위와 일간 요약을 구분할 때 조회·검증·갱신한다.</x:v>
       </x:c>
       <x:c r="K90" s="25" t="str">
-        <x:v>최종 업무 ID로 재사용하지 않는다.</x:v>
+        <x:v>TIME_WINDOW는 MVP에 쓰지 않는다.</x:v>
       </x:c>
       <x:c r="L90" s="25" t="str">
-        <x:v>dcd1c7f7-ce8a-405f-a3a5-f2bb25eaac31</x:v>
+        <x:v>CONVERSATION</x:v>
       </x:c>
     </x:row>
     <x:row r="91">
       <x:c r="A91" s="26" t="str">
-        <x:v>fact_candidate</x:v>
+        <x:v>conversation_summary</x:v>
       </x:c>
       <x:c r="B91" s="26" t="n">
-        <x:v>2</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C91" s="26" t="str">
-        <x:v>senior_id</x:v>
+        <x:v>period_started_at</x:v>
       </x:c>
       <x:c r="D91" s="26" t="str">
-        <x:v>시니어 ID</x:v>
+        <x:v>요약 구간 시작</x:v>
       </x:c>
       <x:c r="E91" s="26" t="str">
-        <x:v>UUID</x:v>
+        <x:v>TIMESTAMPTZ</x:v>
       </x:c>
       <x:c r="F91" s="26" t="str">
         <x:v>Y</x:v>
       </x:c>
-      <x:c r="G91" s="26" t="str">
-        <x:v>FK</x:v>
-      </x:c>
-      <x:c r="H91" s="26" t="str">
-        <x:v>app_user.id</x:v>
-      </x:c>
+      <x:c r="G91" s="26"/>
+      <x:c r="H91" s="26"/>
       <x:c r="I91" s="26" t="str">
-        <x:v>fact_candidate.senior_id에는 후보의 최종 데이터 소유자를 연결하는 값을 저장한다.</x:v>
+        <x:v>conversation_summary.period_started_at에는 요약에 포함된 첫 시간 경계를 기록하는 값을 저장한다.</x:v>
       </x:c>
       <x:c r="J91" s="26" t="str">
-        <x:v>시니어 ID은(는) 후보의 최종 데이터 소유자를 연결할 때 조회·검증·갱신한다.</x:v>
+        <x:v>요약 구간 시작은(는) 요약에 포함된 첫 시간 경계를 기록할 때 조회·검증·갱신한다.</x:v>
       </x:c>
       <x:c r="K91" s="26" t="str">
-        <x:v>소스 대화·답변의 시니어와 일치시킨다.</x:v>
+        <x:v>사용자 현지 구간을 UTC로 변환해 저장한다.</x:v>
       </x:c>
       <x:c r="L91" s="26" t="str">
-        <x:v>a2b64af3-5ee5-42ea-98c5-35ac9de10570</x:v>
+        <x:v>UTC 2026-07-27T00:00:00Z</x:v>
       </x:c>
     </x:row>
     <x:row r="92">
       <x:c r="A92" s="25" t="str">
-        <x:v>fact_candidate</x:v>
+        <x:v>conversation_summary</x:v>
       </x:c>
       <x:c r="B92" s="25" t="n">
-        <x:v>3</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C92" s="25" t="str">
-        <x:v>source_type</x:v>
+        <x:v>period_ended_at</x:v>
       </x:c>
       <x:c r="D92" s="25" t="str">
-        <x:v>출처 유형</x:v>
+        <x:v>요약 구간 종료</x:v>
       </x:c>
       <x:c r="E92" s="25" t="str">
-        <x:v>VARCHAR(40)</x:v>
+        <x:v>TIMESTAMPTZ</x:v>
       </x:c>
       <x:c r="F92" s="25" t="str">
         <x:v>Y</x:v>
       </x:c>
-      <x:c r="G92" s="25" t="str"/>
-      <x:c r="H92" s="25" t="str"/>
+      <x:c r="G92" s="25"/>
+      <x:c r="H92" s="25"/>
       <x:c r="I92" s="25" t="str">
-        <x:v>fact_candidate.source_type에는 온보딩 답변과 대화 메시지 출처를 구분하는 값을 저장한다.</x:v>
+        <x:v>conversation_summary.period_ended_at에는 요약에 포함된 끝 시간 경계를 기록하는 값을 저장한다.</x:v>
       </x:c>
       <x:c r="J92" s="25" t="str">
-        <x:v>출처 유형은(는) 온보딩 답변과 대화 메시지 출처를 구분할 때 조회·검증·갱신한다.</x:v>
+        <x:v>요약 구간 종료은(는) 요약에 포함된 끝 시간 경계를 기록할 때 조회·검증·갱신한다.</x:v>
       </x:c>
       <x:c r="K92" s="25" t="str">
-        <x:v>필수 출처 FK와 CHECK로 묶는다.</x:v>
+        <x:v>시작보다 늦어야 하고 경계 규칙을 일관되게 쓴다.</x:v>
       </x:c>
       <x:c r="L92" s="25" t="str">
-        <x:v>CONVERSATION_MESSAGE</x:v>
+        <x:v>UTC 2026-07-27T10:20:00Z</x:v>
       </x:c>
     </x:row>
     <x:row r="93">
       <x:c r="A93" s="26" t="str">
-        <x:v>fact_candidate</x:v>
+        <x:v>conversation_summary</x:v>
       </x:c>
       <x:c r="B93" s="26" t="n">
-        <x:v>4</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C93" s="26" t="str">
-        <x:v>onboarding_answer_id</x:v>
+        <x:v>content</x:v>
       </x:c>
       <x:c r="D93" s="26" t="str">
-        <x:v>출처 답변 ID</x:v>
+        <x:v>요약 내용</x:v>
       </x:c>
       <x:c r="E93" s="26" t="str">
-        <x:v>UUID</x:v>
+        <x:v>TEXT</x:v>
       </x:c>
       <x:c r="F93" s="26" t="str">
-        <x:v>N</x:v>
-      </x:c>
-      <x:c r="G93" s="26" t="str">
-        <x:v>FK</x:v>
-      </x:c>
-      <x:c r="H93" s="26" t="str">
-        <x:v>onboarding_answer.id</x:v>
-      </x:c>
+        <x:v>Y</x:v>
+      </x:c>
+      <x:c r="G93" s="26"/>
+      <x:c r="H93" s="26"/>
       <x:c r="I93" s="26" t="str">
-        <x:v>fact_candidate.onboarding_answer_id에는 온보딩에서 나온 후보의 답변을 연결하는 값을 저장한다.</x:v>
+        <x:v>conversation_summary.content에는 대화 문맥을 압축한 텍스트를 저장하는 값을 저장한다.</x:v>
       </x:c>
       <x:c r="J93" s="26" t="str">
-        <x:v>출처 답변 ID은(는) 온보딩에서 나온 후보의 답변을 연결할 때 조회·검증·갱신한다.</x:v>
+        <x:v>요약 내용은(는) 대화 문맥을 압축한 텍스트를 저장할 때 조회·검증·갱신한다.</x:v>
       </x:c>
       <x:c r="K93" s="26" t="str">
-        <x:v>source_type이 ONBOARDING_ANSWER일 때 필수다.</x:v>
+        <x:v>장기 사실 전문이나 근거 발화를 복제하지 않는다.</x:v>
       </x:c>
       <x:c r="L93" s="26" t="str">
-        <x:v>066d8e53-5968-4ff7-8450-36fa672f653e</x:v>
+        <x:v>병원 일정과 저녁 복약 시간을 확인했다.</x:v>
       </x:c>
     </x:row>
     <x:row r="94">
       <x:c r="A94" s="25" t="str">
-        <x:v>fact_candidate</x:v>
+        <x:v>conversation_summary</x:v>
       </x:c>
       <x:c r="B94" s="25" t="n">
-        <x:v>5</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C94" s="25" t="str">
-        <x:v>conversation_id</x:v>
+        <x:v>source_message_count</x:v>
       </x:c>
       <x:c r="D94" s="25" t="str">
-        <x:v>출처 대화 ID</x:v>
+        <x:v>원본 메시지 수</x:v>
       </x:c>
       <x:c r="E94" s="25" t="str">
-        <x:v>UUID</x:v>
+        <x:v>INTEGER</x:v>
       </x:c>
       <x:c r="F94" s="25" t="str">
-        <x:v>N</x:v>
-      </x:c>
-      <x:c r="G94" s="25" t="str">
-        <x:v>FK</x:v>
-      </x:c>
-      <x:c r="H94" s="25" t="str">
-        <x:v>conversation.id</x:v>
-      </x:c>
+        <x:v>Y</x:v>
+      </x:c>
+      <x:c r="G94" s="25"/>
+      <x:c r="H94" s="25"/>
       <x:c r="I94" s="25" t="str">
-        <x:v>fact_candidate.conversation_id에는 대화에서 나온 후보의 대화를 연결하는 값을 저장한다.</x:v>
+        <x:v>conversation_summary.source_message_count에는 요약에 실제 사용한 Raw 발화 수를 기록하는 값을 저장한다.</x:v>
       </x:c>
       <x:c r="J94" s="25" t="str">
-        <x:v>출처 대화 ID은(는) 대화에서 나온 후보의 대화를 연결할 때 조회·검증·갱신한다.</x:v>
+        <x:v>원본 메시지 수은(는) 요약에 실제 사용한 Raw 발화 수를 기록할 때 조회·검증·갱신한다.</x:v>
       </x:c>
       <x:c r="K94" s="25" t="str">
-        <x:v>메시지의 conversation과 일치해야 한다.</x:v>
+        <x:v>0보다 커야 하며 품질 점검에 사용한다.</x:v>
       </x:c>
       <x:c r="L94" s="25" t="str">
-        <x:v>1a4fe41a-6464-4e7e-b292-9a507333a3fa</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="95">
       <x:c r="A95" s="26" t="str">
-        <x:v>fact_candidate</x:v>
+        <x:v>conversation_summary</x:v>
       </x:c>
       <x:c r="B95" s="26" t="n">
-        <x:v>6</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C95" s="26" t="str">
-        <x:v>source_message_id</x:v>
+        <x:v>generated_at</x:v>
       </x:c>
       <x:c r="D95" s="26" t="str">
-        <x:v>출처 메시지 ID</x:v>
+        <x:v>요약 생성 시각</x:v>
       </x:c>
       <x:c r="E95" s="26" t="str">
-        <x:v>UUID</x:v>
+        <x:v>TIMESTAMPTZ</x:v>
       </x:c>
       <x:c r="F95" s="26" t="str">
-        <x:v>N</x:v>
-      </x:c>
-      <x:c r="G95" s="26" t="str">
-        <x:v>FK</x:v>
-      </x:c>
-      <x:c r="H95" s="26" t="str">
-        <x:v>conversation_message.id</x:v>
-      </x:c>
+        <x:v>Y</x:v>
+      </x:c>
+      <x:c r="G95" s="26"/>
+      <x:c r="H95" s="26"/>
       <x:c r="I95" s="26" t="str">
-        <x:v>fact_candidate.source_message_id에는 후보를 만든 정확한 발화를 연결하는 값을 저장한다.</x:v>
+        <x:v>conversation_summary.generated_at에는 요약 결과가 생성된 시각을 기록하는 값을 저장한다.</x:v>
       </x:c>
       <x:c r="J95" s="26" t="str">
-        <x:v>출처 메시지 ID은(는) 후보를 만든 정확한 발화를 연결할 때 조회·검증·갱신한다.</x:v>
+        <x:v>요약 생성 시각은(는) 요약 결과가 생성된 시각을 기록할 때 조회·검증·갱신한다.</x:v>
       </x:c>
       <x:c r="K95" s="26" t="str">
-        <x:v>fact_candidate 근거는 Raw 삭제 시 ON DELETE SET NULL로 비운다.</x:v>
+        <x:v>period_ended_at과 의미가 다르다.</x:v>
       </x:c>
       <x:c r="L95" s="26" t="str">
-        <x:v>a6f8cb84-c91c-4a38-a7b6-386ce6aa027f</x:v>
+        <x:v>UTC 2026-07-27T10:21:00Z</x:v>
       </x:c>
     </x:row>
     <x:row r="96">
       <x:c r="A96" s="25" t="str">
-        <x:v>fact_candidate</x:v>
+        <x:v>conversation_summary</x:v>
       </x:c>
       <x:c r="B96" s="25" t="n">
-        <x:v>7</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C96" s="25" t="str">
-        <x:v>target_domain</x:v>
+        <x:v>superseded_by_id</x:v>
       </x:c>
       <x:c r="D96" s="25" t="str">
-        <x:v>대상 도메인</x:v>
+        <x:v>대체 요약 ID</x:v>
       </x:c>
       <x:c r="E96" s="25" t="str">
-        <x:v>VARCHAR(40)</x:v>
+        <x:v>UUID</x:v>
       </x:c>
       <x:c r="F96" s="25" t="str">
-        <x:v>Y</x:v>
-      </x:c>
-      <x:c r="G96" s="25" t="str"/>
-      <x:c r="H96" s="25" t="str"/>
+        <x:v>N</x:v>
+      </x:c>
+      <x:c r="G96" s="25" t="str">
+        <x:v>SELF FK</x:v>
+      </x:c>
+      <x:c r="H96" s="25" t="str">
+        <x:v>conversation_summary.id</x:v>
+      </x:c>
       <x:c r="I96" s="25" t="str">
-        <x:v>fact_candidate.target_domain에는 PROFILE·관계·기억·돌봄 대상을 구분하는 값을 저장한다.</x:v>
+        <x:v>conversation_summary.superseded_by_id에는 재생성된 새 요약을 연결하는 값을 저장한다.</x:v>
       </x:c>
       <x:c r="J96" s="25" t="str">
-        <x:v>대상 도메인은(는) PROFILE·관계·기억·돌봄 대상을 구분할 때 조회·검증·갱신한다.</x:v>
+        <x:v>대체 요약 ID은(는) 재생성된 새 요약을 연결할 때 조회·검증·갱신한다.</x:v>
       </x:c>
       <x:c r="K96" s="25" t="str">
-        <x:v>다형성 ID 검증의 기준이다.</x:v>
+        <x:v>요약 자기 참조와 순환을 금지한다.</x:v>
       </x:c>
       <x:c r="L96" s="25" t="str">
-        <x:v>CARE_RECORD</x:v>
+        <x:v>f3d0dd43-e3dc-4079-9a84-4186c4775327</x:v>
       </x:c>
     </x:row>
     <x:row r="97">
       <x:c r="A97" s="26" t="str">
-        <x:v>fact_candidate</x:v>
+        <x:v>conversation_summary</x:v>
       </x:c>
       <x:c r="B97" s="26" t="n">
-        <x:v>8</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C97" s="26" t="str">
-        <x:v>fact_type</x:v>
+        <x:v>embedding_status</x:v>
       </x:c>
       <x:c r="D97" s="26" t="str">
-        <x:v>사실 유형</x:v>
+        <x:v>벡터 동기화 상태</x:v>
       </x:c>
       <x:c r="E97" s="26" t="str">
-        <x:v>VARCHAR(80)</x:v>
+        <x:v>VARCHAR(20)</x:v>
       </x:c>
       <x:c r="F97" s="26" t="str">
         <x:v>Y</x:v>
@@ -4271,86 +4287,84 @@
       <x:c r="G97" s="26" t="str"/>
       <x:c r="H97" s="26" t="str"/>
       <x:c r="I97" s="26" t="str">
-        <x:v>fact_candidate.fact_type에는 질문 계약과 JSON Schema를 선택하는 값을 저장한다.</x:v>
+        <x:v>외부 Qdrant 벡터가 본문과 동기화됐는지 나타내는 상태를 저장한다.</x:v>
       </x:c>
       <x:c r="J97" s="26" t="str">
-        <x:v>사실 유형은(는) 질문 계약과 JSON Schema를 선택할 때 조회·검증·갱신한다.</x:v>
+        <x:v>PENDING·SYNCED·STALE·FAILED 상태로 재색인 대상을 고른다.</x:v>
       </x:c>
       <x:c r="K97" s="26" t="str">
-        <x:v>자유 문장 대신 안정적 코드를 쓴다.</x:v>
+        <x:v>벡터 자체는 PostgreSQL에 저장하지 않는다.</x:v>
       </x:c>
       <x:c r="L97" s="26" t="str">
-        <x:v>MEDICATION_SCHEDULE</x:v>
+        <x:v>PENDING</x:v>
       </x:c>
     </x:row>
     <x:row r="98">
       <x:c r="A98" s="25" t="str">
-        <x:v>fact_candidate</x:v>
+        <x:v>conversation_summary</x:v>
       </x:c>
       <x:c r="B98" s="25" t="n">
-        <x:v>9</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C98" s="25" t="str">
-        <x:v>operation</x:v>
+        <x:v>embedding_synced_at</x:v>
       </x:c>
       <x:c r="D98" s="25" t="str">
-        <x:v>요청 연산</x:v>
+        <x:v>벡터 동기화 시각</x:v>
       </x:c>
       <x:c r="E98" s="25" t="str">
-        <x:v>VARCHAR(20)</x:v>
+        <x:v>TIMESTAMPTZ</x:v>
       </x:c>
       <x:c r="F98" s="25" t="str">
-        <x:v>Y</x:v>
+        <x:v>N</x:v>
       </x:c>
       <x:c r="G98" s="25" t="str"/>
       <x:c r="H98" s="25" t="str"/>
       <x:c r="I98" s="25" t="str">
-        <x:v>fact_candidate.operation에는 생성·변경·취소 요청을 구분하는 값을 저장한다.</x:v>
+        <x:v>현재 embedding_model로 Qdrant 반영을 완료한 마지막 시각을 저장한다.</x:v>
       </x:c>
       <x:c r="J98" s="25" t="str">
-        <x:v>요청 연산은(는) 생성·변경·취소 요청을 구분할 때 조회·검증·갱신한다.</x:v>
+        <x:v>동기화 성공 뒤 상태와 같은 처리 단위로 갱신한다.</x:v>
       </x:c>
       <x:c r="K98" s="25" t="str">
-        <x:v>UPDATE/CANCEL은 대상 엔터티가 필요하다.</x:v>
+        <x:v>생성 시각이나 마지막 시도 시각으로 해석하지 않는다.</x:v>
       </x:c>
       <x:c r="L98" s="25" t="str">
-        <x:v>UPDATE</x:v>
+        <x:v>UTC 2026-08-05T05:10:00Z</x:v>
       </x:c>
     </x:row>
     <x:row r="99">
       <x:c r="A99" s="26" t="str">
-        <x:v>fact_candidate</x:v>
+        <x:v>conversation_summary</x:v>
       </x:c>
       <x:c r="B99" s="26" t="n">
-        <x:v>10</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C99" s="26" t="str">
-        <x:v>target_entity_id</x:v>
+        <x:v>embedding_model</x:v>
       </x:c>
       <x:c r="D99" s="26" t="str">
-        <x:v>변경 대상 ID</x:v>
+        <x:v>벡터 모델 식별자</x:v>
       </x:c>
       <x:c r="E99" s="26" t="str">
-        <x:v>UUID</x:v>
+        <x:v>VARCHAR(100)</x:v>
       </x:c>
       <x:c r="F99" s="26" t="str">
         <x:v>N</x:v>
       </x:c>
-      <x:c r="G99" s="26" t="str">
-        <x:v>논리 참조</x:v>
-      </x:c>
+      <x:c r="G99" s="26" t="str"/>
       <x:c r="H99" s="26" t="str"/>
       <x:c r="I99" s="26" t="str">
-        <x:v>fact_candidate.target_entity_id에는 갱신·취소할 최종 행을 논리적으로 가리킴하는 값을 저장한다.</x:v>
+        <x:v>Qdrant에 저장된 벡터를 생성한 모델 식별자를 저장한다.</x:v>
       </x:c>
       <x:c r="J99" s="26" t="str">
-        <x:v>변경 대상 ID은(는) 갱신·취소할 최종 행을 논리적으로 가리킴할 때 조회·검증·갱신한다.</x:v>
+        <x:v>현재 모델과 다르면 STALE로 전환해 재색인한다.</x:v>
       </x:c>
       <x:c r="K99" s="26" t="str">
-        <x:v>여러 테이블 대상이므로 물리 FK라고 주장하지 않는다.</x:v>
+        <x:v>서로 다른 모델의 벡터 유사도를 비교하지 않는다.</x:v>
       </x:c>
       <x:c r="L99" s="26" t="str">
-        <x:v>8f3de8c7-7a04-4c74-977b-223a096dc589</x:v>
+        <x:v>embedding-passage</x:v>
       </x:c>
     </x:row>
     <x:row r="100">
@@ -4358,33 +4372,35 @@
         <x:v>fact_candidate</x:v>
       </x:c>
       <x:c r="B100" s="25" t="n">
-        <x:v>11</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C100" s="25" t="str">
-        <x:v>proposed_value</x:v>
+        <x:v>id</x:v>
       </x:c>
       <x:c r="D100" s="25" t="str">
-        <x:v>제안 값</x:v>
+        <x:v>후보 ID</x:v>
       </x:c>
       <x:c r="E100" s="25" t="str">
-        <x:v>JSONB</x:v>
+        <x:v>UUID</x:v>
       </x:c>
       <x:c r="F100" s="25" t="str">
         <x:v>Y</x:v>
       </x:c>
-      <x:c r="G100" s="25" t="str"/>
-      <x:c r="H100" s="25" t="str"/>
+      <x:c r="G100" s="25" t="str">
+        <x:v>PK</x:v>
+      </x:c>
+      <x:c r="H100" s="25"/>
       <x:c r="I100" s="25" t="str">
-        <x:v>fact_candidate.proposed_value에는 추출·입력한 아직 미확정 구조화 값을 저장하는 값을 저장한다.</x:v>
+        <x:v>fact_candidate.id에는 미확정 사실 후보를 식별하는 값을 저장한다.</x:v>
       </x:c>
       <x:c r="J100" s="25" t="str">
-        <x:v>제안 값은(는) 추출·입력한 아직 미확정 구조화 값을 저장할 때 조회·검증·갱신한다.</x:v>
+        <x:v>후보 ID은(는) 미확정 사실 후보를 식별할 때 조회·검증·갱신한다.</x:v>
       </x:c>
       <x:c r="K100" s="25" t="str">
-        <x:v>민감 중간 값은 반영 후 무기한 보존하지 않는다.</x:v>
+        <x:v>최종 업무 ID로 재사용하지 않는다.</x:v>
       </x:c>
       <x:c r="L100" s="25" t="str">
-        <x:v>{"localTime":"15:00","timeZone":"Asia/Seoul"}</x:v>
+        <x:v>dcd1c7f7-ce8a-405f-a3a5-f2bb25eaac31</x:v>
       </x:c>
     </x:row>
     <x:row r="101">
@@ -4392,33 +4408,37 @@
         <x:v>fact_candidate</x:v>
       </x:c>
       <x:c r="B101" s="26" t="n">
-        <x:v>12</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C101" s="26" t="str">
-        <x:v>confirmed_value</x:v>
+        <x:v>senior_id</x:v>
       </x:c>
       <x:c r="D101" s="26" t="str">
-        <x:v>확정 값</x:v>
+        <x:v>시니어 ID</x:v>
       </x:c>
       <x:c r="E101" s="26" t="str">
-        <x:v>JSONB</x:v>
+        <x:v>UUID</x:v>
       </x:c>
       <x:c r="F101" s="26" t="str">
-        <x:v>N</x:v>
-      </x:c>
-      <x:c r="G101" s="26" t="str"/>
-      <x:c r="H101" s="26" t="str"/>
+        <x:v>Y</x:v>
+      </x:c>
+      <x:c r="G101" s="26" t="str">
+        <x:v>FK</x:v>
+      </x:c>
+      <x:c r="H101" s="26" t="str">
+        <x:v>app_user.id</x:v>
+      </x:c>
       <x:c r="I101" s="26" t="str">
-        <x:v>fact_candidate.confirmed_value에는 사용자가 최종 확인한 정규화 값을 저장하는 값을 저장한다.</x:v>
+        <x:v>fact_candidate.senior_id에는 후보의 최종 데이터 소유자를 연결하는 값을 저장한다.</x:v>
       </x:c>
       <x:c r="J101" s="26" t="str">
-        <x:v>확정 값은(는) 사용자가 최종 확인한 정규화 값을 저장할 때 조회·검증·갱신한다.</x:v>
+        <x:v>시니어 ID은(는) 후보의 최종 데이터 소유자를 연결할 때 조회·검증·갱신한다.</x:v>
       </x:c>
       <x:c r="K101" s="26" t="str">
-        <x:v>이 값만 최종 원본에 반영한다.</x:v>
+        <x:v>소스 대화·답변의 시니어와 일치시킨다.</x:v>
       </x:c>
       <x:c r="L101" s="26" t="str">
-        <x:v>{"localTime":"15:00","timeZone":"Asia/Seoul"}</x:v>
+        <x:v>a2b64af3-5ee5-42ea-98c5-35ac9de10570</x:v>
       </x:c>
     </x:row>
     <x:row r="102">
@@ -4426,33 +4446,33 @@
         <x:v>fact_candidate</x:v>
       </x:c>
       <x:c r="B102" s="25" t="n">
-        <x:v>13</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C102" s="25" t="str">
-        <x:v>missing_fields</x:v>
+        <x:v>source_type</x:v>
       </x:c>
       <x:c r="D102" s="25" t="str">
-        <x:v>누락 필드 목록</x:v>
+        <x:v>출처 유형</x:v>
       </x:c>
       <x:c r="E102" s="25" t="str">
-        <x:v>TEXT[]</x:v>
+        <x:v>VARCHAR(40)</x:v>
       </x:c>
       <x:c r="F102" s="25" t="str">
         <x:v>Y</x:v>
       </x:c>
-      <x:c r="G102" s="25" t="str"/>
-      <x:c r="H102" s="25" t="str"/>
+      <x:c r="G102" s="25"/>
+      <x:c r="H102" s="25"/>
       <x:c r="I102" s="25" t="str">
-        <x:v>fact_candidate.missing_fields에는 재질의가 필요한 JSON 필드명을 저장하는 값을 저장한다.</x:v>
+        <x:v>fact_candidate.source_type에는 온보딩 답변과 대화 메시지 출처를 구분하는 값을 저장한다.</x:v>
       </x:c>
       <x:c r="J102" s="25" t="str">
-        <x:v>누락 필드 목록은(는) 재질의가 필요한 JSON 필드명을 저장할 때 조회·검증·갱신한다.</x:v>
+        <x:v>출처 유형은(는) 온보딩 답변과 대화 메시지 출처를 구분할 때 조회·검증·갱신한다.</x:v>
       </x:c>
       <x:c r="K102" s="25" t="str">
-        <x:v>질문 문장이나 사람이 읽는 설명을 넣지 않는다.</x:v>
+        <x:v>필수 출처 FK와 CHECK로 묶는다.</x:v>
       </x:c>
       <x:c r="L102" s="25" t="str">
-        <x:v>["doseUnit"]</x:v>
+        <x:v>CONVERSATION_MESSAGE</x:v>
       </x:c>
     </x:row>
     <x:row r="103">
@@ -4460,33 +4480,37 @@
         <x:v>fact_candidate</x:v>
       </x:c>
       <x:c r="B103" s="26" t="n">
-        <x:v>14</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C103" s="26" t="str">
-        <x:v>risk_level</x:v>
+        <x:v>onboarding_answer_id</x:v>
       </x:c>
       <x:c r="D103" s="26" t="str">
-        <x:v>위험 수준</x:v>
+        <x:v>출처 답변 ID</x:v>
       </x:c>
       <x:c r="E103" s="26" t="str">
-        <x:v>VARCHAR(20)</x:v>
+        <x:v>UUID</x:v>
       </x:c>
       <x:c r="F103" s="26" t="str">
-        <x:v>Y</x:v>
-      </x:c>
-      <x:c r="G103" s="26" t="str"/>
-      <x:c r="H103" s="26" t="str"/>
+        <x:v>N</x:v>
+      </x:c>
+      <x:c r="G103" s="26" t="str">
+        <x:v>FK</x:v>
+      </x:c>
+      <x:c r="H103" s="26" t="str">
+        <x:v>onboarding_answer.id</x:v>
+      </x:c>
       <x:c r="I103" s="26" t="str">
-        <x:v>fact_candidate.risk_level에는 일반·민감·고위험 처리 강도를 구분하는 값을 저장한다.</x:v>
+        <x:v>fact_candidate.onboarding_answer_id에는 온보딩에서 나온 후보의 답변을 연결하는 값을 저장한다.</x:v>
       </x:c>
       <x:c r="J103" s="26" t="str">
-        <x:v>위험 수준은(는) 일반·민감·고위험 처리 강도를 구분할 때 조회·검증·갱신한다.</x:v>
+        <x:v>출처 답변 ID은(는) 온보딩에서 나온 후보의 답변을 연결할 때 조회·검증·갱신한다.</x:v>
       </x:c>
       <x:c r="K103" s="26" t="str">
-        <x:v>민감 이상은 명확해도 최종 확인한다.</x:v>
+        <x:v>source_type이 ONBOARDING_ANSWER일 때 필수다.</x:v>
       </x:c>
       <x:c r="L103" s="26" t="str">
-        <x:v>SENSITIVE</x:v>
+        <x:v>066d8e53-5968-4ff7-8450-36fa672f653e</x:v>
       </x:c>
     </x:row>
     <x:row r="104">
@@ -4494,33 +4518,37 @@
         <x:v>fact_candidate</x:v>
       </x:c>
       <x:c r="B104" s="25" t="n">
-        <x:v>15</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C104" s="25" t="str">
-        <x:v>status</x:v>
+        <x:v>conversation_id</x:v>
       </x:c>
       <x:c r="D104" s="25" t="str">
-        <x:v>후보 처리 상태</x:v>
+        <x:v>출처 대화 ID</x:v>
       </x:c>
       <x:c r="E104" s="25" t="str">
-        <x:v>VARCHAR(40)</x:v>
+        <x:v>UUID</x:v>
       </x:c>
       <x:c r="F104" s="25" t="str">
-        <x:v>Y</x:v>
-      </x:c>
-      <x:c r="G104" s="25" t="str"/>
-      <x:c r="H104" s="25" t="str"/>
+        <x:v>N</x:v>
+      </x:c>
+      <x:c r="G104" s="25" t="str">
+        <x:v>FK</x:v>
+      </x:c>
+      <x:c r="H104" s="25" t="str">
+        <x:v>conversation.id</x:v>
+      </x:c>
       <x:c r="I104" s="25" t="str">
-        <x:v>fact_candidate.status에는 캡처부터 물리 반영까지 처리 단계를 표시하는 값을 저장한다.</x:v>
+        <x:v>fact_candidate.conversation_id에는 대화에서 나온 후보의 대화를 연결하는 값을 저장한다.</x:v>
       </x:c>
       <x:c r="J104" s="25" t="str">
-        <x:v>후보 처리 상태은(는) 캡처부터 물리 반영까지 처리 단계를 표시할 때 조회·검증·갱신한다.</x:v>
+        <x:v>출처 대화 ID은(는) 대화에서 나온 후보의 대화를 연결할 때 조회·검증·갱신한다.</x:v>
       </x:c>
       <x:c r="K104" s="25" t="str">
-        <x:v>협의 결과 상태를 대신하지 않는다.</x:v>
+        <x:v>메시지의 conversation과 일치해야 한다.</x:v>
       </x:c>
       <x:c r="L104" s="25" t="str">
-        <x:v>NEEDS_CONFIRMATION</x:v>
+        <x:v>1a4fe41a-6464-4e7e-b292-9a507333a3fa</x:v>
       </x:c>
     </x:row>
     <x:row r="105">
@@ -4528,33 +4556,37 @@
         <x:v>fact_candidate</x:v>
       </x:c>
       <x:c r="B105" s="26" t="n">
-        <x:v>16</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C105" s="26" t="str">
-        <x:v>clarification_reason</x:v>
+        <x:v>source_message_id</x:v>
       </x:c>
       <x:c r="D105" s="26" t="str">
-        <x:v>재질의 사유</x:v>
+        <x:v>출처 메시지 ID</x:v>
       </x:c>
       <x:c r="E105" s="26" t="str">
-        <x:v>VARCHAR(60)</x:v>
+        <x:v>UUID</x:v>
       </x:c>
       <x:c r="F105" s="26" t="str">
         <x:v>N</x:v>
       </x:c>
-      <x:c r="G105" s="26" t="str"/>
-      <x:c r="H105" s="26" t="str"/>
+      <x:c r="G105" s="26" t="str">
+        <x:v>FK</x:v>
+      </x:c>
+      <x:c r="H105" s="26" t="str">
+        <x:v>conversation_message.id</x:v>
+      </x:c>
       <x:c r="I105" s="26" t="str">
-        <x:v>fact_candidate.clarification_reason에는 누락·모호·낮은 신뢰·충돌·민감 확인을 구분하는 값을 저장한다.</x:v>
+        <x:v>fact_candidate.source_message_id에는 후보를 만든 정확한 발화를 연결하는 값을 저장한다.</x:v>
       </x:c>
       <x:c r="J105" s="26" t="str">
-        <x:v>재질의 사유은(는) 누락·모호·낮은 신뢰·충돌·민감 확인을 구분할 때 조회·검증·갱신한다.</x:v>
+        <x:v>출처 메시지 ID은(는) 후보를 만든 정확한 발화를 연결할 때 조회·검증·갱신한다.</x:v>
       </x:c>
       <x:c r="K105" s="26" t="str">
-        <x:v>복수 원인 중 현재 질문의 직접 원인을 둔다.</x:v>
+        <x:v>fact_candidate 근거는 Raw 삭제 시 ON DELETE SET NULL로 비운다.</x:v>
       </x:c>
       <x:c r="L105" s="26" t="str">
-        <x:v>MISSING_REQUIRED_FIELD</x:v>
+        <x:v>a6f8cb84-c91c-4a38-a7b6-386ce6aa027f</x:v>
       </x:c>
     </x:row>
     <x:row r="106">
@@ -4562,33 +4594,33 @@
         <x:v>fact_candidate</x:v>
       </x:c>
       <x:c r="B106" s="25" t="n">
-        <x:v>17</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C106" s="25" t="str">
-        <x:v>clarification_count</x:v>
+        <x:v>target_domain</x:v>
       </x:c>
       <x:c r="D106" s="25" t="str">
-        <x:v>재질의 횟수</x:v>
+        <x:v>대상 도메인</x:v>
       </x:c>
       <x:c r="E106" s="25" t="str">
-        <x:v>INTEGER</x:v>
+        <x:v>VARCHAR(40)</x:v>
       </x:c>
       <x:c r="F106" s="25" t="str">
         <x:v>Y</x:v>
       </x:c>
-      <x:c r="G106" s="25" t="str"/>
-      <x:c r="H106" s="25" t="str"/>
+      <x:c r="G106" s="25"/>
+      <x:c r="H106" s="25"/>
       <x:c r="I106" s="25" t="str">
-        <x:v>fact_candidate.clarification_count에는 같은 후보에 수행한 재질의 횟수를 기록하는 값을 저장한다.</x:v>
+        <x:v>fact_candidate.target_domain에는 PROFILE·관계·기억·돌봄 대상을 구분하는 값을 저장한다.</x:v>
       </x:c>
       <x:c r="J106" s="25" t="str">
-        <x:v>재질의 횟수은(는) 같은 후보에 수행한 재질의 횟수를 기록할 때 조회·검증·갱신한다.</x:v>
+        <x:v>대상 도메인은(는) PROFILE·관계·기억·돌봄 대상을 구분할 때 조회·검증·갱신한다.</x:v>
       </x:c>
       <x:c r="K106" s="25" t="str">
-        <x:v>음수가 될 수 없고 무한 반복을 막는다.</x:v>
+        <x:v>다형성 ID 검증의 기준이다.</x:v>
       </x:c>
       <x:c r="L106" s="25" t="str">
-        <x:v>1</x:v>
+        <x:v>CARE_RECORD</x:v>
       </x:c>
     </x:row>
     <x:row r="107">
@@ -4596,37 +4628,33 @@
         <x:v>fact_candidate</x:v>
       </x:c>
       <x:c r="B107" s="26" t="n">
-        <x:v>18</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C107" s="26" t="str">
-        <x:v>initiated_by_user_id</x:v>
+        <x:v>fact_type</x:v>
       </x:c>
       <x:c r="D107" s="26" t="str">
-        <x:v>요청 시작 사용자</x:v>
+        <x:v>사실 유형</x:v>
       </x:c>
       <x:c r="E107" s="26" t="str">
-        <x:v>UUID</x:v>
+        <x:v>VARCHAR(80)</x:v>
       </x:c>
       <x:c r="F107" s="26" t="str">
-        <x:v>N</x:v>
-      </x:c>
-      <x:c r="G107" s="26" t="str">
-        <x:v>FK</x:v>
-      </x:c>
-      <x:c r="H107" s="26" t="str">
-        <x:v>app_user.id</x:v>
-      </x:c>
+        <x:v>Y</x:v>
+      </x:c>
+      <x:c r="G107" s="26"/>
+      <x:c r="H107" s="26"/>
       <x:c r="I107" s="26" t="str">
-        <x:v>fact_candidate.initiated_by_user_id에는 등록·변경을 시작한 사람을 연결하는 값을 저장한다.</x:v>
+        <x:v>fact_candidate.fact_type에는 질문 계약과 JSON Schema를 선택하는 값을 저장한다.</x:v>
       </x:c>
       <x:c r="J107" s="26" t="str">
-        <x:v>요청 시작 사용자은(는) 등록·변경을 시작한 사람을 연결할 때 조회·검증·갱신한다.</x:v>
+        <x:v>사실 유형은(는) 질문 계약과 JSON Schema를 선택할 때 조회·검증·갱신한다.</x:v>
       </x:c>
       <x:c r="K107" s="26" t="str">
-        <x:v>AI·시스템 추출이면 null일 수 있다.</x:v>
+        <x:v>자유 문장 대신 안정적 코드를 쓴다.</x:v>
       </x:c>
       <x:c r="L107" s="26" t="str">
-        <x:v>a2b64af3-5ee5-42ea-98c5-35ac9de10570</x:v>
+        <x:v>MEDICATION_SCHEDULE</x:v>
       </x:c>
     </x:row>
     <x:row r="108">
@@ -4634,37 +4662,33 @@
         <x:v>fact_candidate</x:v>
       </x:c>
       <x:c r="B108" s="25" t="n">
-        <x:v>19</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C108" s="25" t="str">
-        <x:v>confirmed_by_user_id</x:v>
+        <x:v>operation</x:v>
       </x:c>
       <x:c r="D108" s="25" t="str">
-        <x:v>최종 확인 사용자</x:v>
+        <x:v>요청 연산</x:v>
       </x:c>
       <x:c r="E108" s="25" t="str">
-        <x:v>UUID</x:v>
+        <x:v>VARCHAR(20)</x:v>
       </x:c>
       <x:c r="F108" s="25" t="str">
-        <x:v>N</x:v>
-      </x:c>
-      <x:c r="G108" s="25" t="str">
-        <x:v>FK</x:v>
-      </x:c>
-      <x:c r="H108" s="25" t="str">
-        <x:v>app_user.id</x:v>
-      </x:c>
+        <x:v>Y</x:v>
+      </x:c>
+      <x:c r="G108" s="25"/>
+      <x:c r="H108" s="25"/>
       <x:c r="I108" s="25" t="str">
-        <x:v>fact_candidate.confirmed_by_user_id에는 confirmed_value를 승인한 사람을 연결하는 값을 저장한다.</x:v>
+        <x:v>fact_candidate.operation에는 생성·변경·취소 요청을 구분하는 값을 저장한다.</x:v>
       </x:c>
       <x:c r="J108" s="25" t="str">
-        <x:v>최종 확인 사용자은(는) confirmed_value를 승인한 사람을 연결할 때 조회·검증·갱신한다.</x:v>
+        <x:v>요청 연산은(는) 생성·변경·취소 요청을 구분할 때 조회·검증·갱신한다.</x:v>
       </x:c>
       <x:c r="K108" s="25" t="str">
-        <x:v>보호자면 활성 PRIMARY 권한을 검사한다.</x:v>
+        <x:v>UPDATE/CANCEL은 대상 엔터티가 필요하다.</x:v>
       </x:c>
       <x:c r="L108" s="25" t="str">
-        <x:v>8e1339cb-b0bf-42df-9a7f-f6592be3e84f</x:v>
+        <x:v>UPDATE</x:v>
       </x:c>
     </x:row>
     <x:row r="109">
@@ -4672,33 +4696,35 @@
         <x:v>fact_candidate</x:v>
       </x:c>
       <x:c r="B109" s="26" t="n">
-        <x:v>20</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C109" s="26" t="str">
-        <x:v>requires_coordination</x:v>
+        <x:v>target_entity_id</x:v>
       </x:c>
       <x:c r="D109" s="26" t="str">
-        <x:v>협의 필요 여부</x:v>
+        <x:v>변경 대상 ID</x:v>
       </x:c>
       <x:c r="E109" s="26" t="str">
-        <x:v>BOOLEAN</x:v>
+        <x:v>UUID</x:v>
       </x:c>
       <x:c r="F109" s="26" t="str">
-        <x:v>Y</x:v>
-      </x:c>
-      <x:c r="G109" s="26" t="str"/>
-      <x:c r="H109" s="26" t="str"/>
+        <x:v>N</x:v>
+      </x:c>
+      <x:c r="G109" s="26" t="str">
+        <x:v>논리 참조</x:v>
+      </x:c>
+      <x:c r="H109" s="26"/>
       <x:c r="I109" s="26" t="str">
-        <x:v>fact_candidate.requires_coordination에는 시니어·PRIMARY 충돌 절차 필요성을 표시하는 값을 저장한다.</x:v>
+        <x:v>fact_candidate.target_entity_id에는 갱신·취소할 최종 행을 논리적으로 가리킴하는 값을 저장한다.</x:v>
       </x:c>
       <x:c r="J109" s="26" t="str">
-        <x:v>협의 필요 여부은(는) 시니어·PRIMARY 충돌 절차 필요성을 표시할 때 조회·검증·갱신한다.</x:v>
+        <x:v>변경 대상 ID은(는) 갱신·취소할 최종 행을 논리적으로 가리킴할 때 조회·검증·갱신한다.</x:v>
       </x:c>
       <x:c r="K109" s="26" t="str">
-        <x:v>coordination_status와 모순되지 않아야 한다.</x:v>
+        <x:v>여러 테이블 대상이므로 물리 FK라고 주장하지 않는다.</x:v>
       </x:c>
       <x:c r="L109" s="26" t="str">
-        <x:v>true</x:v>
+        <x:v>8f3de8c7-7a04-4c74-977b-223a096dc589</x:v>
       </x:c>
     </x:row>
     <x:row r="110">
@@ -4706,33 +4732,33 @@
         <x:v>fact_candidate</x:v>
       </x:c>
       <x:c r="B110" s="25" t="n">
-        <x:v>21</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C110" s="25" t="str">
-        <x:v>coordination_status</x:v>
+        <x:v>proposed_value</x:v>
       </x:c>
       <x:c r="D110" s="25" t="str">
-        <x:v>협의 상태</x:v>
+        <x:v>제안 값</x:v>
       </x:c>
       <x:c r="E110" s="25" t="str">
-        <x:v>VARCHAR(50)</x:v>
+        <x:v>JSONB</x:v>
       </x:c>
       <x:c r="F110" s="25" t="str">
         <x:v>Y</x:v>
       </x:c>
-      <x:c r="G110" s="25" t="str"/>
-      <x:c r="H110" s="25" t="str"/>
+      <x:c r="G110" s="25"/>
+      <x:c r="H110" s="25"/>
       <x:c r="I110" s="25" t="str">
-        <x:v>fact_candidate.coordination_status에는 양쪽 협의의 진행·결과를 별도 축으로 기록하는 값을 저장한다.</x:v>
+        <x:v>fact_candidate.proposed_value에는 추출·입력한 아직 미확정 구조화 값을 저장하는 값을 저장한다.</x:v>
       </x:c>
       <x:c r="J110" s="25" t="str">
-        <x:v>협의 상태은(는) 양쪽 협의의 진행·결과를 별도 축으로 기록할 때 조회·검증·갱신한다.</x:v>
+        <x:v>제안 값은(는) 추출·입력한 아직 미확정 구조화 값을 저장할 때 조회·검증·갱신한다.</x:v>
       </x:c>
       <x:c r="K110" s="25" t="str">
-        <x:v>후보 materialization 상태로 쓰지 않는다.</x:v>
+        <x:v>민감 중간 값은 반영 후 무기한 보존하지 않는다.</x:v>
       </x:c>
       <x:c r="L110" s="25" t="str">
-        <x:v>WAITING_PRIMARY_GUARDIAN</x:v>
+        <x:v>{"localTime":"15:00","timeZone":"Asia/Seoul"}</x:v>
       </x:c>
     </x:row>
     <x:row r="111">
@@ -4740,33 +4766,33 @@
         <x:v>fact_candidate</x:v>
       </x:c>
       <x:c r="B111" s="26" t="n">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C111" s="26" t="str">
-        <x:v>senior_position</x:v>
+        <x:v>confirmed_value</x:v>
       </x:c>
       <x:c r="D111" s="26" t="str">
-        <x:v>시니어 입장</x:v>
+        <x:v>확정 값</x:v>
       </x:c>
       <x:c r="E111" s="26" t="str">
-        <x:v>VARCHAR(30)</x:v>
+        <x:v>JSONB</x:v>
       </x:c>
       <x:c r="F111" s="26" t="str">
-        <x:v>Y</x:v>
-      </x:c>
-      <x:c r="G111" s="26" t="str"/>
-      <x:c r="H111" s="26" t="str"/>
+        <x:v>N</x:v>
+      </x:c>
+      <x:c r="G111" s="26"/>
+      <x:c r="H111" s="26"/>
       <x:c r="I111" s="26" t="str">
-        <x:v>fact_candidate.senior_position에는 시니어의 동의·반대·연락불가를 보존하는 값을 저장한다.</x:v>
+        <x:v>fact_candidate.confirmed_value에는 사용자가 최종 확인한 정규화 값을 저장하는 값을 저장한다.</x:v>
       </x:c>
       <x:c r="J111" s="26" t="str">
-        <x:v>시니어 입장은(는) 시니어의 동의·반대·연락불가를 보존할 때 조회·검증·갱신한다.</x:v>
+        <x:v>확정 값은(는) 사용자가 최종 확인한 정규화 값을 저장할 때 조회·검증·갱신한다.</x:v>
       </x:c>
       <x:c r="K111" s="26" t="str">
-        <x:v>PRIMARY 우선 처리 후에도 반대를 AGREED로 바꾸지 않는다.</x:v>
+        <x:v>이 값만 최종 원본에 반영한다.</x:v>
       </x:c>
       <x:c r="L111" s="26" t="str">
-        <x:v>DISAGREED</x:v>
+        <x:v>{"localTime":"15:00","timeZone":"Asia/Seoul"}</x:v>
       </x:c>
     </x:row>
     <x:row r="112">
@@ -4774,33 +4800,33 @@
         <x:v>fact_candidate</x:v>
       </x:c>
       <x:c r="B112" s="25" t="n">
-        <x:v>23</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C112" s="25" t="str">
-        <x:v>primary_guardian_decision</x:v>
+        <x:v>missing_fields</x:v>
       </x:c>
       <x:c r="D112" s="25" t="str">
-        <x:v>PRIMARY 결정</x:v>
+        <x:v>누락 필드 목록</x:v>
       </x:c>
       <x:c r="E112" s="25" t="str">
-        <x:v>VARCHAR(50)</x:v>
+        <x:v>TEXT[]</x:v>
       </x:c>
       <x:c r="F112" s="25" t="str">
         <x:v>Y</x:v>
       </x:c>
-      <x:c r="G112" s="25" t="str"/>
-      <x:c r="H112" s="25" t="str"/>
+      <x:c r="G112" s="25"/>
+      <x:c r="H112" s="25"/>
       <x:c r="I112" s="25" t="str">
-        <x:v>fact_candidate.primary_guardian_decision에는 기존값·제안값·수정값·취소 중 최종 방향을 기록하는 값을 저장한다.</x:v>
+        <x:v>fact_candidate.missing_fields에는 재질의가 필요한 JSON 필드명을 저장하는 값을 저장한다.</x:v>
       </x:c>
       <x:c r="J112" s="25" t="str">
-        <x:v>PRIMARY 결정은(는) 기존값·제안값·수정값·취소 중 최종 방향을 기록할 때 조회·검증·갱신한다.</x:v>
+        <x:v>누락 필드 목록은(는) 재질의가 필요한 JSON 필드명을 저장할 때 조회·검증·갱신한다.</x:v>
       </x:c>
       <x:c r="K112" s="25" t="str">
-        <x:v>활성 PRIMARY의 명시적 확인만 허용한다.</x:v>
+        <x:v>질문 문장이나 사람이 읽는 설명을 넣지 않는다.</x:v>
       </x:c>
       <x:c r="L112" s="25" t="str">
-        <x:v>REVISED_VALUE</x:v>
+        <x:v>["doseUnit"]</x:v>
       </x:c>
     </x:row>
     <x:row r="113">
@@ -4808,37 +4834,33 @@
         <x:v>fact_candidate</x:v>
       </x:c>
       <x:c r="B113" s="26" t="n">
-        <x:v>24</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C113" s="26" t="str">
-        <x:v>primary_guardian_id</x:v>
+        <x:v>risk_level</x:v>
       </x:c>
       <x:c r="D113" s="26" t="str">
-        <x:v>PRIMARY 보호자 ID</x:v>
+        <x:v>위험 수준</x:v>
       </x:c>
       <x:c r="E113" s="26" t="str">
-        <x:v>UUID</x:v>
+        <x:v>VARCHAR(20)</x:v>
       </x:c>
       <x:c r="F113" s="26" t="str">
-        <x:v>N</x:v>
-      </x:c>
-      <x:c r="G113" s="26" t="str">
-        <x:v>FK</x:v>
-      </x:c>
-      <x:c r="H113" s="26" t="str">
-        <x:v>app_user.id</x:v>
-      </x:c>
+        <x:v>Y</x:v>
+      </x:c>
+      <x:c r="G113" s="26"/>
+      <x:c r="H113" s="26"/>
       <x:c r="I113" s="26" t="str">
-        <x:v>fact_candidate.primary_guardian_id에는 협의를 책임진 PRIMARY를 연결하는 값을 저장한다.</x:v>
+        <x:v>fact_candidate.risk_level에는 일반·민감·고위험 처리 강도를 구분하는 값을 저장한다.</x:v>
       </x:c>
       <x:c r="J113" s="26" t="str">
-        <x:v>PRIMARY 보호자 ID은(는) 협의를 책임진 PRIMARY를 연결할 때 조회·검증·갱신한다.</x:v>
+        <x:v>위험 수준은(는) 일반·민감·고위험 처리 강도를 구분할 때 조회·검증·갱신한다.</x:v>
       </x:c>
       <x:c r="K113" s="26" t="str">
-        <x:v>관계가 ACTIVE·PRIMARY·GRANTED인지 검증한다.</x:v>
+        <x:v>민감 이상은 명확해도 최종 확인한다.</x:v>
       </x:c>
       <x:c r="L113" s="26" t="str">
-        <x:v>8e1339cb-b0bf-42df-9a7f-f6592be3e84f</x:v>
+        <x:v>SENSITIVE</x:v>
       </x:c>
     </x:row>
     <x:row r="114">
@@ -4846,33 +4868,33 @@
         <x:v>fact_candidate</x:v>
       </x:c>
       <x:c r="B114" s="25" t="n">
-        <x:v>25</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C114" s="25" t="str">
-        <x:v>contact_attempt_count</x:v>
+        <x:v>status</x:v>
       </x:c>
       <x:c r="D114" s="25" t="str">
-        <x:v>연락 시도 횟수</x:v>
+        <x:v>후보 처리 상태</x:v>
       </x:c>
       <x:c r="E114" s="25" t="str">
-        <x:v>INTEGER</x:v>
+        <x:v>VARCHAR(40)</x:v>
       </x:c>
       <x:c r="F114" s="25" t="str">
         <x:v>Y</x:v>
       </x:c>
-      <x:c r="G114" s="25" t="str"/>
-      <x:c r="H114" s="25" t="str"/>
+      <x:c r="G114" s="25"/>
+      <x:c r="H114" s="25"/>
       <x:c r="I114" s="25" t="str">
-        <x:v>fact_candidate.contact_attempt_count에는 시니어 또는 보호자 연락 시도 수를 기록하는 값을 저장한다.</x:v>
+        <x:v>fact_candidate.status에는 캡처부터 물리 반영까지 처리 단계를 표시하는 값을 저장한다.</x:v>
       </x:c>
       <x:c r="J114" s="25" t="str">
-        <x:v>연락 시도 횟수은(는) 시니어 또는 보호자 연락 시도 수를 기록할 때 조회·검증·갱신한다.</x:v>
+        <x:v>후보 처리 상태은(는) 캡처부터 물리 반영까지 처리 단계를 표시할 때 조회·검증·갱신한다.</x:v>
       </x:c>
       <x:c r="K114" s="25" t="str">
-        <x:v>실제 통화 성공을 증명하는 값이 아니다.</x:v>
+        <x:v>협의 결과 상태를 대신하지 않는다.</x:v>
       </x:c>
       <x:c r="L114" s="25" t="str">
-        <x:v>2</x:v>
+        <x:v>NEEDS_CONFIRMATION</x:v>
       </x:c>
     </x:row>
     <x:row r="115">
@@ -4880,33 +4902,33 @@
         <x:v>fact_candidate</x:v>
       </x:c>
       <x:c r="B115" s="26" t="n">
-        <x:v>26</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C115" s="26" t="str">
-        <x:v>last_contact_attempted_at</x:v>
+        <x:v>clarification_reason</x:v>
       </x:c>
       <x:c r="D115" s="26" t="str">
-        <x:v>최근 연락 시도 시각</x:v>
+        <x:v>재질의 사유</x:v>
       </x:c>
       <x:c r="E115" s="26" t="str">
-        <x:v>TIMESTAMPTZ</x:v>
+        <x:v>VARCHAR(60)</x:v>
       </x:c>
       <x:c r="F115" s="26" t="str">
         <x:v>N</x:v>
       </x:c>
-      <x:c r="G115" s="26" t="str"/>
-      <x:c r="H115" s="26" t="str"/>
+      <x:c r="G115" s="26"/>
+      <x:c r="H115" s="26"/>
       <x:c r="I115" s="26" t="str">
-        <x:v>fact_candidate.last_contact_attempted_at에는 마지막 디지털·전화 연락 시도 시점을 기록하는 값을 저장한다.</x:v>
+        <x:v>fact_candidate.clarification_reason에는 누락·모호·낮은 신뢰·충돌·민감 확인을 구분하는 값을 저장한다.</x:v>
       </x:c>
       <x:c r="J115" s="26" t="str">
-        <x:v>최근 연락 시도 시각은(는) 마지막 디지털·전화 연락 시도 시점을 기록할 때 조회·검증·갱신한다.</x:v>
+        <x:v>재질의 사유은(는) 누락·모호·낮은 신뢰·충돌·민감 확인을 구분할 때 조회·검증·갱신한다.</x:v>
       </x:c>
       <x:c r="K115" s="26" t="str">
-        <x:v>통화 내용이나 녹음을 저장하지 않는다.</x:v>
+        <x:v>복수 원인 중 현재 질문의 직접 원인을 둔다.</x:v>
       </x:c>
       <x:c r="L115" s="26" t="str">
-        <x:v>UTC 2026-07-27T11:00:00Z</x:v>
+        <x:v>MISSING_REQUIRED_FIELD</x:v>
       </x:c>
     </x:row>
     <x:row r="116">
@@ -4914,33 +4936,33 @@
         <x:v>fact_candidate</x:v>
       </x:c>
       <x:c r="B116" s="25" t="n">
-        <x:v>27</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C116" s="25" t="str">
-        <x:v>unreachable_reason</x:v>
+        <x:v>clarification_count</x:v>
       </x:c>
       <x:c r="D116" s="25" t="str">
-        <x:v>연락 불가 사유</x:v>
+        <x:v>재질의 횟수</x:v>
       </x:c>
       <x:c r="E116" s="25" t="str">
-        <x:v>VARCHAR(50)</x:v>
+        <x:v>INTEGER</x:v>
       </x:c>
       <x:c r="F116" s="25" t="str">
-        <x:v>N</x:v>
-      </x:c>
-      <x:c r="G116" s="25" t="str"/>
-      <x:c r="H116" s="25" t="str"/>
+        <x:v>Y</x:v>
+      </x:c>
+      <x:c r="G116" s="25"/>
+      <x:c r="H116" s="25"/>
       <x:c r="I116" s="25" t="str">
-        <x:v>fact_candidate.unreachable_reason에는 연락이 안 된 운영 사유를 코드로 기록하는 값을 저장한다.</x:v>
+        <x:v>fact_candidate.clarification_count에는 같은 후보에 수행한 재질의 횟수를 기록하는 값을 저장한다.</x:v>
       </x:c>
       <x:c r="J116" s="25" t="str">
-        <x:v>연락 불가 사유은(는) 연락이 안 된 운영 사유를 코드로 기록할 때 조회·검증·갱신한다.</x:v>
+        <x:v>재질의 횟수은(는) 같은 후보에 수행한 재질의 횟수를 기록할 때 조회·검증·갱신한다.</x:v>
       </x:c>
       <x:c r="K116" s="25" t="str">
-        <x:v>추측한 의학적 진단을 넣지 않는다.</x:v>
+        <x:v>음수가 될 수 없고 무한 반복을 막는다.</x:v>
       </x:c>
       <x:c r="L116" s="25" t="str">
-        <x:v>NO_RESPONSE</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="117">
@@ -4948,33 +4970,37 @@
         <x:v>fact_candidate</x:v>
       </x:c>
       <x:c r="B117" s="26" t="n">
-        <x:v>28</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C117" s="26" t="str">
-        <x:v>coordination_deadline_at</x:v>
+        <x:v>initiated_by_user_id</x:v>
       </x:c>
       <x:c r="D117" s="26" t="str">
-        <x:v>협의 기한</x:v>
+        <x:v>요청 시작 사용자</x:v>
       </x:c>
       <x:c r="E117" s="26" t="str">
-        <x:v>TIMESTAMPTZ</x:v>
+        <x:v>UUID</x:v>
       </x:c>
       <x:c r="F117" s="26" t="str">
         <x:v>N</x:v>
       </x:c>
-      <x:c r="G117" s="26" t="str"/>
-      <x:c r="H117" s="26" t="str"/>
+      <x:c r="G117" s="26" t="str">
+        <x:v>FK</x:v>
+      </x:c>
+      <x:c r="H117" s="26" t="str">
+        <x:v>app_user.id</x:v>
+      </x:c>
       <x:c r="I117" s="26" t="str">
-        <x:v>fact_candidate.coordination_deadline_at에는 후보를 방치하지 않을 처리 기한을 기록하는 값을 저장한다.</x:v>
+        <x:v>fact_candidate.initiated_by_user_id에는 등록·변경을 시작한 사람을 연결하는 값을 저장한다.</x:v>
       </x:c>
       <x:c r="J117" s="26" t="str">
-        <x:v>협의 기한은(는) 후보를 방치하지 않을 처리 기한을 기록할 때 조회·검증·갱신한다.</x:v>
+        <x:v>요청 시작 사용자은(는) 등록·변경을 시작한 사람을 연결할 때 조회·검증·갱신한다.</x:v>
       </x:c>
       <x:c r="K117" s="26" t="str">
-        <x:v>의학적 긴급도 판단을 자동 생성하지 않는다.</x:v>
+        <x:v>AI·시스템 추출이면 null일 수 있다.</x:v>
       </x:c>
       <x:c r="L117" s="26" t="str">
-        <x:v>UTC 2026-07-28T11:00:00Z</x:v>
+        <x:v>a2b64af3-5ee5-42ea-98c5-35ac9de10570</x:v>
       </x:c>
     </x:row>
     <x:row r="118">
@@ -4982,33 +5008,37 @@
         <x:v>fact_candidate</x:v>
       </x:c>
       <x:c r="B118" s="25" t="n">
-        <x:v>29</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C118" s="25" t="str">
-        <x:v>coordination_completed_at</x:v>
+        <x:v>confirmed_by_user_id</x:v>
       </x:c>
       <x:c r="D118" s="25" t="str">
-        <x:v>협의 완료 시각</x:v>
+        <x:v>최종 확인 사용자</x:v>
       </x:c>
       <x:c r="E118" s="25" t="str">
-        <x:v>TIMESTAMPTZ</x:v>
+        <x:v>UUID</x:v>
       </x:c>
       <x:c r="F118" s="25" t="str">
         <x:v>N</x:v>
       </x:c>
-      <x:c r="G118" s="25" t="str"/>
-      <x:c r="H118" s="25" t="str"/>
+      <x:c r="G118" s="25" t="str">
+        <x:v>FK</x:v>
+      </x:c>
+      <x:c r="H118" s="25" t="str">
+        <x:v>app_user.id</x:v>
+      </x:c>
       <x:c r="I118" s="25" t="str">
-        <x:v>fact_candidate.coordination_completed_at에는 디지털 협의 절차가 끝난 시각을 기록하는 값을 저장한다.</x:v>
+        <x:v>fact_candidate.confirmed_by_user_id에는 confirmed_value를 승인한 사람을 연결하는 값을 저장한다.</x:v>
       </x:c>
       <x:c r="J118" s="25" t="str">
-        <x:v>협의 완료 시각은(는) 디지털 협의 절차가 끝난 시각을 기록할 때 조회·검증·갱신한다.</x:v>
+        <x:v>최종 확인 사용자은(는) confirmed_value를 승인한 사람을 연결할 때 조회·검증·갱신한다.</x:v>
       </x:c>
       <x:c r="K118" s="25" t="str">
-        <x:v>통화 사실 증명 시각으로 표현하지 않는다.</x:v>
+        <x:v>보호자면 활성 PRIMARY 권한을 검사한다.</x:v>
       </x:c>
       <x:c r="L118" s="25" t="str">
-        <x:v>UTC 2026-07-27T11:30:00Z</x:v>
+        <x:v>8e1339cb-b0bf-42df-9a7f-f6592be3e84f</x:v>
       </x:c>
     </x:row>
     <x:row r="119">
@@ -5016,33 +5046,33 @@
         <x:v>fact_candidate</x:v>
       </x:c>
       <x:c r="B119" s="26" t="n">
-        <x:v>30</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C119" s="26" t="str">
-        <x:v>coordination_note</x:v>
+        <x:v>requires_coordination</x:v>
       </x:c>
       <x:c r="D119" s="26" t="str">
-        <x:v>협의 메모</x:v>
+        <x:v>협의 필요 여부</x:v>
       </x:c>
       <x:c r="E119" s="26" t="str">
-        <x:v>TEXT</x:v>
+        <x:v>BOOLEAN</x:v>
       </x:c>
       <x:c r="F119" s="26" t="str">
-        <x:v>N</x:v>
-      </x:c>
-      <x:c r="G119" s="26" t="str"/>
-      <x:c r="H119" s="26" t="str"/>
+        <x:v>Y</x:v>
+      </x:c>
+      <x:c r="G119" s="26"/>
+      <x:c r="H119" s="26"/>
       <x:c r="I119" s="26" t="str">
-        <x:v>fact_candidate.coordination_note에는 최종 결정에 필요한 짧은 운영 맥락을 기록하는 값을 저장한다.</x:v>
+        <x:v>fact_candidate.requires_coordination에는 시니어·PRIMARY 충돌 절차 필요성을 표시하는 값을 저장한다.</x:v>
       </x:c>
       <x:c r="J119" s="26" t="str">
-        <x:v>협의 메모은(는) 최종 결정에 필요한 짧은 운영 맥락을 기록할 때 조회·검증·갱신한다.</x:v>
+        <x:v>협의 필요 여부은(는) 시니어·PRIMARY 충돌 절차 필요성을 표시할 때 조회·검증·갱신한다.</x:v>
       </x:c>
       <x:c r="K119" s="26" t="str">
-        <x:v>민감 원문·통화 녹취·불필요한 자유 서술을 넣지 않는다.</x:v>
+        <x:v>coordination_status와 모순되지 않아야 한다.</x:v>
       </x:c>
       <x:c r="L119" s="26" t="str">
-        <x:v>시니어 반대 보존, PRIMARY 책임 재확인</x:v>
+        <x:v>true</x:v>
       </x:c>
     </x:row>
     <x:row r="120">
@@ -5050,35 +5080,33 @@
         <x:v>fact_candidate</x:v>
       </x:c>
       <x:c r="B120" s="25" t="n">
-        <x:v>31</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C120" s="25" t="str">
-        <x:v>materialized_target_id</x:v>
+        <x:v>coordination_status</x:v>
       </x:c>
       <x:c r="D120" s="25" t="str">
-        <x:v>반영 대상 ID</x:v>
+        <x:v>협의 상태</x:v>
       </x:c>
       <x:c r="E120" s="25" t="str">
-        <x:v>UUID</x:v>
+        <x:v>VARCHAR(50)</x:v>
       </x:c>
       <x:c r="F120" s="25" t="str">
-        <x:v>N</x:v>
-      </x:c>
-      <x:c r="G120" s="25" t="str">
-        <x:v>논리 참조</x:v>
-      </x:c>
-      <x:c r="H120" s="25" t="str"/>
+        <x:v>Y</x:v>
+      </x:c>
+      <x:c r="G120" s="25"/>
+      <x:c r="H120" s="25"/>
       <x:c r="I120" s="25" t="str">
-        <x:v>fact_candidate.materialized_target_id에는 실제로 생성된 최종 원본 행을 논리적으로 가리킴하는 값을 저장한다.</x:v>
+        <x:v>fact_candidate.coordination_status에는 양쪽 협의의 진행·결과를 별도 축으로 기록하는 값을 저장한다.</x:v>
       </x:c>
       <x:c r="J120" s="25" t="str">
-        <x:v>반영 대상 ID은(는) 실제로 생성된 최종 원본 행을 논리적으로 가리킴할 때 조회·검증·갱신한다.</x:v>
+        <x:v>협의 상태은(는) 양쪽 협의의 진행·결과를 별도 축으로 기록할 때 조회·검증·갱신한다.</x:v>
       </x:c>
       <x:c r="K120" s="25" t="str">
-        <x:v>target_domain에 따라 서비스가 존재를 검증한다.</x:v>
+        <x:v>후보 materialization 상태로 쓰지 않는다.</x:v>
       </x:c>
       <x:c r="L120" s="25" t="str">
-        <x:v>8f3de8c7-7a04-4c74-977b-223a096dc589</x:v>
+        <x:v>WAITING_PRIMARY_GUARDIAN</x:v>
       </x:c>
     </x:row>
     <x:row r="121">
@@ -5086,33 +5114,33 @@
         <x:v>fact_candidate</x:v>
       </x:c>
       <x:c r="B121" s="26" t="n">
-        <x:v>32</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C121" s="26" t="str">
-        <x:v>materialized_at</x:v>
+        <x:v>senior_position</x:v>
       </x:c>
       <x:c r="D121" s="26" t="str">
-        <x:v>물리 반영 시각</x:v>
+        <x:v>시니어 입장</x:v>
       </x:c>
       <x:c r="E121" s="26" t="str">
-        <x:v>TIMESTAMPTZ</x:v>
+        <x:v>VARCHAR(30)</x:v>
       </x:c>
       <x:c r="F121" s="26" t="str">
-        <x:v>N</x:v>
-      </x:c>
-      <x:c r="G121" s="26" t="str"/>
-      <x:c r="H121" s="26" t="str"/>
+        <x:v>Y</x:v>
+      </x:c>
+      <x:c r="G121" s="26"/>
+      <x:c r="H121" s="26"/>
       <x:c r="I121" s="26" t="str">
-        <x:v>fact_candidate.materialized_at에는 최종 원본에 한 번 반영된 시각을 기록하는 값을 저장한다.</x:v>
+        <x:v>fact_candidate.senior_position에는 시니어의 동의·반대·연락불가를 보존하는 값을 저장한다.</x:v>
       </x:c>
       <x:c r="J121" s="26" t="str">
-        <x:v>물리 반영 시각은(는) 최종 원본에 한 번 반영된 시각을 기록할 때 조회·검증·갱신한다.</x:v>
+        <x:v>시니어 입장은(는) 시니어의 동의·반대·연락불가를 보존할 때 조회·검증·갱신한다.</x:v>
       </x:c>
       <x:c r="K121" s="26" t="str">
-        <x:v>재시도는 null 여부와 대상 유일성을 함께 확인한다.</x:v>
+        <x:v>PRIMARY 우선 처리 후에도 반대를 AGREED로 바꾸지 않는다.</x:v>
       </x:c>
       <x:c r="L121" s="26" t="str">
-        <x:v>UTC 2026-07-27T11:31:00Z</x:v>
+        <x:v>DISAGREED</x:v>
       </x:c>
     </x:row>
     <x:row r="122">
@@ -5120,33 +5148,33 @@
         <x:v>fact_candidate</x:v>
       </x:c>
       <x:c r="B122" s="25" t="n">
-        <x:v>33</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C122" s="25" t="str">
-        <x:v>created_at</x:v>
+        <x:v>primary_guardian_decision</x:v>
       </x:c>
       <x:c r="D122" s="25" t="str">
-        <x:v>후보 생성 시각</x:v>
+        <x:v>PRIMARY 결정</x:v>
       </x:c>
       <x:c r="E122" s="25" t="str">
-        <x:v>TIMESTAMPTZ</x:v>
+        <x:v>VARCHAR(50)</x:v>
       </x:c>
       <x:c r="F122" s="25" t="str">
         <x:v>Y</x:v>
       </x:c>
-      <x:c r="G122" s="25" t="str"/>
-      <x:c r="H122" s="25" t="str"/>
+      <x:c r="G122" s="25"/>
+      <x:c r="H122" s="25"/>
       <x:c r="I122" s="25" t="str">
-        <x:v>fact_candidate.created_at에는 후보가 처음 포착된 시각을 기록하는 값을 저장한다.</x:v>
+        <x:v>fact_candidate.primary_guardian_decision에는 기존값·제안값·수정값·취소 중 최종 방향을 기록하는 값을 저장한다.</x:v>
       </x:c>
       <x:c r="J122" s="25" t="str">
-        <x:v>후보 생성 시각은(는) 후보가 처음 포착된 시각을 기록할 때 조회·검증·갱신한다.</x:v>
+        <x:v>PRIMARY 결정은(는) 기존값·제안값·수정값·취소 중 최종 방향을 기록할 때 조회·검증·갱신한다.</x:v>
       </x:c>
       <x:c r="K122" s="25" t="str">
-        <x:v>source_message occurred_at과 다를 수 있다.</x:v>
+        <x:v>활성 PRIMARY의 명시적 확인만 허용한다.</x:v>
       </x:c>
       <x:c r="L122" s="25" t="str">
-        <x:v>UTC 2026-07-27T10:12:32Z</x:v>
+        <x:v>REVISED_VALUE</x:v>
       </x:c>
     </x:row>
     <x:row r="123">
@@ -5154,33 +5182,37 @@
         <x:v>fact_candidate</x:v>
       </x:c>
       <x:c r="B123" s="26" t="n">
-        <x:v>34</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C123" s="26" t="str">
-        <x:v>updated_at</x:v>
+        <x:v>primary_guardian_id</x:v>
       </x:c>
       <x:c r="D123" s="26" t="str">
-        <x:v>후보 수정 시각</x:v>
+        <x:v>PRIMARY 보호자 ID</x:v>
       </x:c>
       <x:c r="E123" s="26" t="str">
-        <x:v>TIMESTAMPTZ</x:v>
+        <x:v>UUID</x:v>
       </x:c>
       <x:c r="F123" s="26" t="str">
-        <x:v>Y</x:v>
-      </x:c>
-      <x:c r="G123" s="26" t="str"/>
-      <x:c r="H123" s="26" t="str"/>
+        <x:v>N</x:v>
+      </x:c>
+      <x:c r="G123" s="26" t="str">
+        <x:v>FK</x:v>
+      </x:c>
+      <x:c r="H123" s="26" t="str">
+        <x:v>app_user.id</x:v>
+      </x:c>
       <x:c r="I123" s="26" t="str">
-        <x:v>fact_candidate.updated_at에는 재질의·협의·상태의 마지막 변경을 기록하는 값을 저장한다.</x:v>
+        <x:v>fact_candidate.primary_guardian_id에는 협의를 책임진 PRIMARY를 연결하는 값을 저장한다.</x:v>
       </x:c>
       <x:c r="J123" s="26" t="str">
-        <x:v>후보 수정 시각은(는) 재질의·협의·상태의 마지막 변경을 기록할 때 조회·검증·갱신한다.</x:v>
+        <x:v>PRIMARY 보호자 ID은(는) 협의를 책임진 PRIMARY를 연결할 때 조회·검증·갱신한다.</x:v>
       </x:c>
       <x:c r="K123" s="26" t="str">
-        <x:v>상세 이벤트 원장을 대신하지 않는다.</x:v>
+        <x:v>관계가 ACTIVE·PRIMARY·GRANTED인지 검증한다.</x:v>
       </x:c>
       <x:c r="L123" s="26" t="str">
-        <x:v>UTC 2026-07-27T11:31:00Z</x:v>
+        <x:v>8e1339cb-b0bf-42df-9a7f-f6592be3e84f</x:v>
       </x:c>
     </x:row>
     <x:row r="124">
@@ -5188,33 +5220,33 @@
         <x:v>fact_candidate</x:v>
       </x:c>
       <x:c r="B124" s="25" t="n">
-        <x:v>35</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C124" s="25" t="str">
-        <x:v>confirmed_at</x:v>
+        <x:v>contact_attempt_count</x:v>
       </x:c>
       <x:c r="D124" s="25" t="str">
-        <x:v>후보 확인 시각</x:v>
+        <x:v>연락 시도 횟수</x:v>
       </x:c>
       <x:c r="E124" s="25" t="str">
-        <x:v>TIMESTAMPTZ</x:v>
+        <x:v>INTEGER</x:v>
       </x:c>
       <x:c r="F124" s="25" t="str">
-        <x:v>N</x:v>
-      </x:c>
-      <x:c r="G124" s="25" t="str"/>
-      <x:c r="H124" s="25" t="str"/>
+        <x:v>Y</x:v>
+      </x:c>
+      <x:c r="G124" s="25"/>
+      <x:c r="H124" s="25"/>
       <x:c r="I124" s="25" t="str">
-        <x:v>fact_candidate.confirmed_at에는 confirmed_value가 확정된 시각을 기록하는 값을 저장한다.</x:v>
+        <x:v>fact_candidate.contact_attempt_count에는 시니어 또는 보호자 연락 시도 수를 기록하는 값을 저장한다.</x:v>
       </x:c>
       <x:c r="J124" s="25" t="str">
-        <x:v>후보 확인 시각은(는) confirmed_value가 확정된 시각을 기록할 때 조회·검증·갱신한다.</x:v>
+        <x:v>연락 시도 횟수은(는) 시니어 또는 보호자 연락 시도 수를 기록할 때 조회·검증·갱신한다.</x:v>
       </x:c>
       <x:c r="K124" s="25" t="str">
-        <x:v>materialized_at과 의미가 다르다.</x:v>
+        <x:v>실제 통화 성공을 증명하는 값이 아니다.</x:v>
       </x:c>
       <x:c r="L124" s="25" t="str">
-        <x:v>UTC 2026-07-27T11:29:00Z</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="125">
@@ -5222,13 +5254,13 @@
         <x:v>fact_candidate</x:v>
       </x:c>
       <x:c r="B125" s="26" t="n">
-        <x:v>36</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C125" s="26" t="str">
-        <x:v>expires_at</x:v>
+        <x:v>last_contact_attempted_at</x:v>
       </x:c>
       <x:c r="D125" s="26" t="str">
-        <x:v>후보 만료 시각</x:v>
+        <x:v>최근 연락 시도 시각</x:v>
       </x:c>
       <x:c r="E125" s="26" t="str">
         <x:v>TIMESTAMPTZ</x:v>
@@ -5236,373 +5268,361 @@
       <x:c r="F125" s="26" t="str">
         <x:v>N</x:v>
       </x:c>
-      <x:c r="G125" s="26" t="str"/>
-      <x:c r="H125" s="26" t="str"/>
+      <x:c r="G125" s="26"/>
+      <x:c r="H125" s="26"/>
       <x:c r="I125" s="26" t="str">
-        <x:v>fact_candidate.expires_at에는 미완료 후보를 만료시킬 예정 시각을 기록하는 값을 저장한다.</x:v>
+        <x:v>fact_candidate.last_contact_attempted_at에는 마지막 디지털·전화 연락 시도 시점을 기록하는 값을 저장한다.</x:v>
       </x:c>
       <x:c r="J125" s="26" t="str">
-        <x:v>후보 만료 시각은(는) 미완료 후보를 만료시킬 예정 시각을 기록할 때 조회·검증·갱신한다.</x:v>
+        <x:v>최근 연락 시도 시각은(는) 마지막 디지털·전화 연락 시도 시점을 기록할 때 조회·검증·갱신한다.</x:v>
       </x:c>
       <x:c r="K125" s="26" t="str">
-        <x:v>협의 중 후보를 무조건 자동 삭제하지 않는다.</x:v>
+        <x:v>통화 내용이나 녹음을 저장하지 않는다.</x:v>
       </x:c>
       <x:c r="L125" s="26" t="str">
-        <x:v>UTC 2026-08-03T10:12:32Z</x:v>
+        <x:v>UTC 2026-07-27T11:00:00Z</x:v>
       </x:c>
     </x:row>
     <x:row r="126">
       <x:c r="A126" s="25" t="str">
-        <x:v>memory</x:v>
+        <x:v>fact_candidate</x:v>
       </x:c>
       <x:c r="B126" s="25" t="n">
-        <x:v>1</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C126" s="25" t="str">
-        <x:v>id</x:v>
+        <x:v>unreachable_reason</x:v>
       </x:c>
       <x:c r="D126" s="25" t="str">
-        <x:v>기억 ID</x:v>
+        <x:v>연락 불가 사유</x:v>
       </x:c>
       <x:c r="E126" s="25" t="str">
-        <x:v>UUID</x:v>
+        <x:v>VARCHAR(50)</x:v>
       </x:c>
       <x:c r="F126" s="25" t="str">
-        <x:v>Y</x:v>
-      </x:c>
-      <x:c r="G126" s="25" t="str">
-        <x:v>PK</x:v>
-      </x:c>
-      <x:c r="H126" s="25" t="str"/>
+        <x:v>N</x:v>
+      </x:c>
+      <x:c r="G126" s="25"/>
+      <x:c r="H126" s="25"/>
       <x:c r="I126" s="25" t="str">
-        <x:v>memory.id에는 장기 개인화 사실을 식별하는 값을 저장한다.</x:v>
+        <x:v>fact_candidate.unreachable_reason에는 연락이 안 된 운영 사유를 코드로 기록하는 값을 저장한다.</x:v>
       </x:c>
       <x:c r="J126" s="25" t="str">
-        <x:v>기억 ID은(는) 장기 개인화 사실을 식별할 때 조회·검증·갱신한다.</x:v>
+        <x:v>연락 불가 사유은(는) 연락이 안 된 운영 사유를 코드로 기록할 때 조회·검증·갱신한다.</x:v>
       </x:c>
       <x:c r="K126" s="25" t="str">
-        <x:v>원문 메시지 ID를 재사용하지 않는다.</x:v>
+        <x:v>추측한 의학적 진단을 넣지 않는다.</x:v>
       </x:c>
       <x:c r="L126" s="25" t="str">
-        <x:v>536df5e2-82a0-43ff-9ed8-41933c9f96f0</x:v>
+        <x:v>NO_RESPONSE</x:v>
       </x:c>
     </x:row>
     <x:row r="127">
       <x:c r="A127" s="26" t="str">
-        <x:v>memory</x:v>
+        <x:v>fact_candidate</x:v>
       </x:c>
       <x:c r="B127" s="26" t="n">
-        <x:v>2</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C127" s="26" t="str">
-        <x:v>senior_id</x:v>
+        <x:v>coordination_deadline_at</x:v>
       </x:c>
       <x:c r="D127" s="26" t="str">
-        <x:v>시니어 ID</x:v>
+        <x:v>협의 기한</x:v>
       </x:c>
       <x:c r="E127" s="26" t="str">
-        <x:v>UUID</x:v>
+        <x:v>TIMESTAMPTZ</x:v>
       </x:c>
       <x:c r="F127" s="26" t="str">
-        <x:v>Y</x:v>
-      </x:c>
-      <x:c r="G127" s="26" t="str">
-        <x:v>FK</x:v>
-      </x:c>
-      <x:c r="H127" s="26" t="str">
-        <x:v>app_user.id</x:v>
-      </x:c>
+        <x:v>N</x:v>
+      </x:c>
+      <x:c r="G127" s="26"/>
+      <x:c r="H127" s="26"/>
       <x:c r="I127" s="26" t="str">
-        <x:v>memory.senior_id에는 기억의 소유자를 연결하는 값을 저장한다.</x:v>
+        <x:v>fact_candidate.coordination_deadline_at에는 후보를 방치하지 않을 처리 기한을 기록하는 값을 저장한다.</x:v>
       </x:c>
       <x:c r="J127" s="26" t="str">
-        <x:v>시니어 ID은(는) 기억의 소유자를 연결할 때 조회·검증·갱신한다.</x:v>
+        <x:v>협의 기한은(는) 후보를 방치하지 않을 처리 기한을 기록할 때 조회·검증·갱신한다.</x:v>
       </x:c>
       <x:c r="K127" s="26" t="str">
-        <x:v>다른 시니어 검색에서 제외한다.</x:v>
+        <x:v>의학적 긴급도 판단을 자동 생성하지 않는다.</x:v>
       </x:c>
       <x:c r="L127" s="26" t="str">
-        <x:v>a2b64af3-5ee5-42ea-98c5-35ac9de10570</x:v>
+        <x:v>UTC 2026-07-28T11:00:00Z</x:v>
       </x:c>
     </x:row>
     <x:row r="128">
       <x:c r="A128" s="25" t="str">
-        <x:v>memory</x:v>
+        <x:v>fact_candidate</x:v>
       </x:c>
       <x:c r="B128" s="25" t="n">
-        <x:v>3</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C128" s="25" t="str">
-        <x:v>source_conversation_id</x:v>
+        <x:v>coordination_completed_at</x:v>
       </x:c>
       <x:c r="D128" s="25" t="str">
-        <x:v>출처 대화 ID</x:v>
+        <x:v>협의 완료 시각</x:v>
       </x:c>
       <x:c r="E128" s="25" t="str">
-        <x:v>UUID</x:v>
+        <x:v>TIMESTAMPTZ</x:v>
       </x:c>
       <x:c r="F128" s="25" t="str">
         <x:v>N</x:v>
       </x:c>
-      <x:c r="G128" s="25" t="str">
-        <x:v>FK</x:v>
-      </x:c>
-      <x:c r="H128" s="25" t="str">
-        <x:v>conversation.id</x:v>
-      </x:c>
+      <x:c r="G128" s="25"/>
+      <x:c r="H128" s="25"/>
       <x:c r="I128" s="25" t="str">
-        <x:v>memory.source_conversation_id에는 사실을 처음 관찰한 대화를 연결하는 값을 저장한다.</x:v>
+        <x:v>fact_candidate.coordination_completed_at에는 디지털 협의 절차가 끝난 시각을 기록하는 값을 저장한다.</x:v>
       </x:c>
       <x:c r="J128" s="25" t="str">
-        <x:v>출처 대화 ID은(는) 사실을 처음 관찰한 대화를 연결할 때 조회·검증·갱신한다.</x:v>
+        <x:v>협의 완료 시각은(는) 디지털 협의 절차가 끝난 시각을 기록할 때 조회·검증·갱신한다.</x:v>
       </x:c>
       <x:c r="K128" s="25" t="str">
-        <x:v>대화가 삭제되어도 사실 의미는 독립적이어야 한다.</x:v>
+        <x:v>통화 사실 증명 시각으로 표현하지 않는다.</x:v>
       </x:c>
       <x:c r="L128" s="25" t="str">
-        <x:v>1a4fe41a-6464-4e7e-b292-9a507333a3fa</x:v>
+        <x:v>UTC 2026-07-27T11:30:00Z</x:v>
       </x:c>
     </x:row>
     <x:row r="129">
       <x:c r="A129" s="26" t="str">
-        <x:v>memory</x:v>
+        <x:v>fact_candidate</x:v>
       </x:c>
       <x:c r="B129" s="26" t="n">
-        <x:v>4</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C129" s="26" t="str">
-        <x:v>superseded_by_id</x:v>
+        <x:v>coordination_note</x:v>
       </x:c>
       <x:c r="D129" s="26" t="str">
-        <x:v>대체 기억 ID</x:v>
+        <x:v>협의 메모</x:v>
       </x:c>
       <x:c r="E129" s="26" t="str">
-        <x:v>UUID</x:v>
+        <x:v>TEXT</x:v>
       </x:c>
       <x:c r="F129" s="26" t="str">
         <x:v>N</x:v>
       </x:c>
-      <x:c r="G129" s="26" t="str">
-        <x:v>SELF FK</x:v>
-      </x:c>
-      <x:c r="H129" s="26" t="str">
-        <x:v>memory.id</x:v>
-      </x:c>
+      <x:c r="G129" s="26"/>
+      <x:c r="H129" s="26"/>
       <x:c r="I129" s="26" t="str">
-        <x:v>memory.superseded_by_id에는 수정된 새 기억을 연결하는 값을 저장한다.</x:v>
+        <x:v>fact_candidate.coordination_note에는 최종 결정에 필요한 짧은 운영 맥락을 기록하는 값을 저장한다.</x:v>
       </x:c>
       <x:c r="J129" s="26" t="str">
-        <x:v>대체 기억 ID은(는) 수정된 새 기억을 연결할 때 조회·검증·갱신한다.</x:v>
+        <x:v>협의 메모은(는) 최종 결정에 필요한 짧은 운영 맥락을 기록할 때 조회·검증·갱신한다.</x:v>
       </x:c>
       <x:c r="K129" s="26" t="str">
-        <x:v>기억 자기 참조와 순환을 금지한다.</x:v>
+        <x:v>민감 원문·통화 녹취·불필요한 자유 서술을 넣지 않는다.</x:v>
       </x:c>
       <x:c r="L129" s="26" t="str">
-        <x:v>950db0a5-782a-40af-939a-f276660289bb</x:v>
+        <x:v>시니어 반대 보존, PRIMARY 책임 재확인</x:v>
       </x:c>
     </x:row>
     <x:row r="130">
       <x:c r="A130" s="25" t="str">
-        <x:v>memory</x:v>
+        <x:v>fact_candidate</x:v>
       </x:c>
       <x:c r="B130" s="25" t="n">
-        <x:v>5</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C130" s="25" t="str">
-        <x:v>memory_type</x:v>
+        <x:v>materialized_target_id</x:v>
       </x:c>
       <x:c r="D130" s="25" t="str">
-        <x:v>기억 유형</x:v>
+        <x:v>반영 대상 ID</x:v>
       </x:c>
       <x:c r="E130" s="25" t="str">
-        <x:v>VARCHAR(50)</x:v>
+        <x:v>UUID</x:v>
       </x:c>
       <x:c r="F130" s="25" t="str">
-        <x:v>Y</x:v>
-      </x:c>
-      <x:c r="G130" s="25" t="str"/>
-      <x:c r="H130" s="25" t="str"/>
+        <x:v>N</x:v>
+      </x:c>
+      <x:c r="G130" s="25" t="str">
+        <x:v>논리 참조</x:v>
+      </x:c>
+      <x:c r="H130" s="25"/>
       <x:c r="I130" s="25" t="str">
-        <x:v>memory.memory_type에는 관계·선호·취미·일상 등 사실을 구분하는 값을 저장한다.</x:v>
+        <x:v>fact_candidate.materialized_target_id에는 실제로 생성된 최종 원본 행을 논리적으로 가리킴하는 값을 저장한다.</x:v>
       </x:c>
       <x:c r="J130" s="25" t="str">
-        <x:v>기억 유형은(는) 관계·선호·취미·일상 등 사실을 구분할 때 조회·검증·갱신한다.</x:v>
+        <x:v>반영 대상 ID은(는) 실제로 생성된 최종 원본 행을 논리적으로 가리킴할 때 조회·검증·갱신한다.</x:v>
       </x:c>
       <x:c r="K130" s="25" t="str">
-        <x:v>대화 요약을 장기 기억 유형으로 쓰지 않는다.</x:v>
+        <x:v>target_domain에 따라 서비스가 존재를 검증한다.</x:v>
       </x:c>
       <x:c r="L130" s="25" t="str">
-        <x:v>PREFERENCE</x:v>
+        <x:v>8f3de8c7-7a04-4c74-977b-223a096dc589</x:v>
       </x:c>
     </x:row>
     <x:row r="131">
       <x:c r="A131" s="26" t="str">
-        <x:v>memory</x:v>
+        <x:v>fact_candidate</x:v>
       </x:c>
       <x:c r="B131" s="26" t="n">
-        <x:v>6</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C131" s="26" t="str">
-        <x:v>content</x:v>
+        <x:v>materialized_at</x:v>
       </x:c>
       <x:c r="D131" s="26" t="str">
-        <x:v>독립 사실 내용</x:v>
+        <x:v>물리 반영 시각</x:v>
       </x:c>
       <x:c r="E131" s="26" t="str">
-        <x:v>TEXT</x:v>
+        <x:v>TIMESTAMPTZ</x:v>
       </x:c>
       <x:c r="F131" s="26" t="str">
-        <x:v>Y</x:v>
-      </x:c>
-      <x:c r="G131" s="26" t="str"/>
-      <x:c r="H131" s="26" t="str"/>
+        <x:v>N</x:v>
+      </x:c>
+      <x:c r="G131" s="26"/>
+      <x:c r="H131" s="26"/>
       <x:c r="I131" s="26" t="str">
-        <x:v>memory.content에는 대화 없이 이해되는 사실 하나를 저장하는 값을 저장한다.</x:v>
+        <x:v>fact_candidate.materialized_at에는 최종 원본에 한 번 반영된 시각을 기록하는 값을 저장한다.</x:v>
       </x:c>
       <x:c r="J131" s="26" t="str">
-        <x:v>독립 사실 내용은(는) 대화 없이 이해되는 사실 하나를 저장할 때 조회·검증·갱신한다.</x:v>
+        <x:v>물리 반영 시각은(는) 최종 원본에 한 번 반영된 시각을 기록할 때 조회·검증·갱신한다.</x:v>
       </x:c>
       <x:c r="K131" s="26" t="str">
-        <x:v>Raw·일간 요약 전문을 복사하지 않는다.</x:v>
+        <x:v>재시도는 null 여부와 대상 유일성을 함께 확인한다.</x:v>
       </x:c>
       <x:c r="L131" s="26" t="str">
-        <x:v>시니어는 따뜻한 보리차를 좋아한다.</x:v>
+        <x:v>UTC 2026-07-27T11:31:00Z</x:v>
       </x:c>
     </x:row>
     <x:row r="132">
       <x:c r="A132" s="25" t="str">
-        <x:v>memory</x:v>
+        <x:v>fact_candidate</x:v>
       </x:c>
       <x:c r="B132" s="25" t="n">
-        <x:v>7</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C132" s="25" t="str">
-        <x:v>verification_status</x:v>
+        <x:v>created_at</x:v>
       </x:c>
       <x:c r="D132" s="25" t="str">
-        <x:v>기억 확인 상태</x:v>
+        <x:v>후보 생성 시각</x:v>
       </x:c>
       <x:c r="E132" s="25" t="str">
-        <x:v>VARCHAR(30)</x:v>
+        <x:v>TIMESTAMPTZ</x:v>
       </x:c>
       <x:c r="F132" s="25" t="str">
         <x:v>Y</x:v>
       </x:c>
-      <x:c r="G132" s="25" t="str"/>
-      <x:c r="H132" s="25" t="str"/>
+      <x:c r="G132" s="25"/>
+      <x:c r="H132" s="25"/>
       <x:c r="I132" s="25" t="str">
-        <x:v>memory.verification_status에는 확인 수준과 거절 여부를 표시하는 값을 저장한다.</x:v>
+        <x:v>fact_candidate.created_at에는 후보가 처음 포착된 시각을 기록하는 값을 저장한다.</x:v>
       </x:c>
       <x:c r="J132" s="25" t="str">
-        <x:v>기억 확인 상태은(는) 확인 수준과 거절 여부를 표시할 때 조회·검증·갱신한다.</x:v>
+        <x:v>후보 생성 시각은(는) 후보가 처음 포착된 시각을 기록할 때 조회·검증·갱신한다.</x:v>
       </x:c>
       <x:c r="K132" s="25" t="str">
-        <x:v>REJECTED는 검색에서 제외한다.</x:v>
+        <x:v>source_message occurred_at과 다를 수 있다.</x:v>
       </x:c>
       <x:c r="L132" s="25" t="str">
-        <x:v>USER_CONFIRMED</x:v>
+        <x:v>UTC 2026-07-27T10:12:32Z</x:v>
       </x:c>
     </x:row>
     <x:row r="133">
       <x:c r="A133" s="26" t="str">
-        <x:v>memory</x:v>
+        <x:v>fact_candidate</x:v>
       </x:c>
       <x:c r="B133" s="26" t="n">
-        <x:v>8</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C133" s="26" t="str">
-        <x:v>lifecycle_status</x:v>
+        <x:v>updated_at</x:v>
       </x:c>
       <x:c r="D133" s="26" t="str">
-        <x:v>기억 수명 상태</x:v>
+        <x:v>후보 수정 시각</x:v>
       </x:c>
       <x:c r="E133" s="26" t="str">
-        <x:v>VARCHAR(30)</x:v>
+        <x:v>TIMESTAMPTZ</x:v>
       </x:c>
       <x:c r="F133" s="26" t="str">
         <x:v>Y</x:v>
       </x:c>
-      <x:c r="G133" s="26" t="str"/>
-      <x:c r="H133" s="26" t="str"/>
+      <x:c r="G133" s="26"/>
+      <x:c r="H133" s="26"/>
       <x:c r="I133" s="26" t="str">
-        <x:v>memory.lifecycle_status에는 활성·분쟁·대체·만료·삭제를 구분하는 값을 저장한다.</x:v>
+        <x:v>fact_candidate.updated_at에는 재질의·협의·상태의 마지막 변경을 기록하는 값을 저장한다.</x:v>
       </x:c>
       <x:c r="J133" s="26" t="str">
-        <x:v>기억 수명 상태은(는) 활성·분쟁·대체·만료·삭제를 구분할 때 조회·검증·갱신한다.</x:v>
+        <x:v>후보 수정 시각은(는) 재질의·협의·상태의 마지막 변경을 기록할 때 조회·검증·갱신한다.</x:v>
       </x:c>
       <x:c r="K133" s="26" t="str">
-        <x:v>ACTIVE만 검색 후보로 사용한다.</x:v>
+        <x:v>상세 이벤트 원장을 대신하지 않는다.</x:v>
       </x:c>
       <x:c r="L133" s="26" t="str">
-        <x:v>ACTIVE</x:v>
+        <x:v>UTC 2026-07-27T11:31:00Z</x:v>
       </x:c>
     </x:row>
     <x:row r="134">
       <x:c r="A134" s="25" t="str">
-        <x:v>memory</x:v>
+        <x:v>fact_candidate</x:v>
       </x:c>
       <x:c r="B134" s="25" t="n">
-        <x:v>9</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C134" s="25" t="str">
-        <x:v>visibility</x:v>
+        <x:v>confirmed_at</x:v>
       </x:c>
       <x:c r="D134" s="25" t="str">
-        <x:v>기억 공개 범위</x:v>
+        <x:v>후보 확인 시각</x:v>
       </x:c>
       <x:c r="E134" s="25" t="str">
-        <x:v>VARCHAR(40)</x:v>
+        <x:v>TIMESTAMPTZ</x:v>
       </x:c>
       <x:c r="F134" s="25" t="str">
-        <x:v>Y</x:v>
-      </x:c>
-      <x:c r="G134" s="25" t="str"/>
-      <x:c r="H134" s="25" t="str"/>
+        <x:v>N</x:v>
+      </x:c>
+      <x:c r="G134" s="25"/>
+      <x:c r="H134" s="25"/>
       <x:c r="I134" s="25" t="str">
-        <x:v>memory.visibility에는 시니어 전용·PRIMARY·전체 보호자 공유를 구분하는 값을 저장한다.</x:v>
+        <x:v>fact_candidate.confirmed_at에는 confirmed_value가 확정된 시각을 기록하는 값을 저장한다.</x:v>
       </x:c>
       <x:c r="J134" s="25" t="str">
-        <x:v>기억 공개 범위은(는) 시니어 전용·PRIMARY·전체 보호자 공유를 구분할 때 조회·검증·갱신한다.</x:v>
+        <x:v>후보 확인 시각은(는) confirmed_value가 확정된 시각을 기록할 때 조회·검증·갱신한다.</x:v>
       </x:c>
       <x:c r="K134" s="25" t="str">
-        <x:v>공유 동의와 활성 관계도 함께 검사한다.</x:v>
+        <x:v>materialized_at과 의미가 다르다.</x:v>
       </x:c>
       <x:c r="L134" s="25" t="str">
-        <x:v>PRIVATE</x:v>
+        <x:v>UTC 2026-07-27T11:29:00Z</x:v>
       </x:c>
     </x:row>
     <x:row r="135">
       <x:c r="A135" s="26" t="str">
-        <x:v>memory</x:v>
+        <x:v>fact_candidate</x:v>
       </x:c>
       <x:c r="B135" s="26" t="n">
-        <x:v>10</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C135" s="26" t="str">
-        <x:v>embedding</x:v>
+        <x:v>expires_at</x:v>
       </x:c>
       <x:c r="D135" s="26" t="str">
-        <x:v>기억 임베딩</x:v>
+        <x:v>후보 만료 시각</x:v>
       </x:c>
       <x:c r="E135" s="26" t="str">
-        <x:v>VECTOR</x:v>
+        <x:v>TIMESTAMPTZ</x:v>
       </x:c>
       <x:c r="F135" s="26" t="str">
         <x:v>N</x:v>
       </x:c>
-      <x:c r="G135" s="26" t="str"/>
-      <x:c r="H135" s="26" t="str"/>
+      <x:c r="G135" s="26"/>
+      <x:c r="H135" s="26"/>
       <x:c r="I135" s="26" t="str">
-        <x:v>memory.embedding에는 의미 유사 기억 검색 벡터를 저장하는 값을 저장한다.</x:v>
+        <x:v>fact_candidate.expires_at에는 미완료 후보를 만료시킬 예정 시각을 기록하는 값을 저장한다.</x:v>
       </x:c>
       <x:c r="J135" s="26" t="str">
-        <x:v>기억 임베딩은(는) 의미 유사 기억 검색 벡터를 저장할 때 조회·검증·갱신한다.</x:v>
+        <x:v>후보 만료 시각은(는) 미완료 후보를 만료시킬 예정 시각을 기록할 때 조회·검증·갱신한다.</x:v>
       </x:c>
       <x:c r="K135" s="26" t="str">
-        <x:v>모델·차원은 TBD이고 혼합 모델을 금지한다.</x:v>
+        <x:v>협의 중 후보를 무조건 자동 삭제하지 않는다.</x:v>
       </x:c>
       <x:c r="L135" s="26" t="str">
-        <x:v>TBD</x:v>
+        <x:v>UTC 2026-08-03T10:12:32Z</x:v>
       </x:c>
     </x:row>
     <x:row r="136">
@@ -5610,37 +5630,35 @@
         <x:v>memory</x:v>
       </x:c>
       <x:c r="B136" s="25" t="n">
-        <x:v>11</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C136" s="25" t="str">
-        <x:v>source_summary_id</x:v>
+        <x:v>id</x:v>
       </x:c>
       <x:c r="D136" s="25" t="str">
-        <x:v>출처 요약 ID</x:v>
+        <x:v>기억 ID</x:v>
       </x:c>
       <x:c r="E136" s="25" t="str">
         <x:v>UUID</x:v>
       </x:c>
       <x:c r="F136" s="25" t="str">
-        <x:v>N</x:v>
+        <x:v>Y</x:v>
       </x:c>
       <x:c r="G136" s="25" t="str">
-        <x:v>FK</x:v>
-      </x:c>
-      <x:c r="H136" s="25" t="str">
-        <x:v>conversation_summary.id</x:v>
-      </x:c>
+        <x:v>PK</x:v>
+      </x:c>
+      <x:c r="H136" s="25"/>
       <x:c r="I136" s="25" t="str">
-        <x:v>memory.source_summary_id에는 기억을 뒷받침한 대화·일간 요약을 연결하는 값을 저장한다.</x:v>
+        <x:v>memory.id에는 장기 개인화 사실을 식별하는 값을 저장한다.</x:v>
       </x:c>
       <x:c r="J136" s="25" t="str">
-        <x:v>출처 요약 ID은(는) 기억을 뒷받침한 대화·일간 요약을 연결할 때 조회·검증·갱신한다.</x:v>
+        <x:v>기억 ID은(는) 장기 개인화 사실을 식별할 때 조회·검증·갱신한다.</x:v>
       </x:c>
       <x:c r="K136" s="25" t="str">
-        <x:v>요약 전문을 content에 복제하지 않는다.</x:v>
+        <x:v>원문 메시지 ID를 재사용하지 않는다.</x:v>
       </x:c>
       <x:c r="L136" s="25" t="str">
-        <x:v>9cd9cbdd-1e7c-4cbb-9014-4ddfb82b73e0</x:v>
+        <x:v>536df5e2-82a0-43ff-9ed8-41933c9f96f0</x:v>
       </x:c>
     </x:row>
     <x:row r="137">
@@ -5648,37 +5666,37 @@
         <x:v>memory</x:v>
       </x:c>
       <x:c r="B137" s="26" t="n">
-        <x:v>12</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C137" s="26" t="str">
-        <x:v>source_candidate_id</x:v>
+        <x:v>senior_id</x:v>
       </x:c>
       <x:c r="D137" s="26" t="str">
-        <x:v>출처 후보 ID</x:v>
+        <x:v>시니어 ID</x:v>
       </x:c>
       <x:c r="E137" s="26" t="str">
         <x:v>UUID</x:v>
       </x:c>
       <x:c r="F137" s="26" t="str">
-        <x:v>N</x:v>
+        <x:v>Y</x:v>
       </x:c>
       <x:c r="G137" s="26" t="str">
         <x:v>FK</x:v>
       </x:c>
       <x:c r="H137" s="26" t="str">
-        <x:v>fact_candidate.id</x:v>
+        <x:v>app_user.id</x:v>
       </x:c>
       <x:c r="I137" s="26" t="str">
-        <x:v>memory.source_candidate_id에는 확인·반영을 통과한 후보를 연결하는 값을 저장한다.</x:v>
+        <x:v>memory.senior_id에는 기억의 소유자를 연결하는 값을 저장한다.</x:v>
       </x:c>
       <x:c r="J137" s="26" t="str">
-        <x:v>출처 후보 ID은(는) 확인·반영을 통과한 후보를 연결할 때 조회·검증·갱신한다.</x:v>
+        <x:v>시니어 ID은(는) 기억의 소유자를 연결할 때 조회·검증·갱신한다.</x:v>
       </x:c>
       <x:c r="K137" s="26" t="str">
-        <x:v>유일성으로 중복 기억 생성을 막는다.</x:v>
+        <x:v>다른 시니어 검색에서 제외한다.</x:v>
       </x:c>
       <x:c r="L137" s="26" t="str">
-        <x:v>dcd1c7f7-ce8a-405f-a3a5-f2bb25eaac31</x:v>
+        <x:v>a2b64af3-5ee5-42ea-98c5-35ac9de10570</x:v>
       </x:c>
     </x:row>
     <x:row r="138">
@@ -5686,33 +5704,37 @@
         <x:v>memory</x:v>
       </x:c>
       <x:c r="B138" s="25" t="n">
-        <x:v>13</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C138" s="25" t="str">
-        <x:v>keywords</x:v>
+        <x:v>source_conversation_id</x:v>
       </x:c>
       <x:c r="D138" s="25" t="str">
-        <x:v>정확 검색 키워드</x:v>
+        <x:v>출처 대화 ID</x:v>
       </x:c>
       <x:c r="E138" s="25" t="str">
-        <x:v>TEXT[]</x:v>
+        <x:v>UUID</x:v>
       </x:c>
       <x:c r="F138" s="25" t="str">
-        <x:v>Y</x:v>
-      </x:c>
-      <x:c r="G138" s="25" t="str"/>
-      <x:c r="H138" s="25" t="str"/>
+        <x:v>N</x:v>
+      </x:c>
+      <x:c r="G138" s="25" t="str">
+        <x:v>FK</x:v>
+      </x:c>
+      <x:c r="H138" s="25" t="str">
+        <x:v>conversation.id</x:v>
+      </x:c>
       <x:c r="I138" s="25" t="str">
-        <x:v>memory.keywords에는 이름·음식·장소 등 정확 일치 단어를 저장하는 값을 저장한다.</x:v>
+        <x:v>memory.source_conversation_id에는 사실을 처음 관찰한 대화를 연결하는 값을 저장한다.</x:v>
       </x:c>
       <x:c r="J138" s="25" t="str">
-        <x:v>정확 검색 키워드은(는) 이름·음식·장소 등 정확 일치 단어를 저장할 때 조회·검증·갱신한다.</x:v>
+        <x:v>출처 대화 ID은(는) 사실을 처음 관찰한 대화를 연결할 때 조회·검증·갱신한다.</x:v>
       </x:c>
       <x:c r="K138" s="25" t="str">
-        <x:v>민감 원문 전문이나 무의미한 토큰을 넣지 않는다.</x:v>
+        <x:v>대화가 삭제되어도 사실 의미는 독립적이어야 한다.</x:v>
       </x:c>
       <x:c r="L138" s="25" t="str">
-        <x:v>["보리차","따뜻한 음료"]</x:v>
+        <x:v>1a4fe41a-6464-4e7e-b292-9a507333a3fa</x:v>
       </x:c>
     </x:row>
     <x:row r="139">
@@ -5720,33 +5742,37 @@
         <x:v>memory</x:v>
       </x:c>
       <x:c r="B139" s="26" t="n">
-        <x:v>14</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C139" s="26" t="str">
-        <x:v>importance</x:v>
+        <x:v>superseded_by_id</x:v>
       </x:c>
       <x:c r="D139" s="26" t="str">
-        <x:v>기억 중요도</x:v>
+        <x:v>대체 기억 ID</x:v>
       </x:c>
       <x:c r="E139" s="26" t="str">
-        <x:v>SMALLINT</x:v>
+        <x:v>UUID</x:v>
       </x:c>
       <x:c r="F139" s="26" t="str">
-        <x:v>Y</x:v>
-      </x:c>
-      <x:c r="G139" s="26" t="str"/>
-      <x:c r="H139" s="26" t="str"/>
+        <x:v>N</x:v>
+      </x:c>
+      <x:c r="G139" s="26" t="str">
+        <x:v>SELF FK</x:v>
+      </x:c>
+      <x:c r="H139" s="26" t="str">
+        <x:v>memory.id</x:v>
+      </x:c>
       <x:c r="I139" s="26" t="str">
-        <x:v>memory.importance에는 재정렬에 사용할 1~5 중요도를 저장하는 값을 저장한다.</x:v>
+        <x:v>memory.superseded_by_id에는 수정된 새 기억을 연결하는 값을 저장한다.</x:v>
       </x:c>
       <x:c r="J139" s="26" t="str">
-        <x:v>기억 중요도은(는) 재정렬에 사용할 1~5 중요도를 저장할 때 조회·검증·갱신한다.</x:v>
+        <x:v>대체 기억 ID은(는) 수정된 새 기억을 연결할 때 조회·검증·갱신한다.</x:v>
       </x:c>
       <x:c r="K139" s="26" t="str">
-        <x:v>주관값 하나로 검색 순위를 독점하지 않게 한다.</x:v>
+        <x:v>기억 자기 참조와 순환을 금지한다.</x:v>
       </x:c>
       <x:c r="L139" s="26" t="str">
-        <x:v>4</x:v>
+        <x:v>950db0a5-782a-40af-939a-f276660289bb</x:v>
       </x:c>
     </x:row>
     <x:row r="140">
@@ -5754,33 +5780,33 @@
         <x:v>memory</x:v>
       </x:c>
       <x:c r="B140" s="25" t="n">
-        <x:v>15</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C140" s="25" t="str">
-        <x:v>first_observed_at</x:v>
+        <x:v>memory_type</x:v>
       </x:c>
       <x:c r="D140" s="25" t="str">
-        <x:v>최초 관찰 시각</x:v>
+        <x:v>기억 유형</x:v>
       </x:c>
       <x:c r="E140" s="25" t="str">
-        <x:v>TIMESTAMPTZ</x:v>
+        <x:v>VARCHAR(50)</x:v>
       </x:c>
       <x:c r="F140" s="25" t="str">
         <x:v>Y</x:v>
       </x:c>
-      <x:c r="G140" s="25" t="str"/>
-      <x:c r="H140" s="25" t="str"/>
+      <x:c r="G140" s="25"/>
+      <x:c r="H140" s="25"/>
       <x:c r="I140" s="25" t="str">
-        <x:v>memory.first_observed_at에는 사실을 처음 알게 된 시각을 기록하는 값을 저장한다.</x:v>
+        <x:v>memory.memory_type에는 관계·선호·취미·일상 등 사실을 구분하는 값을 저장한다.</x:v>
       </x:c>
       <x:c r="J140" s="25" t="str">
-        <x:v>최초 관찰 시각은(는) 사실을 처음 알게 된 시각을 기록할 때 조회·검증·갱신한다.</x:v>
+        <x:v>기억 유형은(는) 관계·선호·취미·일상 등 사실을 구분할 때 조회·검증·갱신한다.</x:v>
       </x:c>
       <x:c r="K140" s="25" t="str">
-        <x:v>기억 행 생성 시각과 다를 수 있다.</x:v>
+        <x:v>대화 요약을 장기 기억 유형으로 쓰지 않는다.</x:v>
       </x:c>
       <x:c r="L140" s="25" t="str">
-        <x:v>UTC 2026-07-20T10:00:00Z</x:v>
+        <x:v>PREFERENCE</x:v>
       </x:c>
     </x:row>
     <x:row r="141">
@@ -5788,33 +5814,33 @@
         <x:v>memory</x:v>
       </x:c>
       <x:c r="B141" s="26" t="n">
-        <x:v>16</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C141" s="26" t="str">
-        <x:v>last_confirmed_at</x:v>
+        <x:v>content</x:v>
       </x:c>
       <x:c r="D141" s="26" t="str">
-        <x:v>최근 확인 시각</x:v>
+        <x:v>독립 사실 내용</x:v>
       </x:c>
       <x:c r="E141" s="26" t="str">
-        <x:v>TIMESTAMPTZ</x:v>
+        <x:v>TEXT</x:v>
       </x:c>
       <x:c r="F141" s="26" t="str">
-        <x:v>N</x:v>
-      </x:c>
-      <x:c r="G141" s="26" t="str"/>
-      <x:c r="H141" s="26" t="str"/>
+        <x:v>Y</x:v>
+      </x:c>
+      <x:c r="G141" s="26"/>
+      <x:c r="H141" s="26"/>
       <x:c r="I141" s="26" t="str">
-        <x:v>memory.last_confirmed_at에는 사실을 마지막으로 재확인한 때를 기록하는 값을 저장한다.</x:v>
+        <x:v>memory.content에는 대화 없이 이해되는 사실 하나를 저장하는 값을 저장한다.</x:v>
       </x:c>
       <x:c r="J141" s="26" t="str">
-        <x:v>최근 확인 시각은(는) 사실을 마지막으로 재확인한 때를 기록할 때 조회·검증·갱신한다.</x:v>
+        <x:v>독립 사실 내용은(는) 대화 없이 이해되는 사실 하나를 저장할 때 조회·검증·갱신한다.</x:v>
       </x:c>
       <x:c r="K141" s="26" t="str">
-        <x:v>단순 검색·사용 시각으로 갱신하지 않는다.</x:v>
+        <x:v>Raw·일간 요약 전문을 복사하지 않는다.</x:v>
       </x:c>
       <x:c r="L141" s="26" t="str">
-        <x:v>UTC 2026-07-27T10:15:00Z</x:v>
+        <x:v>시니어는 따뜻한 보리차를 좋아한다.</x:v>
       </x:c>
     </x:row>
     <x:row r="142">
@@ -5822,235 +5848,217 @@
         <x:v>memory</x:v>
       </x:c>
       <x:c r="B142" s="25" t="n">
-        <x:v>17</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C142" s="25" t="str">
-        <x:v>last_used_at</x:v>
+        <x:v>verification_status</x:v>
       </x:c>
       <x:c r="D142" s="25" t="str">
-        <x:v>최근 사용 시각</x:v>
+        <x:v>기억 확인 상태</x:v>
       </x:c>
       <x:c r="E142" s="25" t="str">
-        <x:v>TIMESTAMPTZ</x:v>
+        <x:v>VARCHAR(30)</x:v>
       </x:c>
       <x:c r="F142" s="25" t="str">
-        <x:v>N</x:v>
-      </x:c>
-      <x:c r="G142" s="25" t="str"/>
-      <x:c r="H142" s="25" t="str"/>
+        <x:v>Y</x:v>
+      </x:c>
+      <x:c r="G142" s="25"/>
+      <x:c r="H142" s="25"/>
       <x:c r="I142" s="25" t="str">
-        <x:v>memory.last_used_at에는 대화 문맥에 실제 채택된 최근 시각을 기록하는 값을 저장한다.</x:v>
+        <x:v>memory.verification_status에는 확인 수준과 거절 여부를 표시하는 값을 저장한다.</x:v>
       </x:c>
       <x:c r="J142" s="25" t="str">
-        <x:v>최근 사용 시각은(는) 대화 문맥에 실제 채택된 최근 시각을 기록할 때 조회·검증·갱신한다.</x:v>
+        <x:v>기억 확인 상태은(는) 확인 수준과 거절 여부를 표시할 때 조회·검증·갱신한다.</x:v>
       </x:c>
       <x:c r="K142" s="25" t="str">
-        <x:v>검색 후보였다는 이유만으로 갱신하지 않는다.</x:v>
+        <x:v>REJECTED는 검색에서 제외한다.</x:v>
       </x:c>
       <x:c r="L142" s="25" t="str">
-        <x:v>UTC 2026-07-27T12:00:00Z</x:v>
+        <x:v>USER_CONFIRMED</x:v>
       </x:c>
     </x:row>
     <x:row r="143">
       <x:c r="A143" s="26" t="str">
-        <x:v>care_record</x:v>
+        <x:v>memory</x:v>
       </x:c>
       <x:c r="B143" s="26" t="n">
-        <x:v>1</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C143" s="26" t="str">
-        <x:v>id</x:v>
+        <x:v>lifecycle_status</x:v>
       </x:c>
       <x:c r="D143" s="26" t="str">
-        <x:v>돌봄 기록 ID</x:v>
+        <x:v>기억 수명 상태</x:v>
       </x:c>
       <x:c r="E143" s="26" t="str">
-        <x:v>UUID</x:v>
+        <x:v>VARCHAR(30)</x:v>
       </x:c>
       <x:c r="F143" s="26" t="str">
         <x:v>Y</x:v>
       </x:c>
-      <x:c r="G143" s="26" t="str">
-        <x:v>PK</x:v>
-      </x:c>
-      <x:c r="H143" s="26" t="str"/>
+      <x:c r="G143" s="26"/>
+      <x:c r="H143" s="26"/>
       <x:c r="I143" s="26" t="str">
-        <x:v>care_record.id에는 확정된 돌봄 사실 버전을 식별하는 값을 저장한다.</x:v>
+        <x:v>memory.lifecycle_status에는 활성·분쟁·대체·만료·삭제를 구분하는 값을 저장한다.</x:v>
       </x:c>
       <x:c r="J143" s="26" t="str">
-        <x:v>돌봄 기록 ID은(는) 확정된 돌봄 사실 버전을 식별할 때 조회·검증·갱신한다.</x:v>
+        <x:v>기억 수명 상태은(는) 활성·분쟁·대체·만료·삭제를 구분할 때 조회·검증·갱신한다.</x:v>
       </x:c>
       <x:c r="K143" s="26" t="str">
-        <x:v>같은 의미라도 변경 시 새 ID를 만든다.</x:v>
+        <x:v>ACTIVE만 검색 후보로 사용한다.</x:v>
       </x:c>
       <x:c r="L143" s="26" t="str">
-        <x:v>8f3de8c7-7a04-4c74-977b-223a096dc589</x:v>
+        <x:v>ACTIVE</x:v>
       </x:c>
     </x:row>
     <x:row r="144">
       <x:c r="A144" s="25" t="str">
-        <x:v>care_record</x:v>
+        <x:v>memory</x:v>
       </x:c>
       <x:c r="B144" s="25" t="n">
-        <x:v>2</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C144" s="25" t="str">
-        <x:v>senior_id</x:v>
+        <x:v>visibility</x:v>
       </x:c>
       <x:c r="D144" s="25" t="str">
-        <x:v>시니어 ID</x:v>
+        <x:v>기억 공개 범위</x:v>
       </x:c>
       <x:c r="E144" s="25" t="str">
-        <x:v>UUID</x:v>
+        <x:v>VARCHAR(40)</x:v>
       </x:c>
       <x:c r="F144" s="25" t="str">
         <x:v>Y</x:v>
       </x:c>
-      <x:c r="G144" s="25" t="str">
-        <x:v>FK</x:v>
-      </x:c>
-      <x:c r="H144" s="25" t="str">
-        <x:v>app_user.id</x:v>
-      </x:c>
+      <x:c r="G144" s="25"/>
+      <x:c r="H144" s="25"/>
       <x:c r="I144" s="25" t="str">
-        <x:v>care_record.senior_id에는 돌봄 사실의 소유자를 연결하는 값을 저장한다.</x:v>
+        <x:v>memory.visibility에는 시니어 전용·PRIMARY·전체 보호자 공유를 구분하는 값을 저장한다.</x:v>
       </x:c>
       <x:c r="J144" s="25" t="str">
-        <x:v>시니어 ID은(는) 돌봄 사실의 소유자를 연결할 때 조회·검증·갱신한다.</x:v>
+        <x:v>기억 공개 범위은(는) 시니어 전용·PRIMARY·전체 보호자 공유를 구분할 때 조회·검증·갱신한다.</x:v>
       </x:c>
       <x:c r="K144" s="25" t="str">
-        <x:v>후보·대화 소유자와 일치시킨다.</x:v>
+        <x:v>공유 동의와 활성 관계도 함께 검사한다.</x:v>
       </x:c>
       <x:c r="L144" s="25" t="str">
-        <x:v>a2b64af3-5ee5-42ea-98c5-35ac9de10570</x:v>
+        <x:v>PRIVATE</x:v>
       </x:c>
     </x:row>
     <x:row r="145">
       <x:c r="A145" s="26" t="str">
-        <x:v>care_record</x:v>
+        <x:v>memory</x:v>
       </x:c>
       <x:c r="B145" s="26" t="n">
-        <x:v>3</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C145" s="26" t="str">
-        <x:v>parent_record_id</x:v>
+        <x:v>embedding_status</x:v>
       </x:c>
       <x:c r="D145" s="26" t="str">
-        <x:v>이전 기록 ID</x:v>
+        <x:v>벡터 동기화 상태</x:v>
       </x:c>
       <x:c r="E145" s="26" t="str">
-        <x:v>UUID</x:v>
+        <x:v>VARCHAR(20)</x:v>
       </x:c>
       <x:c r="F145" s="26" t="str">
-        <x:v>N</x:v>
-      </x:c>
-      <x:c r="G145" s="26" t="str">
-        <x:v>SELF FK</x:v>
-      </x:c>
-      <x:c r="H145" s="26" t="str">
-        <x:v>care_record.id</x:v>
-      </x:c>
+        <x:v>Y</x:v>
+      </x:c>
+      <x:c r="G145" s="26" t="str"/>
+      <x:c r="H145" s="26" t="str"/>
       <x:c r="I145" s="26" t="str">
-        <x:v>care_record.parent_record_id에는 변경·취소된 이전 버전을 연결하는 값을 저장한다.</x:v>
+        <x:v>외부 Qdrant 벡터가 기억 본문과 동기화됐는지 나타내는 상태를 저장한다.</x:v>
       </x:c>
       <x:c r="J145" s="26" t="str">
-        <x:v>이전 기록 ID은(는) 변경·취소된 이전 버전을 연결할 때 조회·검증·갱신한다.</x:v>
+        <x:v>검색 가능한 기억 중 PENDING·STALE·FAILED 대상을 재색인한다.</x:v>
       </x:c>
       <x:c r="K145" s="26" t="str">
-        <x:v>기존 돌봄 기록을 덮어쓰지 않고 버전 순환을 금지한다.</x:v>
+        <x:v>기억 벡터 자체는 PostgreSQL에 저장하지 않는다.</x:v>
       </x:c>
       <x:c r="L145" s="26" t="str">
-        <x:v>3f08933a-76c4-4226-809c-f1efcbe47824</x:v>
+        <x:v>SYNCED</x:v>
       </x:c>
     </x:row>
     <x:row r="146">
       <x:c r="A146" s="25" t="str">
-        <x:v>care_record</x:v>
+        <x:v>memory</x:v>
       </x:c>
       <x:c r="B146" s="25" t="n">
-        <x:v>4</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C146" s="25" t="str">
-        <x:v>scenario_id</x:v>
+        <x:v>embedding_synced_at</x:v>
       </x:c>
       <x:c r="D146" s="25" t="str">
-        <x:v>발생 시나리오 ID</x:v>
+        <x:v>벡터 동기화 시각</x:v>
       </x:c>
       <x:c r="E146" s="25" t="str">
-        <x:v>UUID</x:v>
+        <x:v>TIMESTAMPTZ</x:v>
       </x:c>
       <x:c r="F146" s="25" t="str">
         <x:v>N</x:v>
       </x:c>
-      <x:c r="G146" s="25" t="str">
-        <x:v>FK</x:v>
-      </x:c>
-      <x:c r="H146" s="25" t="str">
-        <x:v>scenario.id</x:v>
-      </x:c>
+      <x:c r="G146" s="25" t="str"/>
+      <x:c r="H146" s="25" t="str"/>
       <x:c r="I146" s="25" t="str">
-        <x:v>care_record.scenario_id에는 관찰·알림이 생긴 로봇 흐름을 연결하는 값을 저장한다.</x:v>
+        <x:v>현재 embedding_model로 기억 벡터 반영을 마친 마지막 시각을 저장한다.</x:v>
       </x:c>
       <x:c r="J146" s="25" t="str">
-        <x:v>발생 시나리오 ID은(는) 관찰·알림이 생긴 로봇 흐름을 연결할 때 조회·검증·갱신한다.</x:v>
+        <x:v>동기화 성공 뒤 상태와 함께 갱신한다.</x:v>
       </x:c>
       <x:c r="K146" s="25" t="str">
-        <x:v>온보딩·앱 입력에는 없을 수 있다.</x:v>
+        <x:v>last_used_at이나 마지막 동기화 시도 시각을 대신하지 않는다.</x:v>
       </x:c>
       <x:c r="L146" s="25" t="str">
-        <x:v>6fd94c8c-3903-4a01-a82d-819e0c8edb12</x:v>
+        <x:v>UTC 2026-08-05T05:11:00Z</x:v>
       </x:c>
     </x:row>
     <x:row r="147">
       <x:c r="A147" s="26" t="str">
-        <x:v>care_record</x:v>
+        <x:v>memory</x:v>
       </x:c>
       <x:c r="B147" s="26" t="n">
-        <x:v>5</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C147" s="26" t="str">
-        <x:v>source_conversation_id</x:v>
+        <x:v>embedding_model</x:v>
       </x:c>
       <x:c r="D147" s="26" t="str">
-        <x:v>근거 대화 ID</x:v>
+        <x:v>벡터 모델 식별자</x:v>
       </x:c>
       <x:c r="E147" s="26" t="str">
-        <x:v>UUID</x:v>
+        <x:v>VARCHAR(100)</x:v>
       </x:c>
       <x:c r="F147" s="26" t="str">
         <x:v>N</x:v>
       </x:c>
-      <x:c r="G147" s="26" t="str">
-        <x:v>FK</x:v>
-      </x:c>
-      <x:c r="H147" s="26" t="str">
-        <x:v>conversation.id</x:v>
-      </x:c>
+      <x:c r="G147" s="26" t="str"/>
+      <x:c r="H147" s="26" t="str"/>
       <x:c r="I147" s="26" t="str">
-        <x:v>care_record.source_conversation_id에는 사실을 확인한 대화를 연결하는 값을 저장한다.</x:v>
+        <x:v>Qdrant의 기억 벡터를 생성한 모델 식별자를 저장한다.</x:v>
       </x:c>
       <x:c r="J147" s="26" t="str">
-        <x:v>근거 대화 ID은(는) 사실을 확인한 대화를 연결할 때 조회·검증·갱신한다.</x:v>
+        <x:v>모델 변경 시 기존 SYNCED 행을 STALE 재색인 대상으로 찾는다.</x:v>
       </x:c>
       <x:c r="K147" s="26" t="str">
-        <x:v>앱 직접 입력에는 없을 수 있다.</x:v>
+        <x:v>모델 이름이 같아도 차원 설정이 일치하는지 별도로 확인한다.</x:v>
       </x:c>
       <x:c r="L147" s="26" t="str">
-        <x:v>1a4fe41a-6464-4e7e-b292-9a507333a3fa</x:v>
+        <x:v>embedding-passage</x:v>
       </x:c>
     </x:row>
     <x:row r="148">
       <x:c r="A148" s="25" t="str">
-        <x:v>care_record</x:v>
+        <x:v>memory</x:v>
       </x:c>
       <x:c r="B148" s="25" t="n">
-        <x:v>6</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C148" s="25" t="str">
-        <x:v>source_message_id</x:v>
+        <x:v>source_summary_id</x:v>
       </x:c>
       <x:c r="D148" s="25" t="str">
-        <x:v>근거 메시지 ID</x:v>
+        <x:v>출처 요약 ID</x:v>
       </x:c>
       <x:c r="E148" s="25" t="str">
         <x:v>UUID</x:v>
@@ -6062,33 +6070,33 @@
         <x:v>FK</x:v>
       </x:c>
       <x:c r="H148" s="25" t="str">
-        <x:v>conversation_message.id</x:v>
+        <x:v>conversation_summary.id</x:v>
       </x:c>
       <x:c r="I148" s="25" t="str">
-        <x:v>care_record.source_message_id에는 정확한 근거 발화를 연결하는 값을 저장한다.</x:v>
+        <x:v>memory.source_summary_id에는 기억을 뒷받침한 대화·일간 요약을 연결하는 값을 저장한다.</x:v>
       </x:c>
       <x:c r="J148" s="25" t="str">
-        <x:v>근거 메시지 ID은(는) 정확한 근거 발화를 연결할 때 조회·검증·갱신한다.</x:v>
+        <x:v>출처 요약 ID은(는) 기억을 뒷받침한 대화·일간 요약을 연결할 때 조회·검증·갱신한다.</x:v>
       </x:c>
       <x:c r="K148" s="25" t="str">
-        <x:v>care_record 근거는 Raw 삭제 시 ON DELETE SET NULL로 비운다.</x:v>
+        <x:v>요약 전문을 content에 복제하지 않는다.</x:v>
       </x:c>
       <x:c r="L148" s="25" t="str">
-        <x:v>a6f8cb84-c91c-4a38-a7b6-386ce6aa027f</x:v>
+        <x:v>9cd9cbdd-1e7c-4cbb-9014-4ddfb82b73e0</x:v>
       </x:c>
     </x:row>
     <x:row r="149">
       <x:c r="A149" s="26" t="str">
-        <x:v>care_record</x:v>
+        <x:v>memory</x:v>
       </x:c>
       <x:c r="B149" s="26" t="n">
-        <x:v>7</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C149" s="26" t="str">
-        <x:v>recipient_guardian_id</x:v>
+        <x:v>source_candidate_id</x:v>
       </x:c>
       <x:c r="D149" s="26" t="str">
-        <x:v>수신 보호자 ID</x:v>
+        <x:v>출처 후보 ID</x:v>
       </x:c>
       <x:c r="E149" s="26" t="str">
         <x:v>UUID</x:v>
@@ -6100,193 +6108,189 @@
         <x:v>FK</x:v>
       </x:c>
       <x:c r="H149" s="26" t="str">
-        <x:v>app_user.id</x:v>
+        <x:v>fact_candidate.id</x:v>
       </x:c>
       <x:c r="I149" s="26" t="str">
-        <x:v>care_record.recipient_guardian_id에는 보호자 알림의 지정 수신자를 연결하는 값을 저장한다.</x:v>
+        <x:v>memory.source_candidate_id에는 확인·반영을 통과한 후보를 연결하는 값을 저장한다.</x:v>
       </x:c>
       <x:c r="J149" s="26" t="str">
-        <x:v>수신 보호자 ID은(는) 보호자 알림의 지정 수신자를 연결할 때 조회·검증·갱신한다.</x:v>
+        <x:v>출처 후보 ID은(는) 확인·반영을 통과한 후보를 연결할 때 조회·검증·갱신한다.</x:v>
       </x:c>
       <x:c r="K149" s="26" t="str">
-        <x:v>활성 관계·공유 동의·권한을 검증한다.</x:v>
+        <x:v>유일성으로 중복 기억 생성을 막는다.</x:v>
       </x:c>
       <x:c r="L149" s="26" t="str">
-        <x:v>8e1339cb-b0bf-42df-9a7f-f6592be3e84f</x:v>
+        <x:v>dcd1c7f7-ce8a-405f-a3a5-f2bb25eaac31</x:v>
       </x:c>
     </x:row>
     <x:row r="150">
       <x:c r="A150" s="25" t="str">
-        <x:v>care_record</x:v>
+        <x:v>memory</x:v>
       </x:c>
       <x:c r="B150" s="25" t="n">
-        <x:v>8</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C150" s="25" t="str">
-        <x:v>created_by_user_id</x:v>
+        <x:v>keywords</x:v>
       </x:c>
       <x:c r="D150" s="25" t="str">
-        <x:v>작성 사용자 ID</x:v>
+        <x:v>정확 검색 키워드</x:v>
       </x:c>
       <x:c r="E150" s="25" t="str">
-        <x:v>UUID</x:v>
+        <x:v>TEXT[]</x:v>
       </x:c>
       <x:c r="F150" s="25" t="str">
-        <x:v>N</x:v>
-      </x:c>
-      <x:c r="G150" s="25" t="str">
-        <x:v>FK</x:v>
-      </x:c>
-      <x:c r="H150" s="25" t="str">
-        <x:v>app_user.id</x:v>
-      </x:c>
+        <x:v>Y</x:v>
+      </x:c>
+      <x:c r="G150" s="25"/>
+      <x:c r="H150" s="25"/>
       <x:c r="I150" s="25" t="str">
-        <x:v>care_record.created_by_user_id에는 직접 입력한 시니어 또는 보호자를 연결하는 값을 저장한다.</x:v>
+        <x:v>memory.keywords에는 이름·음식·장소 등 정확 일치 단어를 저장하는 값을 저장한다.</x:v>
       </x:c>
       <x:c r="J150" s="25" t="str">
-        <x:v>작성 사용자 ID은(는) 직접 입력한 시니어 또는 보호자를 연결할 때 조회·검증·갱신한다.</x:v>
+        <x:v>정확 검색 키워드은(는) 이름·음식·장소 등 정확 일치 단어를 저장할 때 조회·검증·갱신한다.</x:v>
       </x:c>
       <x:c r="K150" s="25" t="str">
-        <x:v>AI·로봇·시스템 생성이면 null일 수 있다.</x:v>
+        <x:v>민감 원문 전문이나 무의미한 토큰을 넣지 않는다.</x:v>
       </x:c>
       <x:c r="L150" s="25" t="str">
-        <x:v>a2b64af3-5ee5-42ea-98c5-35ac9de10570</x:v>
+        <x:v>["보리차","따뜻한 음료"]</x:v>
       </x:c>
     </x:row>
     <x:row r="151">
       <x:c r="A151" s="26" t="str">
-        <x:v>care_record</x:v>
+        <x:v>memory</x:v>
       </x:c>
       <x:c r="B151" s="26" t="n">
-        <x:v>9</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C151" s="26" t="str">
-        <x:v>record_type</x:v>
+        <x:v>importance</x:v>
       </x:c>
       <x:c r="D151" s="26" t="str">
-        <x:v>돌봄 기록 유형</x:v>
+        <x:v>기억 중요도</x:v>
       </x:c>
       <x:c r="E151" s="26" t="str">
-        <x:v>VARCHAR(50)</x:v>
+        <x:v>SMALLINT</x:v>
       </x:c>
       <x:c r="F151" s="26" t="str">
         <x:v>Y</x:v>
       </x:c>
-      <x:c r="G151" s="26" t="str"/>
-      <x:c r="H151" s="26" t="str"/>
+      <x:c r="G151" s="26"/>
+      <x:c r="H151" s="26"/>
       <x:c r="I151" s="26" t="str">
-        <x:v>care_record.record_type에는 건강·약·일정·관찰·알림 구조를 선택하는 값을 저장한다.</x:v>
+        <x:v>memory.importance에는 재정렬에 사용할 1~5 중요도를 저장하는 값을 저장한다.</x:v>
       </x:c>
       <x:c r="J151" s="26" t="str">
-        <x:v>돌봄 기록 유형은(는) 건강·약·일정·관찰·알림 구조를 선택할 때 조회·검증·갱신한다.</x:v>
+        <x:v>기억 중요도은(는) 재정렬에 사용할 1~5 중요도를 저장할 때 조회·검증·갱신한다.</x:v>
       </x:c>
       <x:c r="K151" s="26" t="str">
-        <x:v>details JSON Schema와 반드시 일치시킨다.</x:v>
+        <x:v>주관값 하나로 검색 순위를 독점하지 않게 한다.</x:v>
       </x:c>
       <x:c r="L151" s="26" t="str">
-        <x:v>MEDICATION_SCHEDULE</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="152">
       <x:c r="A152" s="25" t="str">
-        <x:v>care_record</x:v>
+        <x:v>memory</x:v>
       </x:c>
       <x:c r="B152" s="25" t="n">
-        <x:v>10</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C152" s="25" t="str">
-        <x:v>status</x:v>
+        <x:v>first_observed_at</x:v>
       </x:c>
       <x:c r="D152" s="25" t="str">
-        <x:v>돌봄 기록 상태</x:v>
+        <x:v>최초 관찰 시각</x:v>
       </x:c>
       <x:c r="E152" s="25" t="str">
-        <x:v>VARCHAR(30)</x:v>
+        <x:v>TIMESTAMPTZ</x:v>
       </x:c>
       <x:c r="F152" s="25" t="str">
         <x:v>Y</x:v>
       </x:c>
-      <x:c r="G152" s="25" t="str"/>
-      <x:c r="H152" s="25" t="str"/>
+      <x:c r="G152" s="25"/>
+      <x:c r="H152" s="25"/>
       <x:c r="I152" s="25" t="str">
-        <x:v>care_record.status에는 유효·완료·취소·대체를 구분하는 값을 저장한다.</x:v>
+        <x:v>memory.first_observed_at에는 사실을 처음 알게 된 시각을 기록하는 값을 저장한다.</x:v>
       </x:c>
       <x:c r="J152" s="25" t="str">
-        <x:v>돌봄 기록 상태은(는) 유효·완료·취소·대체를 구분할 때 조회·검증·갱신한다.</x:v>
+        <x:v>최초 관찰 시각은(는) 사실을 처음 알게 된 시각을 기록할 때 조회·검증·갱신한다.</x:v>
       </x:c>
       <x:c r="K152" s="25" t="str">
-        <x:v>SUPERSEDED 기록을 현재값으로 조회하지 않는다.</x:v>
+        <x:v>기억 행 생성 시각과 다를 수 있다.</x:v>
       </x:c>
       <x:c r="L152" s="25" t="str">
-        <x:v>ACTIVE</x:v>
+        <x:v>UTC 2026-07-20T10:00:00Z</x:v>
       </x:c>
     </x:row>
     <x:row r="153">
       <x:c r="A153" s="26" t="str">
-        <x:v>care_record</x:v>
+        <x:v>memory</x:v>
       </x:c>
       <x:c r="B153" s="26" t="n">
-        <x:v>11</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C153" s="26" t="str">
-        <x:v>details</x:v>
+        <x:v>last_confirmed_at</x:v>
       </x:c>
       <x:c r="D153" s="26" t="str">
-        <x:v>돌봄 상세</x:v>
+        <x:v>최근 확인 시각</x:v>
       </x:c>
       <x:c r="E153" s="26" t="str">
-        <x:v>JSONB</x:v>
+        <x:v>TIMESTAMPTZ</x:v>
       </x:c>
       <x:c r="F153" s="26" t="str">
-        <x:v>Y</x:v>
-      </x:c>
-      <x:c r="G153" s="26" t="str"/>
-      <x:c r="H153" s="26" t="str"/>
+        <x:v>N</x:v>
+      </x:c>
+      <x:c r="G153" s="26"/>
+      <x:c r="H153" s="26"/>
       <x:c r="I153" s="26" t="str">
-        <x:v>care_record.details에는 record_type별 확인된 구조화 사실을 저장하는 값을 저장한다.</x:v>
+        <x:v>memory.last_confirmed_at에는 사실을 마지막으로 재확인한 때를 기록하는 값을 저장한다.</x:v>
       </x:c>
       <x:c r="J153" s="26" t="str">
-        <x:v>돌봄 상세은(는) record_type별 확인된 구조화 사실을 저장할 때 조회·검증·갱신한다.</x:v>
+        <x:v>최근 확인 시각은(는) 사실을 마지막으로 재확인한 때를 기록할 때 조회·검증·갱신한다.</x:v>
       </x:c>
       <x:c r="K153" s="26" t="str">
-        <x:v>외부 응답 전문·미확정 값·의학적 계산을 넣지 않는다.</x:v>
+        <x:v>단순 검색·사용 시각으로 갱신하지 않는다.</x:v>
       </x:c>
       <x:c r="L153" s="26" t="str">
-        <x:v>{"medicationName":"아스피린","localTime":"09:00"}</x:v>
+        <x:v>UTC 2026-07-27T10:15:00Z</x:v>
       </x:c>
     </x:row>
     <x:row r="154">
       <x:c r="A154" s="25" t="str">
-        <x:v>care_record</x:v>
+        <x:v>memory</x:v>
       </x:c>
       <x:c r="B154" s="25" t="n">
-        <x:v>12</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C154" s="25" t="str">
-        <x:v>recurrence</x:v>
+        <x:v>last_used_at</x:v>
       </x:c>
       <x:c r="D154" s="25" t="str">
-        <x:v>반복 규칙</x:v>
+        <x:v>최근 사용 시각</x:v>
       </x:c>
       <x:c r="E154" s="25" t="str">
-        <x:v>JSONB</x:v>
+        <x:v>TIMESTAMPTZ</x:v>
       </x:c>
       <x:c r="F154" s="25" t="str">
         <x:v>N</x:v>
       </x:c>
-      <x:c r="G154" s="25" t="str"/>
-      <x:c r="H154" s="25" t="str"/>
+      <x:c r="G154" s="25"/>
+      <x:c r="H154" s="25"/>
       <x:c r="I154" s="25" t="str">
-        <x:v>care_record.recurrence에는 복약·일정의 반복 패턴을 구조화하는 값을 저장한다.</x:v>
+        <x:v>memory.last_used_at에는 대화 문맥에 실제 채택된 최근 시각을 기록하는 값을 저장한다.</x:v>
       </x:c>
       <x:c r="J154" s="25" t="str">
-        <x:v>반복 규칙은(는) 복약·일정의 반복 패턴을 구조화할 때 조회·검증·갱신한다.</x:v>
+        <x:v>최근 사용 시각은(는) 대화 문맥에 실제 채택된 최근 시각을 기록할 때 조회·검증·갱신한다.</x:v>
       </x:c>
       <x:c r="K154" s="25" t="str">
-        <x:v>반복이 없으면 null이고 미래 발생분을 전부 펼치지 않는다.</x:v>
+        <x:v>검색 후보였다는 이유만으로 갱신하지 않는다.</x:v>
       </x:c>
       <x:c r="L154" s="25" t="str">
-        <x:v>{"frequency":"DAILY","time":"09:00"}</x:v>
+        <x:v>UTC 2026-07-27T12:00:00Z</x:v>
       </x:c>
     </x:row>
     <x:row r="155">
@@ -6294,37 +6298,757 @@
         <x:v>care_record</x:v>
       </x:c>
       <x:c r="B155" s="28" t="n">
-        <x:v>13</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C155" s="28" t="str">
-        <x:v>source_candidate_id</x:v>
+        <x:v>id</x:v>
       </x:c>
       <x:c r="D155" s="28" t="str">
-        <x:v>출처 후보 ID</x:v>
+        <x:v>돌봄 기록 ID</x:v>
       </x:c>
       <x:c r="E155" s="28" t="str">
         <x:v>UUID</x:v>
       </x:c>
       <x:c r="F155" s="28" t="str">
+        <x:v>Y</x:v>
+      </x:c>
+      <x:c r="G155" s="28" t="str">
+        <x:v>PK</x:v>
+      </x:c>
+      <x:c r="H155" s="28"/>
+      <x:c r="I155" s="28" t="str">
+        <x:v>care_record.id에는 확정된 돌봄 사실 버전을 식별하는 값을 저장한다.</x:v>
+      </x:c>
+      <x:c r="J155" s="28" t="str">
+        <x:v>돌봄 기록 ID은(는) 확정된 돌봄 사실 버전을 식별할 때 조회·검증·갱신한다.</x:v>
+      </x:c>
+      <x:c r="K155" s="28" t="str">
+        <x:v>같은 의미라도 변경 시 새 ID를 만든다.</x:v>
+      </x:c>
+      <x:c r="L155" s="28" t="str">
+        <x:v>8f3de8c7-7a04-4c74-977b-223a096dc589</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="156">
+      <x:c r="A156" t="str">
+        <x:v>care_record</x:v>
+      </x:c>
+      <x:c r="B156" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C156" t="str">
+        <x:v>senior_id</x:v>
+      </x:c>
+      <x:c r="D156" t="str">
+        <x:v>시니어 ID</x:v>
+      </x:c>
+      <x:c r="E156" t="str">
+        <x:v>UUID</x:v>
+      </x:c>
+      <x:c r="F156" t="str">
+        <x:v>Y</x:v>
+      </x:c>
+      <x:c r="G156" t="str">
+        <x:v>FK</x:v>
+      </x:c>
+      <x:c r="H156" t="str">
+        <x:v>app_user.id</x:v>
+      </x:c>
+      <x:c r="I156" t="str">
+        <x:v>care_record.senior_id에는 돌봄 사실의 소유자를 연결하는 값을 저장한다.</x:v>
+      </x:c>
+      <x:c r="J156" t="str">
+        <x:v>시니어 ID은(는) 돌봄 사실의 소유자를 연결할 때 조회·검증·갱신한다.</x:v>
+      </x:c>
+      <x:c r="K156" t="str">
+        <x:v>후보·대화 소유자와 일치시킨다.</x:v>
+      </x:c>
+      <x:c r="L156" t="str">
+        <x:v>a2b64af3-5ee5-42ea-98c5-35ac9de10570</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="157">
+      <x:c r="A157" t="str">
+        <x:v>care_record</x:v>
+      </x:c>
+      <x:c r="B157" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C157" t="str">
+        <x:v>parent_record_id</x:v>
+      </x:c>
+      <x:c r="D157" t="str">
+        <x:v>이전 기록 ID</x:v>
+      </x:c>
+      <x:c r="E157" t="str">
+        <x:v>UUID</x:v>
+      </x:c>
+      <x:c r="F157" t="str">
         <x:v>N</x:v>
       </x:c>
-      <x:c r="G155" s="28" t="str">
+      <x:c r="G157" t="str">
+        <x:v>SELF FK</x:v>
+      </x:c>
+      <x:c r="H157" t="str">
+        <x:v>care_record.id</x:v>
+      </x:c>
+      <x:c r="I157" t="str">
+        <x:v>care_record.parent_record_id에는 변경·취소된 이전 버전을 연결하는 값을 저장한다.</x:v>
+      </x:c>
+      <x:c r="J157" t="str">
+        <x:v>이전 기록 ID은(는) 변경·취소된 이전 버전을 연결할 때 조회·검증·갱신한다.</x:v>
+      </x:c>
+      <x:c r="K157" t="str">
+        <x:v>기존 돌봄 기록을 덮어쓰지 않고 버전 순환을 금지한다.</x:v>
+      </x:c>
+      <x:c r="L157" t="str">
+        <x:v>3f08933a-76c4-4226-809c-f1efcbe47824</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="158">
+      <x:c r="A158" t="str">
+        <x:v>care_record</x:v>
+      </x:c>
+      <x:c r="B158" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C158" t="str">
+        <x:v>scenario_id</x:v>
+      </x:c>
+      <x:c r="D158" t="str">
+        <x:v>발생 시나리오 ID</x:v>
+      </x:c>
+      <x:c r="E158" t="str">
+        <x:v>UUID</x:v>
+      </x:c>
+      <x:c r="F158" t="str">
+        <x:v>N</x:v>
+      </x:c>
+      <x:c r="G158" t="str">
         <x:v>FK</x:v>
       </x:c>
-      <x:c r="H155" s="28" t="str">
+      <x:c r="H158" t="str">
+        <x:v>scenario.id</x:v>
+      </x:c>
+      <x:c r="I158" t="str">
+        <x:v>care_record.scenario_id에는 관찰·알림이 생긴 로봇 흐름을 연결하는 값을 저장한다.</x:v>
+      </x:c>
+      <x:c r="J158" t="str">
+        <x:v>발생 시나리오 ID은(는) 관찰·알림이 생긴 로봇 흐름을 연결할 때 조회·검증·갱신한다.</x:v>
+      </x:c>
+      <x:c r="K158" t="str">
+        <x:v>온보딩·앱 입력에는 없을 수 있다.</x:v>
+      </x:c>
+      <x:c r="L158" t="str">
+        <x:v>6fd94c8c-3903-4a01-a82d-819e0c8edb12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="159">
+      <x:c r="A159" t="str">
+        <x:v>care_record</x:v>
+      </x:c>
+      <x:c r="B159" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C159" t="str">
+        <x:v>source_conversation_id</x:v>
+      </x:c>
+      <x:c r="D159" t="str">
+        <x:v>근거 대화 ID</x:v>
+      </x:c>
+      <x:c r="E159" t="str">
+        <x:v>UUID</x:v>
+      </x:c>
+      <x:c r="F159" t="str">
+        <x:v>N</x:v>
+      </x:c>
+      <x:c r="G159" t="str">
+        <x:v>FK</x:v>
+      </x:c>
+      <x:c r="H159" t="str">
+        <x:v>conversation.id</x:v>
+      </x:c>
+      <x:c r="I159" t="str">
+        <x:v>care_record.source_conversation_id에는 사실을 확인한 대화를 연결하는 값을 저장한다.</x:v>
+      </x:c>
+      <x:c r="J159" t="str">
+        <x:v>근거 대화 ID은(는) 사실을 확인한 대화를 연결할 때 조회·검증·갱신한다.</x:v>
+      </x:c>
+      <x:c r="K159" t="str">
+        <x:v>앱 직접 입력에는 없을 수 있다.</x:v>
+      </x:c>
+      <x:c r="L159" t="str">
+        <x:v>1a4fe41a-6464-4e7e-b292-9a507333a3fa</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="160">
+      <x:c r="A160" t="str">
+        <x:v>care_record</x:v>
+      </x:c>
+      <x:c r="B160" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C160" t="str">
+        <x:v>source_message_id</x:v>
+      </x:c>
+      <x:c r="D160" t="str">
+        <x:v>근거 메시지 ID</x:v>
+      </x:c>
+      <x:c r="E160" t="str">
+        <x:v>UUID</x:v>
+      </x:c>
+      <x:c r="F160" t="str">
+        <x:v>N</x:v>
+      </x:c>
+      <x:c r="G160" t="str">
+        <x:v>FK</x:v>
+      </x:c>
+      <x:c r="H160" t="str">
+        <x:v>conversation_message.id</x:v>
+      </x:c>
+      <x:c r="I160" t="str">
+        <x:v>care_record.source_message_id에는 정확한 근거 발화를 연결하는 값을 저장한다.</x:v>
+      </x:c>
+      <x:c r="J160" t="str">
+        <x:v>근거 메시지 ID은(는) 정확한 근거 발화를 연결할 때 조회·검증·갱신한다.</x:v>
+      </x:c>
+      <x:c r="K160" t="str">
+        <x:v>care_record 근거는 Raw 삭제 시 ON DELETE SET NULL로 비운다.</x:v>
+      </x:c>
+      <x:c r="L160" t="str">
+        <x:v>a6f8cb84-c91c-4a38-a7b6-386ce6aa027f</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="161">
+      <x:c r="A161" t="str">
+        <x:v>care_record</x:v>
+      </x:c>
+      <x:c r="B161" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C161" t="str">
+        <x:v>recipient_guardian_id</x:v>
+      </x:c>
+      <x:c r="D161" t="str">
+        <x:v>수신 보호자 ID</x:v>
+      </x:c>
+      <x:c r="E161" t="str">
+        <x:v>UUID</x:v>
+      </x:c>
+      <x:c r="F161" t="str">
+        <x:v>N</x:v>
+      </x:c>
+      <x:c r="G161" t="str">
+        <x:v>FK</x:v>
+      </x:c>
+      <x:c r="H161" t="str">
+        <x:v>app_user.id</x:v>
+      </x:c>
+      <x:c r="I161" t="str">
+        <x:v>care_record.recipient_guardian_id에는 보호자 알림의 지정 수신자를 연결하는 값을 저장한다.</x:v>
+      </x:c>
+      <x:c r="J161" t="str">
+        <x:v>수신 보호자 ID은(는) 보호자 알림의 지정 수신자를 연결할 때 조회·검증·갱신한다.</x:v>
+      </x:c>
+      <x:c r="K161" t="str">
+        <x:v>활성 관계·공유 동의·권한을 검증한다.</x:v>
+      </x:c>
+      <x:c r="L161" t="str">
+        <x:v>8e1339cb-b0bf-42df-9a7f-f6592be3e84f</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="162">
+      <x:c r="A162" t="str">
+        <x:v>care_record</x:v>
+      </x:c>
+      <x:c r="B162" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C162" t="str">
+        <x:v>created_by_user_id</x:v>
+      </x:c>
+      <x:c r="D162" t="str">
+        <x:v>작성 사용자 ID</x:v>
+      </x:c>
+      <x:c r="E162" t="str">
+        <x:v>UUID</x:v>
+      </x:c>
+      <x:c r="F162" t="str">
+        <x:v>N</x:v>
+      </x:c>
+      <x:c r="G162" t="str">
+        <x:v>FK</x:v>
+      </x:c>
+      <x:c r="H162" t="str">
+        <x:v>app_user.id</x:v>
+      </x:c>
+      <x:c r="I162" t="str">
+        <x:v>care_record.created_by_user_id에는 직접 입력한 시니어 또는 보호자를 연결하는 값을 저장한다.</x:v>
+      </x:c>
+      <x:c r="J162" t="str">
+        <x:v>작성 사용자 ID은(는) 직접 입력한 시니어 또는 보호자를 연결할 때 조회·검증·갱신한다.</x:v>
+      </x:c>
+      <x:c r="K162" t="str">
+        <x:v>AI·로봇·시스템 생성이면 null일 수 있다.</x:v>
+      </x:c>
+      <x:c r="L162" t="str">
+        <x:v>a2b64af3-5ee5-42ea-98c5-35ac9de10570</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="163">
+      <x:c r="A163" t="str">
+        <x:v>care_record</x:v>
+      </x:c>
+      <x:c r="B163" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C163" t="str">
+        <x:v>record_type</x:v>
+      </x:c>
+      <x:c r="D163" t="str">
+        <x:v>돌봄 기록 유형</x:v>
+      </x:c>
+      <x:c r="E163" t="str">
+        <x:v>VARCHAR(50)</x:v>
+      </x:c>
+      <x:c r="F163" t="str">
+        <x:v>Y</x:v>
+      </x:c>
+      <x:c r="G163"/>
+      <x:c r="H163"/>
+      <x:c r="I163" t="str">
+        <x:v>care_record.record_type에는 건강·약·일정·관찰·알림 구조를 선택하는 값을 저장한다.</x:v>
+      </x:c>
+      <x:c r="J163" t="str">
+        <x:v>돌봄 기록 유형은(는) 건강·약·일정·관찰·알림 구조를 선택할 때 조회·검증·갱신한다.</x:v>
+      </x:c>
+      <x:c r="K163" t="str">
+        <x:v>details JSON Schema와 반드시 일치시킨다.</x:v>
+      </x:c>
+      <x:c r="L163" t="str">
+        <x:v>MEDICATION_SCHEDULE</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="164" ht="30" hidden="0" customHeight="1">
+      <x:c r="A164" t="str">
+        <x:v>care_record</x:v>
+      </x:c>
+      <x:c r="B164" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C164" t="str">
+        <x:v>status</x:v>
+      </x:c>
+      <x:c r="D164" t="str">
+        <x:v>돌봄 기록 상태</x:v>
+      </x:c>
+      <x:c r="E164" t="str">
+        <x:v>VARCHAR(30)</x:v>
+      </x:c>
+      <x:c r="F164" t="str">
+        <x:v>Y</x:v>
+      </x:c>
+      <x:c r="G164"/>
+      <x:c r="H164"/>
+      <x:c r="I164" t="str">
+        <x:v>care_record.status에는 유효·완료·취소·대체를 구분하는 값을 저장한다.</x:v>
+      </x:c>
+      <x:c r="J164" t="str">
+        <x:v>돌봄 기록 상태은(는) 유효·완료·취소·대체를 구분할 때 조회·검증·갱신한다.</x:v>
+      </x:c>
+      <x:c r="K164" t="str">
+        <x:v>SUPERSEDED 기록을 현재값으로 조회하지 않는다.</x:v>
+      </x:c>
+      <x:c r="L164" t="str">
+        <x:v>ACTIVE</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="165" ht="30" hidden="0" customHeight="1">
+      <x:c r="A165" t="str">
+        <x:v>care_record</x:v>
+      </x:c>
+      <x:c r="B165" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C165" t="str">
+        <x:v>details</x:v>
+      </x:c>
+      <x:c r="D165" t="str">
+        <x:v>돌봄 상세</x:v>
+      </x:c>
+      <x:c r="E165" t="str">
+        <x:v>JSONB</x:v>
+      </x:c>
+      <x:c r="F165" t="str">
+        <x:v>Y</x:v>
+      </x:c>
+      <x:c r="G165"/>
+      <x:c r="H165"/>
+      <x:c r="I165" t="str">
+        <x:v>care_record.details에는 record_type별 확인된 구조화 사실을 저장하는 값을 저장한다.</x:v>
+      </x:c>
+      <x:c r="J165" t="str">
+        <x:v>돌봄 상세은(는) record_type별 확인된 구조화 사실을 저장할 때 조회·검증·갱신한다.</x:v>
+      </x:c>
+      <x:c r="K165" t="str">
+        <x:v>외부 응답 전문·미확정 값·의학적 계산을 넣지 않는다.</x:v>
+      </x:c>
+      <x:c r="L165" t="str">
+        <x:v>{"medicationName":"아스피린","localTime":"09:00"}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="166" ht="30" hidden="0" customHeight="1">
+      <x:c r="A166" t="str">
+        <x:v>care_record</x:v>
+      </x:c>
+      <x:c r="B166" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C166" t="str">
+        <x:v>recurrence</x:v>
+      </x:c>
+      <x:c r="D166" t="str">
+        <x:v>반복 규칙</x:v>
+      </x:c>
+      <x:c r="E166" t="str">
+        <x:v>JSONB</x:v>
+      </x:c>
+      <x:c r="F166" t="str">
+        <x:v>N</x:v>
+      </x:c>
+      <x:c r="G166"/>
+      <x:c r="H166"/>
+      <x:c r="I166" t="str">
+        <x:v>care_record.recurrence에는 복약·일정의 반복 패턴을 구조화하는 값을 저장한다.</x:v>
+      </x:c>
+      <x:c r="J166" t="str">
+        <x:v>반복 규칙은(는) 복약·일정의 반복 패턴을 구조화할 때 조회·검증·갱신한다.</x:v>
+      </x:c>
+      <x:c r="K166" t="str">
+        <x:v>반복이 없으면 null이고 미래 발생분을 전부 펼치지 않는다.</x:v>
+      </x:c>
+      <x:c r="L166" t="str">
+        <x:v>{"frequency":"DAILY","time":"09:00"}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="167" ht="30" hidden="0" customHeight="1">
+      <x:c r="A167" t="str">
+        <x:v>care_record</x:v>
+      </x:c>
+      <x:c r="B167" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C167" t="str">
+        <x:v>source_candidate_id</x:v>
+      </x:c>
+      <x:c r="D167" t="str">
+        <x:v>출처 후보 ID</x:v>
+      </x:c>
+      <x:c r="E167" t="str">
+        <x:v>UUID</x:v>
+      </x:c>
+      <x:c r="F167" t="str">
+        <x:v>N</x:v>
+      </x:c>
+      <x:c r="G167" t="str">
+        <x:v>FK</x:v>
+      </x:c>
+      <x:c r="H167" t="str">
         <x:v>fact_candidate.id</x:v>
       </x:c>
-      <x:c r="I155" s="28" t="str">
+      <x:c r="I167" t="str">
         <x:v>care_record.source_candidate_id에는 최종 반영을 만든 후보를 연결하는 값을 저장한다.</x:v>
       </x:c>
-      <x:c r="J155" s="28" t="str">
+      <x:c r="J167" t="str">
         <x:v>출처 후보 ID은(는) 최종 반영을 만든 후보를 연결할 때 조회·검증·갱신한다.</x:v>
       </x:c>
-      <x:c r="K155" s="28" t="str">
+      <x:c r="K167" t="str">
         <x:v>유일성으로 중복 돌봄 기록 생성을 막는다.</x:v>
       </x:c>
-      <x:c r="L155" s="28" t="str">
+      <x:c r="L167" t="str">
         <x:v>dcd1c7f7-ce8a-405f-a3a5-f2bb25eaac31</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="168" ht="30" hidden="0" customHeight="1">
+      <x:c r="A168" t="str">
+        <x:v>wake_word_trigger_receipt</x:v>
+      </x:c>
+      <x:c r="B168" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C168" t="str">
+        <x:v>event_id</x:v>
+      </x:c>
+      <x:c r="D168" t="str">
+        <x:v>웨이크 이벤트 ID</x:v>
+      </x:c>
+      <x:c r="E168" t="str">
+        <x:v>VARCHAR(64)</x:v>
+      </x:c>
+      <x:c r="F168" t="str">
+        <x:v>Y</x:v>
+      </x:c>
+      <x:c r="G168" t="str">
+        <x:v>PK</x:v>
+      </x:c>
+      <x:c r="H168" t="str"/>
+      <x:c r="I168" t="str">
+        <x:v>AI가 발행한 WAKE_WORD_DETECTED eventId를 영속 멱등 키로 저장한다.</x:v>
+      </x:c>
+      <x:c r="J168" t="str">
+        <x:v>같은 사건의 순차·동시 재전송과 Backend 재시작 중복을 차단한다.</x:v>
+      </x:c>
+      <x:c r="K168" t="str">
+        <x:v>다른 시나리오의 external_event_id 전체를 전역 UNIQUE로 만들지 않는다.</x:v>
+      </x:c>
+      <x:c r="L168" t="str">
+        <x:v>01K1WAKE7F5M2N1Q9R6S3T8VXC</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="169" ht="30" hidden="0" customHeight="1">
+      <x:c r="A169" t="str">
+        <x:v>wake_word_trigger_receipt</x:v>
+      </x:c>
+      <x:c r="B169" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C169" t="str">
+        <x:v>robot_device_id</x:v>
+      </x:c>
+      <x:c r="D169" t="str">
+        <x:v>발행 로봇 deviceId</x:v>
+      </x:c>
+      <x:c r="E169" t="str">
+        <x:v>VARCHAR(64)</x:v>
+      </x:c>
+      <x:c r="F169" t="str">
+        <x:v>Y</x:v>
+      </x:c>
+      <x:c r="G169" t="str">
+        <x:v>논리 참조</x:v>
+      </x:c>
+      <x:c r="H169" t="str">
+        <x:v>robot.device_id</x:v>
+      </x:c>
+      <x:c r="I169" t="str">
+        <x:v>MQTT 토픽과 본문에서 검증된 발행 Robot deviceId를 저장한다.</x:v>
+      </x:c>
+      <x:c r="J169" t="str">
+        <x:v>중복 eventId가 같은 발행 Robot 이벤트인지 검증하고 Robot을 권위 조회한다.</x:v>
+      </x:c>
+      <x:c r="K169" t="str">
+        <x:v>DB UUID robot.id로 해석하지 않는다.</x:v>
+      </x:c>
+      <x:c r="L169" t="str">
+        <x:v>bomi-AA001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="170" ht="30" hidden="0" customHeight="1">
+      <x:c r="A170" t="str">
+        <x:v>wake_word_trigger_receipt</x:v>
+      </x:c>
+      <x:c r="B170" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C170" t="str">
+        <x:v>occurred_at</x:v>
+      </x:c>
+      <x:c r="D170" t="str">
+        <x:v>감지 시각</x:v>
+      </x:c>
+      <x:c r="E170" t="str">
+        <x:v>TIMESTAMPTZ</x:v>
+      </x:c>
+      <x:c r="F170" t="str">
+        <x:v>Y</x:v>
+      </x:c>
+      <x:c r="G170" t="str"/>
+      <x:c r="H170" t="str"/>
+      <x:c r="I170" t="str">
+        <x:v>AI가 웨이크워드를 확정한 occurredAt을 저장한다.</x:v>
+      </x:c>
+      <x:c r="J170" t="str">
+        <x:v>같은 eventId가 같은 논리 이벤트인지 최소 문맥을 비교한다.</x:v>
+      </x:c>
+      <x:c r="K170" t="str">
+        <x:v>Backend 수신 시각으로 바꾸지 않는다.</x:v>
+      </x:c>
+      <x:c r="L170" t="n">
+        <x:v>46239.208333333336</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="171" ht="30" hidden="0" customHeight="1">
+      <x:c r="A171" t="str">
+        <x:v>wake_word_trigger_receipt</x:v>
+      </x:c>
+      <x:c r="B171" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C171" t="str">
+        <x:v>keyword</x:v>
+      </x:c>
+      <x:c r="D171" t="str">
+        <x:v>감지 키워드</x:v>
+      </x:c>
+      <x:c r="E171" t="str">
+        <x:v>VARCHAR(20)</x:v>
+      </x:c>
+      <x:c r="F171" t="str">
+        <x:v>Y</x:v>
+      </x:c>
+      <x:c r="G171" t="str"/>
+      <x:c r="H171" t="str"/>
+      <x:c r="I171" t="str">
+        <x:v>AI가 확정한 1~20자 호출 키워드만 저장한다.</x:v>
+      </x:c>
+      <x:c r="J171" t="str">
+        <x:v>eventId 재사용 검증과 호출 트리거 이력에 사용한다.</x:v>
+      </x:c>
+      <x:c r="K171" t="str">
+        <x:v>원본 음성·전체 STT 문장을 넣지 않는다.</x:v>
+      </x:c>
+      <x:c r="L171" t="str">
+        <x:v>보미야</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="172" ht="30" hidden="0" customHeight="1">
+      <x:c r="A172" t="str">
+        <x:v>wake_word_trigger_receipt</x:v>
+      </x:c>
+      <x:c r="B172" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C172" t="str">
+        <x:v>confidence</x:v>
+      </x:c>
+      <x:c r="D172" t="str">
+        <x:v>감지 신뢰도</x:v>
+      </x:c>
+      <x:c r="E172" t="str">
+        <x:v>DOUBLE PRECISION</x:v>
+      </x:c>
+      <x:c r="F172" t="str">
+        <x:v>N</x:v>
+      </x:c>
+      <x:c r="G172" t="str"/>
+      <x:c r="H172" t="str"/>
+      <x:c r="I172" t="str">
+        <x:v>AI가 선택적으로 보낸 0 이상 1 이하 신뢰도를 저장한다.</x:v>
+      </x:c>
+      <x:c r="J172" t="str">
+        <x:v>수신된 경우 같은 eventId 문맥 비교와 운영 진단에 사용한다.</x:v>
+      </x:c>
+      <x:c r="K172" t="str">
+        <x:v>누락을 0으로 바꾸거나 Backend가 추정하지 않는다.</x:v>
+      </x:c>
+      <x:c r="L172" t="n">
+        <x:v>0.92</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="173" ht="30" hidden="0" customHeight="1">
+      <x:c r="A173" t="str">
+        <x:v>wake_word_trigger_receipt</x:v>
+      </x:c>
+      <x:c r="B173" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C173" t="str">
+        <x:v>disposition</x:v>
+      </x:c>
+      <x:c r="D173" t="str">
+        <x:v>처리 결정</x:v>
+      </x:c>
+      <x:c r="E173" t="str">
+        <x:v>VARCHAR(40)</x:v>
+      </x:c>
+      <x:c r="F173" t="str">
+        <x:v>Y</x:v>
+      </x:c>
+      <x:c r="G173" t="str"/>
+      <x:c r="H173" t="str"/>
+      <x:c r="I173" t="str">
+        <x:v>호출 트리거의 수락 또는 안정적인 거절 결정을 저장한다.</x:v>
+      </x:c>
+      <x:c r="J173" t="str">
+        <x:v>재전송 때 최초 결정을 그대로 적용해 뒤늦은 이동 시작을 막는다.</x:v>
+      </x:c>
+      <x:c r="K173" t="str">
+        <x:v>RECEIVED는 처리 트랜잭션 중간 상태이며 최종 성공으로 해석하지 않는다.</x:v>
+      </x:c>
+      <x:c r="L173" t="str">
+        <x:v>ACCEPTED</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="174" ht="30" hidden="0" customHeight="1">
+      <x:c r="A174" t="str">
+        <x:v>wake_word_trigger_receipt</x:v>
+      </x:c>
+      <x:c r="B174" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C174" t="str">
+        <x:v>scenario_id</x:v>
+      </x:c>
+      <x:c r="D174" t="str">
+        <x:v>수락 시나리오 ID</x:v>
+      </x:c>
+      <x:c r="E174" t="str">
+        <x:v>UUID</x:v>
+      </x:c>
+      <x:c r="F174" t="str">
+        <x:v>N</x:v>
+      </x:c>
+      <x:c r="G174" t="str">
+        <x:v>논리 참조</x:v>
+      </x:c>
+      <x:c r="H174" t="str">
+        <x:v>scenario.id</x:v>
+      </x:c>
+      <x:c r="I174" t="str">
+        <x:v>수락된 이벤트로 생성한 WAKE_WORD_CALL scenario.id를 저장한다.</x:v>
+      </x:c>
+      <x:c r="J174" t="str">
+        <x:v>ACCEPTED일 때 시나리오 이력을 연결한다.</x:v>
+      </x:c>
+      <x:c r="K174" t="str">
+        <x:v>거절 결정에는 null이고 대화 ID로 재사용하지 않는다.</x:v>
+      </x:c>
+      <x:c r="L174" t="str">
+        <x:v>6fd94c8c-3903-4a01-a82d-819e0c8edb12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="175" ht="30" hidden="0" customHeight="1">
+      <x:c r="A175" t="str">
+        <x:v>wake_word_trigger_receipt</x:v>
+      </x:c>
+      <x:c r="B175" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C175" t="str">
+        <x:v>created_at</x:v>
+      </x:c>
+      <x:c r="D175" t="str">
+        <x:v>처리 영수증 생성 시각</x:v>
+      </x:c>
+      <x:c r="E175" t="str">
+        <x:v>TIMESTAMPTZ</x:v>
+      </x:c>
+      <x:c r="F175" t="str">
+        <x:v>Y</x:v>
+      </x:c>
+      <x:c r="G175" t="str"/>
+      <x:c r="H175" t="str"/>
+      <x:c r="I175" t="str">
+        <x:v>Backend가 이벤트 처리 영수증을 만든 시각을 저장한다.</x:v>
+      </x:c>
+      <x:c r="J175" t="str">
+        <x:v>멱등 처리 이력의 생성 순서와 운영 진단에 사용한다.</x:v>
+      </x:c>
+      <x:c r="K175" t="str">
+        <x:v>AI occurredAt과 구분한다.</x:v>
+      </x:c>
+      <x:c r="L175" t="str">
+        <x:v>UTC 2026-08-05T05:00:01Z</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -7018,6 +7742,186 @@
         <x:v>DB CHECK</x:v>
       </x:c>
     </x:row>
+    <x:row r="37" ht="24" hidden="0" customHeight="1">
+      <x:c r="A37" t="str">
+        <x:v>pk_wake_word_trigger_receipt</x:v>
+      </x:c>
+      <x:c r="B37" t="str">
+        <x:v>PK</x:v>
+      </x:c>
+      <x:c r="C37" t="str">
+        <x:v>wake_word_trigger_receipt.event_id</x:v>
+      </x:c>
+      <x:c r="D37" t="str">
+        <x:v>WAKE_WORD_DETECTED eventId 기본키</x:v>
+      </x:c>
+      <x:c r="E37" t="str">
+        <x:v>재시작과 QoS 1 재전송에도 처리 결정 하나</x:v>
+      </x:c>
+      <x:c r="F37" t="str">
+        <x:v>DB PRIMARY KEY</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" ht="24" hidden="0" customHeight="1">
+      <x:c r="A38" t="str">
+        <x:v>ck_scenario_active_navigation_pair</x:v>
+      </x:c>
+      <x:c r="B38" t="str">
+        <x:v>조건</x:v>
+      </x:c>
+      <x:c r="C38" t="str">
+        <x:v>scenario.active_navigation_command_id/target</x:v>
+      </x:c>
+      <x:c r="D38" t="str">
+        <x:v>commandId와 target은 함께 존재하거나 함께 null</x:v>
+      </x:c>
+      <x:c r="E38" t="str">
+        <x:v>부분 상관정보로 잘못된 결과를 받는 문제 방지</x:v>
+      </x:c>
+      <x:c r="F38" t="str">
+        <x:v>DB CHECK</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" ht="24" hidden="0" customHeight="1">
+      <x:c r="A39" t="str">
+        <x:v>ck_scenario_active_navigation_target</x:v>
+      </x:c>
+      <x:c r="B39" t="str">
+        <x:v>허용 값</x:v>
+      </x:c>
+      <x:c r="C39" t="str">
+        <x:v>scenario.active_navigation_target</x:v>
+      </x:c>
+      <x:c r="D39" t="str">
+        <x:v>LIVING_ROOM·ENTRANCE·DEFAULT만 허용</x:v>
+      </x:c>
+      <x:c r="E39" t="str">
+        <x:v>합의되지 않은 이동 목적지 저장 방지</x:v>
+      </x:c>
+      <x:c r="F39" t="str">
+        <x:v>DB CHECK</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" ht="24" hidden="0" customHeight="1">
+      <x:c r="A40" t="str">
+        <x:v>ck_scenario_trigger_context_object</x:v>
+      </x:c>
+      <x:c r="B40" t="str">
+        <x:v>JSON 구조</x:v>
+      </x:c>
+      <x:c r="C40" t="str">
+        <x:v>scenario.trigger_context</x:v>
+      </x:c>
+      <x:c r="D40" t="str">
+        <x:v>null 또는 JSON object</x:v>
+      </x:c>
+      <x:c r="E40" t="str">
+        <x:v>호출 트리거의 구조화된 최소 문맥 보장</x:v>
+      </x:c>
+      <x:c r="F40" t="str">
+        <x:v>DB CHECK</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" ht="24" hidden="0" customHeight="1">
+      <x:c r="A41" t="str">
+        <x:v>ck_scenario_wake_word_external_event</x:v>
+      </x:c>
+      <x:c r="B41" t="str">
+        <x:v>조건</x:v>
+      </x:c>
+      <x:c r="C41" t="str">
+        <x:v>scenario.external_event_id</x:v>
+      </x:c>
+      <x:c r="D41" t="str">
+        <x:v>WAKE_WORD_CALL이면 MQTT eventId 필수</x:v>
+      </x:c>
+      <x:c r="E41" t="str">
+        <x:v>호출 시나리오가 영속 멱등 키 없이 생성되는 경로 차단</x:v>
+      </x:c>
+      <x:c r="F41" t="str">
+        <x:v>DB CHECK</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" ht="24" hidden="0" customHeight="1">
+      <x:c r="A42" t="str">
+        <x:v>uq_scenario_wake_word_event</x:v>
+      </x:c>
+      <x:c r="B42" t="str">
+        <x:v>부분 유일</x:v>
+      </x:c>
+      <x:c r="C42" t="str">
+        <x:v>scenario.external_event_id</x:v>
+      </x:c>
+      <x:c r="D42" t="str">
+        <x:v>scenario_type='WAKE_WORD_CALL'인 non-null eventId는 하나</x:v>
+      </x:c>
+      <x:c r="E42" t="str">
+        <x:v>수락된 동일 호출의 시나리오 중복 방지</x:v>
+      </x:c>
+      <x:c r="F42" t="str">
+        <x:v>DB UNIQUE INDEX</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" ht="24" hidden="0" customHeight="1">
+      <x:c r="A43" t="str">
+        <x:v>uq_scenario_one_active_per_senior</x:v>
+      </x:c>
+      <x:c r="B43" t="str">
+        <x:v>부분 유일</x:v>
+      </x:c>
+      <x:c r="C43" t="str">
+        <x:v>scenario.senior_id</x:v>
+      </x:c>
+      <x:c r="D43" t="str">
+        <x:v>종료 상태가 아닌 시나리오는 시니어당 하나</x:v>
+      </x:c>
+      <x:c r="E43" t="str">
+        <x:v>서로 다른 동시 시작도 이동 흐름 하나로 제한</x:v>
+      </x:c>
+      <x:c r="F43" t="str">
+        <x:v>DB UNIQUE INDEX</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" ht="24" hidden="0" customHeight="1">
+      <x:c r="A44" t="str">
+        <x:v>ck_wake_word_trigger_confidence</x:v>
+      </x:c>
+      <x:c r="B44" t="str">
+        <x:v>범위</x:v>
+      </x:c>
+      <x:c r="C44" t="str">
+        <x:v>wake_word_trigger_receipt.confidence</x:v>
+      </x:c>
+      <x:c r="D44" t="str">
+        <x:v>null 또는 0 이상 1 이하</x:v>
+      </x:c>
+      <x:c r="E44" t="str">
+        <x:v>유효하지 않은 감지 신뢰도 저장 방지</x:v>
+      </x:c>
+      <x:c r="F44" t="str">
+        <x:v>DB CHECK</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" ht="24" hidden="0" customHeight="1">
+      <x:c r="A45" t="str">
+        <x:v>ck_wake_word_trigger_resolution</x:v>
+      </x:c>
+      <x:c r="B45" t="str">
+        <x:v>조건</x:v>
+      </x:c>
+      <x:c r="C45" t="str">
+        <x:v>wake_word_trigger_receipt</x:v>
+      </x:c>
+      <x:c r="D45" t="str">
+        <x:v>ACCEPTED만 scenario_id 필수, 거절은 null</x:v>
+      </x:c>
+      <x:c r="E45" t="str">
+        <x:v>처리 결정과 생성 시나리오 연결의 모순 방지</x:v>
+      </x:c>
+      <x:c r="F45" t="str">
+        <x:v>DB CHECK</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:F1"/>
@@ -7131,79 +8035,79 @@
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="25" t="str">
-        <x:v>idx_scenario_external_event</x:v>
+        <x:v>idx_conversation_senior_started</x:v>
       </x:c>
       <x:c r="B8" s="25" t="str">
-        <x:v>scenario</x:v>
+        <x:v>conversation</x:v>
       </x:c>
       <x:c r="C8" s="25" t="str">
-        <x:v>external_event_id</x:v>
+        <x:v>senior_id, started_at DESC</x:v>
       </x:c>
       <x:c r="D8" s="25" t="str">
-        <x:v>미확정</x:v>
+        <x:v>N</x:v>
       </x:c>
       <x:c r="E8" s="25" t="str">
-        <x:v>같은 시작 사건의 시나리오 확인</x:v>
+        <x:v>시니어 최근 대화 목록</x:v>
       </x:c>
       <x:c r="F8" s="25" t="str">
-        <x:v>eventId 유일성 범위 합의 후</x:v>
+        <x:v>대화 구현 시</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="26" t="str">
-        <x:v>idx_conversation_senior_started</x:v>
+        <x:v>idx_conversation_expiry</x:v>
       </x:c>
       <x:c r="B9" s="26" t="str">
         <x:v>conversation</x:v>
       </x:c>
       <x:c r="C9" s="26" t="str">
-        <x:v>senior_id, started_at DESC</x:v>
+        <x:v>raw_messages_expires_at</x:v>
       </x:c>
       <x:c r="D9" s="26" t="str">
         <x:v>N</x:v>
       </x:c>
       <x:c r="E9" s="26" t="str">
-        <x:v>시니어 최근 대화 목록</x:v>
+        <x:v>Raw 보존 만료 후보 조회</x:v>
       </x:c>
       <x:c r="F9" s="26" t="str">
-        <x:v>대화 구현 시</x:v>
+        <x:v>보존 배치 구현 시</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="25" t="str">
-        <x:v>idx_conversation_expiry</x:v>
+        <x:v>idx_message_conversation_sequence</x:v>
       </x:c>
       <x:c r="B10" s="25" t="str">
-        <x:v>conversation</x:v>
+        <x:v>conversation_message</x:v>
       </x:c>
       <x:c r="C10" s="25" t="str">
-        <x:v>raw_messages_expires_at</x:v>
+        <x:v>conversation_id, sequence_no</x:v>
       </x:c>
       <x:c r="D10" s="25" t="str">
-        <x:v>N</x:v>
+        <x:v>Y</x:v>
       </x:c>
       <x:c r="E10" s="25" t="str">
-        <x:v>Raw 보존 만료 후보 조회</x:v>
+        <x:v>현재 대화 최근 N개·전체 순서 조회</x:v>
       </x:c>
       <x:c r="F10" s="25" t="str">
-        <x:v>보존 배치 구현 시</x:v>
+        <x:v>메시지 구현 시</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="26" t="str">
-        <x:v>idx_message_conversation_sequence</x:v>
+        <x:v>idx_message_conversation_occurred</x:v>
       </x:c>
       <x:c r="B11" s="26" t="str">
         <x:v>conversation_message</x:v>
       </x:c>
       <x:c r="C11" s="26" t="str">
-        <x:v>conversation_id, sequence_no</x:v>
+        <x:v>conversation_id, occurred_at</x:v>
       </x:c>
       <x:c r="D11" s="26" t="str">
-        <x:v>Y</x:v>
+        <x:v>N</x:v>
       </x:c>
       <x:c r="E11" s="26" t="str">
-        <x:v>현재 대화 최근 N개·전체 순서 조회</x:v>
+        <x:v>대화 시간 범위 조회</x:v>
       </x:c>
       <x:c r="F11" s="26" t="str">
         <x:v>메시지 구현 시</x:v>
@@ -7211,59 +8115,59 @@
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="25" t="str">
-        <x:v>idx_message_conversation_occurred</x:v>
+        <x:v>idx_message_occurred</x:v>
       </x:c>
       <x:c r="B12" s="25" t="str">
         <x:v>conversation_message</x:v>
       </x:c>
       <x:c r="C12" s="25" t="str">
-        <x:v>conversation_id, occurred_at</x:v>
+        <x:v>occurred_at</x:v>
       </x:c>
       <x:c r="D12" s="25" t="str">
         <x:v>N</x:v>
       </x:c>
       <x:c r="E12" s="25" t="str">
-        <x:v>대화 시간 범위 조회</x:v>
+        <x:v>사용자 현지 오늘 메시지 UTC 범위 조회</x:v>
       </x:c>
       <x:c r="F12" s="25" t="str">
-        <x:v>메시지 구현 시</x:v>
+        <x:v>일간 요약 구현 시</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="26" t="str">
-        <x:v>idx_message_occurred</x:v>
+        <x:v>idx_summary_senior_generated</x:v>
       </x:c>
       <x:c r="B13" s="26" t="str">
-        <x:v>conversation_message</x:v>
+        <x:v>conversation_summary</x:v>
       </x:c>
       <x:c r="C13" s="26" t="str">
-        <x:v>occurred_at</x:v>
+        <x:v>senior_id, generated_at DESC</x:v>
       </x:c>
       <x:c r="D13" s="26" t="str">
         <x:v>N</x:v>
       </x:c>
       <x:c r="E13" s="26" t="str">
-        <x:v>사용자 현지 오늘 메시지 UTC 범위 조회</x:v>
+        <x:v>최근 생성 요약 조회</x:v>
       </x:c>
       <x:c r="F13" s="26" t="str">
-        <x:v>일간 요약 구현 시</x:v>
+        <x:v>요약 구현 시</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="25" t="str">
-        <x:v>idx_summary_senior_generated</x:v>
+        <x:v>idx_summary_conversation</x:v>
       </x:c>
       <x:c r="B14" s="25" t="str">
         <x:v>conversation_summary</x:v>
       </x:c>
       <x:c r="C14" s="25" t="str">
-        <x:v>senior_id, generated_at DESC</x:v>
+        <x:v>conversation_id, summary_type</x:v>
       </x:c>
       <x:c r="D14" s="25" t="str">
         <x:v>N</x:v>
       </x:c>
       <x:c r="E14" s="25" t="str">
-        <x:v>최근 생성 요약 조회</x:v>
+        <x:v>현재 대화 요약 조회</x:v>
       </x:c>
       <x:c r="F14" s="25" t="str">
         <x:v>요약 구현 시</x:v>
@@ -7271,182 +8175,202 @@
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="26" t="str">
-        <x:v>idx_summary_conversation</x:v>
+        <x:v>idx_candidate_senior_status</x:v>
       </x:c>
       <x:c r="B15" s="26" t="str">
-        <x:v>conversation_summary</x:v>
+        <x:v>fact_candidate</x:v>
       </x:c>
       <x:c r="C15" s="26" t="str">
-        <x:v>conversation_id, summary_type</x:v>
+        <x:v>senior_id, status, updated_at</x:v>
       </x:c>
       <x:c r="D15" s="26" t="str">
         <x:v>N</x:v>
       </x:c>
       <x:c r="E15" s="26" t="str">
-        <x:v>현재 대화 요약 조회</x:v>
+        <x:v>시니어의 활성 재질의·확인 후보 조회</x:v>
       </x:c>
       <x:c r="F15" s="26" t="str">
-        <x:v>요약 구현 시</x:v>
+        <x:v>후보 구현 시</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="25" t="str">
-        <x:v>idx_candidate_senior_status</x:v>
+        <x:v>idx_candidate_coordination</x:v>
       </x:c>
       <x:c r="B16" s="25" t="str">
         <x:v>fact_candidate</x:v>
       </x:c>
       <x:c r="C16" s="25" t="str">
-        <x:v>senior_id, status, updated_at</x:v>
+        <x:v>coordination_status, coordination_deadline_at</x:v>
       </x:c>
       <x:c r="D16" s="25" t="str">
         <x:v>N</x:v>
       </x:c>
       <x:c r="E16" s="25" t="str">
-        <x:v>시니어의 활성 재질의·확인 후보 조회</x:v>
+        <x:v>협의 대기·기한 초과 운영 조회</x:v>
       </x:c>
       <x:c r="F16" s="25" t="str">
-        <x:v>후보 구현 시</x:v>
+        <x:v>보호자 협의 구현 시</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="26" t="str">
-        <x:v>idx_candidate_coordination</x:v>
+        <x:v>idx_candidate_source_message</x:v>
       </x:c>
       <x:c r="B17" s="26" t="str">
         <x:v>fact_candidate</x:v>
       </x:c>
       <x:c r="C17" s="26" t="str">
-        <x:v>coordination_status, coordination_deadline_at</x:v>
+        <x:v>source_message_id</x:v>
       </x:c>
       <x:c r="D17" s="26" t="str">
         <x:v>N</x:v>
       </x:c>
       <x:c r="E17" s="26" t="str">
-        <x:v>협의 대기·기한 초과 운영 조회</x:v>
+        <x:v>Raw 삭제 전 활성 후보 확인</x:v>
       </x:c>
       <x:c r="F17" s="26" t="str">
-        <x:v>보호자 협의 구현 시</x:v>
+        <x:v>보존 배치 구현 시</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="25" t="str">
-        <x:v>idx_candidate_source_message</x:v>
+        <x:v>idx_memory_search_filter</x:v>
       </x:c>
       <x:c r="B18" s="25" t="str">
-        <x:v>fact_candidate</x:v>
+        <x:v>memory</x:v>
       </x:c>
       <x:c r="C18" s="25" t="str">
-        <x:v>source_message_id</x:v>
+        <x:v>senior_id, lifecycle_status, verification_status</x:v>
       </x:c>
       <x:c r="D18" s="25" t="str">
         <x:v>N</x:v>
       </x:c>
       <x:c r="E18" s="25" t="str">
-        <x:v>Raw 삭제 전 활성 후보 확인</x:v>
+        <x:v>키워드·벡터 검색 전 사용 가능 기억 필터</x:v>
       </x:c>
       <x:c r="F18" s="25" t="str">
-        <x:v>보존 배치 구현 시</x:v>
+        <x:v>기억 검색 구현 시</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="26" t="str">
-        <x:v>idx_memory_search_filter</x:v>
+        <x:v>idx_memory_keywords</x:v>
       </x:c>
       <x:c r="B19" s="26" t="str">
         <x:v>memory</x:v>
       </x:c>
       <x:c r="C19" s="26" t="str">
-        <x:v>senior_id, lifecycle_status, verification_status</x:v>
+        <x:v>keywords</x:v>
       </x:c>
       <x:c r="D19" s="26" t="str">
         <x:v>N</x:v>
       </x:c>
       <x:c r="E19" s="26" t="str">
-        <x:v>키워드·벡터 검색 전 사용 가능 기억 필터</x:v>
+        <x:v>이름·음식·장소 정확 키워드 검색</x:v>
       </x:c>
       <x:c r="F19" s="26" t="str">
-        <x:v>기억 검색 구현 시</x:v>
+        <x:v>PostgreSQL GIN 검토</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="25" t="str">
-        <x:v>idx_memory_keywords</x:v>
+        <x:v>idx_memory_last_used</x:v>
       </x:c>
       <x:c r="B20" s="25" t="str">
         <x:v>memory</x:v>
       </x:c>
       <x:c r="C20" s="25" t="str">
-        <x:v>keywords</x:v>
+        <x:v>senior_id, last_used_at</x:v>
       </x:c>
       <x:c r="D20" s="25" t="str">
         <x:v>N</x:v>
       </x:c>
       <x:c r="E20" s="25" t="str">
-        <x:v>이름·음식·장소 정확 키워드 검색</x:v>
+        <x:v>과도한 기억 반복 억제</x:v>
       </x:c>
       <x:c r="F20" s="25" t="str">
-        <x:v>PostgreSQL GIN 검토</x:v>
+        <x:v>대화 문맥 구현 시</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="26" t="str">
-        <x:v>idx_memory_last_used</x:v>
+        <x:v>idx_care_record_senior_type_status</x:v>
       </x:c>
       <x:c r="B21" s="26" t="str">
-        <x:v>memory</x:v>
+        <x:v>care_record</x:v>
       </x:c>
       <x:c r="C21" s="26" t="str">
-        <x:v>senior_id, last_used_at</x:v>
+        <x:v>senior_id, record_type, status</x:v>
       </x:c>
       <x:c r="D21" s="26" t="str">
         <x:v>N</x:v>
       </x:c>
       <x:c r="E21" s="26" t="str">
-        <x:v>과도한 기억 반복 억제</x:v>
+        <x:v>시니어의 현재 돌봄 사실 조회</x:v>
       </x:c>
       <x:c r="F21" s="26" t="str">
-        <x:v>대화 문맥 구현 시</x:v>
+        <x:v>돌봄 조회 구현 시</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="25" t="str">
-        <x:v>idx_care_record_senior_type_status</x:v>
+        <x:v>idx_care_record_recipient</x:v>
       </x:c>
       <x:c r="B22" s="25" t="str">
         <x:v>care_record</x:v>
       </x:c>
       <x:c r="C22" s="25" t="str">
-        <x:v>senior_id, record_type, status</x:v>
+        <x:v>recipient_guardian_id, record_type, status</x:v>
       </x:c>
       <x:c r="D22" s="25" t="str">
         <x:v>N</x:v>
       </x:c>
       <x:c r="E22" s="25" t="str">
-        <x:v>시니어의 현재 돌봄 사실 조회</x:v>
+        <x:v>보호자별 알림·공유 기록 조회</x:v>
       </x:c>
       <x:c r="F22" s="25" t="str">
-        <x:v>돌봄 조회 구현 시</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23">
+        <x:v>보호자 알림 구현 시</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="15" hidden="0" customHeight="1">
       <x:c r="A23" s="28" t="str">
-        <x:v>idx_care_record_recipient</x:v>
+        <x:v>uq_scenario_wake_word_event</x:v>
       </x:c>
       <x:c r="B23" s="28" t="str">
-        <x:v>care_record</x:v>
+        <x:v>scenario</x:v>
       </x:c>
       <x:c r="C23" s="28" t="str">
-        <x:v>recipient_guardian_id, record_type, status</x:v>
+        <x:v>external_event_id (WAKE_WORD_CALL만)</x:v>
       </x:c>
       <x:c r="D23" s="28" t="str">
-        <x:v>N</x:v>
+        <x:v>Y</x:v>
       </x:c>
       <x:c r="E23" s="28" t="str">
-        <x:v>보호자별 알림·공유 기록 조회</x:v>
+        <x:v>수락된 같은 WAKE eventId의 시나리오 중복 차단</x:v>
       </x:c>
       <x:c r="F23" s="28" t="str">
-        <x:v>보호자 알림 구현 시</x:v>
+        <x:v>V15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="15" hidden="0" customHeight="1">
+      <x:c r="A24" t="str">
+        <x:v>uq_scenario_one_active_per_senior</x:v>
+      </x:c>
+      <x:c r="B24" t="str">
+        <x:v>scenario</x:v>
+      </x:c>
+      <x:c r="C24" t="str">
+        <x:v>senior_id (활성 상태만)</x:v>
+      </x:c>
+      <x:c r="D24" t="str">
+        <x:v>Y</x:v>
+      </x:c>
+      <x:c r="E24" t="str">
+        <x:v>시니어당 활성 시나리오 하나를 DB 불변식으로 보장</x:v>
+      </x:c>
+      <x:c r="F24" t="str">
+        <x:v>V15</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -7640,6 +8564,52 @@
       </x:c>
       <x:c r="G10" s="27" t="str">
         <x:v>반복 없으면 null</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="32" hidden="0" customHeight="1">
+      <x:c r="A11" t="str">
+        <x:v>scenario.conversation_request</x:v>
+      </x:c>
+      <x:c r="B11" t="str">
+        <x:v>이동 전에 준비한 대화 요청</x:v>
+      </x:c>
+      <x:c r="C11" t="str">
+        <x:v>{"intent":"HOMECOMING_GREETING","text":"어서 오세요","triggerContext":{"location":"ENTRANCE"}}</x:v>
+      </x:c>
+      <x:c r="D11" t="str">
+        <x:v>intent, text, triggerContext</x:v>
+      </x:c>
+      <x:c r="E11" t="str">
+        <x:v>확정된 대화 intent·첫 문장·최소 트리거 문맥</x:v>
+      </x:c>
+      <x:c r="F11" t="str">
+        <x:v>원본 음성, 전체 STT, 외부 응답 전문</x:v>
+      </x:c>
+      <x:c r="G11" t="str">
+        <x:v>대화형 시나리오에서만 저장하고 WAKE_WORD_CALL은 null</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="32" hidden="0" customHeight="1">
+      <x:c r="A12" t="str">
+        <x:v>scenario.trigger_context</x:v>
+      </x:c>
+      <x:c r="B12" t="str">
+        <x:v>호출 트리거 최소 문맥</x:v>
+      </x:c>
+      <x:c r="C12" t="str">
+        <x:v>{"robotId":"bomi-AA001","occurredAt":"2026-08-05T14:00:00+09:00","keyword":"보미야","confidence":0.92}</x:v>
+      </x:c>
+      <x:c r="D12" t="str">
+        <x:v>robotId, occurredAt, keyword</x:v>
+      </x:c>
+      <x:c r="E12" t="str">
+        <x:v>confidence는 선택, keyword는 1~20자</x:v>
+      </x:c>
+      <x:c r="F12" t="str">
+        <x:v>원본 음성, 전체 STT, 자유 대화 문장</x:v>
+      </x:c>
+      <x:c r="G12" t="str">
+        <x:v>WAKE_WORD_CALL 생성 시 최초 이벤트 값으로 한 번 저장</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -8803,7 +9773,7 @@
         <x:v>검색·반영에서 제외</x:v>
       </x:c>
     </x:row>
-    <x:row r="64">
+    <x:row r="64" ht="15" hidden="0" customHeight="1">
       <x:c r="A64" s="25" t="str">
         <x:v>scenario.scenario_type</x:v>
       </x:c>
@@ -8820,15 +9790,15 @@
         <x:v>정의되지 않은 값을 성공으로 처리하지 않음</x:v>
       </x:c>
     </x:row>
-    <x:row r="65">
+    <x:row r="65" ht="15" hidden="0" customHeight="1">
       <x:c r="A65" s="26" t="str">
         <x:v>scenario.scenario_type</x:v>
       </x:c>
       <x:c r="B65" s="26" t="str">
-        <x:v>FALL_RESPONSE</x:v>
+        <x:v>WELLNESS_CHECK</x:v>
       </x:c>
       <x:c r="C65" s="26" t="str">
-        <x:v>시나리오 유형: FALL_RESPONSE</x:v>
+        <x:v>시나리오 유형: WELLNESS_CHECK</x:v>
       </x:c>
       <x:c r="D65" s="26" t="str">
         <x:v>scenario.scenario_type의 상태·분기 판단</x:v>
@@ -8837,15 +9807,15 @@
         <x:v>정의되지 않은 값을 성공으로 처리하지 않음</x:v>
       </x:c>
     </x:row>
-    <x:row r="66">
+    <x:row r="66" ht="15" hidden="0" customHeight="1">
       <x:c r="A66" s="25" t="str">
         <x:v>scenario.scenario_type</x:v>
       </x:c>
       <x:c r="B66" s="25" t="str">
-        <x:v>MANUAL_INTERACTION</x:v>
+        <x:v>MEDICATION_REMINDER</x:v>
       </x:c>
       <x:c r="C66" s="25" t="str">
-        <x:v>시나리오 유형: MANUAL_INTERACTION</x:v>
+        <x:v>시나리오 유형: MEDICATION_REMINDER</x:v>
       </x:c>
       <x:c r="D66" s="25" t="str">
         <x:v>scenario.scenario_type의 상태·분기 판단</x:v>
@@ -8854,66 +9824,66 @@
         <x:v>정의되지 않은 값을 성공으로 처리하지 않음</x:v>
       </x:c>
     </x:row>
-    <x:row r="67">
+    <x:row r="67" ht="15" hidden="0" customHeight="1">
       <x:c r="A67" s="26" t="str">
-        <x:v>scenario.final_status</x:v>
+        <x:v>scenario.scenario_type</x:v>
       </x:c>
       <x:c r="B67" s="26" t="str">
-        <x:v>RECEIVED</x:v>
+        <x:v>WAKE_WORD_CALL</x:v>
       </x:c>
       <x:c r="C67" s="26" t="str">
-        <x:v>시나리오 진행·종료 상태: RECEIVED</x:v>
+        <x:v>시나리오 유형: WAKE_WORD_CALL</x:v>
       </x:c>
       <x:c r="D67" s="26" t="str">
-        <x:v>scenario.final_status의 상태·분기 판단</x:v>
+        <x:v>scenario.scenario_type의 상태·분기 판단</x:v>
       </x:c>
       <x:c r="E67" s="26" t="str">
         <x:v>정의되지 않은 값을 성공으로 처리하지 않음</x:v>
       </x:c>
     </x:row>
-    <x:row r="68">
+    <x:row r="68" ht="15" hidden="0" customHeight="1">
       <x:c r="A68" s="25" t="str">
-        <x:v>scenario.final_status</x:v>
+        <x:v>scenario.scenario_type</x:v>
       </x:c>
       <x:c r="B68" s="25" t="str">
-        <x:v>MOVING_TO_ENTRANCE</x:v>
+        <x:v>FALL_RESPONSE</x:v>
       </x:c>
       <x:c r="C68" s="25" t="str">
-        <x:v>시나리오 진행·종료 상태: MOVING_TO_ENTRANCE</x:v>
+        <x:v>시나리오 유형: FALL_RESPONSE</x:v>
       </x:c>
       <x:c r="D68" s="25" t="str">
-        <x:v>scenario.final_status의 상태·분기 판단</x:v>
+        <x:v>scenario.scenario_type의 상태·분기 판단</x:v>
       </x:c>
       <x:c r="E68" s="25" t="str">
         <x:v>정의되지 않은 값을 성공으로 처리하지 않음</x:v>
       </x:c>
     </x:row>
-    <x:row r="69">
+    <x:row r="69" ht="15" hidden="0" customHeight="1">
       <x:c r="A69" s="26" t="str">
-        <x:v>scenario.final_status</x:v>
+        <x:v>scenario.scenario_type</x:v>
       </x:c>
       <x:c r="B69" s="26" t="str">
-        <x:v>CHECKING_INTERACTION</x:v>
+        <x:v>MANUAL_INTERACTION</x:v>
       </x:c>
       <x:c r="C69" s="26" t="str">
-        <x:v>시나리오 진행·종료 상태: CHECKING_INTERACTION</x:v>
+        <x:v>시나리오 유형: MANUAL_INTERACTION</x:v>
       </x:c>
       <x:c r="D69" s="26" t="str">
-        <x:v>scenario.final_status의 상태·분기 판단</x:v>
+        <x:v>scenario.scenario_type의 상태·분기 판단</x:v>
       </x:c>
       <x:c r="E69" s="26" t="str">
         <x:v>정의되지 않은 값을 성공으로 처리하지 않음</x:v>
       </x:c>
     </x:row>
-    <x:row r="70">
+    <x:row r="70" ht="15" hidden="0" customHeight="1">
       <x:c r="A70" s="25" t="str">
         <x:v>scenario.final_status</x:v>
       </x:c>
       <x:c r="B70" s="25" t="str">
-        <x:v>CONVERSING</x:v>
+        <x:v>RECEIVED</x:v>
       </x:c>
       <x:c r="C70" s="25" t="str">
-        <x:v>시나리오 진행·종료 상태: CONVERSING</x:v>
+        <x:v>시나리오 진행·종료 상태: RECEIVED</x:v>
       </x:c>
       <x:c r="D70" s="25" t="str">
         <x:v>scenario.final_status의 상태·분기 판단</x:v>
@@ -8922,15 +9892,15 @@
         <x:v>정의되지 않은 값을 성공으로 처리하지 않음</x:v>
       </x:c>
     </x:row>
-    <x:row r="71">
+    <x:row r="71" ht="15" hidden="0" customHeight="1">
       <x:c r="A71" s="26" t="str">
         <x:v>scenario.final_status</x:v>
       </x:c>
       <x:c r="B71" s="26" t="str">
-        <x:v>RETURN_DECISION</x:v>
+        <x:v>NAVIGATING</x:v>
       </x:c>
       <x:c r="C71" s="26" t="str">
-        <x:v>시나리오 진행·종료 상태: RETURN_DECISION</x:v>
+        <x:v>시나리오 진행·종료 상태: NAVIGATING</x:v>
       </x:c>
       <x:c r="D71" s="26" t="str">
         <x:v>scenario.final_status의 상태·분기 판단</x:v>
@@ -8939,15 +9909,15 @@
         <x:v>정의되지 않은 값을 성공으로 처리하지 않음</x:v>
       </x:c>
     </x:row>
-    <x:row r="72">
+    <x:row r="72" ht="15" hidden="0" customHeight="1">
       <x:c r="A72" s="25" t="str">
         <x:v>scenario.final_status</x:v>
       </x:c>
       <x:c r="B72" s="25" t="str">
-        <x:v>RETURNING_TO_DEFAULT</x:v>
+        <x:v>MOVING_TO_ENTRANCE</x:v>
       </x:c>
       <x:c r="C72" s="25" t="str">
-        <x:v>시나리오 진행·종료 상태: RETURNING_TO_DEFAULT</x:v>
+        <x:v>시나리오 진행·종료 상태: MOVING_TO_ENTRANCE</x:v>
       </x:c>
       <x:c r="D72" s="25" t="str">
         <x:v>scenario.final_status의 상태·분기 판단</x:v>
@@ -8956,15 +9926,15 @@
         <x:v>정의되지 않은 값을 성공으로 처리하지 않음</x:v>
       </x:c>
     </x:row>
-    <x:row r="73">
+    <x:row r="73" ht="15" hidden="0" customHeight="1">
       <x:c r="A73" s="26" t="str">
         <x:v>scenario.final_status</x:v>
       </x:c>
       <x:c r="B73" s="26" t="str">
-        <x:v>COMPLETED</x:v>
+        <x:v>CHECKING_INTERACTION</x:v>
       </x:c>
       <x:c r="C73" s="26" t="str">
-        <x:v>시나리오 진행·종료 상태: COMPLETED</x:v>
+        <x:v>시나리오 진행·종료 상태: CHECKING_INTERACTION</x:v>
       </x:c>
       <x:c r="D73" s="26" t="str">
         <x:v>scenario.final_status의 상태·분기 판단</x:v>
@@ -8973,15 +9943,15 @@
         <x:v>정의되지 않은 값을 성공으로 처리하지 않음</x:v>
       </x:c>
     </x:row>
-    <x:row r="74">
+    <x:row r="74" ht="15" hidden="0" customHeight="1">
       <x:c r="A74" s="25" t="str">
         <x:v>scenario.final_status</x:v>
       </x:c>
       <x:c r="B74" s="25" t="str">
-        <x:v>FAILED</x:v>
+        <x:v>CONVERSING</x:v>
       </x:c>
       <x:c r="C74" s="25" t="str">
-        <x:v>시나리오 진행·종료 상태: FAILED</x:v>
+        <x:v>시나리오 진행·종료 상태: CONVERSING</x:v>
       </x:c>
       <x:c r="D74" s="25" t="str">
         <x:v>scenario.final_status의 상태·분기 판단</x:v>
@@ -8990,15 +9960,15 @@
         <x:v>정의되지 않은 값을 성공으로 처리하지 않음</x:v>
       </x:c>
     </x:row>
-    <x:row r="75">
+    <x:row r="75" ht="15" hidden="0" customHeight="1">
       <x:c r="A75" s="26" t="str">
         <x:v>scenario.final_status</x:v>
       </x:c>
       <x:c r="B75" s="26" t="str">
-        <x:v>CANCELLED</x:v>
+        <x:v>RETURN_DECISION</x:v>
       </x:c>
       <x:c r="C75" s="26" t="str">
-        <x:v>시나리오 진행·종료 상태: CANCELLED</x:v>
+        <x:v>시나리오 진행·종료 상태: RETURN_DECISION</x:v>
       </x:c>
       <x:c r="D75" s="26" t="str">
         <x:v>scenario.final_status의 상태·분기 판단</x:v>
@@ -9007,15 +9977,15 @@
         <x:v>정의되지 않은 값을 성공으로 처리하지 않음</x:v>
       </x:c>
     </x:row>
-    <x:row r="76">
+    <x:row r="76" ht="15" hidden="0" customHeight="1">
       <x:c r="A76" s="25" t="str">
         <x:v>scenario.final_status</x:v>
       </x:c>
       <x:c r="B76" s="25" t="str">
-        <x:v>TIMED_OUT</x:v>
+        <x:v>RETURNING_TO_DEFAULT</x:v>
       </x:c>
       <x:c r="C76" s="25" t="str">
-        <x:v>시나리오 진행·종료 상태: TIMED_OUT</x:v>
+        <x:v>시나리오 진행·종료 상태: RETURNING_TO_DEFAULT</x:v>
       </x:c>
       <x:c r="D76" s="25" t="str">
         <x:v>scenario.final_status의 상태·분기 판단</x:v>
@@ -9024,222 +9994,222 @@
         <x:v>정의되지 않은 값을 성공으로 처리하지 않음</x:v>
       </x:c>
     </x:row>
-    <x:row r="77">
+    <x:row r="77" ht="15" hidden="0" customHeight="1">
       <x:c r="A77" s="26" t="str">
-        <x:v>conversation.status</x:v>
+        <x:v>scenario.final_status</x:v>
       </x:c>
       <x:c r="B77" s="26" t="str">
-        <x:v>OPEN</x:v>
+        <x:v>COMPLETED</x:v>
       </x:c>
       <x:c r="C77" s="26" t="str">
-        <x:v>대화 상태: OPEN</x:v>
+        <x:v>시나리오 진행·종료 상태: COMPLETED</x:v>
       </x:c>
       <x:c r="D77" s="26" t="str">
-        <x:v>conversation.status의 상태·분기 판단</x:v>
+        <x:v>scenario.final_status의 상태·분기 판단</x:v>
       </x:c>
       <x:c r="E77" s="26" t="str">
         <x:v>정의되지 않은 값을 성공으로 처리하지 않음</x:v>
       </x:c>
     </x:row>
-    <x:row r="78">
+    <x:row r="78" ht="15" hidden="0" customHeight="1">
       <x:c r="A78" s="25" t="str">
-        <x:v>conversation.status</x:v>
+        <x:v>scenario.final_status</x:v>
       </x:c>
       <x:c r="B78" s="25" t="str">
-        <x:v>COMPLETED</x:v>
+        <x:v>FAILED</x:v>
       </x:c>
       <x:c r="C78" s="25" t="str">
-        <x:v>대화 상태: COMPLETED</x:v>
+        <x:v>시나리오 진행·종료 상태: FAILED</x:v>
       </x:c>
       <x:c r="D78" s="25" t="str">
-        <x:v>conversation.status의 상태·분기 판단</x:v>
+        <x:v>scenario.final_status의 상태·분기 판단</x:v>
       </x:c>
       <x:c r="E78" s="25" t="str">
         <x:v>정의되지 않은 값을 성공으로 처리하지 않음</x:v>
       </x:c>
     </x:row>
-    <x:row r="79">
+    <x:row r="79" ht="15" hidden="0" customHeight="1">
       <x:c r="A79" s="26" t="str">
-        <x:v>conversation.status</x:v>
+        <x:v>scenario.final_status</x:v>
       </x:c>
       <x:c r="B79" s="26" t="str">
-        <x:v>FAILED</x:v>
+        <x:v>CANCELLED</x:v>
       </x:c>
       <x:c r="C79" s="26" t="str">
-        <x:v>대화 상태: FAILED</x:v>
+        <x:v>시나리오 진행·종료 상태: CANCELLED</x:v>
       </x:c>
       <x:c r="D79" s="26" t="str">
-        <x:v>conversation.status의 상태·분기 판단</x:v>
+        <x:v>scenario.final_status의 상태·분기 판단</x:v>
       </x:c>
       <x:c r="E79" s="26" t="str">
         <x:v>정의되지 않은 값을 성공으로 처리하지 않음</x:v>
       </x:c>
     </x:row>
-    <x:row r="80">
+    <x:row r="80" ht="15" hidden="0" customHeight="1">
       <x:c r="A80" s="25" t="str">
-        <x:v>conversation.status</x:v>
+        <x:v>scenario.final_status</x:v>
       </x:c>
       <x:c r="B80" s="25" t="str">
-        <x:v>CANCELLED</x:v>
+        <x:v>TIMED_OUT</x:v>
       </x:c>
       <x:c r="C80" s="25" t="str">
-        <x:v>대화 상태: CANCELLED</x:v>
+        <x:v>시나리오 진행·종료 상태: TIMED_OUT</x:v>
       </x:c>
       <x:c r="D80" s="25" t="str">
-        <x:v>conversation.status의 상태·분기 판단</x:v>
+        <x:v>scenario.final_status의 상태·분기 판단</x:v>
       </x:c>
       <x:c r="E80" s="25" t="str">
         <x:v>정의되지 않은 값을 성공으로 처리하지 않음</x:v>
       </x:c>
     </x:row>
-    <x:row r="81">
+    <x:row r="81" ht="15" hidden="0" customHeight="1">
       <x:c r="A81" s="26" t="str">
-        <x:v>conversation_message.role</x:v>
+        <x:v>wake_word_trigger_receipt.disposition</x:v>
       </x:c>
       <x:c r="B81" s="26" t="str">
-        <x:v>SENIOR</x:v>
+        <x:v>RECEIVED</x:v>
       </x:c>
       <x:c r="C81" s="26" t="str">
-        <x:v>발화자: SENIOR</x:v>
+        <x:v>웨이크 트리거 처리 결정: RECEIVED</x:v>
       </x:c>
       <x:c r="D81" s="26" t="str">
-        <x:v>conversation_message.role의 상태·분기 판단</x:v>
+        <x:v>동일 eventId 재수신의 영속 처리 결정</x:v>
       </x:c>
       <x:c r="E81" s="26" t="str">
-        <x:v>정의되지 않은 값을 성공으로 처리하지 않음</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="82">
+        <x:v>RECEIVED를 최종 성공으로 처리하지 않음</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="82" ht="15" hidden="0" customHeight="1">
       <x:c r="A82" s="25" t="str">
-        <x:v>conversation_message.role</x:v>
+        <x:v>wake_word_trigger_receipt.disposition</x:v>
       </x:c>
       <x:c r="B82" s="25" t="str">
-        <x:v>ROBOT</x:v>
+        <x:v>ACCEPTED</x:v>
       </x:c>
       <x:c r="C82" s="25" t="str">
-        <x:v>발화자: ROBOT</x:v>
+        <x:v>웨이크 트리거 처리 결정: ACCEPTED</x:v>
       </x:c>
       <x:c r="D82" s="25" t="str">
-        <x:v>conversation_message.role의 상태·분기 판단</x:v>
+        <x:v>동일 eventId 재수신의 영속 처리 결정</x:v>
       </x:c>
       <x:c r="E82" s="25" t="str">
-        <x:v>정의되지 않은 값을 성공으로 처리하지 않음</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="83">
+        <x:v>RECEIVED를 최종 성공으로 처리하지 않음</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="83" ht="15" hidden="0" customHeight="1">
       <x:c r="A83" s="26" t="str">
-        <x:v>conversation_summary.summary_type</x:v>
+        <x:v>wake_word_trigger_receipt.disposition</x:v>
       </x:c>
       <x:c r="B83" s="26" t="str">
-        <x:v>CONVERSATION</x:v>
+        <x:v>REJECTED_UNKNOWN_ROBOT</x:v>
       </x:c>
       <x:c r="C83" s="26" t="str">
-        <x:v>요약 범위: CONVERSATION</x:v>
+        <x:v>웨이크 트리거 처리 결정: REJECTED_UNKNOWN_ROBOT</x:v>
       </x:c>
       <x:c r="D83" s="26" t="str">
-        <x:v>conversation_summary.summary_type의 상태·분기 판단</x:v>
+        <x:v>동일 eventId 재수신의 영속 처리 결정</x:v>
       </x:c>
       <x:c r="E83" s="26" t="str">
-        <x:v>정의되지 않은 값을 성공으로 처리하지 않음</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="84">
+        <x:v>RECEIVED를 최종 성공으로 처리하지 않음</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="84" ht="15" hidden="0" customHeight="1">
       <x:c r="A84" s="25" t="str">
-        <x:v>conversation_summary.summary_type</x:v>
+        <x:v>wake_word_trigger_receipt.disposition</x:v>
       </x:c>
       <x:c r="B84" s="25" t="str">
-        <x:v>DAILY</x:v>
+        <x:v>REJECTED_INACTIVE_ROBOT</x:v>
       </x:c>
       <x:c r="C84" s="25" t="str">
-        <x:v>요약 범위: DAILY</x:v>
+        <x:v>웨이크 트리거 처리 결정: REJECTED_INACTIVE_ROBOT</x:v>
       </x:c>
       <x:c r="D84" s="25" t="str">
-        <x:v>conversation_summary.summary_type의 상태·분기 판단</x:v>
+        <x:v>동일 eventId 재수신의 영속 처리 결정</x:v>
       </x:c>
       <x:c r="E84" s="25" t="str">
-        <x:v>정의되지 않은 값을 성공으로 처리하지 않음</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="85">
+        <x:v>RECEIVED를 최종 성공으로 처리하지 않음</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="85" ht="15" hidden="0" customHeight="1">
       <x:c r="A85" s="26" t="str">
-        <x:v>fact_candidate.source_type</x:v>
+        <x:v>wake_word_trigger_receipt.disposition</x:v>
       </x:c>
       <x:c r="B85" s="26" t="str">
-        <x:v>ONBOARDING_ANSWER</x:v>
+        <x:v>REJECTED_UNASSIGNED_ROBOT</x:v>
       </x:c>
       <x:c r="C85" s="26" t="str">
-        <x:v>후보 출처: ONBOARDING_ANSWER</x:v>
+        <x:v>웨이크 트리거 처리 결정: REJECTED_UNASSIGNED_ROBOT</x:v>
       </x:c>
       <x:c r="D85" s="26" t="str">
-        <x:v>fact_candidate.source_type의 상태·분기 판단</x:v>
+        <x:v>동일 eventId 재수신의 영속 처리 결정</x:v>
       </x:c>
       <x:c r="E85" s="26" t="str">
-        <x:v>정의되지 않은 값을 성공으로 처리하지 않음</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="86">
+        <x:v>RECEIVED를 최종 성공으로 처리하지 않음</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="86" ht="15" hidden="0" customHeight="1">
       <x:c r="A86" s="25" t="str">
-        <x:v>fact_candidate.source_type</x:v>
+        <x:v>wake_word_trigger_receipt.disposition</x:v>
       </x:c>
       <x:c r="B86" s="25" t="str">
-        <x:v>CONVERSATION_MESSAGE</x:v>
+        <x:v>REJECTED_SAFE_STOP</x:v>
       </x:c>
       <x:c r="C86" s="25" t="str">
-        <x:v>후보 출처: CONVERSATION_MESSAGE</x:v>
+        <x:v>웨이크 트리거 처리 결정: REJECTED_SAFE_STOP</x:v>
       </x:c>
       <x:c r="D86" s="25" t="str">
-        <x:v>fact_candidate.source_type의 상태·분기 판단</x:v>
+        <x:v>동일 eventId 재수신의 영속 처리 결정</x:v>
       </x:c>
       <x:c r="E86" s="25" t="str">
-        <x:v>정의되지 않은 값을 성공으로 처리하지 않음</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="87">
+        <x:v>RECEIVED를 최종 성공으로 처리하지 않음</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="87" ht="15" hidden="0" customHeight="1">
       <x:c r="A87" s="26" t="str">
-        <x:v>fact_candidate.target_domain</x:v>
+        <x:v>wake_word_trigger_receipt.disposition</x:v>
       </x:c>
       <x:c r="B87" s="26" t="str">
-        <x:v>PROFILE</x:v>
+        <x:v>REJECTED_ACTIVE_SCENARIO</x:v>
       </x:c>
       <x:c r="C87" s="26" t="str">
-        <x:v>최종 대상 도메인: PROFILE</x:v>
+        <x:v>웨이크 트리거 처리 결정: REJECTED_ACTIVE_SCENARIO</x:v>
       </x:c>
       <x:c r="D87" s="26" t="str">
-        <x:v>fact_candidate.target_domain의 상태·분기 판단</x:v>
+        <x:v>동일 eventId 재수신의 영속 처리 결정</x:v>
       </x:c>
       <x:c r="E87" s="26" t="str">
-        <x:v>정의되지 않은 값을 성공으로 처리하지 않음</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="88">
+        <x:v>RECEIVED를 최종 성공으로 처리하지 않음</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="88" ht="15" hidden="0" customHeight="1">
       <x:c r="A88" s="25" t="str">
-        <x:v>fact_candidate.target_domain</x:v>
+        <x:v>wake_word_trigger_receipt.disposition</x:v>
       </x:c>
       <x:c r="B88" s="25" t="str">
-        <x:v>CARE_RELATIONSHIP</x:v>
+        <x:v>REJECTED_BUSY_MODE</x:v>
       </x:c>
       <x:c r="C88" s="25" t="str">
-        <x:v>최종 대상 도메인: CARE_RELATIONSHIP</x:v>
+        <x:v>웨이크 트리거 처리 결정: REJECTED_BUSY_MODE</x:v>
       </x:c>
       <x:c r="D88" s="25" t="str">
-        <x:v>fact_candidate.target_domain의 상태·분기 판단</x:v>
+        <x:v>동일 eventId 재수신의 영속 처리 결정</x:v>
       </x:c>
       <x:c r="E88" s="25" t="str">
-        <x:v>정의되지 않은 값을 성공으로 처리하지 않음</x:v>
+        <x:v>RECEIVED를 최종 성공으로 처리하지 않음</x:v>
       </x:c>
     </x:row>
     <x:row r="89">
       <x:c r="A89" s="26" t="str">
-        <x:v>fact_candidate.target_domain</x:v>
+        <x:v>conversation.status</x:v>
       </x:c>
       <x:c r="B89" s="26" t="str">
-        <x:v>MEMORY</x:v>
+        <x:v>OPEN</x:v>
       </x:c>
       <x:c r="C89" s="26" t="str">
-        <x:v>최종 대상 도메인: MEMORY</x:v>
+        <x:v>대화 상태: OPEN</x:v>
       </x:c>
       <x:c r="D89" s="26" t="str">
-        <x:v>fact_candidate.target_domain의 상태·분기 판단</x:v>
+        <x:v>conversation.status의 상태·분기 판단</x:v>
       </x:c>
       <x:c r="E89" s="26" t="str">
         <x:v>정의되지 않은 값을 성공으로 처리하지 않음</x:v>
@@ -9247,16 +10217,16 @@
     </x:row>
     <x:row r="90">
       <x:c r="A90" s="25" t="str">
-        <x:v>fact_candidate.target_domain</x:v>
+        <x:v>conversation.status</x:v>
       </x:c>
       <x:c r="B90" s="25" t="str">
-        <x:v>CARE_RECORD</x:v>
+        <x:v>COMPLETED</x:v>
       </x:c>
       <x:c r="C90" s="25" t="str">
-        <x:v>최종 대상 도메인: CARE_RECORD</x:v>
+        <x:v>대화 상태: COMPLETED</x:v>
       </x:c>
       <x:c r="D90" s="25" t="str">
-        <x:v>fact_candidate.target_domain의 상태·분기 판단</x:v>
+        <x:v>conversation.status의 상태·분기 판단</x:v>
       </x:c>
       <x:c r="E90" s="25" t="str">
         <x:v>정의되지 않은 값을 성공으로 처리하지 않음</x:v>
@@ -9264,16 +10234,16 @@
     </x:row>
     <x:row r="91">
       <x:c r="A91" s="26" t="str">
-        <x:v>fact_candidate.operation</x:v>
+        <x:v>conversation.status</x:v>
       </x:c>
       <x:c r="B91" s="26" t="str">
-        <x:v>CREATE</x:v>
+        <x:v>FAILED</x:v>
       </x:c>
       <x:c r="C91" s="26" t="str">
-        <x:v>요청 연산: CREATE</x:v>
+        <x:v>대화 상태: FAILED</x:v>
       </x:c>
       <x:c r="D91" s="26" t="str">
-        <x:v>fact_candidate.operation의 상태·분기 판단</x:v>
+        <x:v>conversation.status의 상태·분기 판단</x:v>
       </x:c>
       <x:c r="E91" s="26" t="str">
         <x:v>정의되지 않은 값을 성공으로 처리하지 않음</x:v>
@@ -9281,16 +10251,16 @@
     </x:row>
     <x:row r="92">
       <x:c r="A92" s="25" t="str">
-        <x:v>fact_candidate.operation</x:v>
+        <x:v>conversation.status</x:v>
       </x:c>
       <x:c r="B92" s="25" t="str">
-        <x:v>UPDATE</x:v>
+        <x:v>CANCELLED</x:v>
       </x:c>
       <x:c r="C92" s="25" t="str">
-        <x:v>요청 연산: UPDATE</x:v>
+        <x:v>대화 상태: CANCELLED</x:v>
       </x:c>
       <x:c r="D92" s="25" t="str">
-        <x:v>fact_candidate.operation의 상태·분기 판단</x:v>
+        <x:v>conversation.status의 상태·분기 판단</x:v>
       </x:c>
       <x:c r="E92" s="25" t="str">
         <x:v>정의되지 않은 값을 성공으로 처리하지 않음</x:v>
@@ -9298,16 +10268,16 @@
     </x:row>
     <x:row r="93">
       <x:c r="A93" s="26" t="str">
-        <x:v>fact_candidate.operation</x:v>
+        <x:v>conversation_message.role</x:v>
       </x:c>
       <x:c r="B93" s="26" t="str">
-        <x:v>CANCEL</x:v>
+        <x:v>SENIOR</x:v>
       </x:c>
       <x:c r="C93" s="26" t="str">
-        <x:v>요청 연산: CANCEL</x:v>
+        <x:v>발화자: SENIOR</x:v>
       </x:c>
       <x:c r="D93" s="26" t="str">
-        <x:v>fact_candidate.operation의 상태·분기 판단</x:v>
+        <x:v>conversation_message.role의 상태·분기 판단</x:v>
       </x:c>
       <x:c r="E93" s="26" t="str">
         <x:v>정의되지 않은 값을 성공으로 처리하지 않음</x:v>
@@ -9315,16 +10285,16 @@
     </x:row>
     <x:row r="94">
       <x:c r="A94" s="25" t="str">
-        <x:v>fact_candidate.risk_level</x:v>
+        <x:v>conversation_message.role</x:v>
       </x:c>
       <x:c r="B94" s="25" t="str">
-        <x:v>NORMAL</x:v>
+        <x:v>ROBOT</x:v>
       </x:c>
       <x:c r="C94" s="25" t="str">
-        <x:v>후보 위험도: NORMAL</x:v>
+        <x:v>발화자: ROBOT</x:v>
       </x:c>
       <x:c r="D94" s="25" t="str">
-        <x:v>fact_candidate.risk_level의 상태·분기 판단</x:v>
+        <x:v>conversation_message.role의 상태·분기 판단</x:v>
       </x:c>
       <x:c r="E94" s="25" t="str">
         <x:v>정의되지 않은 값을 성공으로 처리하지 않음</x:v>
@@ -9332,16 +10302,16 @@
     </x:row>
     <x:row r="95">
       <x:c r="A95" s="26" t="str">
-        <x:v>fact_candidate.risk_level</x:v>
+        <x:v>conversation_summary.summary_type</x:v>
       </x:c>
       <x:c r="B95" s="26" t="str">
-        <x:v>SENSITIVE</x:v>
+        <x:v>CONVERSATION</x:v>
       </x:c>
       <x:c r="C95" s="26" t="str">
-        <x:v>후보 위험도: SENSITIVE</x:v>
+        <x:v>요약 범위: CONVERSATION</x:v>
       </x:c>
       <x:c r="D95" s="26" t="str">
-        <x:v>fact_candidate.risk_level의 상태·분기 판단</x:v>
+        <x:v>conversation_summary.summary_type의 상태·분기 판단</x:v>
       </x:c>
       <x:c r="E95" s="26" t="str">
         <x:v>정의되지 않은 값을 성공으로 처리하지 않음</x:v>
@@ -9349,16 +10319,16 @@
     </x:row>
     <x:row r="96">
       <x:c r="A96" s="25" t="str">
-        <x:v>fact_candidate.risk_level</x:v>
+        <x:v>conversation_summary.summary_type</x:v>
       </x:c>
       <x:c r="B96" s="25" t="str">
-        <x:v>HIGH</x:v>
+        <x:v>DAILY</x:v>
       </x:c>
       <x:c r="C96" s="25" t="str">
-        <x:v>후보 위험도: HIGH</x:v>
+        <x:v>요약 범위: DAILY</x:v>
       </x:c>
       <x:c r="D96" s="25" t="str">
-        <x:v>fact_candidate.risk_level의 상태·분기 판단</x:v>
+        <x:v>conversation_summary.summary_type의 상태·분기 판단</x:v>
       </x:c>
       <x:c r="E96" s="25" t="str">
         <x:v>정의되지 않은 값을 성공으로 처리하지 않음</x:v>
@@ -9366,16 +10336,16 @@
     </x:row>
     <x:row r="97">
       <x:c r="A97" s="26" t="str">
-        <x:v>fact_candidate.status</x:v>
+        <x:v>fact_candidate.source_type</x:v>
       </x:c>
       <x:c r="B97" s="26" t="str">
-        <x:v>CAPTURED</x:v>
+        <x:v>ONBOARDING_ANSWER</x:v>
       </x:c>
       <x:c r="C97" s="26" t="str">
-        <x:v>후보 처리 상태: CAPTURED</x:v>
+        <x:v>후보 출처: ONBOARDING_ANSWER</x:v>
       </x:c>
       <x:c r="D97" s="26" t="str">
-        <x:v>fact_candidate.status의 상태·분기 판단</x:v>
+        <x:v>fact_candidate.source_type의 상태·분기 판단</x:v>
       </x:c>
       <x:c r="E97" s="26" t="str">
         <x:v>정의되지 않은 값을 성공으로 처리하지 않음</x:v>
@@ -9383,16 +10353,16 @@
     </x:row>
     <x:row r="98">
       <x:c r="A98" s="25" t="str">
-        <x:v>fact_candidate.status</x:v>
+        <x:v>fact_candidate.source_type</x:v>
       </x:c>
       <x:c r="B98" s="25" t="str">
-        <x:v>NEEDS_CLARIFICATION</x:v>
+        <x:v>CONVERSATION_MESSAGE</x:v>
       </x:c>
       <x:c r="C98" s="25" t="str">
-        <x:v>후보 처리 상태: NEEDS_CLARIFICATION</x:v>
+        <x:v>후보 출처: CONVERSATION_MESSAGE</x:v>
       </x:c>
       <x:c r="D98" s="25" t="str">
-        <x:v>fact_candidate.status의 상태·분기 판단</x:v>
+        <x:v>fact_candidate.source_type의 상태·분기 판단</x:v>
       </x:c>
       <x:c r="E98" s="25" t="str">
         <x:v>정의되지 않은 값을 성공으로 처리하지 않음</x:v>
@@ -9400,16 +10370,16 @@
     </x:row>
     <x:row r="99">
       <x:c r="A99" s="26" t="str">
-        <x:v>fact_candidate.status</x:v>
+        <x:v>fact_candidate.target_domain</x:v>
       </x:c>
       <x:c r="B99" s="26" t="str">
-        <x:v>NEEDS_CONFIRMATION</x:v>
+        <x:v>PROFILE</x:v>
       </x:c>
       <x:c r="C99" s="26" t="str">
-        <x:v>후보 처리 상태: NEEDS_CONFIRMATION</x:v>
+        <x:v>최종 대상 도메인: PROFILE</x:v>
       </x:c>
       <x:c r="D99" s="26" t="str">
-        <x:v>fact_candidate.status의 상태·분기 판단</x:v>
+        <x:v>fact_candidate.target_domain의 상태·분기 판단</x:v>
       </x:c>
       <x:c r="E99" s="26" t="str">
         <x:v>정의되지 않은 값을 성공으로 처리하지 않음</x:v>
@@ -9417,16 +10387,16 @@
     </x:row>
     <x:row r="100">
       <x:c r="A100" s="25" t="str">
-        <x:v>fact_candidate.status</x:v>
+        <x:v>fact_candidate.target_domain</x:v>
       </x:c>
       <x:c r="B100" s="25" t="str">
-        <x:v>COORDINATION_REQUIRED</x:v>
+        <x:v>CARE_RELATIONSHIP</x:v>
       </x:c>
       <x:c r="C100" s="25" t="str">
-        <x:v>후보 처리 상태: COORDINATION_REQUIRED</x:v>
+        <x:v>최종 대상 도메인: CARE_RELATIONSHIP</x:v>
       </x:c>
       <x:c r="D100" s="25" t="str">
-        <x:v>fact_candidate.status의 상태·분기 판단</x:v>
+        <x:v>fact_candidate.target_domain의 상태·분기 판단</x:v>
       </x:c>
       <x:c r="E100" s="25" t="str">
         <x:v>정의되지 않은 값을 성공으로 처리하지 않음</x:v>
@@ -9434,16 +10404,16 @@
     </x:row>
     <x:row r="101">
       <x:c r="A101" s="26" t="str">
-        <x:v>fact_candidate.status</x:v>
+        <x:v>fact_candidate.target_domain</x:v>
       </x:c>
       <x:c r="B101" s="26" t="str">
-        <x:v>CONFIRMED</x:v>
+        <x:v>MEMORY</x:v>
       </x:c>
       <x:c r="C101" s="26" t="str">
-        <x:v>후보 처리 상태: CONFIRMED</x:v>
+        <x:v>최종 대상 도메인: MEMORY</x:v>
       </x:c>
       <x:c r="D101" s="26" t="str">
-        <x:v>fact_candidate.status의 상태·분기 판단</x:v>
+        <x:v>fact_candidate.target_domain의 상태·분기 판단</x:v>
       </x:c>
       <x:c r="E101" s="26" t="str">
         <x:v>정의되지 않은 값을 성공으로 처리하지 않음</x:v>
@@ -9451,16 +10421,16 @@
     </x:row>
     <x:row r="102">
       <x:c r="A102" s="25" t="str">
-        <x:v>fact_candidate.status</x:v>
+        <x:v>fact_candidate.target_domain</x:v>
       </x:c>
       <x:c r="B102" s="25" t="str">
-        <x:v>MATERIALIZED</x:v>
+        <x:v>CARE_RECORD</x:v>
       </x:c>
       <x:c r="C102" s="25" t="str">
-        <x:v>후보 처리 상태: MATERIALIZED</x:v>
+        <x:v>최종 대상 도메인: CARE_RECORD</x:v>
       </x:c>
       <x:c r="D102" s="25" t="str">
-        <x:v>fact_candidate.status의 상태·분기 판단</x:v>
+        <x:v>fact_candidate.target_domain의 상태·분기 판단</x:v>
       </x:c>
       <x:c r="E102" s="25" t="str">
         <x:v>정의되지 않은 값을 성공으로 처리하지 않음</x:v>
@@ -9468,33 +10438,33 @@
     </x:row>
     <x:row r="103">
       <x:c r="A103" s="26" t="str">
-        <x:v>fact_candidate.status</x:v>
+        <x:v>fact_candidate.operation</x:v>
       </x:c>
       <x:c r="B103" s="26" t="str">
-        <x:v>REJECTED</x:v>
+        <x:v>CREATE</x:v>
       </x:c>
       <x:c r="C103" s="26" t="str">
-        <x:v>후보 처리 상태: REJECTED</x:v>
+        <x:v>요청 연산: CREATE</x:v>
       </x:c>
       <x:c r="D103" s="26" t="str">
-        <x:v>fact_candidate.status의 상태·분기 판단</x:v>
+        <x:v>fact_candidate.operation의 상태·분기 판단</x:v>
       </x:c>
       <x:c r="E103" s="26" t="str">
-        <x:v>검색·반영에서 제외</x:v>
+        <x:v>정의되지 않은 값을 성공으로 처리하지 않음</x:v>
       </x:c>
     </x:row>
     <x:row r="104">
       <x:c r="A104" s="25" t="str">
-        <x:v>fact_candidate.status</x:v>
+        <x:v>fact_candidate.operation</x:v>
       </x:c>
       <x:c r="B104" s="25" t="str">
-        <x:v>EXPIRED</x:v>
+        <x:v>UPDATE</x:v>
       </x:c>
       <x:c r="C104" s="25" t="str">
-        <x:v>후보 처리 상태: EXPIRED</x:v>
+        <x:v>요청 연산: UPDATE</x:v>
       </x:c>
       <x:c r="D104" s="25" t="str">
-        <x:v>fact_candidate.status의 상태·분기 판단</x:v>
+        <x:v>fact_candidate.operation의 상태·분기 판단</x:v>
       </x:c>
       <x:c r="E104" s="25" t="str">
         <x:v>정의되지 않은 값을 성공으로 처리하지 않음</x:v>
@@ -9502,16 +10472,16 @@
     </x:row>
     <x:row r="105">
       <x:c r="A105" s="26" t="str">
-        <x:v>fact_candidate.clarification_reason</x:v>
+        <x:v>fact_candidate.operation</x:v>
       </x:c>
       <x:c r="B105" s="26" t="str">
-        <x:v>MISSING_REQUIRED_FIELD</x:v>
+        <x:v>CANCEL</x:v>
       </x:c>
       <x:c r="C105" s="26" t="str">
-        <x:v>재질의 사유: MISSING_REQUIRED_FIELD</x:v>
+        <x:v>요청 연산: CANCEL</x:v>
       </x:c>
       <x:c r="D105" s="26" t="str">
-        <x:v>fact_candidate.clarification_reason의 상태·분기 판단</x:v>
+        <x:v>fact_candidate.operation의 상태·분기 판단</x:v>
       </x:c>
       <x:c r="E105" s="26" t="str">
         <x:v>정의되지 않은 값을 성공으로 처리하지 않음</x:v>
@@ -9519,16 +10489,16 @@
     </x:row>
     <x:row r="106">
       <x:c r="A106" s="25" t="str">
-        <x:v>fact_candidate.clarification_reason</x:v>
+        <x:v>fact_candidate.risk_level</x:v>
       </x:c>
       <x:c r="B106" s="25" t="str">
-        <x:v>AMBIGUOUS_VALUE</x:v>
+        <x:v>NORMAL</x:v>
       </x:c>
       <x:c r="C106" s="25" t="str">
-        <x:v>재질의 사유: AMBIGUOUS_VALUE</x:v>
+        <x:v>후보 위험도: NORMAL</x:v>
       </x:c>
       <x:c r="D106" s="25" t="str">
-        <x:v>fact_candidate.clarification_reason의 상태·분기 판단</x:v>
+        <x:v>fact_candidate.risk_level의 상태·분기 판단</x:v>
       </x:c>
       <x:c r="E106" s="25" t="str">
         <x:v>정의되지 않은 값을 성공으로 처리하지 않음</x:v>
@@ -9536,16 +10506,16 @@
     </x:row>
     <x:row r="107">
       <x:c r="A107" s="26" t="str">
-        <x:v>fact_candidate.clarification_reason</x:v>
+        <x:v>fact_candidate.risk_level</x:v>
       </x:c>
       <x:c r="B107" s="26" t="str">
-        <x:v>LOW_RECOGNITION_CONFIDENCE</x:v>
+        <x:v>SENSITIVE</x:v>
       </x:c>
       <x:c r="C107" s="26" t="str">
-        <x:v>재질의 사유: LOW_RECOGNITION_CONFIDENCE</x:v>
+        <x:v>후보 위험도: SENSITIVE</x:v>
       </x:c>
       <x:c r="D107" s="26" t="str">
-        <x:v>fact_candidate.clarification_reason의 상태·분기 판단</x:v>
+        <x:v>fact_candidate.risk_level의 상태·분기 판단</x:v>
       </x:c>
       <x:c r="E107" s="26" t="str">
         <x:v>정의되지 않은 값을 성공으로 처리하지 않음</x:v>
@@ -9553,16 +10523,16 @@
     </x:row>
     <x:row r="108">
       <x:c r="A108" s="25" t="str">
-        <x:v>fact_candidate.clarification_reason</x:v>
+        <x:v>fact_candidate.risk_level</x:v>
       </x:c>
       <x:c r="B108" s="25" t="str">
-        <x:v>CONFLICT_WITH_EXISTING_DATA</x:v>
+        <x:v>HIGH</x:v>
       </x:c>
       <x:c r="C108" s="25" t="str">
-        <x:v>재질의 사유: CONFLICT_WITH_EXISTING_DATA</x:v>
+        <x:v>후보 위험도: HIGH</x:v>
       </x:c>
       <x:c r="D108" s="25" t="str">
-        <x:v>fact_candidate.clarification_reason의 상태·분기 판단</x:v>
+        <x:v>fact_candidate.risk_level의 상태·분기 판단</x:v>
       </x:c>
       <x:c r="E108" s="25" t="str">
         <x:v>정의되지 않은 값을 성공으로 처리하지 않음</x:v>
@@ -9570,16 +10540,16 @@
     </x:row>
     <x:row r="109">
       <x:c r="A109" s="26" t="str">
-        <x:v>fact_candidate.clarification_reason</x:v>
+        <x:v>fact_candidate.status</x:v>
       </x:c>
       <x:c r="B109" s="26" t="str">
-        <x:v>SENSITIVE_INFORMATION_CONFIRMATION</x:v>
+        <x:v>CAPTURED</x:v>
       </x:c>
       <x:c r="C109" s="26" t="str">
-        <x:v>재질의 사유: SENSITIVE_INFORMATION_CONFIRMATION</x:v>
+        <x:v>후보 처리 상태: CAPTURED</x:v>
       </x:c>
       <x:c r="D109" s="26" t="str">
-        <x:v>fact_candidate.clarification_reason의 상태·분기 판단</x:v>
+        <x:v>fact_candidate.status의 상태·분기 판단</x:v>
       </x:c>
       <x:c r="E109" s="26" t="str">
         <x:v>정의되지 않은 값을 성공으로 처리하지 않음</x:v>
@@ -9587,16 +10557,16 @@
     </x:row>
     <x:row r="110">
       <x:c r="A110" s="25" t="str">
-        <x:v>fact_candidate.coordination_status</x:v>
+        <x:v>fact_candidate.status</x:v>
       </x:c>
       <x:c r="B110" s="25" t="str">
-        <x:v>NOT_REQUIRED</x:v>
+        <x:v>NEEDS_CLARIFICATION</x:v>
       </x:c>
       <x:c r="C110" s="25" t="str">
-        <x:v>협의 상태: NOT_REQUIRED</x:v>
+        <x:v>후보 처리 상태: NEEDS_CLARIFICATION</x:v>
       </x:c>
       <x:c r="D110" s="25" t="str">
-        <x:v>fact_candidate.coordination_status의 상태·분기 판단</x:v>
+        <x:v>fact_candidate.status의 상태·분기 판단</x:v>
       </x:c>
       <x:c r="E110" s="25" t="str">
         <x:v>정의되지 않은 값을 성공으로 처리하지 않음</x:v>
@@ -9604,16 +10574,16 @@
     </x:row>
     <x:row r="111">
       <x:c r="A111" s="26" t="str">
-        <x:v>fact_candidate.coordination_status</x:v>
+        <x:v>fact_candidate.status</x:v>
       </x:c>
       <x:c r="B111" s="26" t="str">
-        <x:v>COORDINATION_REQUIRED</x:v>
+        <x:v>NEEDS_CONFIRMATION</x:v>
       </x:c>
       <x:c r="C111" s="26" t="str">
-        <x:v>협의 상태: COORDINATION_REQUIRED</x:v>
+        <x:v>후보 처리 상태: NEEDS_CONFIRMATION</x:v>
       </x:c>
       <x:c r="D111" s="26" t="str">
-        <x:v>fact_candidate.coordination_status의 상태·분기 판단</x:v>
+        <x:v>fact_candidate.status의 상태·분기 판단</x:v>
       </x:c>
       <x:c r="E111" s="26" t="str">
         <x:v>정의되지 않은 값을 성공으로 처리하지 않음</x:v>
@@ -9621,16 +10591,16 @@
     </x:row>
     <x:row r="112">
       <x:c r="A112" s="25" t="str">
-        <x:v>fact_candidate.coordination_status</x:v>
+        <x:v>fact_candidate.status</x:v>
       </x:c>
       <x:c r="B112" s="25" t="str">
-        <x:v>WAITING_PRIMARY_GUARDIAN</x:v>
+        <x:v>COORDINATION_REQUIRED</x:v>
       </x:c>
       <x:c r="C112" s="25" t="str">
-        <x:v>협의 상태: WAITING_PRIMARY_GUARDIAN</x:v>
+        <x:v>후보 처리 상태: COORDINATION_REQUIRED</x:v>
       </x:c>
       <x:c r="D112" s="25" t="str">
-        <x:v>fact_candidate.coordination_status의 상태·분기 판단</x:v>
+        <x:v>fact_candidate.status의 상태·분기 판단</x:v>
       </x:c>
       <x:c r="E112" s="25" t="str">
         <x:v>정의되지 않은 값을 성공으로 처리하지 않음</x:v>
@@ -9638,16 +10608,16 @@
     </x:row>
     <x:row r="113">
       <x:c r="A113" s="26" t="str">
-        <x:v>fact_candidate.coordination_status</x:v>
+        <x:v>fact_candidate.status</x:v>
       </x:c>
       <x:c r="B113" s="26" t="str">
-        <x:v>WAITING_SENIOR</x:v>
+        <x:v>CONFIRMED</x:v>
       </x:c>
       <x:c r="C113" s="26" t="str">
-        <x:v>협의 상태: WAITING_SENIOR</x:v>
+        <x:v>후보 처리 상태: CONFIRMED</x:v>
       </x:c>
       <x:c r="D113" s="26" t="str">
-        <x:v>fact_candidate.coordination_status의 상태·분기 판단</x:v>
+        <x:v>fact_candidate.status의 상태·분기 판단</x:v>
       </x:c>
       <x:c r="E113" s="26" t="str">
         <x:v>정의되지 않은 값을 성공으로 처리하지 않음</x:v>
@@ -9655,16 +10625,16 @@
     </x:row>
     <x:row r="114">
       <x:c r="A114" s="25" t="str">
-        <x:v>fact_candidate.coordination_status</x:v>
+        <x:v>fact_candidate.status</x:v>
       </x:c>
       <x:c r="B114" s="25" t="str">
-        <x:v>AGREED</x:v>
+        <x:v>MATERIALIZED</x:v>
       </x:c>
       <x:c r="C114" s="25" t="str">
-        <x:v>협의 상태: AGREED</x:v>
+        <x:v>후보 처리 상태: MATERIALIZED</x:v>
       </x:c>
       <x:c r="D114" s="25" t="str">
-        <x:v>fact_candidate.coordination_status의 상태·분기 판단</x:v>
+        <x:v>fact_candidate.status의 상태·분기 판단</x:v>
       </x:c>
       <x:c r="E114" s="25" t="str">
         <x:v>정의되지 않은 값을 성공으로 처리하지 않음</x:v>
@@ -9672,33 +10642,33 @@
     </x:row>
     <x:row r="115">
       <x:c r="A115" s="26" t="str">
-        <x:v>fact_candidate.coordination_status</x:v>
+        <x:v>fact_candidate.status</x:v>
       </x:c>
       <x:c r="B115" s="26" t="str">
-        <x:v>DISAGREED</x:v>
+        <x:v>REJECTED</x:v>
       </x:c>
       <x:c r="C115" s="26" t="str">
-        <x:v>협의 상태: DISAGREED</x:v>
+        <x:v>후보 처리 상태: REJECTED</x:v>
       </x:c>
       <x:c r="D115" s="26" t="str">
-        <x:v>fact_candidate.coordination_status의 상태·분기 판단</x:v>
+        <x:v>fact_candidate.status의 상태·분기 판단</x:v>
       </x:c>
       <x:c r="E115" s="26" t="str">
-        <x:v>정의되지 않은 값을 성공으로 처리하지 않음</x:v>
+        <x:v>검색·반영에서 제외</x:v>
       </x:c>
     </x:row>
     <x:row r="116">
       <x:c r="A116" s="25" t="str">
-        <x:v>fact_candidate.coordination_status</x:v>
+        <x:v>fact_candidate.status</x:v>
       </x:c>
       <x:c r="B116" s="25" t="str">
-        <x:v>SENIOR_UNREACHABLE</x:v>
+        <x:v>EXPIRED</x:v>
       </x:c>
       <x:c r="C116" s="25" t="str">
-        <x:v>협의 상태: SENIOR_UNREACHABLE</x:v>
+        <x:v>후보 처리 상태: EXPIRED</x:v>
       </x:c>
       <x:c r="D116" s="25" t="str">
-        <x:v>fact_candidate.coordination_status의 상태·분기 판단</x:v>
+        <x:v>fact_candidate.status의 상태·분기 판단</x:v>
       </x:c>
       <x:c r="E116" s="25" t="str">
         <x:v>정의되지 않은 값을 성공으로 처리하지 않음</x:v>
@@ -9706,16 +10676,16 @@
     </x:row>
     <x:row r="117">
       <x:c r="A117" s="26" t="str">
-        <x:v>fact_candidate.coordination_status</x:v>
+        <x:v>fact_candidate.clarification_reason</x:v>
       </x:c>
       <x:c r="B117" s="26" t="str">
-        <x:v>GUARDIAN_OVERRIDE_CONFIRMED</x:v>
+        <x:v>MISSING_REQUIRED_FIELD</x:v>
       </x:c>
       <x:c r="C117" s="26" t="str">
-        <x:v>협의 상태: GUARDIAN_OVERRIDE_CONFIRMED</x:v>
+        <x:v>재질의 사유: MISSING_REQUIRED_FIELD</x:v>
       </x:c>
       <x:c r="D117" s="26" t="str">
-        <x:v>fact_candidate.coordination_status의 상태·분기 판단</x:v>
+        <x:v>fact_candidate.clarification_reason의 상태·분기 판단</x:v>
       </x:c>
       <x:c r="E117" s="26" t="str">
         <x:v>정의되지 않은 값을 성공으로 처리하지 않음</x:v>
@@ -9723,16 +10693,16 @@
     </x:row>
     <x:row r="118">
       <x:c r="A118" s="25" t="str">
-        <x:v>fact_candidate.coordination_status</x:v>
+        <x:v>fact_candidate.clarification_reason</x:v>
       </x:c>
       <x:c r="B118" s="25" t="str">
-        <x:v>COMPLETED</x:v>
+        <x:v>AMBIGUOUS_VALUE</x:v>
       </x:c>
       <x:c r="C118" s="25" t="str">
-        <x:v>협의 상태: COMPLETED</x:v>
+        <x:v>재질의 사유: AMBIGUOUS_VALUE</x:v>
       </x:c>
       <x:c r="D118" s="25" t="str">
-        <x:v>fact_candidate.coordination_status의 상태·분기 판단</x:v>
+        <x:v>fact_candidate.clarification_reason의 상태·분기 판단</x:v>
       </x:c>
       <x:c r="E118" s="25" t="str">
         <x:v>정의되지 않은 값을 성공으로 처리하지 않음</x:v>
@@ -9740,16 +10710,16 @@
     </x:row>
     <x:row r="119">
       <x:c r="A119" s="26" t="str">
-        <x:v>fact_candidate.senior_position</x:v>
+        <x:v>fact_candidate.clarification_reason</x:v>
       </x:c>
       <x:c r="B119" s="26" t="str">
-        <x:v>NOT_REQUESTED</x:v>
+        <x:v>LOW_RECOGNITION_CONFIDENCE</x:v>
       </x:c>
       <x:c r="C119" s="26" t="str">
-        <x:v>시니어 입장: NOT_REQUESTED</x:v>
+        <x:v>재질의 사유: LOW_RECOGNITION_CONFIDENCE</x:v>
       </x:c>
       <x:c r="D119" s="26" t="str">
-        <x:v>fact_candidate.senior_position의 상태·분기 판단</x:v>
+        <x:v>fact_candidate.clarification_reason의 상태·분기 판단</x:v>
       </x:c>
       <x:c r="E119" s="26" t="str">
         <x:v>정의되지 않은 값을 성공으로 처리하지 않음</x:v>
@@ -9757,16 +10727,16 @@
     </x:row>
     <x:row r="120">
       <x:c r="A120" s="25" t="str">
-        <x:v>fact_candidate.senior_position</x:v>
+        <x:v>fact_candidate.clarification_reason</x:v>
       </x:c>
       <x:c r="B120" s="25" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>CONFLICT_WITH_EXISTING_DATA</x:v>
       </x:c>
       <x:c r="C120" s="25" t="str">
-        <x:v>시니어 입장: PENDING</x:v>
+        <x:v>재질의 사유: CONFLICT_WITH_EXISTING_DATA</x:v>
       </x:c>
       <x:c r="D120" s="25" t="str">
-        <x:v>fact_candidate.senior_position의 상태·분기 판단</x:v>
+        <x:v>fact_candidate.clarification_reason의 상태·분기 판단</x:v>
       </x:c>
       <x:c r="E120" s="25" t="str">
         <x:v>정의되지 않은 값을 성공으로 처리하지 않음</x:v>
@@ -9774,16 +10744,16 @@
     </x:row>
     <x:row r="121">
       <x:c r="A121" s="26" t="str">
-        <x:v>fact_candidate.senior_position</x:v>
+        <x:v>fact_candidate.clarification_reason</x:v>
       </x:c>
       <x:c r="B121" s="26" t="str">
-        <x:v>AGREED</x:v>
+        <x:v>SENSITIVE_INFORMATION_CONFIRMATION</x:v>
       </x:c>
       <x:c r="C121" s="26" t="str">
-        <x:v>시니어 입장: AGREED</x:v>
+        <x:v>재질의 사유: SENSITIVE_INFORMATION_CONFIRMATION</x:v>
       </x:c>
       <x:c r="D121" s="26" t="str">
-        <x:v>fact_candidate.senior_position의 상태·분기 판단</x:v>
+        <x:v>fact_candidate.clarification_reason의 상태·분기 판단</x:v>
       </x:c>
       <x:c r="E121" s="26" t="str">
         <x:v>정의되지 않은 값을 성공으로 처리하지 않음</x:v>
@@ -9791,16 +10761,16 @@
     </x:row>
     <x:row r="122">
       <x:c r="A122" s="25" t="str">
-        <x:v>fact_candidate.senior_position</x:v>
+        <x:v>fact_candidate.coordination_status</x:v>
       </x:c>
       <x:c r="B122" s="25" t="str">
-        <x:v>DISAGREED</x:v>
+        <x:v>NOT_REQUIRED</x:v>
       </x:c>
       <x:c r="C122" s="25" t="str">
-        <x:v>시니어 입장: DISAGREED</x:v>
+        <x:v>협의 상태: NOT_REQUIRED</x:v>
       </x:c>
       <x:c r="D122" s="25" t="str">
-        <x:v>fact_candidate.senior_position의 상태·분기 판단</x:v>
+        <x:v>fact_candidate.coordination_status의 상태·분기 판단</x:v>
       </x:c>
       <x:c r="E122" s="25" t="str">
         <x:v>정의되지 않은 값을 성공으로 처리하지 않음</x:v>
@@ -9808,16 +10778,16 @@
     </x:row>
     <x:row r="123">
       <x:c r="A123" s="26" t="str">
-        <x:v>fact_candidate.senior_position</x:v>
+        <x:v>fact_candidate.coordination_status</x:v>
       </x:c>
       <x:c r="B123" s="26" t="str">
-        <x:v>UNREACHABLE</x:v>
+        <x:v>COORDINATION_REQUIRED</x:v>
       </x:c>
       <x:c r="C123" s="26" t="str">
-        <x:v>시니어 입장: UNREACHABLE</x:v>
+        <x:v>협의 상태: COORDINATION_REQUIRED</x:v>
       </x:c>
       <x:c r="D123" s="26" t="str">
-        <x:v>fact_candidate.senior_position의 상태·분기 판단</x:v>
+        <x:v>fact_candidate.coordination_status의 상태·분기 판단</x:v>
       </x:c>
       <x:c r="E123" s="26" t="str">
         <x:v>정의되지 않은 값을 성공으로 처리하지 않음</x:v>
@@ -9825,16 +10795,16 @@
     </x:row>
     <x:row r="124">
       <x:c r="A124" s="25" t="str">
-        <x:v>fact_candidate.primary_guardian_decision</x:v>
+        <x:v>fact_candidate.coordination_status</x:v>
       </x:c>
       <x:c r="B124" s="25" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>WAITING_PRIMARY_GUARDIAN</x:v>
       </x:c>
       <x:c r="C124" s="25" t="str">
-        <x:v>PRIMARY 결정: PENDING</x:v>
+        <x:v>협의 상태: WAITING_PRIMARY_GUARDIAN</x:v>
       </x:c>
       <x:c r="D124" s="25" t="str">
-        <x:v>fact_candidate.primary_guardian_decision의 상태·분기 판단</x:v>
+        <x:v>fact_candidate.coordination_status의 상태·분기 판단</x:v>
       </x:c>
       <x:c r="E124" s="25" t="str">
         <x:v>정의되지 않은 값을 성공으로 처리하지 않음</x:v>
@@ -9842,16 +10812,16 @@
     </x:row>
     <x:row r="125">
       <x:c r="A125" s="26" t="str">
-        <x:v>fact_candidate.primary_guardian_decision</x:v>
+        <x:v>fact_candidate.coordination_status</x:v>
       </x:c>
       <x:c r="B125" s="26" t="str">
-        <x:v>CONFIRMED_EXISTING_VALUE</x:v>
+        <x:v>WAITING_SENIOR</x:v>
       </x:c>
       <x:c r="C125" s="26" t="str">
-        <x:v>PRIMARY 결정: CONFIRMED_EXISTING_VALUE</x:v>
+        <x:v>협의 상태: WAITING_SENIOR</x:v>
       </x:c>
       <x:c r="D125" s="26" t="str">
-        <x:v>fact_candidate.primary_guardian_decision의 상태·분기 판단</x:v>
+        <x:v>fact_candidate.coordination_status의 상태·분기 판단</x:v>
       </x:c>
       <x:c r="E125" s="26" t="str">
         <x:v>정의되지 않은 값을 성공으로 처리하지 않음</x:v>
@@ -9859,16 +10829,16 @@
     </x:row>
     <x:row r="126">
       <x:c r="A126" s="25" t="str">
-        <x:v>fact_candidate.primary_guardian_decision</x:v>
+        <x:v>fact_candidate.coordination_status</x:v>
       </x:c>
       <x:c r="B126" s="25" t="str">
-        <x:v>CONFIRMED_PROPOSED_VALUE</x:v>
+        <x:v>AGREED</x:v>
       </x:c>
       <x:c r="C126" s="25" t="str">
-        <x:v>PRIMARY 결정: CONFIRMED_PROPOSED_VALUE</x:v>
+        <x:v>협의 상태: AGREED</x:v>
       </x:c>
       <x:c r="D126" s="25" t="str">
-        <x:v>fact_candidate.primary_guardian_decision의 상태·분기 판단</x:v>
+        <x:v>fact_candidate.coordination_status의 상태·분기 판단</x:v>
       </x:c>
       <x:c r="E126" s="25" t="str">
         <x:v>정의되지 않은 값을 성공으로 처리하지 않음</x:v>
@@ -9876,16 +10846,16 @@
     </x:row>
     <x:row r="127">
       <x:c r="A127" s="26" t="str">
-        <x:v>fact_candidate.primary_guardian_decision</x:v>
+        <x:v>fact_candidate.coordination_status</x:v>
       </x:c>
       <x:c r="B127" s="26" t="str">
-        <x:v>REVISED_VALUE</x:v>
+        <x:v>DISAGREED</x:v>
       </x:c>
       <x:c r="C127" s="26" t="str">
-        <x:v>PRIMARY 결정: REVISED_VALUE</x:v>
+        <x:v>협의 상태: DISAGREED</x:v>
       </x:c>
       <x:c r="D127" s="26" t="str">
-        <x:v>fact_candidate.primary_guardian_decision의 상태·분기 판단</x:v>
+        <x:v>fact_candidate.coordination_status의 상태·분기 판단</x:v>
       </x:c>
       <x:c r="E127" s="26" t="str">
         <x:v>정의되지 않은 값을 성공으로 처리하지 않음</x:v>
@@ -9893,16 +10863,16 @@
     </x:row>
     <x:row r="128">
       <x:c r="A128" s="25" t="str">
-        <x:v>fact_candidate.primary_guardian_decision</x:v>
+        <x:v>fact_candidate.coordination_status</x:v>
       </x:c>
       <x:c r="B128" s="25" t="str">
-        <x:v>CANCELLED_CHANGE</x:v>
+        <x:v>SENIOR_UNREACHABLE</x:v>
       </x:c>
       <x:c r="C128" s="25" t="str">
-        <x:v>PRIMARY 결정: CANCELLED_CHANGE</x:v>
+        <x:v>협의 상태: SENIOR_UNREACHABLE</x:v>
       </x:c>
       <x:c r="D128" s="25" t="str">
-        <x:v>fact_candidate.primary_guardian_decision의 상태·분기 판단</x:v>
+        <x:v>fact_candidate.coordination_status의 상태·분기 판단</x:v>
       </x:c>
       <x:c r="E128" s="25" t="str">
         <x:v>정의되지 않은 값을 성공으로 처리하지 않음</x:v>
@@ -9910,16 +10880,16 @@
     </x:row>
     <x:row r="129">
       <x:c r="A129" s="26" t="str">
-        <x:v>fact_candidate.unreachable_reason</x:v>
+        <x:v>fact_candidate.coordination_status</x:v>
       </x:c>
       <x:c r="B129" s="26" t="str">
-        <x:v>NO_RESPONSE</x:v>
+        <x:v>GUARDIAN_OVERRIDE_CONFIRMED</x:v>
       </x:c>
       <x:c r="C129" s="26" t="str">
-        <x:v>연락 불가 사유: NO_RESPONSE</x:v>
+        <x:v>협의 상태: GUARDIAN_OVERRIDE_CONFIRMED</x:v>
       </x:c>
       <x:c r="D129" s="26" t="str">
-        <x:v>fact_candidate.unreachable_reason의 상태·분기 판단</x:v>
+        <x:v>fact_candidate.coordination_status의 상태·분기 판단</x:v>
       </x:c>
       <x:c r="E129" s="26" t="str">
         <x:v>정의되지 않은 값을 성공으로 처리하지 않음</x:v>
@@ -9927,16 +10897,16 @@
     </x:row>
     <x:row r="130">
       <x:c r="A130" s="25" t="str">
-        <x:v>fact_candidate.unreachable_reason</x:v>
+        <x:v>fact_candidate.coordination_status</x:v>
       </x:c>
       <x:c r="B130" s="25" t="str">
-        <x:v>PHONE_UNAVAILABLE</x:v>
+        <x:v>COMPLETED</x:v>
       </x:c>
       <x:c r="C130" s="25" t="str">
-        <x:v>연락 불가 사유: PHONE_UNAVAILABLE</x:v>
+        <x:v>협의 상태: COMPLETED</x:v>
       </x:c>
       <x:c r="D130" s="25" t="str">
-        <x:v>fact_candidate.unreachable_reason의 상태·분기 판단</x:v>
+        <x:v>fact_candidate.coordination_status의 상태·분기 판단</x:v>
       </x:c>
       <x:c r="E130" s="25" t="str">
         <x:v>정의되지 않은 값을 성공으로 처리하지 않음</x:v>
@@ -9944,16 +10914,16 @@
     </x:row>
     <x:row r="131">
       <x:c r="A131" s="26" t="str">
-        <x:v>fact_candidate.unreachable_reason</x:v>
+        <x:v>fact_candidate.senior_position</x:v>
       </x:c>
       <x:c r="B131" s="26" t="str">
-        <x:v>TEMPORARY_HEALTH_CONDITION</x:v>
+        <x:v>NOT_REQUESTED</x:v>
       </x:c>
       <x:c r="C131" s="26" t="str">
-        <x:v>연락 불가 사유: TEMPORARY_HEALTH_CONDITION</x:v>
+        <x:v>시니어 입장: NOT_REQUESTED</x:v>
       </x:c>
       <x:c r="D131" s="26" t="str">
-        <x:v>fact_candidate.unreachable_reason의 상태·분기 판단</x:v>
+        <x:v>fact_candidate.senior_position의 상태·분기 판단</x:v>
       </x:c>
       <x:c r="E131" s="26" t="str">
         <x:v>정의되지 않은 값을 성공으로 처리하지 않음</x:v>
@@ -9961,16 +10931,16 @@
     </x:row>
     <x:row r="132">
       <x:c r="A132" s="25" t="str">
-        <x:v>fact_candidate.unreachable_reason</x:v>
+        <x:v>fact_candidate.senior_position</x:v>
       </x:c>
       <x:c r="B132" s="25" t="str">
-        <x:v>COMMUNICATION_DIFFICULTY</x:v>
+        <x:v>PENDING</x:v>
       </x:c>
       <x:c r="C132" s="25" t="str">
-        <x:v>연락 불가 사유: COMMUNICATION_DIFFICULTY</x:v>
+        <x:v>시니어 입장: PENDING</x:v>
       </x:c>
       <x:c r="D132" s="25" t="str">
-        <x:v>fact_candidate.unreachable_reason의 상태·분기 판단</x:v>
+        <x:v>fact_candidate.senior_position의 상태·분기 판단</x:v>
       </x:c>
       <x:c r="E132" s="25" t="str">
         <x:v>정의되지 않은 값을 성공으로 처리하지 않음</x:v>
@@ -9978,16 +10948,16 @@
     </x:row>
     <x:row r="133">
       <x:c r="A133" s="26" t="str">
-        <x:v>fact_candidate.unreachable_reason</x:v>
+        <x:v>fact_candidate.senior_position</x:v>
       </x:c>
       <x:c r="B133" s="26" t="str">
-        <x:v>OTHER</x:v>
+        <x:v>AGREED</x:v>
       </x:c>
       <x:c r="C133" s="26" t="str">
-        <x:v>연락 불가 사유: OTHER</x:v>
+        <x:v>시니어 입장: AGREED</x:v>
       </x:c>
       <x:c r="D133" s="26" t="str">
-        <x:v>fact_candidate.unreachable_reason의 상태·분기 판단</x:v>
+        <x:v>fact_candidate.senior_position의 상태·분기 판단</x:v>
       </x:c>
       <x:c r="E133" s="26" t="str">
         <x:v>정의되지 않은 값을 성공으로 처리하지 않음</x:v>
@@ -9995,16 +10965,16 @@
     </x:row>
     <x:row r="134">
       <x:c r="A134" s="25" t="str">
-        <x:v>memory.memory_type</x:v>
+        <x:v>fact_candidate.senior_position</x:v>
       </x:c>
       <x:c r="B134" s="25" t="str">
-        <x:v>PERSONAL_RELATIONSHIP</x:v>
+        <x:v>DISAGREED</x:v>
       </x:c>
       <x:c r="C134" s="25" t="str">
-        <x:v>장기 기억 유형: PERSONAL_RELATIONSHIP</x:v>
+        <x:v>시니어 입장: DISAGREED</x:v>
       </x:c>
       <x:c r="D134" s="25" t="str">
-        <x:v>memory.memory_type의 상태·분기 판단</x:v>
+        <x:v>fact_candidate.senior_position의 상태·분기 판단</x:v>
       </x:c>
       <x:c r="E134" s="25" t="str">
         <x:v>정의되지 않은 값을 성공으로 처리하지 않음</x:v>
@@ -10012,16 +10982,16 @@
     </x:row>
     <x:row r="135">
       <x:c r="A135" s="26" t="str">
-        <x:v>memory.memory_type</x:v>
+        <x:v>fact_candidate.senior_position</x:v>
       </x:c>
       <x:c r="B135" s="26" t="str">
-        <x:v>PREFERENCE</x:v>
+        <x:v>UNREACHABLE</x:v>
       </x:c>
       <x:c r="C135" s="26" t="str">
-        <x:v>장기 기억 유형: PREFERENCE</x:v>
+        <x:v>시니어 입장: UNREACHABLE</x:v>
       </x:c>
       <x:c r="D135" s="26" t="str">
-        <x:v>memory.memory_type의 상태·분기 판단</x:v>
+        <x:v>fact_candidate.senior_position의 상태·분기 판단</x:v>
       </x:c>
       <x:c r="E135" s="26" t="str">
         <x:v>정의되지 않은 값을 성공으로 처리하지 않음</x:v>
@@ -10029,16 +10999,16 @@
     </x:row>
     <x:row r="136">
       <x:c r="A136" s="25" t="str">
-        <x:v>memory.memory_type</x:v>
+        <x:v>fact_candidate.primary_guardian_decision</x:v>
       </x:c>
       <x:c r="B136" s="25" t="str">
-        <x:v>HOBBY</x:v>
+        <x:v>PENDING</x:v>
       </x:c>
       <x:c r="C136" s="25" t="str">
-        <x:v>장기 기억 유형: HOBBY</x:v>
+        <x:v>PRIMARY 결정: PENDING</x:v>
       </x:c>
       <x:c r="D136" s="25" t="str">
-        <x:v>memory.memory_type의 상태·분기 판단</x:v>
+        <x:v>fact_candidate.primary_guardian_decision의 상태·분기 판단</x:v>
       </x:c>
       <x:c r="E136" s="25" t="str">
         <x:v>정의되지 않은 값을 성공으로 처리하지 않음</x:v>
@@ -10046,16 +11016,16 @@
     </x:row>
     <x:row r="137">
       <x:c r="A137" s="26" t="str">
-        <x:v>memory.memory_type</x:v>
+        <x:v>fact_candidate.primary_guardian_decision</x:v>
       </x:c>
       <x:c r="B137" s="26" t="str">
-        <x:v>DAILY_ROUTINE</x:v>
+        <x:v>CONFIRMED_EXISTING_VALUE</x:v>
       </x:c>
       <x:c r="C137" s="26" t="str">
-        <x:v>장기 기억 유형: DAILY_ROUTINE</x:v>
+        <x:v>PRIMARY 결정: CONFIRMED_EXISTING_VALUE</x:v>
       </x:c>
       <x:c r="D137" s="26" t="str">
-        <x:v>memory.memory_type의 상태·분기 판단</x:v>
+        <x:v>fact_candidate.primary_guardian_decision의 상태·분기 판단</x:v>
       </x:c>
       <x:c r="E137" s="26" t="str">
         <x:v>정의되지 않은 값을 성공으로 처리하지 않음</x:v>
@@ -10063,16 +11033,16 @@
     </x:row>
     <x:row r="138">
       <x:c r="A138" s="25" t="str">
-        <x:v>memory.memory_type</x:v>
+        <x:v>fact_candidate.primary_guardian_decision</x:v>
       </x:c>
       <x:c r="B138" s="25" t="str">
-        <x:v>LIFE_EVENT</x:v>
+        <x:v>CONFIRMED_PROPOSED_VALUE</x:v>
       </x:c>
       <x:c r="C138" s="25" t="str">
-        <x:v>장기 기억 유형: LIFE_EVENT</x:v>
+        <x:v>PRIMARY 결정: CONFIRMED_PROPOSED_VALUE</x:v>
       </x:c>
       <x:c r="D138" s="25" t="str">
-        <x:v>memory.memory_type의 상태·분기 판단</x:v>
+        <x:v>fact_candidate.primary_guardian_decision의 상태·분기 판단</x:v>
       </x:c>
       <x:c r="E138" s="25" t="str">
         <x:v>정의되지 않은 값을 성공으로 처리하지 않음</x:v>
@@ -10080,16 +11050,16 @@
     </x:row>
     <x:row r="139">
       <x:c r="A139" s="26" t="str">
-        <x:v>memory.memory_type</x:v>
+        <x:v>fact_candidate.primary_guardian_decision</x:v>
       </x:c>
       <x:c r="B139" s="26" t="str">
-        <x:v>FAMILY_MEMORY</x:v>
+        <x:v>REVISED_VALUE</x:v>
       </x:c>
       <x:c r="C139" s="26" t="str">
-        <x:v>장기 기억 유형: FAMILY_MEMORY</x:v>
+        <x:v>PRIMARY 결정: REVISED_VALUE</x:v>
       </x:c>
       <x:c r="D139" s="26" t="str">
-        <x:v>memory.memory_type의 상태·분기 판단</x:v>
+        <x:v>fact_candidate.primary_guardian_decision의 상태·분기 판단</x:v>
       </x:c>
       <x:c r="E139" s="26" t="str">
         <x:v>정의되지 않은 값을 성공으로 처리하지 않음</x:v>
@@ -10097,16 +11067,16 @@
     </x:row>
     <x:row r="140">
       <x:c r="A140" s="25" t="str">
-        <x:v>memory.memory_type</x:v>
+        <x:v>fact_candidate.primary_guardian_decision</x:v>
       </x:c>
       <x:c r="B140" s="25" t="str">
-        <x:v>EMOTIONAL_EVENT</x:v>
+        <x:v>CANCELLED_CHANGE</x:v>
       </x:c>
       <x:c r="C140" s="25" t="str">
-        <x:v>장기 기억 유형: EMOTIONAL_EVENT</x:v>
+        <x:v>PRIMARY 결정: CANCELLED_CHANGE</x:v>
       </x:c>
       <x:c r="D140" s="25" t="str">
-        <x:v>memory.memory_type의 상태·분기 판단</x:v>
+        <x:v>fact_candidate.primary_guardian_decision의 상태·분기 판단</x:v>
       </x:c>
       <x:c r="E140" s="25" t="str">
         <x:v>정의되지 않은 값을 성공으로 처리하지 않음</x:v>
@@ -10114,16 +11084,16 @@
     </x:row>
     <x:row r="141">
       <x:c r="A141" s="26" t="str">
-        <x:v>memory.memory_type</x:v>
+        <x:v>fact_candidate.unreachable_reason</x:v>
       </x:c>
       <x:c r="B141" s="26" t="str">
-        <x:v>OTHER</x:v>
+        <x:v>NO_RESPONSE</x:v>
       </x:c>
       <x:c r="C141" s="26" t="str">
-        <x:v>장기 기억 유형: OTHER</x:v>
+        <x:v>연락 불가 사유: NO_RESPONSE</x:v>
       </x:c>
       <x:c r="D141" s="26" t="str">
-        <x:v>memory.memory_type의 상태·분기 판단</x:v>
+        <x:v>fact_candidate.unreachable_reason의 상태·분기 판단</x:v>
       </x:c>
       <x:c r="E141" s="26" t="str">
         <x:v>정의되지 않은 값을 성공으로 처리하지 않음</x:v>
@@ -10131,16 +11101,16 @@
     </x:row>
     <x:row r="142">
       <x:c r="A142" s="25" t="str">
-        <x:v>memory.lifecycle_status</x:v>
+        <x:v>fact_candidate.unreachable_reason</x:v>
       </x:c>
       <x:c r="B142" s="25" t="str">
-        <x:v>ACTIVE</x:v>
+        <x:v>PHONE_UNAVAILABLE</x:v>
       </x:c>
       <x:c r="C142" s="25" t="str">
-        <x:v>기억 수명: ACTIVE</x:v>
+        <x:v>연락 불가 사유: PHONE_UNAVAILABLE</x:v>
       </x:c>
       <x:c r="D142" s="25" t="str">
-        <x:v>memory.lifecycle_status의 상태·분기 판단</x:v>
+        <x:v>fact_candidate.unreachable_reason의 상태·분기 판단</x:v>
       </x:c>
       <x:c r="E142" s="25" t="str">
         <x:v>정의되지 않은 값을 성공으로 처리하지 않음</x:v>
@@ -10148,16 +11118,16 @@
     </x:row>
     <x:row r="143">
       <x:c r="A143" s="26" t="str">
-        <x:v>memory.lifecycle_status</x:v>
+        <x:v>fact_candidate.unreachable_reason</x:v>
       </x:c>
       <x:c r="B143" s="26" t="str">
-        <x:v>DISPUTED</x:v>
+        <x:v>TEMPORARY_HEALTH_CONDITION</x:v>
       </x:c>
       <x:c r="C143" s="26" t="str">
-        <x:v>기억 수명: DISPUTED</x:v>
+        <x:v>연락 불가 사유: TEMPORARY_HEALTH_CONDITION</x:v>
       </x:c>
       <x:c r="D143" s="26" t="str">
-        <x:v>memory.lifecycle_status의 상태·분기 판단</x:v>
+        <x:v>fact_candidate.unreachable_reason의 상태·분기 판단</x:v>
       </x:c>
       <x:c r="E143" s="26" t="str">
         <x:v>정의되지 않은 값을 성공으로 처리하지 않음</x:v>
@@ -10165,16 +11135,16 @@
     </x:row>
     <x:row r="144">
       <x:c r="A144" s="25" t="str">
-        <x:v>memory.lifecycle_status</x:v>
+        <x:v>fact_candidate.unreachable_reason</x:v>
       </x:c>
       <x:c r="B144" s="25" t="str">
-        <x:v>SUPERSEDED</x:v>
+        <x:v>COMMUNICATION_DIFFICULTY</x:v>
       </x:c>
       <x:c r="C144" s="25" t="str">
-        <x:v>기억 수명: SUPERSEDED</x:v>
+        <x:v>연락 불가 사유: COMMUNICATION_DIFFICULTY</x:v>
       </x:c>
       <x:c r="D144" s="25" t="str">
-        <x:v>memory.lifecycle_status의 상태·분기 판단</x:v>
+        <x:v>fact_candidate.unreachable_reason의 상태·분기 판단</x:v>
       </x:c>
       <x:c r="E144" s="25" t="str">
         <x:v>정의되지 않은 값을 성공으로 처리하지 않음</x:v>
@@ -10182,16 +11152,16 @@
     </x:row>
     <x:row r="145">
       <x:c r="A145" s="26" t="str">
-        <x:v>memory.lifecycle_status</x:v>
+        <x:v>fact_candidate.unreachable_reason</x:v>
       </x:c>
       <x:c r="B145" s="26" t="str">
-        <x:v>EXPIRED</x:v>
+        <x:v>OTHER</x:v>
       </x:c>
       <x:c r="C145" s="26" t="str">
-        <x:v>기억 수명: EXPIRED</x:v>
+        <x:v>연락 불가 사유: OTHER</x:v>
       </x:c>
       <x:c r="D145" s="26" t="str">
-        <x:v>memory.lifecycle_status의 상태·분기 판단</x:v>
+        <x:v>fact_candidate.unreachable_reason의 상태·분기 판단</x:v>
       </x:c>
       <x:c r="E145" s="26" t="str">
         <x:v>정의되지 않은 값을 성공으로 처리하지 않음</x:v>
@@ -10199,16 +11169,16 @@
     </x:row>
     <x:row r="146">
       <x:c r="A146" s="25" t="str">
-        <x:v>memory.lifecycle_status</x:v>
+        <x:v>memory.memory_type</x:v>
       </x:c>
       <x:c r="B146" s="25" t="str">
-        <x:v>DELETED</x:v>
+        <x:v>PERSONAL_RELATIONSHIP</x:v>
       </x:c>
       <x:c r="C146" s="25" t="str">
-        <x:v>기억 수명: DELETED</x:v>
+        <x:v>장기 기억 유형: PERSONAL_RELATIONSHIP</x:v>
       </x:c>
       <x:c r="D146" s="25" t="str">
-        <x:v>memory.lifecycle_status의 상태·분기 판단</x:v>
+        <x:v>memory.memory_type의 상태·분기 판단</x:v>
       </x:c>
       <x:c r="E146" s="25" t="str">
         <x:v>정의되지 않은 값을 성공으로 처리하지 않음</x:v>
@@ -10216,16 +11186,16 @@
     </x:row>
     <x:row r="147">
       <x:c r="A147" s="26" t="str">
-        <x:v>memory.visibility</x:v>
+        <x:v>memory.memory_type</x:v>
       </x:c>
       <x:c r="B147" s="26" t="str">
-        <x:v>PRIVATE</x:v>
+        <x:v>PREFERENCE</x:v>
       </x:c>
       <x:c r="C147" s="26" t="str">
-        <x:v>기억 공개 범위: PRIVATE</x:v>
+        <x:v>장기 기억 유형: PREFERENCE</x:v>
       </x:c>
       <x:c r="D147" s="26" t="str">
-        <x:v>memory.visibility의 상태·분기 판단</x:v>
+        <x:v>memory.memory_type의 상태·분기 판단</x:v>
       </x:c>
       <x:c r="E147" s="26" t="str">
         <x:v>정의되지 않은 값을 성공으로 처리하지 않음</x:v>
@@ -10233,16 +11203,16 @@
     </x:row>
     <x:row r="148">
       <x:c r="A148" s="25" t="str">
-        <x:v>memory.visibility</x:v>
+        <x:v>memory.memory_type</x:v>
       </x:c>
       <x:c r="B148" s="25" t="str">
-        <x:v>SHARED_WITH_PRIMARY</x:v>
+        <x:v>HOBBY</x:v>
       </x:c>
       <x:c r="C148" s="25" t="str">
-        <x:v>기억 공개 범위: SHARED_WITH_PRIMARY</x:v>
+        <x:v>장기 기억 유형: HOBBY</x:v>
       </x:c>
       <x:c r="D148" s="25" t="str">
-        <x:v>memory.visibility의 상태·분기 판단</x:v>
+        <x:v>memory.memory_type의 상태·분기 판단</x:v>
       </x:c>
       <x:c r="E148" s="25" t="str">
         <x:v>정의되지 않은 값을 성공으로 처리하지 않음</x:v>
@@ -10250,16 +11220,16 @@
     </x:row>
     <x:row r="149">
       <x:c r="A149" s="26" t="str">
-        <x:v>memory.visibility</x:v>
+        <x:v>memory.memory_type</x:v>
       </x:c>
       <x:c r="B149" s="26" t="str">
-        <x:v>SHARED_WITH_GUARDIANS</x:v>
+        <x:v>DAILY_ROUTINE</x:v>
       </x:c>
       <x:c r="C149" s="26" t="str">
-        <x:v>기억 공개 범위: SHARED_WITH_GUARDIANS</x:v>
+        <x:v>장기 기억 유형: DAILY_ROUTINE</x:v>
       </x:c>
       <x:c r="D149" s="26" t="str">
-        <x:v>memory.visibility의 상태·분기 판단</x:v>
+        <x:v>memory.memory_type의 상태·분기 판단</x:v>
       </x:c>
       <x:c r="E149" s="26" t="str">
         <x:v>정의되지 않은 값을 성공으로 처리하지 않음</x:v>
@@ -10267,16 +11237,16 @@
     </x:row>
     <x:row r="150">
       <x:c r="A150" s="25" t="str">
-        <x:v>care_record.record_type</x:v>
+        <x:v>memory.memory_type</x:v>
       </x:c>
       <x:c r="B150" s="25" t="str">
-        <x:v>HEALTH_CONDITION</x:v>
+        <x:v>LIFE_EVENT</x:v>
       </x:c>
       <x:c r="C150" s="25" t="str">
-        <x:v>돌봄 기록 유형: HEALTH_CONDITION</x:v>
+        <x:v>장기 기억 유형: LIFE_EVENT</x:v>
       </x:c>
       <x:c r="D150" s="25" t="str">
-        <x:v>care_record.record_type의 상태·분기 판단</x:v>
+        <x:v>memory.memory_type의 상태·분기 판단</x:v>
       </x:c>
       <x:c r="E150" s="25" t="str">
         <x:v>정의되지 않은 값을 성공으로 처리하지 않음</x:v>
@@ -10284,16 +11254,16 @@
     </x:row>
     <x:row r="151">
       <x:c r="A151" s="26" t="str">
-        <x:v>care_record.record_type</x:v>
+        <x:v>memory.memory_type</x:v>
       </x:c>
       <x:c r="B151" s="26" t="str">
-        <x:v>ALLERGY</x:v>
+        <x:v>FAMILY_MEMORY</x:v>
       </x:c>
       <x:c r="C151" s="26" t="str">
-        <x:v>돌봄 기록 유형: ALLERGY</x:v>
+        <x:v>장기 기억 유형: FAMILY_MEMORY</x:v>
       </x:c>
       <x:c r="D151" s="26" t="str">
-        <x:v>care_record.record_type의 상태·분기 판단</x:v>
+        <x:v>memory.memory_type의 상태·분기 판단</x:v>
       </x:c>
       <x:c r="E151" s="26" t="str">
         <x:v>정의되지 않은 값을 성공으로 처리하지 않음</x:v>
@@ -10301,16 +11271,16 @@
     </x:row>
     <x:row r="152">
       <x:c r="A152" s="25" t="str">
-        <x:v>care_record.record_type</x:v>
+        <x:v>memory.memory_type</x:v>
       </x:c>
       <x:c r="B152" s="25" t="str">
-        <x:v>PHYSICAL_LIMITATION</x:v>
+        <x:v>EMOTIONAL_EVENT</x:v>
       </x:c>
       <x:c r="C152" s="25" t="str">
-        <x:v>돌봄 기록 유형: PHYSICAL_LIMITATION</x:v>
+        <x:v>장기 기억 유형: EMOTIONAL_EVENT</x:v>
       </x:c>
       <x:c r="D152" s="25" t="str">
-        <x:v>care_record.record_type의 상태·분기 판단</x:v>
+        <x:v>memory.memory_type의 상태·분기 판단</x:v>
       </x:c>
       <x:c r="E152" s="25" t="str">
         <x:v>정의되지 않은 값을 성공으로 처리하지 않음</x:v>
@@ -10318,16 +11288,16 @@
     </x:row>
     <x:row r="153">
       <x:c r="A153" s="26" t="str">
-        <x:v>care_record.record_type</x:v>
+        <x:v>memory.memory_type</x:v>
       </x:c>
       <x:c r="B153" s="26" t="str">
-        <x:v>MEDICATION</x:v>
+        <x:v>OTHER</x:v>
       </x:c>
       <x:c r="C153" s="26" t="str">
-        <x:v>돌봄 기록 유형: MEDICATION</x:v>
+        <x:v>장기 기억 유형: OTHER</x:v>
       </x:c>
       <x:c r="D153" s="26" t="str">
-        <x:v>care_record.record_type의 상태·분기 판단</x:v>
+        <x:v>memory.memory_type의 상태·분기 판단</x:v>
       </x:c>
       <x:c r="E153" s="26" t="str">
         <x:v>정의되지 않은 값을 성공으로 처리하지 않음</x:v>
@@ -10335,16 +11305,16 @@
     </x:row>
     <x:row r="154">
       <x:c r="A154" s="25" t="str">
-        <x:v>care_record.record_type</x:v>
+        <x:v>memory.lifecycle_status</x:v>
       </x:c>
       <x:c r="B154" s="25" t="str">
-        <x:v>MEDICATION_SCHEDULE</x:v>
+        <x:v>ACTIVE</x:v>
       </x:c>
       <x:c r="C154" s="25" t="str">
-        <x:v>돌봄 기록 유형: MEDICATION_SCHEDULE</x:v>
+        <x:v>기억 수명: ACTIVE</x:v>
       </x:c>
       <x:c r="D154" s="25" t="str">
-        <x:v>care_record.record_type의 상태·분기 판단</x:v>
+        <x:v>memory.lifecycle_status의 상태·분기 판단</x:v>
       </x:c>
       <x:c r="E154" s="25" t="str">
         <x:v>정의되지 않은 값을 성공으로 처리하지 않음</x:v>
@@ -10352,16 +11322,16 @@
     </x:row>
     <x:row r="155">
       <x:c r="A155" s="26" t="str">
-        <x:v>care_record.record_type</x:v>
+        <x:v>memory.lifecycle_status</x:v>
       </x:c>
       <x:c r="B155" s="26" t="str">
-        <x:v>MEDICATION_REMINDER</x:v>
+        <x:v>DISPUTED</x:v>
       </x:c>
       <x:c r="C155" s="26" t="str">
-        <x:v>돌봄 기록 유형: MEDICATION_REMINDER</x:v>
+        <x:v>기억 수명: DISPUTED</x:v>
       </x:c>
       <x:c r="D155" s="26" t="str">
-        <x:v>care_record.record_type의 상태·분기 판단</x:v>
+        <x:v>memory.lifecycle_status의 상태·분기 판단</x:v>
       </x:c>
       <x:c r="E155" s="26" t="str">
         <x:v>정의되지 않은 값을 성공으로 처리하지 않음</x:v>
@@ -10369,16 +11339,16 @@
     </x:row>
     <x:row r="156">
       <x:c r="A156" s="25" t="str">
-        <x:v>care_record.record_type</x:v>
+        <x:v>memory.lifecycle_status</x:v>
       </x:c>
       <x:c r="B156" s="25" t="str">
-        <x:v>MEDICATION_TAKEN</x:v>
+        <x:v>SUPERSEDED</x:v>
       </x:c>
       <x:c r="C156" s="25" t="str">
-        <x:v>돌봄 기록 유형: MEDICATION_TAKEN</x:v>
+        <x:v>기억 수명: SUPERSEDED</x:v>
       </x:c>
       <x:c r="D156" s="25" t="str">
-        <x:v>care_record.record_type의 상태·분기 판단</x:v>
+        <x:v>memory.lifecycle_status의 상태·분기 판단</x:v>
       </x:c>
       <x:c r="E156" s="25" t="str">
         <x:v>정의되지 않은 값을 성공으로 처리하지 않음</x:v>
@@ -10386,16 +11356,16 @@
     </x:row>
     <x:row r="157">
       <x:c r="A157" s="26" t="str">
-        <x:v>care_record.record_type</x:v>
+        <x:v>memory.lifecycle_status</x:v>
       </x:c>
       <x:c r="B157" s="26" t="str">
-        <x:v>APPOINTMENT</x:v>
+        <x:v>EXPIRED</x:v>
       </x:c>
       <x:c r="C157" s="26" t="str">
-        <x:v>돌봄 기록 유형: APPOINTMENT</x:v>
+        <x:v>기억 수명: EXPIRED</x:v>
       </x:c>
       <x:c r="D157" s="26" t="str">
-        <x:v>care_record.record_type의 상태·분기 판단</x:v>
+        <x:v>memory.lifecycle_status의 상태·분기 판단</x:v>
       </x:c>
       <x:c r="E157" s="26" t="str">
         <x:v>정의되지 않은 값을 성공으로 처리하지 않음</x:v>
@@ -10403,16 +11373,16 @@
     </x:row>
     <x:row r="158">
       <x:c r="A158" s="25" t="str">
-        <x:v>care_record.record_type</x:v>
+        <x:v>memory.lifecycle_status</x:v>
       </x:c>
       <x:c r="B158" s="25" t="str">
-        <x:v>PERSONAL_SCHEDULE</x:v>
+        <x:v>DELETED</x:v>
       </x:c>
       <x:c r="C158" s="25" t="str">
-        <x:v>돌봄 기록 유형: PERSONAL_SCHEDULE</x:v>
+        <x:v>기억 수명: DELETED</x:v>
       </x:c>
       <x:c r="D158" s="25" t="str">
-        <x:v>care_record.record_type의 상태·분기 판단</x:v>
+        <x:v>memory.lifecycle_status의 상태·분기 판단</x:v>
       </x:c>
       <x:c r="E158" s="25" t="str">
         <x:v>정의되지 않은 값을 성공으로 처리하지 않음</x:v>
@@ -10420,16 +11390,16 @@
     </x:row>
     <x:row r="159">
       <x:c r="A159" s="26" t="str">
-        <x:v>care_record.record_type</x:v>
+        <x:v>memory.visibility</x:v>
       </x:c>
       <x:c r="B159" s="26" t="str">
-        <x:v>HEALTH_OBSERVATION</x:v>
+        <x:v>PRIVATE</x:v>
       </x:c>
       <x:c r="C159" s="26" t="str">
-        <x:v>돌봄 기록 유형: HEALTH_OBSERVATION</x:v>
+        <x:v>기억 공개 범위: PRIVATE</x:v>
       </x:c>
       <x:c r="D159" s="26" t="str">
-        <x:v>care_record.record_type의 상태·분기 판단</x:v>
+        <x:v>memory.visibility의 상태·분기 판단</x:v>
       </x:c>
       <x:c r="E159" s="26" t="str">
         <x:v>정의되지 않은 값을 성공으로 처리하지 않음</x:v>
@@ -10437,16 +11407,16 @@
     </x:row>
     <x:row r="160">
       <x:c r="A160" s="25" t="str">
-        <x:v>care_record.record_type</x:v>
+        <x:v>memory.visibility</x:v>
       </x:c>
       <x:c r="B160" s="25" t="str">
-        <x:v>REST_OBSERVATION</x:v>
+        <x:v>SHARED_WITH_PRIMARY</x:v>
       </x:c>
       <x:c r="C160" s="25" t="str">
-        <x:v>돌봄 기록 유형: REST_OBSERVATION</x:v>
+        <x:v>기억 공개 범위: SHARED_WITH_PRIMARY</x:v>
       </x:c>
       <x:c r="D160" s="25" t="str">
-        <x:v>care_record.record_type의 상태·분기 판단</x:v>
+        <x:v>memory.visibility의 상태·분기 판단</x:v>
       </x:c>
       <x:c r="E160" s="25" t="str">
         <x:v>정의되지 않은 값을 성공으로 처리하지 않음</x:v>
@@ -10454,16 +11424,16 @@
     </x:row>
     <x:row r="161">
       <x:c r="A161" s="26" t="str">
-        <x:v>care_record.record_type</x:v>
+        <x:v>memory.visibility</x:v>
       </x:c>
       <x:c r="B161" s="26" t="str">
-        <x:v>ENVIRONMENT_OBSERVATION</x:v>
+        <x:v>SHARED_WITH_GUARDIANS</x:v>
       </x:c>
       <x:c r="C161" s="26" t="str">
-        <x:v>돌봄 기록 유형: ENVIRONMENT_OBSERVATION</x:v>
+        <x:v>기억 공개 범위: SHARED_WITH_GUARDIANS</x:v>
       </x:c>
       <x:c r="D161" s="26" t="str">
-        <x:v>care_record.record_type의 상태·분기 판단</x:v>
+        <x:v>memory.visibility의 상태·분기 판단</x:v>
       </x:c>
       <x:c r="E161" s="26" t="str">
         <x:v>정의되지 않은 값을 성공으로 처리하지 않음</x:v>
@@ -10474,10 +11444,10 @@
         <x:v>care_record.record_type</x:v>
       </x:c>
       <x:c r="B162" s="25" t="str">
-        <x:v>COGNITIVE_ASSESSMENT</x:v>
+        <x:v>HEALTH_CONDITION</x:v>
       </x:c>
       <x:c r="C162" s="25" t="str">
-        <x:v>돌봄 기록 유형: COGNITIVE_ASSESSMENT</x:v>
+        <x:v>돌봄 기록 유형: HEALTH_CONDITION</x:v>
       </x:c>
       <x:c r="D162" s="25" t="str">
         <x:v>care_record.record_type의 상태·분기 판단</x:v>
@@ -10491,10 +11461,10 @@
         <x:v>care_record.record_type</x:v>
       </x:c>
       <x:c r="B163" s="26" t="str">
-        <x:v>GUARDIAN_NOTIFICATION</x:v>
+        <x:v>ALLERGY</x:v>
       </x:c>
       <x:c r="C163" s="26" t="str">
-        <x:v>돌봄 기록 유형: GUARDIAN_NOTIFICATION</x:v>
+        <x:v>돌봄 기록 유형: ALLERGY</x:v>
       </x:c>
       <x:c r="D163" s="26" t="str">
         <x:v>care_record.record_type의 상태·분기 판단</x:v>
@@ -10505,16 +11475,16 @@
     </x:row>
     <x:row r="164">
       <x:c r="A164" s="25" t="str">
-        <x:v>care_record.status</x:v>
+        <x:v>care_record.record_type</x:v>
       </x:c>
       <x:c r="B164" s="25" t="str">
-        <x:v>ACTIVE</x:v>
+        <x:v>PHYSICAL_LIMITATION</x:v>
       </x:c>
       <x:c r="C164" s="25" t="str">
-        <x:v>돌봄 기록 상태: ACTIVE</x:v>
+        <x:v>돌봄 기록 유형: PHYSICAL_LIMITATION</x:v>
       </x:c>
       <x:c r="D164" s="25" t="str">
-        <x:v>care_record.status의 상태·분기 판단</x:v>
+        <x:v>care_record.record_type의 상태·분기 판단</x:v>
       </x:c>
       <x:c r="E164" s="25" t="str">
         <x:v>정의되지 않은 값을 성공으로 처리하지 않음</x:v>
@@ -10522,16 +11492,16 @@
     </x:row>
     <x:row r="165">
       <x:c r="A165" s="26" t="str">
-        <x:v>care_record.status</x:v>
+        <x:v>care_record.record_type</x:v>
       </x:c>
       <x:c r="B165" s="26" t="str">
-        <x:v>COMPLETED</x:v>
+        <x:v>MEDICATION</x:v>
       </x:c>
       <x:c r="C165" s="26" t="str">
-        <x:v>돌봄 기록 상태: COMPLETED</x:v>
+        <x:v>돌봄 기록 유형: MEDICATION</x:v>
       </x:c>
       <x:c r="D165" s="26" t="str">
-        <x:v>care_record.status의 상태·분기 판단</x:v>
+        <x:v>care_record.record_type의 상태·분기 판단</x:v>
       </x:c>
       <x:c r="E165" s="26" t="str">
         <x:v>정의되지 않은 값을 성공으로 처리하지 않음</x:v>
@@ -10539,16 +11509,16 @@
     </x:row>
     <x:row r="166">
       <x:c r="A166" s="25" t="str">
-        <x:v>care_record.status</x:v>
+        <x:v>care_record.record_type</x:v>
       </x:c>
       <x:c r="B166" s="25" t="str">
-        <x:v>CANCELLED</x:v>
+        <x:v>MEDICATION_SCHEDULE</x:v>
       </x:c>
       <x:c r="C166" s="25" t="str">
-        <x:v>돌봄 기록 상태: CANCELLED</x:v>
+        <x:v>돌봄 기록 유형: MEDICATION_SCHEDULE</x:v>
       </x:c>
       <x:c r="D166" s="25" t="str">
-        <x:v>care_record.status의 상태·분기 판단</x:v>
+        <x:v>care_record.record_type의 상태·분기 판단</x:v>
       </x:c>
       <x:c r="E166" s="25" t="str">
         <x:v>정의되지 않은 값을 성공으로 처리하지 않음</x:v>
@@ -10556,16 +11526,16 @@
     </x:row>
     <x:row r="167">
       <x:c r="A167" s="26" t="str">
-        <x:v>care_record.status</x:v>
+        <x:v>care_record.record_type</x:v>
       </x:c>
       <x:c r="B167" s="26" t="str">
-        <x:v>SUPERSEDED</x:v>
+        <x:v>MEDICATION_REMINDER</x:v>
       </x:c>
       <x:c r="C167" s="26" t="str">
-        <x:v>돌봄 기록 상태: SUPERSEDED</x:v>
+        <x:v>돌봄 기록 유형: MEDICATION_REMINDER</x:v>
       </x:c>
       <x:c r="D167" s="26" t="str">
-        <x:v>care_record.status의 상태·분기 판단</x:v>
+        <x:v>care_record.record_type의 상태·분기 판단</x:v>
       </x:c>
       <x:c r="E167" s="26" t="str">
         <x:v>정의되지 않은 값을 성공으로 처리하지 않음</x:v>
@@ -10573,16 +11543,16 @@
     </x:row>
     <x:row r="168">
       <x:c r="A168" s="25" t="str">
-        <x:v>care_record.recurrence.frequency</x:v>
+        <x:v>care_record.record_type</x:v>
       </x:c>
       <x:c r="B168" s="25" t="str">
-        <x:v>DAILY</x:v>
+        <x:v>MEDICATION_TAKEN</x:v>
       </x:c>
       <x:c r="C168" s="25" t="str">
-        <x:v>반복 주기: DAILY</x:v>
+        <x:v>돌봄 기록 유형: MEDICATION_TAKEN</x:v>
       </x:c>
       <x:c r="D168" s="25" t="str">
-        <x:v>care_record.recurrence.frequency의 상태·분기 판단</x:v>
+        <x:v>care_record.record_type의 상태·분기 판단</x:v>
       </x:c>
       <x:c r="E168" s="25" t="str">
         <x:v>정의되지 않은 값을 성공으로 처리하지 않음</x:v>
@@ -10590,18 +11560,222 @@
     </x:row>
     <x:row r="169">
       <x:c r="A169" s="28" t="str">
+        <x:v>care_record.record_type</x:v>
+      </x:c>
+      <x:c r="B169" s="28" t="str">
+        <x:v>APPOINTMENT</x:v>
+      </x:c>
+      <x:c r="C169" s="28" t="str">
+        <x:v>돌봄 기록 유형: APPOINTMENT</x:v>
+      </x:c>
+      <x:c r="D169" s="28" t="str">
+        <x:v>care_record.record_type의 상태·분기 판단</x:v>
+      </x:c>
+      <x:c r="E169" s="28" t="str">
+        <x:v>정의되지 않은 값을 성공으로 처리하지 않음</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="170">
+      <x:c r="A170" t="str">
+        <x:v>care_record.record_type</x:v>
+      </x:c>
+      <x:c r="B170" t="str">
+        <x:v>PERSONAL_SCHEDULE</x:v>
+      </x:c>
+      <x:c r="C170" t="str">
+        <x:v>돌봄 기록 유형: PERSONAL_SCHEDULE</x:v>
+      </x:c>
+      <x:c r="D170" t="str">
+        <x:v>care_record.record_type의 상태·분기 판단</x:v>
+      </x:c>
+      <x:c r="E170" t="str">
+        <x:v>정의되지 않은 값을 성공으로 처리하지 않음</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="171">
+      <x:c r="A171" t="str">
+        <x:v>care_record.record_type</x:v>
+      </x:c>
+      <x:c r="B171" t="str">
+        <x:v>HEALTH_OBSERVATION</x:v>
+      </x:c>
+      <x:c r="C171" t="str">
+        <x:v>돌봄 기록 유형: HEALTH_OBSERVATION</x:v>
+      </x:c>
+      <x:c r="D171" t="str">
+        <x:v>care_record.record_type의 상태·분기 판단</x:v>
+      </x:c>
+      <x:c r="E171" t="str">
+        <x:v>정의되지 않은 값을 성공으로 처리하지 않음</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="172">
+      <x:c r="A172" t="str">
+        <x:v>care_record.record_type</x:v>
+      </x:c>
+      <x:c r="B172" t="str">
+        <x:v>REST_OBSERVATION</x:v>
+      </x:c>
+      <x:c r="C172" t="str">
+        <x:v>돌봄 기록 유형: REST_OBSERVATION</x:v>
+      </x:c>
+      <x:c r="D172" t="str">
+        <x:v>care_record.record_type의 상태·분기 판단</x:v>
+      </x:c>
+      <x:c r="E172" t="str">
+        <x:v>정의되지 않은 값을 성공으로 처리하지 않음</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="173">
+      <x:c r="A173" t="str">
+        <x:v>care_record.record_type</x:v>
+      </x:c>
+      <x:c r="B173" t="str">
+        <x:v>ENVIRONMENT_OBSERVATION</x:v>
+      </x:c>
+      <x:c r="C173" t="str">
+        <x:v>돌봄 기록 유형: ENVIRONMENT_OBSERVATION</x:v>
+      </x:c>
+      <x:c r="D173" t="str">
+        <x:v>care_record.record_type의 상태·분기 판단</x:v>
+      </x:c>
+      <x:c r="E173" t="str">
+        <x:v>정의되지 않은 값을 성공으로 처리하지 않음</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="174">
+      <x:c r="A174" t="str">
+        <x:v>care_record.record_type</x:v>
+      </x:c>
+      <x:c r="B174" t="str">
+        <x:v>COGNITIVE_ASSESSMENT</x:v>
+      </x:c>
+      <x:c r="C174" t="str">
+        <x:v>돌봄 기록 유형: COGNITIVE_ASSESSMENT</x:v>
+      </x:c>
+      <x:c r="D174" t="str">
+        <x:v>care_record.record_type의 상태·분기 판단</x:v>
+      </x:c>
+      <x:c r="E174" t="str">
+        <x:v>정의되지 않은 값을 성공으로 처리하지 않음</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="175">
+      <x:c r="A175" t="str">
+        <x:v>care_record.record_type</x:v>
+      </x:c>
+      <x:c r="B175" t="str">
+        <x:v>GUARDIAN_NOTIFICATION</x:v>
+      </x:c>
+      <x:c r="C175" t="str">
+        <x:v>돌봄 기록 유형: GUARDIAN_NOTIFICATION</x:v>
+      </x:c>
+      <x:c r="D175" t="str">
+        <x:v>care_record.record_type의 상태·분기 판단</x:v>
+      </x:c>
+      <x:c r="E175" t="str">
+        <x:v>정의되지 않은 값을 성공으로 처리하지 않음</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="176">
+      <x:c r="A176" t="str">
+        <x:v>care_record.status</x:v>
+      </x:c>
+      <x:c r="B176" t="str">
+        <x:v>ACTIVE</x:v>
+      </x:c>
+      <x:c r="C176" t="str">
+        <x:v>돌봄 기록 상태: ACTIVE</x:v>
+      </x:c>
+      <x:c r="D176" t="str">
+        <x:v>care_record.status의 상태·분기 판단</x:v>
+      </x:c>
+      <x:c r="E176" t="str">
+        <x:v>정의되지 않은 값을 성공으로 처리하지 않음</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="177">
+      <x:c r="A177" t="str">
+        <x:v>care_record.status</x:v>
+      </x:c>
+      <x:c r="B177" t="str">
+        <x:v>COMPLETED</x:v>
+      </x:c>
+      <x:c r="C177" t="str">
+        <x:v>돌봄 기록 상태: COMPLETED</x:v>
+      </x:c>
+      <x:c r="D177" t="str">
+        <x:v>care_record.status의 상태·분기 판단</x:v>
+      </x:c>
+      <x:c r="E177" t="str">
+        <x:v>정의되지 않은 값을 성공으로 처리하지 않음</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="178">
+      <x:c r="A178" t="str">
+        <x:v>care_record.status</x:v>
+      </x:c>
+      <x:c r="B178" t="str">
+        <x:v>CANCELLED</x:v>
+      </x:c>
+      <x:c r="C178" t="str">
+        <x:v>돌봄 기록 상태: CANCELLED</x:v>
+      </x:c>
+      <x:c r="D178" t="str">
+        <x:v>care_record.status의 상태·분기 판단</x:v>
+      </x:c>
+      <x:c r="E178" t="str">
+        <x:v>정의되지 않은 값을 성공으로 처리하지 않음</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="179">
+      <x:c r="A179" t="str">
+        <x:v>care_record.status</x:v>
+      </x:c>
+      <x:c r="B179" t="str">
+        <x:v>SUPERSEDED</x:v>
+      </x:c>
+      <x:c r="C179" t="str">
+        <x:v>돌봄 기록 상태: SUPERSEDED</x:v>
+      </x:c>
+      <x:c r="D179" t="str">
+        <x:v>care_record.status의 상태·분기 판단</x:v>
+      </x:c>
+      <x:c r="E179" t="str">
+        <x:v>정의되지 않은 값을 성공으로 처리하지 않음</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="180">
+      <x:c r="A180" t="str">
         <x:v>care_record.recurrence.frequency</x:v>
       </x:c>
-      <x:c r="B169" s="28" t="str">
+      <x:c r="B180" t="str">
+        <x:v>DAILY</x:v>
+      </x:c>
+      <x:c r="C180" t="str">
+        <x:v>반복 주기: DAILY</x:v>
+      </x:c>
+      <x:c r="D180" t="str">
+        <x:v>care_record.recurrence.frequency의 상태·분기 판단</x:v>
+      </x:c>
+      <x:c r="E180" t="str">
+        <x:v>정의되지 않은 값을 성공으로 처리하지 않음</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="181">
+      <x:c r="A181" t="str">
+        <x:v>care_record.recurrence.frequency</x:v>
+      </x:c>
+      <x:c r="B181" t="str">
         <x:v>WEEKLY</x:v>
       </x:c>
-      <x:c r="C169" s="28" t="str">
+      <x:c r="C181" t="str">
         <x:v>반복 주기: WEEKLY</x:v>
       </x:c>
-      <x:c r="D169" s="28" t="str">
+      <x:c r="D181" t="str">
         <x:v>care_record.recurrence.frequency의 상태·분기 판단</x:v>
       </x:c>
-      <x:c r="E169" s="28" t="str">
+      <x:c r="E181" t="str">
         <x:v>정의되지 않은 값을 성공으로 처리하지 않음</x:v>
       </x:c>
     </x:row>
@@ -10733,7 +11907,7 @@
         <x:v>미저장</x:v>
       </x:c>
       <x:c r="F8" s="25" t="str">
-        <x:v>현재 수신 원장·Outbox 없음</x:v>
+        <x:v>호출 전용 상관 필드는 별도 행처럼 저장하며 그 외 수신 원장·Outbox는 없음</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -10954,6 +12128,86 @@
       </x:c>
       <x:c r="F19" s="28" t="str">
         <x:v>온도·관측시각과 함께 갱신</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="24" hidden="0" customHeight="1">
+      <x:c r="A20" t="str">
+        <x:v>WAKE_WORD_DETECTED.eventId</x:v>
+      </x:c>
+      <x:c r="B20" t="str">
+        <x:v>AI → Backend</x:v>
+      </x:c>
+      <x:c r="C20" t="str">
+        <x:v>호출 최초 이벤트 멱등 키</x:v>
+      </x:c>
+      <x:c r="D20" t="str">
+        <x:v>wake_word_trigger_receipt.event_id, scenario.external_event_id</x:v>
+      </x:c>
+      <x:c r="E20" t="str">
+        <x:v>저장</x:v>
+      </x:c>
+      <x:c r="F20" t="str">
+        <x:v>호출 전용 receipt PK와 수락 시나리오에 같은 값을 저장</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="24" hidden="0" customHeight="1">
+      <x:c r="A21" t="str">
+        <x:v>WAKE_WORD_DETECTED.occurredAt/keyword/confidence</x:v>
+      </x:c>
+      <x:c r="B21" t="str">
+        <x:v>AI → Backend</x:v>
+      </x:c>
+      <x:c r="C21" t="str">
+        <x:v>호출 확정 최소 문맥</x:v>
+      </x:c>
+      <x:c r="D21" t="str">
+        <x:v>wake_word_trigger_receipt 및 scenario.trigger_context</x:v>
+      </x:c>
+      <x:c r="E21" t="str">
+        <x:v>저장</x:v>
+      </x:c>
+      <x:c r="F21" t="str">
+        <x:v>원본 음성·전체 STT는 저장하지 않음</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="24" hidden="0" customHeight="1">
+      <x:c r="A22" t="str">
+        <x:v>NAVIGATE.commandId/target</x:v>
+      </x:c>
+      <x:c r="B22" t="str">
+        <x:v>Backend → Robot</x:v>
+      </x:c>
+      <x:c r="C22" t="str">
+        <x:v>현재 이동 결과 상관관계</x:v>
+      </x:c>
+      <x:c r="D22" t="str">
+        <x:v>scenario.active_navigation_command_id/active_navigation_target</x:v>
+      </x:c>
+      <x:c r="E22" t="str">
+        <x:v>조건부 저장</x:v>
+      </x:c>
+      <x:c r="F22" t="str">
+        <x:v>최종 결과 반영 뒤 함께 null</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="24" hidden="0" customHeight="1">
+      <x:c r="A23" t="str">
+        <x:v>NAVIGATION_RESULT.resultCode/reasonCode</x:v>
+      </x:c>
+      <x:c r="B23" t="str">
+        <x:v>Robot → Backend</x:v>
+      </x:c>
+      <x:c r="C23" t="str">
+        <x:v>호출 이동 종료 코드</x:v>
+      </x:c>
+      <x:c r="D23" t="str">
+        <x:v>scenario.completion_result_code/completion_reason_code</x:v>
+      </x:c>
+      <x:c r="E23" t="str">
+        <x:v>조건부 저장</x:v>
+      </x:c>
+      <x:c r="F23" t="str">
+        <x:v>상관 검증을 통과한 최종 결과만 반영</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/docs/database/column-definition/BOMI_컬럼정의서.xlsx
+++ b/docs/database/column-definition/BOMI_컬럼정의서.xlsx
@@ -784,7 +784,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -807,6 +807,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="13" t="inlineStr">
         <is>
@@ -936,6 +937,28 @@
       <c r="D9" t="inlineStr">
         <is>
           <t>'오늘 날씨 어때?'의 기본 지역이 없어 로봇이 되묻거나 지어내던 문제를 없애기 위해. 로봇 대화 문맥 채널 전용이며 가디언웹에는 노출하지 않는다</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>fact_candidate.status 에 CANCELLED_BY_SENIOR 추가 (S15P11E102-348)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>fact_candidate</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>어르신의 '기억하지 마' 요청으로 이미 제출된 미확정 후보를 닫는 상태가 없어, 지운 이야기가 재질의로 되살아날 수 있던 문제를 없애기 위해. DB CHECK 없는 varchar(40)이라 DDL 변경은 없다</t>
         </is>
       </c>
     </row>
@@ -18940,7 +18963,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E223"/>
+  <dimension ref="A1:E224"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -18964,6 +18987,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="13" t="inlineStr">
         <is>
@@ -22016,1458 +22040,1454 @@
       </c>
     </row>
     <row r="117" ht="15" customHeight="1">
-      <c r="A117" s="26" t="inlineStr">
+      <c r="A117" s="25" t="inlineStr">
+        <is>
+          <t>fact_candidate.status</t>
+        </is>
+      </c>
+      <c r="B117" s="25" t="inlineStr">
+        <is>
+          <t>CANCELLED_BY_SENIOR</t>
+        </is>
+      </c>
+      <c r="C117" s="25" t="inlineStr">
+        <is>
+          <t>어르신 요청 취소</t>
+        </is>
+      </c>
+      <c r="D117" s="25" t="inlineStr">
+        <is>
+          <t>어르신 본인이 '기억하지 마'로 닫은 미확정 후보. 재질의·확인요청·검색·반영에서 제외한다. REJECTED(보호자·시스템 거절)와 구분한다 — 누가 왜 닫았는지가 T4 신뢰의 근거다.</t>
+        </is>
+      </c>
+      <c r="E117" s="25" t="n"/>
+    </row>
+    <row r="118" ht="15" customHeight="1">
+      <c r="A118" s="26" t="inlineStr">
         <is>
           <t>fact_candidate.clarification_reason</t>
         </is>
       </c>
-      <c r="B117" s="26" t="inlineStr">
+      <c r="B118" s="26" t="inlineStr">
         <is>
           <t>MISSING_REQUIRED_FIELD</t>
         </is>
       </c>
-      <c r="C117" s="26" t="inlineStr">
+      <c r="C118" s="26" t="inlineStr">
         <is>
           <t>재질의 사유: MISSING_REQUIRED_FIELD</t>
         </is>
       </c>
-      <c r="D117" s="26" t="inlineStr">
+      <c r="D118" s="26" t="inlineStr">
         <is>
           <t>fact_candidate.clarification_reason의 상태·분기 판단</t>
         </is>
       </c>
-      <c r="E117" s="26" t="inlineStr">
+      <c r="E118" s="26" t="inlineStr">
         <is>
           <t>정의되지 않은 값을 성공으로 처리하지 않음</t>
         </is>
       </c>
     </row>
-    <row r="118" ht="15" customHeight="1">
-      <c r="A118" s="25" t="inlineStr">
+    <row r="119" ht="15" customHeight="1">
+      <c r="A119" s="25" t="inlineStr">
         <is>
           <t>fact_candidate.clarification_reason</t>
         </is>
       </c>
-      <c r="B118" s="25" t="inlineStr">
+      <c r="B119" s="25" t="inlineStr">
         <is>
           <t>AMBIGUOUS_VALUE</t>
         </is>
       </c>
-      <c r="C118" s="25" t="inlineStr">
+      <c r="C119" s="25" t="inlineStr">
         <is>
           <t>재질의 사유: AMBIGUOUS_VALUE</t>
         </is>
       </c>
-      <c r="D118" s="25" t="inlineStr">
+      <c r="D119" s="25" t="inlineStr">
         <is>
           <t>fact_candidate.clarification_reason의 상태·분기 판단</t>
         </is>
       </c>
-      <c r="E118" s="25" t="inlineStr">
+      <c r="E119" s="25" t="inlineStr">
         <is>
           <t>정의되지 않은 값을 성공으로 처리하지 않음</t>
         </is>
       </c>
     </row>
-    <row r="119" ht="15" customHeight="1">
-      <c r="A119" s="26" t="inlineStr">
+    <row r="120" ht="15" customHeight="1">
+      <c r="A120" s="26" t="inlineStr">
         <is>
           <t>fact_candidate.clarification_reason</t>
         </is>
       </c>
-      <c r="B119" s="26" t="inlineStr">
+      <c r="B120" s="26" t="inlineStr">
         <is>
           <t>LOW_RECOGNITION_CONFIDENCE</t>
         </is>
       </c>
-      <c r="C119" s="26" t="inlineStr">
+      <c r="C120" s="26" t="inlineStr">
         <is>
           <t>재질의 사유: LOW_RECOGNITION_CONFIDENCE</t>
         </is>
       </c>
-      <c r="D119" s="26" t="inlineStr">
+      <c r="D120" s="26" t="inlineStr">
         <is>
           <t>fact_candidate.clarification_reason의 상태·분기 판단</t>
         </is>
       </c>
-      <c r="E119" s="26" t="inlineStr">
+      <c r="E120" s="26" t="inlineStr">
         <is>
           <t>정의되지 않은 값을 성공으로 처리하지 않음</t>
         </is>
       </c>
     </row>
-    <row r="120" ht="15" customHeight="1">
-      <c r="A120" s="25" t="inlineStr">
+    <row r="121" ht="15" customHeight="1">
+      <c r="A121" s="25" t="inlineStr">
         <is>
           <t>fact_candidate.clarification_reason</t>
         </is>
       </c>
-      <c r="B120" s="25" t="inlineStr">
+      <c r="B121" s="25" t="inlineStr">
         <is>
           <t>CONFLICT_WITH_EXISTING_DATA</t>
         </is>
       </c>
-      <c r="C120" s="25" t="inlineStr">
+      <c r="C121" s="25" t="inlineStr">
         <is>
           <t>재질의 사유: CONFLICT_WITH_EXISTING_DATA</t>
         </is>
       </c>
-      <c r="D120" s="25" t="inlineStr">
+      <c r="D121" s="25" t="inlineStr">
         <is>
           <t>fact_candidate.clarification_reason의 상태·분기 판단</t>
         </is>
       </c>
-      <c r="E120" s="25" t="inlineStr">
+      <c r="E121" s="25" t="inlineStr">
         <is>
           <t>정의되지 않은 값을 성공으로 처리하지 않음</t>
         </is>
       </c>
     </row>
-    <row r="121" ht="15" customHeight="1">
-      <c r="A121" s="26" t="inlineStr">
+    <row r="122" ht="15" customHeight="1">
+      <c r="A122" s="26" t="inlineStr">
         <is>
           <t>fact_candidate.clarification_reason</t>
         </is>
       </c>
-      <c r="B121" s="26" t="inlineStr">
+      <c r="B122" s="26" t="inlineStr">
         <is>
           <t>SENSITIVE_INFORMATION_CONFIRMATION</t>
         </is>
       </c>
-      <c r="C121" s="26" t="inlineStr">
+      <c r="C122" s="26" t="inlineStr">
         <is>
           <t>재질의 사유: SENSITIVE_INFORMATION_CONFIRMATION</t>
         </is>
       </c>
-      <c r="D121" s="26" t="inlineStr">
+      <c r="D122" s="26" t="inlineStr">
         <is>
           <t>fact_candidate.clarification_reason의 상태·분기 판단</t>
         </is>
       </c>
-      <c r="E121" s="26" t="inlineStr">
+      <c r="E122" s="26" t="inlineStr">
         <is>
           <t>정의되지 않은 값을 성공으로 처리하지 않음</t>
         </is>
       </c>
     </row>
-    <row r="122" ht="15" customHeight="1">
-      <c r="A122" s="25" t="inlineStr">
+    <row r="123" ht="15" customHeight="1">
+      <c r="A123" s="25" t="inlineStr">
         <is>
           <t>fact_candidate.coordination_status</t>
         </is>
       </c>
-      <c r="B122" s="25" t="inlineStr">
+      <c r="B123" s="25" t="inlineStr">
         <is>
           <t>NOT_REQUIRED</t>
         </is>
       </c>
-      <c r="C122" s="25" t="inlineStr">
+      <c r="C123" s="25" t="inlineStr">
         <is>
           <t>협의 상태: NOT_REQUIRED</t>
         </is>
       </c>
-      <c r="D122" s="25" t="inlineStr">
+      <c r="D123" s="25" t="inlineStr">
         <is>
           <t>fact_candidate.coordination_status의 상태·분기 판단</t>
         </is>
       </c>
-      <c r="E122" s="25" t="inlineStr">
+      <c r="E123" s="25" t="inlineStr">
         <is>
           <t>정의되지 않은 값을 성공으로 처리하지 않음</t>
         </is>
       </c>
     </row>
-    <row r="123" ht="15" customHeight="1">
-      <c r="A123" s="26" t="inlineStr">
+    <row r="124" ht="15" customHeight="1">
+      <c r="A124" s="26" t="inlineStr">
         <is>
           <t>fact_candidate.coordination_status</t>
         </is>
       </c>
-      <c r="B123" s="26" t="inlineStr">
+      <c r="B124" s="26" t="inlineStr">
         <is>
           <t>COORDINATION_REQUIRED</t>
         </is>
       </c>
-      <c r="C123" s="26" t="inlineStr">
+      <c r="C124" s="26" t="inlineStr">
         <is>
           <t>협의 상태: COORDINATION_REQUIRED</t>
         </is>
       </c>
-      <c r="D123" s="26" t="inlineStr">
+      <c r="D124" s="26" t="inlineStr">
         <is>
           <t>fact_candidate.coordination_status의 상태·분기 판단</t>
         </is>
       </c>
-      <c r="E123" s="26" t="inlineStr">
+      <c r="E124" s="26" t="inlineStr">
         <is>
           <t>정의되지 않은 값을 성공으로 처리하지 않음</t>
         </is>
       </c>
     </row>
-    <row r="124" ht="15" customHeight="1">
-      <c r="A124" s="25" t="inlineStr">
+    <row r="125" ht="15" customHeight="1">
+      <c r="A125" s="25" t="inlineStr">
         <is>
           <t>fact_candidate.coordination_status</t>
         </is>
       </c>
-      <c r="B124" s="25" t="inlineStr">
+      <c r="B125" s="25" t="inlineStr">
         <is>
           <t>WAITING_PRIMARY_GUARDIAN</t>
         </is>
       </c>
-      <c r="C124" s="25" t="inlineStr">
+      <c r="C125" s="25" t="inlineStr">
         <is>
           <t>협의 상태: WAITING_PRIMARY_GUARDIAN</t>
         </is>
       </c>
-      <c r="D124" s="25" t="inlineStr">
+      <c r="D125" s="25" t="inlineStr">
         <is>
           <t>fact_candidate.coordination_status의 상태·분기 판단</t>
         </is>
       </c>
-      <c r="E124" s="25" t="inlineStr">
+      <c r="E125" s="25" t="inlineStr">
         <is>
           <t>정의되지 않은 값을 성공으로 처리하지 않음</t>
         </is>
       </c>
     </row>
-    <row r="125" ht="15" customHeight="1">
-      <c r="A125" s="26" t="inlineStr">
+    <row r="126" ht="15" customHeight="1">
+      <c r="A126" s="26" t="inlineStr">
         <is>
           <t>fact_candidate.coordination_status</t>
         </is>
       </c>
-      <c r="B125" s="26" t="inlineStr">
+      <c r="B126" s="26" t="inlineStr">
         <is>
           <t>WAITING_SENIOR</t>
         </is>
       </c>
-      <c r="C125" s="26" t="inlineStr">
+      <c r="C126" s="26" t="inlineStr">
         <is>
           <t>협의 상태: WAITING_SENIOR</t>
         </is>
       </c>
-      <c r="D125" s="26" t="inlineStr">
+      <c r="D126" s="26" t="inlineStr">
         <is>
           <t>fact_candidate.coordination_status의 상태·분기 판단</t>
         </is>
       </c>
-      <c r="E125" s="26" t="inlineStr">
+      <c r="E126" s="26" t="inlineStr">
         <is>
           <t>정의되지 않은 값을 성공으로 처리하지 않음</t>
         </is>
       </c>
     </row>
-    <row r="126" ht="15" customHeight="1">
-      <c r="A126" s="25" t="inlineStr">
+    <row r="127" ht="15" customHeight="1">
+      <c r="A127" s="25" t="inlineStr">
         <is>
           <t>fact_candidate.coordination_status</t>
         </is>
       </c>
-      <c r="B126" s="25" t="inlineStr">
+      <c r="B127" s="25" t="inlineStr">
         <is>
           <t>AGREED</t>
         </is>
       </c>
-      <c r="C126" s="25" t="inlineStr">
+      <c r="C127" s="25" t="inlineStr">
         <is>
           <t>협의 상태: AGREED</t>
         </is>
       </c>
-      <c r="D126" s="25" t="inlineStr">
+      <c r="D127" s="25" t="inlineStr">
         <is>
           <t>fact_candidate.coordination_status의 상태·분기 판단</t>
         </is>
       </c>
-      <c r="E126" s="25" t="inlineStr">
+      <c r="E127" s="25" t="inlineStr">
         <is>
           <t>정의되지 않은 값을 성공으로 처리하지 않음</t>
         </is>
       </c>
     </row>
-    <row r="127" ht="15" customHeight="1">
-      <c r="A127" s="26" t="inlineStr">
+    <row r="128" ht="15" customHeight="1">
+      <c r="A128" s="26" t="inlineStr">
         <is>
           <t>fact_candidate.coordination_status</t>
         </is>
       </c>
-      <c r="B127" s="26" t="inlineStr">
+      <c r="B128" s="26" t="inlineStr">
         <is>
           <t>DISAGREED</t>
         </is>
       </c>
-      <c r="C127" s="26" t="inlineStr">
+      <c r="C128" s="26" t="inlineStr">
         <is>
           <t>협의 상태: DISAGREED</t>
         </is>
       </c>
-      <c r="D127" s="26" t="inlineStr">
+      <c r="D128" s="26" t="inlineStr">
         <is>
           <t>fact_candidate.coordination_status의 상태·분기 판단</t>
         </is>
       </c>
-      <c r="E127" s="26" t="inlineStr">
+      <c r="E128" s="26" t="inlineStr">
         <is>
           <t>정의되지 않은 값을 성공으로 처리하지 않음</t>
         </is>
       </c>
     </row>
-    <row r="128" ht="15" customHeight="1">
-      <c r="A128" s="25" t="inlineStr">
+    <row r="129" ht="15" customHeight="1">
+      <c r="A129" s="25" t="inlineStr">
         <is>
           <t>fact_candidate.coordination_status</t>
         </is>
       </c>
-      <c r="B128" s="25" t="inlineStr">
+      <c r="B129" s="25" t="inlineStr">
         <is>
           <t>SENIOR_UNREACHABLE</t>
         </is>
       </c>
-      <c r="C128" s="25" t="inlineStr">
+      <c r="C129" s="25" t="inlineStr">
         <is>
           <t>협의 상태: SENIOR_UNREACHABLE</t>
         </is>
       </c>
-      <c r="D128" s="25" t="inlineStr">
+      <c r="D129" s="25" t="inlineStr">
         <is>
           <t>fact_candidate.coordination_status의 상태·분기 판단</t>
         </is>
       </c>
-      <c r="E128" s="25" t="inlineStr">
+      <c r="E129" s="25" t="inlineStr">
         <is>
           <t>정의되지 않은 값을 성공으로 처리하지 않음</t>
         </is>
       </c>
     </row>
-    <row r="129" ht="15" customHeight="1">
-      <c r="A129" s="26" t="inlineStr">
+    <row r="130" ht="15" customHeight="1">
+      <c r="A130" s="26" t="inlineStr">
         <is>
           <t>fact_candidate.coordination_status</t>
         </is>
       </c>
-      <c r="B129" s="26" t="inlineStr">
+      <c r="B130" s="26" t="inlineStr">
         <is>
           <t>GUARDIAN_OVERRIDE_CONFIRMED</t>
         </is>
       </c>
-      <c r="C129" s="26" t="inlineStr">
+      <c r="C130" s="26" t="inlineStr">
         <is>
           <t>협의 상태: GUARDIAN_OVERRIDE_CONFIRMED</t>
         </is>
       </c>
-      <c r="D129" s="26" t="inlineStr">
+      <c r="D130" s="26" t="inlineStr">
         <is>
           <t>fact_candidate.coordination_status의 상태·분기 판단</t>
         </is>
       </c>
-      <c r="E129" s="26" t="inlineStr">
+      <c r="E130" s="26" t="inlineStr">
         <is>
           <t>정의되지 않은 값을 성공으로 처리하지 않음</t>
         </is>
       </c>
     </row>
-    <row r="130" ht="15" customHeight="1">
-      <c r="A130" s="25" t="inlineStr">
+    <row r="131" ht="15" customHeight="1">
+      <c r="A131" s="25" t="inlineStr">
         <is>
           <t>fact_candidate.coordination_status</t>
         </is>
       </c>
-      <c r="B130" s="25" t="inlineStr">
+      <c r="B131" s="25" t="inlineStr">
         <is>
           <t>COMPLETED</t>
         </is>
       </c>
-      <c r="C130" s="25" t="inlineStr">
+      <c r="C131" s="25" t="inlineStr">
         <is>
           <t>협의 상태: COMPLETED</t>
         </is>
       </c>
-      <c r="D130" s="25" t="inlineStr">
+      <c r="D131" s="25" t="inlineStr">
         <is>
           <t>fact_candidate.coordination_status의 상태·분기 판단</t>
         </is>
       </c>
-      <c r="E130" s="25" t="inlineStr">
+      <c r="E131" s="25" t="inlineStr">
         <is>
           <t>정의되지 않은 값을 성공으로 처리하지 않음</t>
         </is>
       </c>
     </row>
-    <row r="131" ht="15" customHeight="1">
-      <c r="A131" s="26" t="inlineStr">
+    <row r="132" ht="15" customHeight="1">
+      <c r="A132" s="26" t="inlineStr">
         <is>
           <t>fact_candidate.senior_position</t>
         </is>
       </c>
-      <c r="B131" s="26" t="inlineStr">
+      <c r="B132" s="26" t="inlineStr">
         <is>
           <t>NOT_REQUESTED</t>
         </is>
       </c>
-      <c r="C131" s="26" t="inlineStr">
+      <c r="C132" s="26" t="inlineStr">
         <is>
           <t>시니어 입장: NOT_REQUESTED</t>
         </is>
       </c>
-      <c r="D131" s="26" t="inlineStr">
+      <c r="D132" s="26" t="inlineStr">
         <is>
           <t>fact_candidate.senior_position의 상태·분기 판단</t>
         </is>
       </c>
-      <c r="E131" s="26" t="inlineStr">
+      <c r="E132" s="26" t="inlineStr">
         <is>
           <t>정의되지 않은 값을 성공으로 처리하지 않음</t>
         </is>
       </c>
     </row>
-    <row r="132" ht="15" customHeight="1">
-      <c r="A132" s="25" t="inlineStr">
+    <row r="133" ht="15" customHeight="1">
+      <c r="A133" s="25" t="inlineStr">
         <is>
           <t>fact_candidate.senior_position</t>
         </is>
       </c>
-      <c r="B132" s="25" t="inlineStr">
+      <c r="B133" s="25" t="inlineStr">
         <is>
           <t>PENDING</t>
         </is>
       </c>
-      <c r="C132" s="25" t="inlineStr">
+      <c r="C133" s="25" t="inlineStr">
         <is>
           <t>시니어 입장: PENDING</t>
         </is>
       </c>
-      <c r="D132" s="25" t="inlineStr">
+      <c r="D133" s="25" t="inlineStr">
         <is>
           <t>fact_candidate.senior_position의 상태·분기 판단</t>
         </is>
       </c>
-      <c r="E132" s="25" t="inlineStr">
+      <c r="E133" s="25" t="inlineStr">
         <is>
           <t>정의되지 않은 값을 성공으로 처리하지 않음</t>
         </is>
       </c>
     </row>
-    <row r="133" ht="15" customHeight="1">
-      <c r="A133" s="26" t="inlineStr">
+    <row r="134" ht="15" customHeight="1">
+      <c r="A134" s="26" t="inlineStr">
         <is>
           <t>fact_candidate.senior_position</t>
         </is>
       </c>
-      <c r="B133" s="26" t="inlineStr">
+      <c r="B134" s="26" t="inlineStr">
         <is>
           <t>AGREED</t>
         </is>
       </c>
-      <c r="C133" s="26" t="inlineStr">
+      <c r="C134" s="26" t="inlineStr">
         <is>
           <t>시니어 입장: AGREED</t>
         </is>
       </c>
-      <c r="D133" s="26" t="inlineStr">
+      <c r="D134" s="26" t="inlineStr">
         <is>
           <t>fact_candidate.senior_position의 상태·분기 판단</t>
         </is>
       </c>
-      <c r="E133" s="26" t="inlineStr">
+      <c r="E134" s="26" t="inlineStr">
         <is>
           <t>정의되지 않은 값을 성공으로 처리하지 않음</t>
         </is>
       </c>
     </row>
-    <row r="134" ht="15" customHeight="1">
-      <c r="A134" s="25" t="inlineStr">
+    <row r="135" ht="15" customHeight="1">
+      <c r="A135" s="25" t="inlineStr">
         <is>
           <t>fact_candidate.senior_position</t>
         </is>
       </c>
-      <c r="B134" s="25" t="inlineStr">
+      <c r="B135" s="25" t="inlineStr">
         <is>
           <t>DISAGREED</t>
         </is>
       </c>
-      <c r="C134" s="25" t="inlineStr">
+      <c r="C135" s="25" t="inlineStr">
         <is>
           <t>시니어 입장: DISAGREED</t>
         </is>
       </c>
-      <c r="D134" s="25" t="inlineStr">
+      <c r="D135" s="25" t="inlineStr">
         <is>
           <t>fact_candidate.senior_position의 상태·분기 판단</t>
         </is>
       </c>
-      <c r="E134" s="25" t="inlineStr">
+      <c r="E135" s="25" t="inlineStr">
         <is>
           <t>정의되지 않은 값을 성공으로 처리하지 않음</t>
         </is>
       </c>
     </row>
-    <row r="135" ht="15" customHeight="1">
-      <c r="A135" s="26" t="inlineStr">
+    <row r="136" ht="15" customHeight="1">
+      <c r="A136" s="26" t="inlineStr">
         <is>
           <t>fact_candidate.senior_position</t>
         </is>
       </c>
-      <c r="B135" s="26" t="inlineStr">
+      <c r="B136" s="26" t="inlineStr">
         <is>
           <t>UNREACHABLE</t>
         </is>
       </c>
-      <c r="C135" s="26" t="inlineStr">
+      <c r="C136" s="26" t="inlineStr">
         <is>
           <t>시니어 입장: UNREACHABLE</t>
         </is>
       </c>
-      <c r="D135" s="26" t="inlineStr">
+      <c r="D136" s="26" t="inlineStr">
         <is>
           <t>fact_candidate.senior_position의 상태·분기 판단</t>
         </is>
       </c>
-      <c r="E135" s="26" t="inlineStr">
+      <c r="E136" s="26" t="inlineStr">
         <is>
           <t>정의되지 않은 값을 성공으로 처리하지 않음</t>
         </is>
       </c>
     </row>
-    <row r="136" ht="15" customHeight="1">
-      <c r="A136" s="25" t="inlineStr">
+    <row r="137" ht="15" customHeight="1">
+      <c r="A137" s="25" t="inlineStr">
         <is>
           <t>fact_candidate.primary_guardian_decision</t>
         </is>
       </c>
-      <c r="B136" s="25" t="inlineStr">
+      <c r="B137" s="25" t="inlineStr">
         <is>
           <t>PENDING</t>
         </is>
       </c>
-      <c r="C136" s="25" t="inlineStr">
+      <c r="C137" s="25" t="inlineStr">
         <is>
           <t>PRIMARY 결정: PENDING</t>
         </is>
       </c>
-      <c r="D136" s="25" t="inlineStr">
+      <c r="D137" s="25" t="inlineStr">
         <is>
           <t>fact_candidate.primary_guardian_decision의 상태·분기 판단</t>
         </is>
       </c>
-      <c r="E136" s="25" t="inlineStr">
+      <c r="E137" s="25" t="inlineStr">
         <is>
           <t>정의되지 않은 값을 성공으로 처리하지 않음</t>
         </is>
       </c>
     </row>
-    <row r="137" ht="15" customHeight="1">
-      <c r="A137" s="26" t="inlineStr">
+    <row r="138" ht="15" customHeight="1">
+      <c r="A138" s="26" t="inlineStr">
         <is>
           <t>fact_candidate.primary_guardian_decision</t>
         </is>
       </c>
-      <c r="B137" s="26" t="inlineStr">
+      <c r="B138" s="26" t="inlineStr">
         <is>
           <t>CONFIRMED_EXISTING_VALUE</t>
         </is>
       </c>
-      <c r="C137" s="26" t="inlineStr">
+      <c r="C138" s="26" t="inlineStr">
         <is>
           <t>PRIMARY 결정: CONFIRMED_EXISTING_VALUE</t>
         </is>
       </c>
-      <c r="D137" s="26" t="inlineStr">
+      <c r="D138" s="26" t="inlineStr">
         <is>
           <t>fact_candidate.primary_guardian_decision의 상태·분기 판단</t>
         </is>
       </c>
-      <c r="E137" s="26" t="inlineStr">
+      <c r="E138" s="26" t="inlineStr">
         <is>
           <t>정의되지 않은 값을 성공으로 처리하지 않음</t>
         </is>
       </c>
     </row>
-    <row r="138" ht="15" customHeight="1">
-      <c r="A138" s="25" t="inlineStr">
+    <row r="139" ht="15" customHeight="1">
+      <c r="A139" s="25" t="inlineStr">
         <is>
           <t>fact_candidate.primary_guardian_decision</t>
         </is>
       </c>
-      <c r="B138" s="25" t="inlineStr">
+      <c r="B139" s="25" t="inlineStr">
         <is>
           <t>CONFIRMED_PROPOSED_VALUE</t>
         </is>
       </c>
-      <c r="C138" s="25" t="inlineStr">
+      <c r="C139" s="25" t="inlineStr">
         <is>
           <t>PRIMARY 결정: CONFIRMED_PROPOSED_VALUE</t>
         </is>
       </c>
-      <c r="D138" s="25" t="inlineStr">
+      <c r="D139" s="25" t="inlineStr">
         <is>
           <t>fact_candidate.primary_guardian_decision의 상태·분기 판단</t>
         </is>
       </c>
-      <c r="E138" s="25" t="inlineStr">
+      <c r="E139" s="25" t="inlineStr">
         <is>
           <t>정의되지 않은 값을 성공으로 처리하지 않음</t>
         </is>
       </c>
     </row>
-    <row r="139" ht="15" customHeight="1">
-      <c r="A139" s="26" t="inlineStr">
+    <row r="140" ht="15" customHeight="1">
+      <c r="A140" s="26" t="inlineStr">
         <is>
           <t>fact_candidate.primary_guardian_decision</t>
         </is>
       </c>
-      <c r="B139" s="26" t="inlineStr">
+      <c r="B140" s="26" t="inlineStr">
         <is>
           <t>REVISED_VALUE</t>
         </is>
       </c>
-      <c r="C139" s="26" t="inlineStr">
+      <c r="C140" s="26" t="inlineStr">
         <is>
           <t>PRIMARY 결정: REVISED_VALUE</t>
         </is>
       </c>
-      <c r="D139" s="26" t="inlineStr">
+      <c r="D140" s="26" t="inlineStr">
         <is>
           <t>fact_candidate.primary_guardian_decision의 상태·분기 판단</t>
         </is>
       </c>
-      <c r="E139" s="26" t="inlineStr">
+      <c r="E140" s="26" t="inlineStr">
         <is>
           <t>정의되지 않은 값을 성공으로 처리하지 않음</t>
         </is>
       </c>
     </row>
-    <row r="140" ht="15" customHeight="1">
-      <c r="A140" s="25" t="inlineStr">
+    <row r="141" ht="15" customHeight="1">
+      <c r="A141" s="25" t="inlineStr">
         <is>
           <t>fact_candidate.primary_guardian_decision</t>
         </is>
       </c>
-      <c r="B140" s="25" t="inlineStr">
+      <c r="B141" s="25" t="inlineStr">
         <is>
           <t>CANCELLED_CHANGE</t>
         </is>
       </c>
-      <c r="C140" s="25" t="inlineStr">
+      <c r="C141" s="25" t="inlineStr">
         <is>
           <t>PRIMARY 결정: CANCELLED_CHANGE</t>
         </is>
       </c>
-      <c r="D140" s="25" t="inlineStr">
+      <c r="D141" s="25" t="inlineStr">
         <is>
           <t>fact_candidate.primary_guardian_decision의 상태·분기 판단</t>
         </is>
       </c>
-      <c r="E140" s="25" t="inlineStr">
+      <c r="E141" s="25" t="inlineStr">
         <is>
           <t>정의되지 않은 값을 성공으로 처리하지 않음</t>
         </is>
       </c>
     </row>
-    <row r="141" ht="15" customHeight="1">
-      <c r="A141" s="26" t="inlineStr">
+    <row r="142" ht="15" customHeight="1">
+      <c r="A142" s="26" t="inlineStr">
         <is>
           <t>fact_candidate.unreachable_reason</t>
         </is>
       </c>
-      <c r="B141" s="26" t="inlineStr">
+      <c r="B142" s="26" t="inlineStr">
         <is>
           <t>NO_RESPONSE</t>
         </is>
       </c>
-      <c r="C141" s="26" t="inlineStr">
+      <c r="C142" s="26" t="inlineStr">
         <is>
           <t>연락 불가 사유: NO_RESPONSE</t>
         </is>
       </c>
-      <c r="D141" s="26" t="inlineStr">
+      <c r="D142" s="26" t="inlineStr">
         <is>
           <t>fact_candidate.unreachable_reason의 상태·분기 판단</t>
         </is>
       </c>
-      <c r="E141" s="26" t="inlineStr">
+      <c r="E142" s="26" t="inlineStr">
         <is>
           <t>정의되지 않은 값을 성공으로 처리하지 않음</t>
         </is>
       </c>
     </row>
-    <row r="142" ht="15" customHeight="1">
-      <c r="A142" s="25" t="inlineStr">
+    <row r="143" ht="15" customHeight="1">
+      <c r="A143" s="25" t="inlineStr">
         <is>
           <t>fact_candidate.unreachable_reason</t>
         </is>
       </c>
-      <c r="B142" s="25" t="inlineStr">
+      <c r="B143" s="25" t="inlineStr">
         <is>
           <t>PHONE_UNAVAILABLE</t>
         </is>
       </c>
-      <c r="C142" s="25" t="inlineStr">
+      <c r="C143" s="25" t="inlineStr">
         <is>
           <t>연락 불가 사유: PHONE_UNAVAILABLE</t>
         </is>
       </c>
-      <c r="D142" s="25" t="inlineStr">
+      <c r="D143" s="25" t="inlineStr">
         <is>
           <t>fact_candidate.unreachable_reason의 상태·분기 판단</t>
         </is>
       </c>
-      <c r="E142" s="25" t="inlineStr">
+      <c r="E143" s="25" t="inlineStr">
         <is>
           <t>정의되지 않은 값을 성공으로 처리하지 않음</t>
         </is>
       </c>
     </row>
-    <row r="143" ht="15" customHeight="1">
-      <c r="A143" s="26" t="inlineStr">
+    <row r="144" ht="15" customHeight="1">
+      <c r="A144" s="26" t="inlineStr">
         <is>
           <t>fact_candidate.unreachable_reason</t>
         </is>
       </c>
-      <c r="B143" s="26" t="inlineStr">
+      <c r="B144" s="26" t="inlineStr">
         <is>
           <t>TEMPORARY_HEALTH_CONDITION</t>
         </is>
       </c>
-      <c r="C143" s="26" t="inlineStr">
+      <c r="C144" s="26" t="inlineStr">
         <is>
           <t>연락 불가 사유: TEMPORARY_HEALTH_CONDITION</t>
         </is>
       </c>
-      <c r="D143" s="26" t="inlineStr">
+      <c r="D144" s="26" t="inlineStr">
         <is>
           <t>fact_candidate.unreachable_reason의 상태·분기 판단</t>
         </is>
       </c>
-      <c r="E143" s="26" t="inlineStr">
+      <c r="E144" s="26" t="inlineStr">
         <is>
           <t>정의되지 않은 값을 성공으로 처리하지 않음</t>
         </is>
       </c>
     </row>
-    <row r="144" ht="15" customHeight="1">
-      <c r="A144" s="25" t="inlineStr">
+    <row r="145" ht="15" customHeight="1">
+      <c r="A145" s="25" t="inlineStr">
         <is>
           <t>fact_candidate.unreachable_reason</t>
         </is>
       </c>
-      <c r="B144" s="25" t="inlineStr">
+      <c r="B145" s="25" t="inlineStr">
         <is>
           <t>COMMUNICATION_DIFFICULTY</t>
         </is>
       </c>
-      <c r="C144" s="25" t="inlineStr">
+      <c r="C145" s="25" t="inlineStr">
         <is>
           <t>연락 불가 사유: COMMUNICATION_DIFFICULTY</t>
         </is>
       </c>
-      <c r="D144" s="25" t="inlineStr">
+      <c r="D145" s="25" t="inlineStr">
         <is>
           <t>fact_candidate.unreachable_reason의 상태·분기 판단</t>
         </is>
       </c>
-      <c r="E144" s="25" t="inlineStr">
+      <c r="E145" s="25" t="inlineStr">
         <is>
           <t>정의되지 않은 값을 성공으로 처리하지 않음</t>
         </is>
       </c>
     </row>
-    <row r="145" ht="15" customHeight="1">
-      <c r="A145" s="26" t="inlineStr">
+    <row r="146" ht="15" customHeight="1">
+      <c r="A146" s="26" t="inlineStr">
         <is>
           <t>fact_candidate.unreachable_reason</t>
         </is>
       </c>
-      <c r="B145" s="26" t="inlineStr">
+      <c r="B146" s="26" t="inlineStr">
         <is>
           <t>OTHER</t>
         </is>
       </c>
-      <c r="C145" s="26" t="inlineStr">
+      <c r="C146" s="26" t="inlineStr">
         <is>
           <t>연락 불가 사유: OTHER</t>
         </is>
       </c>
-      <c r="D145" s="26" t="inlineStr">
+      <c r="D146" s="26" t="inlineStr">
         <is>
           <t>fact_candidate.unreachable_reason의 상태·분기 판단</t>
         </is>
       </c>
-      <c r="E145" s="26" t="inlineStr">
+      <c r="E146" s="26" t="inlineStr">
         <is>
           <t>정의되지 않은 값을 성공으로 처리하지 않음</t>
         </is>
       </c>
     </row>
-    <row r="146" ht="15" customHeight="1">
-      <c r="A146" s="25" t="inlineStr">
+    <row r="147" ht="15" customHeight="1">
+      <c r="A147" s="25" t="inlineStr">
         <is>
           <t>memory.memory_type</t>
         </is>
       </c>
-      <c r="B146" s="25" t="inlineStr">
+      <c r="B147" s="25" t="inlineStr">
         <is>
           <t>PERSONAL_RELATIONSHIP</t>
         </is>
       </c>
-      <c r="C146" s="25" t="inlineStr">
+      <c r="C147" s="25" t="inlineStr">
         <is>
           <t>장기 기억 유형: PERSONAL_RELATIONSHIP</t>
         </is>
       </c>
-      <c r="D146" s="25" t="inlineStr">
+      <c r="D147" s="25" t="inlineStr">
         <is>
           <t>memory.memory_type의 상태·분기 판단</t>
         </is>
       </c>
-      <c r="E146" s="25" t="inlineStr">
+      <c r="E147" s="25" t="inlineStr">
         <is>
           <t>정의되지 않은 값을 성공으로 처리하지 않음</t>
         </is>
       </c>
     </row>
-    <row r="147" ht="15" customHeight="1">
-      <c r="A147" s="26" t="inlineStr">
+    <row r="148" ht="15" customHeight="1">
+      <c r="A148" s="26" t="inlineStr">
         <is>
           <t>memory.memory_type</t>
         </is>
       </c>
-      <c r="B147" s="26" t="inlineStr">
+      <c r="B148" s="26" t="inlineStr">
         <is>
           <t>PREFERENCE</t>
         </is>
       </c>
-      <c r="C147" s="26" t="inlineStr">
+      <c r="C148" s="26" t="inlineStr">
         <is>
           <t>장기 기억 유형: PREFERENCE</t>
         </is>
       </c>
-      <c r="D147" s="26" t="inlineStr">
+      <c r="D148" s="26" t="inlineStr">
         <is>
           <t>memory.memory_type의 상태·분기 판단</t>
         </is>
       </c>
-      <c r="E147" s="26" t="inlineStr">
+      <c r="E148" s="26" t="inlineStr">
         <is>
           <t>정의되지 않은 값을 성공으로 처리하지 않음</t>
         </is>
       </c>
     </row>
-    <row r="148" ht="15" customHeight="1">
-      <c r="A148" s="25" t="inlineStr">
+    <row r="149" ht="15" customHeight="1">
+      <c r="A149" s="25" t="inlineStr">
         <is>
           <t>memory.memory_type</t>
         </is>
       </c>
-      <c r="B148" s="25" t="inlineStr">
+      <c r="B149" s="25" t="inlineStr">
         <is>
           <t>HOBBY</t>
         </is>
       </c>
-      <c r="C148" s="25" t="inlineStr">
+      <c r="C149" s="25" t="inlineStr">
         <is>
           <t>장기 기억 유형: HOBBY</t>
         </is>
       </c>
-      <c r="D148" s="25" t="inlineStr">
+      <c r="D149" s="25" t="inlineStr">
         <is>
           <t>memory.memory_type의 상태·분기 판단</t>
         </is>
       </c>
-      <c r="E148" s="25" t="inlineStr">
+      <c r="E149" s="25" t="inlineStr">
         <is>
           <t>정의되지 않은 값을 성공으로 처리하지 않음</t>
         </is>
       </c>
     </row>
-    <row r="149" ht="15" customHeight="1">
-      <c r="A149" s="26" t="inlineStr">
+    <row r="150" ht="15" customHeight="1">
+      <c r="A150" s="26" t="inlineStr">
         <is>
           <t>memory.memory_type</t>
         </is>
       </c>
-      <c r="B149" s="26" t="inlineStr">
+      <c r="B150" s="26" t="inlineStr">
         <is>
           <t>DAILY_ROUTINE</t>
         </is>
       </c>
-      <c r="C149" s="26" t="inlineStr">
+      <c r="C150" s="26" t="inlineStr">
         <is>
           <t>장기 기억 유형: DAILY_ROUTINE</t>
         </is>
       </c>
-      <c r="D149" s="26" t="inlineStr">
+      <c r="D150" s="26" t="inlineStr">
         <is>
           <t>memory.memory_type의 상태·분기 판단</t>
         </is>
       </c>
-      <c r="E149" s="26" t="inlineStr">
+      <c r="E150" s="26" t="inlineStr">
         <is>
           <t>정의되지 않은 값을 성공으로 처리하지 않음</t>
         </is>
       </c>
     </row>
-    <row r="150" ht="15" customHeight="1">
-      <c r="A150" s="25" t="inlineStr">
+    <row r="151" ht="15" customHeight="1">
+      <c r="A151" s="25" t="inlineStr">
         <is>
           <t>memory.memory_type</t>
         </is>
       </c>
-      <c r="B150" s="25" t="inlineStr">
+      <c r="B151" s="25" t="inlineStr">
         <is>
           <t>LIFE_EVENT</t>
         </is>
       </c>
-      <c r="C150" s="25" t="inlineStr">
+      <c r="C151" s="25" t="inlineStr">
         <is>
           <t>장기 기억 유형: LIFE_EVENT</t>
         </is>
       </c>
-      <c r="D150" s="25" t="inlineStr">
+      <c r="D151" s="25" t="inlineStr">
         <is>
           <t>memory.memory_type의 상태·분기 판단</t>
         </is>
       </c>
-      <c r="E150" s="25" t="inlineStr">
+      <c r="E151" s="25" t="inlineStr">
         <is>
           <t>정의되지 않은 값을 성공으로 처리하지 않음</t>
         </is>
       </c>
     </row>
-    <row r="151" ht="15" customHeight="1">
-      <c r="A151" s="26" t="inlineStr">
+    <row r="152" ht="15" customHeight="1">
+      <c r="A152" s="26" t="inlineStr">
         <is>
           <t>memory.memory_type</t>
         </is>
       </c>
-      <c r="B151" s="26" t="inlineStr">
+      <c r="B152" s="26" t="inlineStr">
         <is>
           <t>FAMILY_MEMORY</t>
         </is>
       </c>
-      <c r="C151" s="26" t="inlineStr">
+      <c r="C152" s="26" t="inlineStr">
         <is>
           <t>장기 기억 유형: FAMILY_MEMORY</t>
         </is>
       </c>
-      <c r="D151" s="26" t="inlineStr">
+      <c r="D152" s="26" t="inlineStr">
         <is>
           <t>memory.memory_type의 상태·분기 판단</t>
         </is>
       </c>
-      <c r="E151" s="26" t="inlineStr">
+      <c r="E152" s="26" t="inlineStr">
         <is>
           <t>정의되지 않은 값을 성공으로 처리하지 않음</t>
         </is>
       </c>
     </row>
-    <row r="152" ht="15" customHeight="1">
-      <c r="A152" s="25" t="inlineStr">
+    <row r="153" ht="15" customHeight="1">
+      <c r="A153" s="25" t="inlineStr">
         <is>
           <t>memory.memory_type</t>
         </is>
       </c>
-      <c r="B152" s="25" t="inlineStr">
+      <c r="B153" s="25" t="inlineStr">
         <is>
           <t>EMOTIONAL_EVENT</t>
         </is>
       </c>
-      <c r="C152" s="25" t="inlineStr">
+      <c r="C153" s="25" t="inlineStr">
         <is>
           <t>장기 기억 유형: EMOTIONAL_EVENT</t>
         </is>
       </c>
-      <c r="D152" s="25" t="inlineStr">
+      <c r="D153" s="25" t="inlineStr">
         <is>
           <t>memory.memory_type의 상태·분기 판단</t>
         </is>
       </c>
-      <c r="E152" s="25" t="inlineStr">
+      <c r="E153" s="25" t="inlineStr">
         <is>
           <t>정의되지 않은 값을 성공으로 처리하지 않음</t>
         </is>
       </c>
     </row>
-    <row r="153" ht="15" customHeight="1">
-      <c r="A153" s="26" t="inlineStr">
+    <row r="154" ht="15" customHeight="1">
+      <c r="A154" s="26" t="inlineStr">
         <is>
           <t>memory.memory_type</t>
         </is>
       </c>
-      <c r="B153" s="26" t="inlineStr">
+      <c r="B154" s="26" t="inlineStr">
         <is>
           <t>OTHER</t>
         </is>
       </c>
-      <c r="C153" s="26" t="inlineStr">
+      <c r="C154" s="26" t="inlineStr">
         <is>
           <t>장기 기억 유형: OTHER</t>
         </is>
       </c>
-      <c r="D153" s="26" t="inlineStr">
+      <c r="D154" s="26" t="inlineStr">
         <is>
           <t>memory.memory_type의 상태·분기 판단</t>
         </is>
       </c>
-      <c r="E153" s="26" t="inlineStr">
+      <c r="E154" s="26" t="inlineStr">
         <is>
           <t>정의되지 않은 값을 성공으로 처리하지 않음</t>
         </is>
       </c>
     </row>
-    <row r="154" ht="15" customHeight="1">
-      <c r="A154" s="25" t="inlineStr">
+    <row r="155" ht="15" customHeight="1">
+      <c r="A155" s="25" t="inlineStr">
         <is>
           <t>memory.lifecycle_status</t>
         </is>
       </c>
-      <c r="B154" s="25" t="inlineStr">
+      <c r="B155" s="25" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="C154" s="25" t="inlineStr">
+      <c r="C155" s="25" t="inlineStr">
         <is>
           <t>기억 수명: ACTIVE</t>
         </is>
       </c>
-      <c r="D154" s="25" t="inlineStr">
+      <c r="D155" s="25" t="inlineStr">
         <is>
           <t>memory.lifecycle_status의 상태·분기 판단</t>
         </is>
       </c>
-      <c r="E154" s="25" t="inlineStr">
+      <c r="E155" s="25" t="inlineStr">
         <is>
           <t>정의되지 않은 값을 성공으로 처리하지 않음</t>
         </is>
       </c>
     </row>
-    <row r="155" ht="15" customHeight="1">
-      <c r="A155" s="26" t="inlineStr">
+    <row r="156" ht="15" customHeight="1">
+      <c r="A156" s="26" t="inlineStr">
         <is>
           <t>memory.lifecycle_status</t>
         </is>
       </c>
-      <c r="B155" s="26" t="inlineStr">
+      <c r="B156" s="26" t="inlineStr">
         <is>
           <t>DISPUTED</t>
         </is>
       </c>
-      <c r="C155" s="26" t="inlineStr">
+      <c r="C156" s="26" t="inlineStr">
         <is>
           <t>기억 수명: DISPUTED</t>
         </is>
       </c>
-      <c r="D155" s="26" t="inlineStr">
+      <c r="D156" s="26" t="inlineStr">
         <is>
           <t>memory.lifecycle_status의 상태·분기 판단</t>
         </is>
       </c>
-      <c r="E155" s="26" t="inlineStr">
+      <c r="E156" s="26" t="inlineStr">
         <is>
           <t>정의되지 않은 값을 성공으로 처리하지 않음</t>
         </is>
       </c>
     </row>
-    <row r="156" ht="15" customHeight="1">
-      <c r="A156" s="25" t="inlineStr">
+    <row r="157" ht="15" customHeight="1">
+      <c r="A157" s="25" t="inlineStr">
         <is>
           <t>memory.lifecycle_status</t>
         </is>
       </c>
-      <c r="B156" s="25" t="inlineStr">
+      <c r="B157" s="25" t="inlineStr">
         <is>
           <t>SUPERSEDED</t>
         </is>
       </c>
-      <c r="C156" s="25" t="inlineStr">
+      <c r="C157" s="25" t="inlineStr">
         <is>
           <t>기억 수명: SUPERSEDED</t>
         </is>
       </c>
-      <c r="D156" s="25" t="inlineStr">
+      <c r="D157" s="25" t="inlineStr">
         <is>
           <t>memory.lifecycle_status의 상태·분기 판단</t>
         </is>
       </c>
-      <c r="E156" s="25" t="inlineStr">
+      <c r="E157" s="25" t="inlineStr">
         <is>
           <t>정의되지 않은 값을 성공으로 처리하지 않음</t>
         </is>
       </c>
     </row>
-    <row r="157" ht="15" customHeight="1">
-      <c r="A157" s="26" t="inlineStr">
+    <row r="158" ht="15" customHeight="1">
+      <c r="A158" s="26" t="inlineStr">
         <is>
           <t>memory.lifecycle_status</t>
         </is>
       </c>
-      <c r="B157" s="26" t="inlineStr">
+      <c r="B158" s="26" t="inlineStr">
         <is>
           <t>EXPIRED</t>
         </is>
       </c>
-      <c r="C157" s="26" t="inlineStr">
+      <c r="C158" s="26" t="inlineStr">
         <is>
           <t>기억 수명: EXPIRED</t>
         </is>
       </c>
-      <c r="D157" s="26" t="inlineStr">
+      <c r="D158" s="26" t="inlineStr">
         <is>
           <t>memory.lifecycle_status의 상태·분기 판단</t>
         </is>
       </c>
-      <c r="E157" s="26" t="inlineStr">
+      <c r="E158" s="26" t="inlineStr">
         <is>
           <t>정의되지 않은 값을 성공으로 처리하지 않음</t>
         </is>
       </c>
     </row>
-    <row r="158" ht="15" customHeight="1">
-      <c r="A158" s="25" t="inlineStr">
+    <row r="159" ht="15" customHeight="1">
+      <c r="A159" s="25" t="inlineStr">
         <is>
           <t>memory.lifecycle_status</t>
         </is>
       </c>
-      <c r="B158" s="25" t="inlineStr">
+      <c r="B159" s="25" t="inlineStr">
         <is>
           <t>DELETED</t>
         </is>
       </c>
-      <c r="C158" s="25" t="inlineStr">
+      <c r="C159" s="25" t="inlineStr">
         <is>
           <t>기억 수명: DELETED</t>
         </is>
       </c>
-      <c r="D158" s="25" t="inlineStr">
+      <c r="D159" s="25" t="inlineStr">
         <is>
           <t>memory.lifecycle_status의 상태·분기 판단</t>
         </is>
       </c>
-      <c r="E158" s="25" t="inlineStr">
+      <c r="E159" s="25" t="inlineStr">
         <is>
           <t>정의되지 않은 값을 성공으로 처리하지 않음</t>
         </is>
       </c>
     </row>
-    <row r="159" ht="15" customHeight="1">
-      <c r="A159" s="26" t="inlineStr">
+    <row r="160" ht="15" customHeight="1">
+      <c r="A160" s="26" t="inlineStr">
         <is>
           <t>memory.visibility</t>
         </is>
       </c>
-      <c r="B159" s="26" t="inlineStr">
+      <c r="B160" s="26" t="inlineStr">
         <is>
           <t>PRIVATE</t>
         </is>
       </c>
-      <c r="C159" s="26" t="inlineStr">
+      <c r="C160" s="26" t="inlineStr">
         <is>
           <t>기억 공개 범위: PRIVATE</t>
         </is>
       </c>
-      <c r="D159" s="26" t="inlineStr">
+      <c r="D160" s="26" t="inlineStr">
         <is>
           <t>memory.visibility의 상태·분기 판단</t>
         </is>
       </c>
-      <c r="E159" s="26" t="inlineStr">
+      <c r="E160" s="26" t="inlineStr">
         <is>
           <t>정의되지 않은 값을 성공으로 처리하지 않음</t>
         </is>
       </c>
     </row>
-    <row r="160" ht="15" customHeight="1">
-      <c r="A160" s="25" t="inlineStr">
+    <row r="161" ht="15" customHeight="1">
+      <c r="A161" s="25" t="inlineStr">
         <is>
           <t>memory.visibility</t>
         </is>
       </c>
-      <c r="B160" s="25" t="inlineStr">
+      <c r="B161" s="25" t="inlineStr">
         <is>
           <t>SHARED_WITH_PRIMARY</t>
         </is>
       </c>
-      <c r="C160" s="25" t="inlineStr">
+      <c r="C161" s="25" t="inlineStr">
         <is>
           <t>기억 공개 범위: SHARED_WITH_PRIMARY</t>
         </is>
       </c>
-      <c r="D160" s="25" t="inlineStr">
+      <c r="D161" s="25" t="inlineStr">
         <is>
           <t>memory.visibility의 상태·분기 판단</t>
         </is>
       </c>
-      <c r="E160" s="25" t="inlineStr">
+      <c r="E161" s="25" t="inlineStr">
         <is>
           <t>정의되지 않은 값을 성공으로 처리하지 않음</t>
         </is>
       </c>
     </row>
-    <row r="161" ht="15" customHeight="1">
-      <c r="A161" s="26" t="inlineStr">
+    <row r="162" ht="15" customHeight="1">
+      <c r="A162" s="26" t="inlineStr">
         <is>
           <t>memory.visibility</t>
         </is>
       </c>
-      <c r="B161" s="26" t="inlineStr">
+      <c r="B162" s="26" t="inlineStr">
         <is>
           <t>SHARED_WITH_GUARDIANS</t>
         </is>
       </c>
-      <c r="C161" s="26" t="inlineStr">
+      <c r="C162" s="26" t="inlineStr">
         <is>
           <t>기억 공개 범위: SHARED_WITH_GUARDIANS</t>
         </is>
       </c>
-      <c r="D161" s="26" t="inlineStr">
+      <c r="D162" s="26" t="inlineStr">
         <is>
           <t>memory.visibility의 상태·분기 판단</t>
         </is>
       </c>
-      <c r="E161" s="26" t="inlineStr">
+      <c r="E162" s="26" t="inlineStr">
         <is>
           <t>정의되지 않은 값을 성공으로 처리하지 않음</t>
         </is>
       </c>
     </row>
-    <row r="162" ht="15" customHeight="1">
-      <c r="A162" s="25" t="inlineStr">
+    <row r="163" ht="15" customHeight="1">
+      <c r="A163" s="25" t="inlineStr">
         <is>
           <t>care_record.record_type</t>
         </is>
       </c>
-      <c r="B162" s="25" t="inlineStr">
+      <c r="B163" s="25" t="inlineStr">
         <is>
           <t>HEALTH_CONDITION</t>
         </is>
       </c>
-      <c r="C162" s="25" t="inlineStr">
+      <c r="C163" s="25" t="inlineStr">
         <is>
           <t>돌봄 기록 유형: HEALTH_CONDITION</t>
         </is>
       </c>
-      <c r="D162" s="25" t="inlineStr">
+      <c r="D163" s="25" t="inlineStr">
         <is>
           <t>care_record.record_type의 상태·분기 판단</t>
         </is>
       </c>
-      <c r="E162" s="25" t="inlineStr">
+      <c r="E163" s="25" t="inlineStr">
         <is>
           <t>정의되지 않은 값을 성공으로 처리하지 않음</t>
         </is>
       </c>
     </row>
-    <row r="163" ht="15" customHeight="1">
-      <c r="A163" s="26" t="inlineStr">
+    <row r="164" ht="15" customHeight="1">
+      <c r="A164" s="26" t="inlineStr">
         <is>
           <t>care_record.record_type</t>
         </is>
       </c>
-      <c r="B163" s="26" t="inlineStr">
+      <c r="B164" s="26" t="inlineStr">
         <is>
           <t>ALLERGY</t>
         </is>
       </c>
-      <c r="C163" s="26" t="inlineStr">
+      <c r="C164" s="26" t="inlineStr">
         <is>
           <t>돌봄 기록 유형: ALLERGY</t>
         </is>
       </c>
-      <c r="D163" s="26" t="inlineStr">
+      <c r="D164" s="26" t="inlineStr">
         <is>
           <t>care_record.record_type의 상태·분기 판단</t>
         </is>
       </c>
-      <c r="E163" s="26" t="inlineStr">
+      <c r="E164" s="26" t="inlineStr">
         <is>
           <t>정의되지 않은 값을 성공으로 처리하지 않음</t>
         </is>
       </c>
     </row>
-    <row r="164" ht="15" customHeight="1">
-      <c r="A164" s="25" t="inlineStr">
+    <row r="165" ht="15" customHeight="1">
+      <c r="A165" s="25" t="inlineStr">
         <is>
           <t>care_record.record_type</t>
         </is>
       </c>
-      <c r="B164" s="25" t="inlineStr">
+      <c r="B165" s="25" t="inlineStr">
         <is>
           <t>PHYSICAL_LIMITATION</t>
         </is>
       </c>
-      <c r="C164" s="25" t="inlineStr">
+      <c r="C165" s="25" t="inlineStr">
         <is>
           <t>돌봄 기록 유형: PHYSICAL_LIMITATION</t>
         </is>
       </c>
-      <c r="D164" s="25" t="inlineStr">
+      <c r="D165" s="25" t="inlineStr">
         <is>
           <t>care_record.record_type의 상태·분기 판단</t>
         </is>
       </c>
-      <c r="E164" s="25" t="inlineStr">
+      <c r="E165" s="25" t="inlineStr">
         <is>
           <t>정의되지 않은 값을 성공으로 처리하지 않음</t>
         </is>
       </c>
     </row>
-    <row r="165" ht="15" customHeight="1">
-      <c r="A165" s="26" t="inlineStr">
+    <row r="166" ht="15" customHeight="1">
+      <c r="A166" s="26" t="inlineStr">
         <is>
           <t>care_record.record_type</t>
         </is>
       </c>
-      <c r="B165" s="26" t="inlineStr">
+      <c r="B166" s="26" t="inlineStr">
         <is>
           <t>MEDICATION</t>
         </is>
       </c>
-      <c r="C165" s="26" t="inlineStr">
+      <c r="C166" s="26" t="inlineStr">
         <is>
           <t>돌봄 기록 유형: MEDICATION</t>
         </is>
       </c>
-      <c r="D165" s="26" t="inlineStr">
+      <c r="D166" s="26" t="inlineStr">
         <is>
           <t>care_record.record_type의 상태·분기 판단</t>
         </is>
       </c>
-      <c r="E165" s="26" t="inlineStr">
+      <c r="E166" s="26" t="inlineStr">
         <is>
           <t>정의되지 않은 값을 성공으로 처리하지 않음</t>
         </is>
       </c>
     </row>
-    <row r="166" ht="15" customHeight="1">
-      <c r="A166" s="25" t="inlineStr">
+    <row r="167" ht="15" customHeight="1">
+      <c r="A167" s="25" t="inlineStr">
         <is>
           <t>care_record.record_type</t>
         </is>
       </c>
-      <c r="B166" s="25" t="inlineStr">
+      <c r="B167" s="25" t="inlineStr">
         <is>
           <t>MEDICATION_SCHEDULE</t>
         </is>
       </c>
-      <c r="C166" s="25" t="inlineStr">
+      <c r="C167" s="25" t="inlineStr">
         <is>
           <t>돌봄 기록 유형: MEDICATION_SCHEDULE</t>
         </is>
       </c>
-      <c r="D166" s="25" t="inlineStr">
+      <c r="D167" s="25" t="inlineStr">
         <is>
           <t>care_record.record_type의 상태·분기 판단</t>
         </is>
       </c>
-      <c r="E166" s="25" t="inlineStr">
+      <c r="E167" s="25" t="inlineStr">
         <is>
           <t>정의되지 않은 값을 성공으로 처리하지 않음</t>
         </is>
       </c>
     </row>
-    <row r="167" ht="15" customHeight="1">
-      <c r="A167" s="26" t="inlineStr">
+    <row r="168" ht="15" customHeight="1">
+      <c r="A168" s="26" t="inlineStr">
         <is>
           <t>care_record.record_type</t>
         </is>
       </c>
-      <c r="B167" s="26" t="inlineStr">
+      <c r="B168" s="26" t="inlineStr">
         <is>
           <t>MEDICATION_REMINDER</t>
         </is>
       </c>
-      <c r="C167" s="26" t="inlineStr">
+      <c r="C168" s="26" t="inlineStr">
         <is>
           <t>돌봄 기록 유형: MEDICATION_REMINDER</t>
         </is>
       </c>
-      <c r="D167" s="26" t="inlineStr">
+      <c r="D168" s="26" t="inlineStr">
         <is>
           <t>care_record.record_type의 상태·분기 판단</t>
         </is>
       </c>
-      <c r="E167" s="26" t="inlineStr">
+      <c r="E168" s="26" t="inlineStr">
         <is>
           <t>정의되지 않은 값을 성공으로 처리하지 않음</t>
         </is>
       </c>
     </row>
-    <row r="168" ht="15" customHeight="1">
-      <c r="A168" s="25" t="inlineStr">
+    <row r="169" ht="15" customHeight="1">
+      <c r="A169" s="25" t="inlineStr">
         <is>
           <t>care_record.record_type</t>
         </is>
       </c>
-      <c r="B168" s="25" t="inlineStr">
+      <c r="B169" s="25" t="inlineStr">
         <is>
           <t>MEDICATION_TAKEN</t>
         </is>
       </c>
-      <c r="C168" s="25" t="inlineStr">
+      <c r="C169" s="25" t="inlineStr">
         <is>
           <t>돌봄 기록 유형: MEDICATION_TAKEN</t>
         </is>
       </c>
-      <c r="D168" s="25" t="inlineStr">
+      <c r="D169" s="25" t="inlineStr">
         <is>
           <t>care_record.record_type의 상태·분기 판단</t>
         </is>
       </c>
-      <c r="E168" s="25" t="inlineStr">
+      <c r="E169" s="25" t="inlineStr">
         <is>
           <t>정의되지 않은 값을 성공으로 처리하지 않음</t>
         </is>
       </c>
     </row>
-    <row r="169" ht="15" customHeight="1">
-      <c r="A169" s="28" t="inlineStr">
+    <row r="170" ht="15" customHeight="1">
+      <c r="A170" s="28" t="inlineStr">
         <is>
           <t>care_record.record_type</t>
         </is>
       </c>
-      <c r="B169" s="28" t="inlineStr">
+      <c r="B170" s="28" t="inlineStr">
         <is>
           <t>APPOINTMENT</t>
         </is>
       </c>
-      <c r="C169" s="28" t="inlineStr">
+      <c r="C170" s="28" t="inlineStr">
         <is>
           <t>돌봄 기록 유형: APPOINTMENT</t>
         </is>
       </c>
-      <c r="D169" s="28" t="inlineStr">
+      <c r="D170" s="28" t="inlineStr">
         <is>
           <t>care_record.record_type의 상태·분기 판단</t>
         </is>
       </c>
-      <c r="E169" s="28" t="inlineStr">
-        <is>
-          <t>정의되지 않은 값을 성공으로 처리하지 않음</t>
-        </is>
-      </c>
-    </row>
-    <row r="170" ht="15" customHeight="1">
-      <c r="A170" s="32" t="inlineStr">
-        <is>
-          <t>care_record.record_type</t>
-        </is>
-      </c>
-      <c r="B170" s="32" t="inlineStr">
-        <is>
-          <t>PERSONAL_SCHEDULE</t>
-        </is>
-      </c>
-      <c r="C170" s="32" t="inlineStr">
-        <is>
-          <t>돌봄 기록 유형: PERSONAL_SCHEDULE</t>
-        </is>
-      </c>
-      <c r="D170" s="32" t="inlineStr">
-        <is>
-          <t>care_record.record_type의 상태·분기 판단</t>
-        </is>
-      </c>
-      <c r="E170" s="32" t="inlineStr">
+      <c r="E170" s="28" t="inlineStr">
         <is>
           <t>정의되지 않은 값을 성공으로 처리하지 않음</t>
         </is>
@@ -23481,12 +23501,12 @@
       </c>
       <c r="B171" s="32" t="inlineStr">
         <is>
-          <t>HEALTH_OBSERVATION</t>
+          <t>PERSONAL_SCHEDULE</t>
         </is>
       </c>
       <c r="C171" s="32" t="inlineStr">
         <is>
-          <t>돌봄 기록 유형: HEALTH_OBSERVATION</t>
+          <t>돌봄 기록 유형: PERSONAL_SCHEDULE</t>
         </is>
       </c>
       <c r="D171" s="32" t="inlineStr">
@@ -23508,12 +23528,12 @@
       </c>
       <c r="B172" s="32" t="inlineStr">
         <is>
-          <t>REST_OBSERVATION</t>
+          <t>HEALTH_OBSERVATION</t>
         </is>
       </c>
       <c r="C172" s="32" t="inlineStr">
         <is>
-          <t>돌봄 기록 유형: REST_OBSERVATION</t>
+          <t>돌봄 기록 유형: HEALTH_OBSERVATION</t>
         </is>
       </c>
       <c r="D172" s="32" t="inlineStr">
@@ -23535,12 +23555,12 @@
       </c>
       <c r="B173" s="32" t="inlineStr">
         <is>
-          <t>ENVIRONMENT_OBSERVATION</t>
+          <t>REST_OBSERVATION</t>
         </is>
       </c>
       <c r="C173" s="32" t="inlineStr">
         <is>
-          <t>돌봄 기록 유형: ENVIRONMENT_OBSERVATION</t>
+          <t>돌봄 기록 유형: REST_OBSERVATION</t>
         </is>
       </c>
       <c r="D173" s="32" t="inlineStr">
@@ -23562,12 +23582,12 @@
       </c>
       <c r="B174" s="32" t="inlineStr">
         <is>
-          <t>COGNITIVE_ASSESSMENT</t>
+          <t>ENVIRONMENT_OBSERVATION</t>
         </is>
       </c>
       <c r="C174" s="32" t="inlineStr">
         <is>
-          <t>돌봄 기록 유형: COGNITIVE_ASSESSMENT</t>
+          <t>돌봄 기록 유형: ENVIRONMENT_OBSERVATION</t>
         </is>
       </c>
       <c r="D174" s="32" t="inlineStr">
@@ -23589,12 +23609,12 @@
       </c>
       <c r="B175" s="32" t="inlineStr">
         <is>
-          <t>GUARDIAN_NOTIFICATION</t>
+          <t>COGNITIVE_ASSESSMENT</t>
         </is>
       </c>
       <c r="C175" s="32" t="inlineStr">
         <is>
-          <t>돌봄 기록 유형: GUARDIAN_NOTIFICATION</t>
+          <t>돌봄 기록 유형: COGNITIVE_ASSESSMENT</t>
         </is>
       </c>
       <c r="D175" s="32" t="inlineStr">
@@ -23611,22 +23631,22 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" s="32" t="inlineStr">
         <is>
-          <t>care_record.status</t>
+          <t>care_record.record_type</t>
         </is>
       </c>
       <c r="B176" s="32" t="inlineStr">
         <is>
-          <t>ACTIVE</t>
+          <t>GUARDIAN_NOTIFICATION</t>
         </is>
       </c>
       <c r="C176" s="32" t="inlineStr">
         <is>
-          <t>돌봄 기록 상태: ACTIVE</t>
+          <t>돌봄 기록 유형: GUARDIAN_NOTIFICATION</t>
         </is>
       </c>
       <c r="D176" s="32" t="inlineStr">
         <is>
-          <t>care_record.status의 상태·분기 판단</t>
+          <t>care_record.record_type의 상태·분기 판단</t>
         </is>
       </c>
       <c r="E176" s="32" t="inlineStr">
@@ -23643,12 +23663,12 @@
       </c>
       <c r="B177" s="32" t="inlineStr">
         <is>
-          <t>COMPLETED</t>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="C177" s="32" t="inlineStr">
         <is>
-          <t>돌봄 기록 상태: COMPLETED</t>
+          <t>돌봄 기록 상태: ACTIVE</t>
         </is>
       </c>
       <c r="D177" s="32" t="inlineStr">
@@ -23670,12 +23690,12 @@
       </c>
       <c r="B178" s="32" t="inlineStr">
         <is>
-          <t>CANCELLED</t>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="C178" s="32" t="inlineStr">
         <is>
-          <t>돌봄 기록 상태: CANCELLED</t>
+          <t>돌봄 기록 상태: COMPLETED</t>
         </is>
       </c>
       <c r="D178" s="32" t="inlineStr">
@@ -23697,12 +23717,12 @@
       </c>
       <c r="B179" s="32" t="inlineStr">
         <is>
-          <t>SUPERSEDED</t>
+          <t>CANCELLED</t>
         </is>
       </c>
       <c r="C179" s="32" t="inlineStr">
         <is>
-          <t>돌봄 기록 상태: SUPERSEDED</t>
+          <t>돌봄 기록 상태: CANCELLED</t>
         </is>
       </c>
       <c r="D179" s="32" t="inlineStr">
@@ -23719,22 +23739,22 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" s="32" t="inlineStr">
         <is>
-          <t>care_record.recurrence.frequency</t>
+          <t>care_record.status</t>
         </is>
       </c>
       <c r="B180" s="32" t="inlineStr">
         <is>
-          <t>DAILY</t>
+          <t>SUPERSEDED</t>
         </is>
       </c>
       <c r="C180" s="32" t="inlineStr">
         <is>
-          <t>반복 주기: DAILY</t>
+          <t>돌봄 기록 상태: SUPERSEDED</t>
         </is>
       </c>
       <c r="D180" s="32" t="inlineStr">
         <is>
-          <t>care_record.recurrence.frequency의 상태·분기 판단</t>
+          <t>care_record.status의 상태·분기 판단</t>
         </is>
       </c>
       <c r="E180" s="32" t="inlineStr">
@@ -23751,12 +23771,12 @@
       </c>
       <c r="B181" s="32" t="inlineStr">
         <is>
-          <t>WEEKLY</t>
+          <t>DAILY</t>
         </is>
       </c>
       <c r="C181" s="32" t="inlineStr">
         <is>
-          <t>반복 주기: WEEKLY</t>
+          <t>반복 주기: DAILY</t>
         </is>
       </c>
       <c r="D181" s="32" t="inlineStr">
@@ -23773,54 +23793,54 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" s="32" t="inlineStr">
         <is>
-          <t>scenario.scenario_type</t>
+          <t>care_record.recurrence.frequency</t>
         </is>
       </c>
       <c r="B182" s="32" t="inlineStr">
         <is>
-          <t>WALK</t>
+          <t>WEEKLY</t>
         </is>
       </c>
       <c r="C182" s="32" t="inlineStr">
         <is>
-          <t>시나리오 유형: 산책</t>
+          <t>반복 주기: WEEKLY</t>
         </is>
       </c>
       <c r="D182" s="32" t="inlineStr">
         <is>
-          <t>scenario.scenario_type의 상태·분기 판단</t>
+          <t>care_record.recurrence.frequency의 상태·분기 판단</t>
         </is>
       </c>
       <c r="E182" s="32" t="inlineStr">
         <is>
-          <t>FOLLOW 제어만 관리하고 tracking은 Robot 책임</t>
+          <t>정의되지 않은 값을 성공으로 처리하지 않음</t>
         </is>
       </c>
     </row>
     <row r="183" ht="15" customHeight="1">
       <c r="A183" s="32" t="inlineStr">
         <is>
-          <t>scenario.final_status</t>
+          <t>scenario.scenario_type</t>
         </is>
       </c>
       <c r="B183" s="32" t="inlineStr">
         <is>
-          <t>STARTING_FOLLOW</t>
+          <t>WALK</t>
         </is>
       </c>
       <c r="C183" s="32" t="inlineStr">
         <is>
-          <t>FOLLOW_START 결과 대기</t>
+          <t>시나리오 유형: 산책</t>
         </is>
       </c>
       <c r="D183" s="32" t="inlineStr">
         <is>
-          <t>WALK 시작 명령 발행 뒤 사용</t>
+          <t>scenario.scenario_type의 상태·분기 판단</t>
         </is>
       </c>
       <c r="E183" s="32" t="inlineStr">
         <is>
-          <t>늦은 STARTED가 STOPPING을 되돌리지 않음</t>
+          <t>FOLLOW 제어만 관리하고 tracking은 Robot 책임</t>
         </is>
       </c>
     </row>
@@ -23832,22 +23852,22 @@
       </c>
       <c r="B184" s="32" t="inlineStr">
         <is>
-          <t>FOLLOWING</t>
+          <t>STARTING_FOLLOW</t>
         </is>
       </c>
       <c r="C184" s="32" t="inlineStr">
         <is>
-          <t>Robot 추종 진행 중</t>
+          <t>FOLLOW_START 결과 대기</t>
         </is>
       </c>
       <c r="D184" s="32" t="inlineStr">
         <is>
-          <t>유효한 STARTED·UNCHANGED 뒤 사용</t>
+          <t>WALK 시작 명령 발행 뒤 사용</t>
         </is>
       </c>
       <c r="E184" s="32" t="inlineStr">
         <is>
-          <t>공용 20분 watchdog에서 제외</t>
+          <t>늦은 STARTED가 STOPPING을 되돌리지 않음</t>
         </is>
       </c>
     </row>
@@ -23859,49 +23879,49 @@
       </c>
       <c r="B185" s="32" t="inlineStr">
         <is>
-          <t>STOPPING_FOLLOW</t>
+          <t>FOLLOWING</t>
         </is>
       </c>
       <c r="C185" s="32" t="inlineStr">
         <is>
-          <t>FOLLOW_STOP 결과 대기</t>
+          <t>Robot 추종 진행 중</t>
         </is>
       </c>
       <c r="D185" s="32" t="inlineStr">
         <is>
-          <t>명시적 STOP 또는 안전 종료 시 사용</t>
+          <t>유효한 STARTED·UNCHANGED 뒤 사용</t>
         </is>
       </c>
       <c r="E185" s="32" t="inlineStr">
         <is>
-          <t>같은 STOP 요청은 새 command를 만들지 않음</t>
+          <t>공용 20분 watchdog에서 제외</t>
         </is>
       </c>
     </row>
     <row r="186" ht="15" customHeight="1">
       <c r="A186" s="32" t="inlineStr">
         <is>
-          <t>walk_request_receipt.ingress</t>
+          <t>scenario.final_status</t>
         </is>
       </c>
       <c r="B186" s="32" t="inlineStr">
         <is>
-          <t>MQTT</t>
+          <t>STOPPING_FOLLOW</t>
         </is>
       </c>
       <c r="C186" s="32" t="inlineStr">
         <is>
-          <t>Voice/AI MQTT 유입</t>
+          <t>FOLLOW_STOP 결과 대기</t>
         </is>
       </c>
       <c r="D186" s="32" t="inlineStr">
         <is>
-          <t>request_id 멱등 범위를 정함</t>
+          <t>명시적 STOP 또는 안전 종료 시 사용</t>
         </is>
       </c>
       <c r="E186" s="32" t="inlineStr">
         <is>
-          <t>payload source와 구분</t>
+          <t>같은 STOP 요청은 새 command를 만들지 않음</t>
         </is>
       </c>
     </row>
@@ -23913,49 +23933,49 @@
       </c>
       <c r="B187" s="32" t="inlineStr">
         <is>
-          <t>GUARDIAN_REST</t>
+          <t>MQTT</t>
         </is>
       </c>
       <c r="C187" s="32" t="inlineStr">
         <is>
-          <t>Guardian REST 유입</t>
+          <t>Voice/AI MQTT 유입</t>
         </is>
       </c>
       <c r="D187" s="32" t="inlineStr">
         <is>
-          <t>App requestId 멱등 범위를 정함</t>
+          <t>request_id 멱등 범위를 정함</t>
         </is>
       </c>
       <c r="E187" s="32" t="inlineStr">
         <is>
-          <t>MQTT의 같은 문자열 ID와 충돌하지 않음</t>
+          <t>payload source와 구분</t>
         </is>
       </c>
     </row>
     <row r="188" ht="15" customHeight="1">
       <c r="A188" s="32" t="inlineStr">
         <is>
-          <t>walk_request_receipt.action</t>
+          <t>walk_request_receipt.ingress</t>
         </is>
       </c>
       <c r="B188" s="32" t="inlineStr">
         <is>
-          <t>START</t>
+          <t>GUARDIAN_REST</t>
         </is>
       </c>
       <c r="C188" s="32" t="inlineStr">
         <is>
-          <t>산책 시작 요청</t>
+          <t>Guardian REST 유입</t>
         </is>
       </c>
       <c r="D188" s="32" t="inlineStr">
         <is>
-          <t>새 WALK 입장 정책 실행</t>
+          <t>App requestId 멱등 범위를 정함</t>
         </is>
       </c>
       <c r="E188" s="32" t="inlineStr">
         <is>
-          <t>활성 시나리오를 선점하지 않음</t>
+          <t>MQTT의 같은 문자열 ID와 충돌하지 않음</t>
         </is>
       </c>
     </row>
@@ -23967,49 +23987,49 @@
       </c>
       <c r="B189" s="32" t="inlineStr">
         <is>
-          <t>STOP</t>
+          <t>START</t>
         </is>
       </c>
       <c r="C189" s="32" t="inlineStr">
         <is>
-          <t>산책 종료 요청</t>
+          <t>산책 시작 요청</t>
         </is>
       </c>
       <c r="D189" s="32" t="inlineStr">
         <is>
-          <t>같은 Robot의 활성 WALK를 잠금 조회</t>
+          <t>새 WALK 입장 정책 실행</t>
         </is>
       </c>
       <c r="E189" s="32" t="inlineStr">
         <is>
-          <t>새 Scenario를 만들지 않음</t>
+          <t>활성 시나리오를 선점하지 않음</t>
         </is>
       </c>
     </row>
     <row r="190" ht="15" customHeight="1">
       <c r="A190" s="32" t="inlineStr">
         <is>
-          <t>walk_request_receipt.source</t>
+          <t>walk_request_receipt.action</t>
         </is>
       </c>
       <c r="B190" s="32" t="inlineStr">
         <is>
-          <t>VOICE</t>
+          <t>STOP</t>
         </is>
       </c>
       <c r="C190" s="32" t="inlineStr">
         <is>
-          <t>음성 의도 판정 출처</t>
+          <t>산책 종료 요청</t>
         </is>
       </c>
       <c r="D190" s="32" t="inlineStr">
         <is>
-          <t>MQTT 요청 문맥 비교</t>
+          <t>같은 Robot의 활성 WALK를 잠금 조회</t>
         </is>
       </c>
       <c r="E190" s="32" t="inlineStr">
         <is>
-          <t>Backend가 대화 intent를 새로 만들지 않음</t>
+          <t>새 Scenario를 만들지 않음</t>
         </is>
       </c>
     </row>
@@ -24021,49 +24041,49 @@
       </c>
       <c r="B191" s="32" t="inlineStr">
         <is>
-          <t>APP</t>
+          <t>VOICE</t>
         </is>
       </c>
       <c r="C191" s="32" t="inlineStr">
         <is>
-          <t>Guardian App 출처</t>
+          <t>음성 의도 판정 출처</t>
         </is>
       </c>
       <c r="D191" s="32" t="inlineStr">
         <is>
-          <t>REST adapter가 서버에서 고정</t>
+          <t>MQTT 요청 문맥 비교</t>
         </is>
       </c>
       <c r="E191" s="32" t="inlineStr">
         <is>
-          <t>클라이언트가 다른 값으로 지정할 수 없음</t>
+          <t>Backend가 대화 intent를 새로 만들지 않음</t>
         </is>
       </c>
     </row>
     <row r="192" ht="15" customHeight="1">
       <c r="A192" s="32" t="inlineStr">
         <is>
-          <t>walk_request_receipt.disposition</t>
+          <t>walk_request_receipt.source</t>
         </is>
       </c>
       <c r="B192" s="32" t="inlineStr">
         <is>
-          <t>RECEIVED</t>
+          <t>APP</t>
         </is>
       </c>
       <c r="C192" s="32" t="inlineStr">
         <is>
-          <t>처리 중 임시 결정</t>
+          <t>Guardian App 출처</t>
         </is>
       </c>
       <c r="D192" s="32" t="inlineStr">
         <is>
-          <t>영수증 생성 직후 사용</t>
+          <t>REST adapter가 서버에서 고정</t>
         </is>
       </c>
       <c r="E192" s="32" t="inlineStr">
         <is>
-          <t>최종 응답으로 해석하지 않음</t>
+          <t>클라이언트가 다른 값으로 지정할 수 없음</t>
         </is>
       </c>
     </row>
@@ -24075,22 +24095,22 @@
       </c>
       <c r="B193" s="32" t="inlineStr">
         <is>
-          <t>ACCEPTED</t>
+          <t>RECEIVED</t>
         </is>
       </c>
       <c r="C193" s="32" t="inlineStr">
         <is>
-          <t>새 FOLLOW 명령 수락</t>
+          <t>처리 중 임시 결정</t>
         </is>
       </c>
       <c r="D193" s="32" t="inlineStr">
         <is>
-          <t>START 또는 STOP 명령 발행 결정</t>
+          <t>영수증 생성 직후 사용</t>
         </is>
       </c>
       <c r="E193" s="32" t="inlineStr">
         <is>
-          <t>scenario_id·scenario_status 필수</t>
+          <t>최종 응답으로 해석하지 않음</t>
         </is>
       </c>
     </row>
@@ -24102,22 +24122,22 @@
       </c>
       <c r="B194" s="32" t="inlineStr">
         <is>
-          <t>NO_OP_ALREADY_STOPPING</t>
+          <t>ACCEPTED</t>
         </is>
       </c>
       <c r="C194" s="32" t="inlineStr">
         <is>
-          <t>이미 종료 명령 대기 중</t>
+          <t>새 FOLLOW 명령 수락</t>
         </is>
       </c>
       <c r="D194" s="32" t="inlineStr">
         <is>
-          <t>STOPPING 중 다른 STOP을 결정적으로 수락</t>
+          <t>START 또는 STOP 명령 발행 결정</t>
         </is>
       </c>
       <c r="E194" s="32" t="inlineStr">
         <is>
-          <t>기존 commandId를 다시 만들지 않음</t>
+          <t>scenario_id·scenario_status 필수</t>
         </is>
       </c>
     </row>
@@ -24129,22 +24149,22 @@
       </c>
       <c r="B195" s="32" t="inlineStr">
         <is>
-          <t>REJECTED_NO_ACTIVE_WALK</t>
+          <t>NO_OP_ALREADY_STOPPING</t>
         </is>
       </c>
       <c r="C195" s="32" t="inlineStr">
         <is>
-          <t>종료할 활성 산책 없음</t>
+          <t>이미 종료 명령 대기 중</t>
         </is>
       </c>
       <c r="D195" s="32" t="inlineStr">
         <is>
-          <t>STOP without active 응답</t>
+          <t>STOPPING 중 다른 STOP을 결정적으로 수락</t>
         </is>
       </c>
       <c r="E195" s="32" t="inlineStr">
         <is>
-          <t>나중에 생긴 산책을 같은 ID로 멈추지 않음</t>
+          <t>기존 commandId를 다시 만들지 않음</t>
         </is>
       </c>
     </row>
@@ -24156,22 +24176,22 @@
       </c>
       <c r="B196" s="32" t="inlineStr">
         <is>
-          <t>REJECTED_UNKNOWN_ROBOT</t>
+          <t>REJECTED_NO_ACTIVE_WALK</t>
         </is>
       </c>
       <c r="C196" s="32" t="inlineStr">
         <is>
-          <t>미등록 Robot</t>
+          <t>종료할 활성 산책 없음</t>
         </is>
       </c>
       <c r="D196" s="32" t="inlineStr">
         <is>
-          <t>deviceId 권위 조회 실패</t>
+          <t>STOP without active 응답</t>
         </is>
       </c>
       <c r="E196" s="32" t="inlineStr">
         <is>
-          <t>명령 미발행</t>
+          <t>나중에 생긴 산책을 같은 ID로 멈추지 않음</t>
         </is>
       </c>
     </row>
@@ -24183,22 +24203,22 @@
       </c>
       <c r="B197" s="32" t="inlineStr">
         <is>
-          <t>REJECTED_INACTIVE_ROBOT</t>
+          <t>REJECTED_UNKNOWN_ROBOT</t>
         </is>
       </c>
       <c r="C197" s="32" t="inlineStr">
         <is>
-          <t>비활성 Robot</t>
+          <t>미등록 Robot</t>
         </is>
       </c>
       <c r="D197" s="32" t="inlineStr">
         <is>
-          <t>START 입장 정책</t>
+          <t>deviceId 권위 조회 실패</t>
         </is>
       </c>
       <c r="E197" s="32" t="inlineStr">
         <is>
-          <t>STOP 안전 시도에는 적용하지 않음</t>
+          <t>명령 미발행</t>
         </is>
       </c>
     </row>
@@ -24210,22 +24230,22 @@
       </c>
       <c r="B198" s="32" t="inlineStr">
         <is>
-          <t>REJECTED_UNASSIGNED_ROBOT</t>
+          <t>REJECTED_INACTIVE_ROBOT</t>
         </is>
       </c>
       <c r="C198" s="32" t="inlineStr">
         <is>
-          <t>시니어 미배정 Robot</t>
+          <t>비활성 Robot</t>
         </is>
       </c>
       <c r="D198" s="32" t="inlineStr">
         <is>
-          <t>START 대상 검증</t>
+          <t>START 입장 정책</t>
         </is>
       </c>
       <c r="E198" s="32" t="inlineStr">
         <is>
-          <t>어르신 잠금 없이 시작하지 않음</t>
+          <t>STOP 안전 시도에는 적용하지 않음</t>
         </is>
       </c>
     </row>
@@ -24237,22 +24257,22 @@
       </c>
       <c r="B199" s="32" t="inlineStr">
         <is>
-          <t>REJECTED_SAFE_STOP</t>
+          <t>REJECTED_UNASSIGNED_ROBOT</t>
         </is>
       </c>
       <c r="C199" s="32" t="inlineStr">
         <is>
-          <t>SAFE_STOP Robot</t>
+          <t>시니어 미배정 Robot</t>
         </is>
       </c>
       <c r="D199" s="32" t="inlineStr">
         <is>
-          <t>START 안전 정책</t>
+          <t>START 대상 검증</t>
         </is>
       </c>
       <c r="E199" s="32" t="inlineStr">
         <is>
-          <t>안전 정지 상태에서 추종을 시작하지 않음</t>
+          <t>어르신 잠금 없이 시작하지 않음</t>
         </is>
       </c>
     </row>
@@ -24264,22 +24284,22 @@
       </c>
       <c r="B200" s="32" t="inlineStr">
         <is>
-          <t>REJECTED_REST_GUARD</t>
+          <t>REJECTED_SAFE_STOP</t>
         </is>
       </c>
       <c r="C200" s="32" t="inlineStr">
         <is>
-          <t>REST_GUARD Robot</t>
+          <t>SAFE_STOP Robot</t>
         </is>
       </c>
       <c r="D200" s="32" t="inlineStr">
         <is>
-          <t>START 휴식 보호 정책</t>
+          <t>START 안전 정책</t>
         </is>
       </c>
       <c r="E200" s="32" t="inlineStr">
         <is>
-          <t>휴식 상태를 산책이 선점하지 않음</t>
+          <t>안전 정지 상태에서 추종을 시작하지 않음</t>
         </is>
       </c>
     </row>
@@ -24291,22 +24311,22 @@
       </c>
       <c r="B201" s="32" t="inlineStr">
         <is>
-          <t>REJECTED_ACTIVE_SCENARIO</t>
+          <t>REJECTED_REST_GUARD</t>
         </is>
       </c>
       <c r="C201" s="32" t="inlineStr">
         <is>
-          <t>다른 활성 시나리오 존재</t>
+          <t>REST_GUARD Robot</t>
         </is>
       </c>
       <c r="D201" s="32" t="inlineStr">
         <is>
-          <t>시니어 단위 시작 직렬화</t>
+          <t>START 휴식 보호 정책</t>
         </is>
       </c>
       <c r="E201" s="32" t="inlineStr">
         <is>
-          <t>기존 흐름을 취소하지 않음</t>
+          <t>휴식 상태를 산책이 선점하지 않음</t>
         </is>
       </c>
     </row>
@@ -24318,22 +24338,22 @@
       </c>
       <c r="B202" s="32" t="inlineStr">
         <is>
-          <t>REJECTED_BUSY_MODE</t>
+          <t>REJECTED_ACTIVE_SCENARIO</t>
         </is>
       </c>
       <c r="C202" s="32" t="inlineStr">
         <is>
-          <t>지원하지 않는 활성 Robot mode</t>
+          <t>다른 활성 시나리오 존재</t>
         </is>
       </c>
       <c r="D202" s="32" t="inlineStr">
         <is>
-          <t>START mode 검사</t>
+          <t>시니어 단위 시작 직렬화</t>
         </is>
       </c>
       <c r="E202" s="32" t="inlineStr">
         <is>
-          <t>IDLE에서만 산책 시작</t>
+          <t>기존 흐름을 취소하지 않음</t>
         </is>
       </c>
     </row>
@@ -24345,22 +24365,22 @@
       </c>
       <c r="B203" s="32" t="inlineStr">
         <is>
-          <t>REJECTED_REQUEST_ID_REUSED</t>
+          <t>REJECTED_BUSY_MODE</t>
         </is>
       </c>
       <c r="C203" s="32" t="inlineStr">
         <is>
-          <t>요청 ID 문맥 불일치</t>
+          <t>지원하지 않는 활성 Robot mode</t>
         </is>
       </c>
       <c r="D203" s="32" t="inlineStr">
         <is>
-          <t>같은 키의 robot/action/source 비교</t>
+          <t>START mode 검사</t>
         </is>
       </c>
       <c r="E203" s="32" t="inlineStr">
         <is>
-          <t>기존 결정을 덮어쓰지 않음</t>
+          <t>IDLE에서만 산책 시작</t>
         </is>
       </c>
     </row>
@@ -24372,49 +24392,49 @@
       </c>
       <c r="B204" s="32" t="inlineStr">
         <is>
-          <t>REJECTED_MQTT_UNAVAILABLE</t>
+          <t>REJECTED_REQUEST_ID_REUSED</t>
         </is>
       </c>
       <c r="C204" s="32" t="inlineStr">
         <is>
-          <t>명령 gateway 비활성</t>
+          <t>요청 ID 문맥 불일치</t>
         </is>
       </c>
       <c r="D204" s="32" t="inlineStr">
         <is>
-          <t>REST 문서 profile·운영 장애 응답</t>
+          <t>같은 키의 robot/action/source 비교</t>
         </is>
       </c>
       <c r="E204" s="32" t="inlineStr">
         <is>
-          <t>영수증을 확정하지 않아 재시도 가능</t>
+          <t>기존 결정을 덮어쓰지 않음</t>
         </is>
       </c>
     </row>
     <row r="205" ht="15" customHeight="1">
       <c r="A205" s="32" t="inlineStr">
         <is>
-          <t>scenario.last_follow_result_code</t>
+          <t>walk_request_receipt.disposition</t>
         </is>
       </c>
       <c r="B205" s="32" t="inlineStr">
         <is>
-          <t>STARTED</t>
+          <t>REJECTED_MQTT_UNAVAILABLE</t>
         </is>
       </c>
       <c r="C205" s="32" t="inlineStr">
         <is>
-          <t>추종 시작 확인</t>
+          <t>명령 gateway 비활성</t>
         </is>
       </c>
       <c r="D205" s="32" t="inlineStr">
         <is>
-          <t>FOLLOW_START 성공 결과</t>
+          <t>REST 문서 profile·운영 장애 응답</t>
         </is>
       </c>
       <c r="E205" s="32" t="inlineStr">
         <is>
-          <t>START commandId와 함께 검증</t>
+          <t>영수증을 확정하지 않아 재시도 가능</t>
         </is>
       </c>
     </row>
@@ -24426,22 +24446,22 @@
       </c>
       <c r="B206" s="32" t="inlineStr">
         <is>
-          <t>STOPPED</t>
+          <t>STARTED</t>
         </is>
       </c>
       <c r="C206" s="32" t="inlineStr">
         <is>
-          <t>추종 종료 확인</t>
+          <t>추종 시작 확인</t>
         </is>
       </c>
       <c r="D206" s="32" t="inlineStr">
         <is>
-          <t>명시적 STOP 또는 Robot 자체 종료</t>
+          <t>FOLLOW_START 성공 결과</t>
         </is>
       </c>
       <c r="E206" s="32" t="inlineStr">
         <is>
-          <t>어느 commandId인지 함께 보존</t>
+          <t>START commandId와 함께 검증</t>
         </is>
       </c>
     </row>
@@ -24453,49 +24473,49 @@
       </c>
       <c r="B207" s="32" t="inlineStr">
         <is>
-          <t>UNCHANGED</t>
+          <t>STOPPED</t>
         </is>
       </c>
       <c r="C207" s="32" t="inlineStr">
         <is>
-          <t>이미 원하는 추종 상태 또는 Backend synthetic timeout 기록 코드</t>
+          <t>추종 종료 확인</t>
         </is>
       </c>
       <c r="D207" s="32" t="inlineStr">
         <is>
-          <t>Robot 멱등 성공 결과 또는 timeout- eventId의 Backend 안전 종료</t>
+          <t>명시적 STOP 또는 Robot 자체 종료</t>
         </is>
       </c>
       <c r="E207" s="32" t="inlineStr">
         <is>
-          <t>synthetic timeout은 Robot 성공 증거가 아니며 eventId·reasonCode와 함께 판별</t>
+          <t>어느 commandId인지 함께 보존</t>
         </is>
       </c>
     </row>
     <row r="208" ht="15" customHeight="1">
       <c r="A208" s="32" t="inlineStr">
         <is>
-          <t>scenario.last_follow_reason_code</t>
+          <t>scenario.last_follow_result_code</t>
         </is>
       </c>
       <c r="B208" s="32" t="inlineStr">
         <is>
-          <t>PERSON_LOST</t>
+          <t>UNCHANGED</t>
         </is>
       </c>
       <c r="C208" s="32" t="inlineStr">
         <is>
-          <t>추종 대상 놓침</t>
+          <t>이미 원하는 추종 상태 또는 Backend synthetic timeout 기록 코드</t>
         </is>
       </c>
       <c r="D208" s="32" t="inlineStr">
         <is>
-          <t>실패 FOLLOW_RESULT</t>
+          <t>Robot 멱등 성공 결과 또는 timeout- eventId의 Backend 안전 종료</t>
         </is>
       </c>
       <c r="E208" s="32" t="inlineStr">
         <is>
-          <t>고빈도 tracking 정보는 저장하지 않음</t>
+          <t>synthetic timeout은 Robot 성공 증거가 아니며 eventId·reasonCode와 함께 판별</t>
         </is>
       </c>
     </row>
@@ -24507,22 +24527,22 @@
       </c>
       <c r="B209" s="32" t="inlineStr">
         <is>
-          <t>COMMAND_EXPIRED</t>
+          <t>PERSON_LOST</t>
         </is>
       </c>
       <c r="C209" s="32" t="inlineStr">
         <is>
-          <t>명령 만료</t>
+          <t>추종 대상 놓침</t>
         </is>
       </c>
       <c r="D209" s="32" t="inlineStr">
         <is>
-          <t>실패·시간초과 결과</t>
+          <t>실패 FOLLOW_RESULT</t>
         </is>
       </c>
       <c r="E209" s="32" t="inlineStr">
         <is>
-          <t>expiresAt과 구분해 코드만 저장</t>
+          <t>고빈도 tracking 정보는 저장하지 않음</t>
         </is>
       </c>
     </row>
@@ -24534,22 +24554,22 @@
       </c>
       <c r="B210" s="32" t="inlineStr">
         <is>
-          <t>EXECUTION_TIMEOUT</t>
+          <t>COMMAND_EXPIRED</t>
         </is>
       </c>
       <c r="C210" s="32" t="inlineStr">
         <is>
-          <t>실행 시간초과</t>
+          <t>명령 만료</t>
         </is>
       </c>
       <c r="D210" s="32" t="inlineStr">
         <is>
-          <t>Robot 또는 Backend timeout</t>
+          <t>실패·시간초과 결과</t>
         </is>
       </c>
       <c r="E210" s="32" t="inlineStr">
         <is>
-          <t>늦은 STOPPED가 원인을 덮어쓰지 않음</t>
+          <t>expiresAt과 구분해 코드만 저장</t>
         </is>
       </c>
     </row>
@@ -24561,22 +24581,22 @@
       </c>
       <c r="B211" s="32" t="inlineStr">
         <is>
-          <t>SAFETY_STOP</t>
+          <t>EXECUTION_TIMEOUT</t>
         </is>
       </c>
       <c r="C211" s="32" t="inlineStr">
         <is>
-          <t>Robot 안전 정지</t>
+          <t>실행 시간초과</t>
         </is>
       </c>
       <c r="D211" s="32" t="inlineStr">
         <is>
-          <t>취소·실패 결과</t>
+          <t>Robot 또는 Backend timeout</t>
         </is>
       </c>
       <c r="E211" s="32" t="inlineStr">
         <is>
-          <t>terminal Robot mode는 SAFE_STOP</t>
+          <t>늦은 STOPPED가 원인을 덮어쓰지 않음</t>
         </is>
       </c>
     </row>
@@ -24588,49 +24608,49 @@
       </c>
       <c r="B212" s="32" t="inlineStr">
         <is>
-          <t>INTERNAL_ERROR</t>
+          <t>SAFETY_STOP</t>
         </is>
       </c>
       <c r="C212" s="32" t="inlineStr">
         <is>
-          <t>Robot 내부 오류</t>
+          <t>Robot 안전 정지</t>
         </is>
       </c>
       <c r="D212" s="32" t="inlineStr">
         <is>
-          <t>실패 FOLLOW_RESULT</t>
+          <t>취소·실패 결과</t>
         </is>
       </c>
       <c r="E212" s="32" t="inlineStr">
         <is>
-          <t>상세 예외 전문은 로그 경계에 둠</t>
+          <t>terminal Robot mode는 SAFE_STOP</t>
         </is>
       </c>
     </row>
     <row r="213" ht="26.39999961853027" customHeight="1">
       <c r="A213" s="32" t="inlineStr">
         <is>
-          <t>robot.occupancy_status / occupancy_event.resulting_occupancy</t>
+          <t>scenario.last_follow_reason_code</t>
         </is>
       </c>
       <c r="B213" s="32" t="inlineStr">
         <is>
-          <t>HOME</t>
+          <t>INTERNAL_ERROR</t>
         </is>
       </c>
       <c r="C213" s="32" t="inlineStr">
         <is>
-          <t>재실 확인</t>
+          <t>Robot 내부 오류</t>
         </is>
       </c>
       <c r="D213" s="32" t="inlineStr">
         <is>
-          <t>현관 IN 또는 발화 증거 적용 뒤 사용</t>
+          <t>실패 FOLLOW_RESULT</t>
         </is>
       </c>
       <c r="E213" s="32" t="inlineStr">
         <is>
-          <t>현재 스냅샷과 이벤트 결과를 같은 코드로 유지</t>
+          <t>상세 예외 전문은 로그 경계에 둠</t>
         </is>
       </c>
     </row>
@@ -24642,22 +24662,22 @@
       </c>
       <c r="B214" s="32" t="inlineStr">
         <is>
-          <t>AWAY</t>
+          <t>HOME</t>
         </is>
       </c>
       <c r="C214" s="32" t="inlineStr">
         <is>
-          <t>외출 확인</t>
+          <t>재실 확인</t>
         </is>
       </c>
       <c r="D214" s="32" t="inlineStr">
         <is>
-          <t>현관 OUT 증거 적용 뒤 사용</t>
+          <t>현관 IN 또는 발화 증거 적용 뒤 사용</t>
         </is>
       </c>
       <c r="E214" s="32" t="inlineStr">
         <is>
-          <t>침묵을 이상으로 오판하지 않게 함</t>
+          <t>현재 스냅샷과 이벤트 결과를 같은 코드로 유지</t>
         </is>
       </c>
     </row>
@@ -24669,49 +24689,49 @@
       </c>
       <c r="B215" s="32" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>AWAY</t>
         </is>
       </c>
       <c r="C215" s="32" t="inlineStr">
         <is>
-          <t>재실 불명</t>
+          <t>외출 확인</t>
         </is>
       </c>
       <c r="D215" s="32" t="inlineStr">
         <is>
-          <t>관측 전 또는 현관 하트비트 timeout 뒤 사용</t>
+          <t>현관 OUT 증거 적용 뒤 사용</t>
         </is>
       </c>
       <c r="E215" s="32" t="inlineStr">
         <is>
-          <t>HOME으로 낙관하지 않음</t>
+          <t>침묵을 이상으로 오판하지 않게 함</t>
         </is>
       </c>
     </row>
     <row r="216" ht="15" customHeight="1">
       <c r="A216" s="32" t="inlineStr">
         <is>
-          <t>occupancy_event.direction</t>
+          <t>robot.occupancy_status / occupancy_event.resulting_occupancy</t>
         </is>
       </c>
       <c r="B216" s="32" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="C216" s="32" t="inlineStr">
         <is>
-          <t>현관 안쪽 통과</t>
+          <t>재실 불명</t>
         </is>
       </c>
       <c r="D216" s="32" t="inlineStr">
         <is>
-          <t>귀가 이벤트에 사용</t>
+          <t>관측 전 또는 현관 하트비트 timeout 뒤 사용</t>
         </is>
       </c>
       <c r="E216" s="32" t="inlineStr">
         <is>
-          <t>방향 없는 재실 변화는 null</t>
+          <t>HOME으로 낙관하지 않음</t>
         </is>
       </c>
     </row>
@@ -24723,17 +24743,17 @@
       </c>
       <c r="B217" s="32" t="inlineStr">
         <is>
-          <t>OUT</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="C217" s="32" t="inlineStr">
         <is>
-          <t>현관 바깥쪽 통과</t>
+          <t>현관 안쪽 통과</t>
         </is>
       </c>
       <c r="D217" s="32" t="inlineStr">
         <is>
-          <t>외출 이벤트에 사용</t>
+          <t>귀가 이벤트에 사용</t>
         </is>
       </c>
       <c r="E217" s="32" t="inlineStr">
@@ -24745,27 +24765,27 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" s="32" t="inlineStr">
         <is>
-          <t>occupancy_event.source</t>
+          <t>occupancy_event.direction</t>
         </is>
       </c>
       <c r="B218" s="32" t="inlineStr">
         <is>
-          <t>DOOR_SENSOR</t>
+          <t>OUT</t>
         </is>
       </c>
       <c r="C218" s="32" t="inlineStr">
         <is>
-          <t>현관 센서 확정</t>
+          <t>현관 바깥쪽 통과</t>
         </is>
       </c>
       <c r="D218" s="32" t="inlineStr">
         <is>
-          <t>문 통과 재실 변화에 사용</t>
+          <t>외출 이벤트에 사용</t>
         </is>
       </c>
       <c r="E218" s="32" t="inlineStr">
         <is>
-          <t>센서 reportedAt은 참고 시각</t>
+          <t>방향 없는 재실 변화는 null</t>
         </is>
       </c>
     </row>
@@ -24777,22 +24797,22 @@
       </c>
       <c r="B219" s="32" t="inlineStr">
         <is>
-          <t>SPEECH</t>
+          <t>DOOR_SENSOR</t>
         </is>
       </c>
       <c r="C219" s="32" t="inlineStr">
         <is>
-          <t>발화로 HOME 확정</t>
+          <t>현관 센서 확정</t>
         </is>
       </c>
       <c r="D219" s="32" t="inlineStr">
         <is>
-          <t>어르신 발화 감지 시 사용</t>
+          <t>문 통과 재실 변화에 사용</t>
         </is>
       </c>
       <c r="E219" s="32" t="inlineStr">
         <is>
-          <t>발화는 집 안 존재의 강한 증거</t>
+          <t>센서 reportedAt은 참고 시각</t>
         </is>
       </c>
     </row>
@@ -24804,49 +24824,49 @@
       </c>
       <c r="B220" s="32" t="inlineStr">
         <is>
-          <t>HEARTBEAT_TIMEOUT</t>
+          <t>SPEECH</t>
         </is>
       </c>
       <c r="C220" s="32" t="inlineStr">
         <is>
-          <t>현관 노드 통신 만료</t>
+          <t>발화로 HOME 확정</t>
         </is>
       </c>
       <c r="D220" s="32" t="inlineStr">
         <is>
-          <t>재실을 UNKNOWN으로 강등할 때 사용</t>
+          <t>어르신 발화 감지 시 사용</t>
         </is>
       </c>
       <c r="E220" s="32" t="inlineStr">
         <is>
-          <t>문 통과 사건이 아님</t>
+          <t>발화는 집 안 존재의 강한 증거</t>
         </is>
       </c>
     </row>
     <row r="221" ht="15" customHeight="1">
       <c r="A221" s="32" t="inlineStr">
         <is>
-          <t>care_record.notification_tier</t>
+          <t>occupancy_event.source</t>
         </is>
       </c>
       <c r="B221" s="32" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>HEARTBEAT_TIMEOUT</t>
         </is>
       </c>
       <c r="C221" s="32" t="inlineStr">
         <is>
-          <t>즉시 보호자 알림</t>
+          <t>현관 노드 통신 만료</t>
         </is>
       </c>
       <c r="D221" s="32" t="inlineStr">
         <is>
-          <t>응급·즉시 공유 사건</t>
+          <t>재실을 UNKNOWN으로 강등할 때 사용</t>
         </is>
       </c>
       <c r="E221" s="32" t="inlineStr">
         <is>
-          <t>T4는 이 컬럼에 저장하지 않음</t>
+          <t>문 통과 사건이 아님</t>
         </is>
       </c>
     </row>
@@ -24858,22 +24878,22 @@
       </c>
       <c r="B222" s="32" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="C222" s="32" t="inlineStr">
         <is>
-          <t>일간 요약</t>
+          <t>즉시 보호자 알림</t>
         </is>
       </c>
       <c r="D222" s="32" t="inlineStr">
         <is>
-          <t>추세·비응급 관찰 집계</t>
+          <t>응급·즉시 공유 사건</t>
         </is>
       </c>
       <c r="E222" s="32" t="inlineStr">
         <is>
-          <t>중복 발송은 summary_sent_at으로 방지</t>
+          <t>T4는 이 컬럼에 저장하지 않음</t>
         </is>
       </c>
     </row>
@@ -24885,20 +24905,47 @@
       </c>
       <c r="B223" s="32" t="inlineStr">
         <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="C223" s="32" t="inlineStr">
+        <is>
+          <t>일간 요약</t>
+        </is>
+      </c>
+      <c r="D223" s="32" t="inlineStr">
+        <is>
+          <t>추세·비응급 관찰 집계</t>
+        </is>
+      </c>
+      <c r="E223" s="32" t="inlineStr">
+        <is>
+          <t>중복 발송은 summary_sent_at으로 방지</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="32" t="inlineStr">
+        <is>
+          <t>care_record.notification_tier</t>
+        </is>
+      </c>
+      <c r="B224" s="32" t="inlineStr">
+        <is>
           <t>T3</t>
         </is>
       </c>
-      <c r="C223" s="32" t="inlineStr">
+      <c r="C224" s="32" t="inlineStr">
         <is>
           <t>시니어 동의 필요</t>
         </is>
       </c>
-      <c r="D223" s="32" t="inlineStr">
+      <c r="D224" s="32" t="inlineStr">
         <is>
           <t>민감 사실 공유 전 동의 흐름</t>
         </is>
       </c>
-      <c r="E223" s="32" t="inlineStr">
+      <c r="E224" s="32" t="inlineStr">
         <is>
           <t>권한·동의를 우회하지 않음</t>
         </is>
